--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120208692</v>
+        <v>120208756</v>
       </c>
       <c r="B2" t="n">
-        <v>101074</v>
+        <v>57326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668538</v>
+        <v>668467</v>
       </c>
       <c r="R2" t="n">
-        <v>6696322</v>
+        <v>6696630</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120208737</v>
+        <v>120208777</v>
       </c>
       <c r="B3" t="n">
-        <v>56522</v>
+        <v>97885</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668566</v>
+        <v>668188</v>
       </c>
       <c r="R3" t="n">
-        <v>6696455</v>
+        <v>6696531</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120208718</v>
+        <v>120208815</v>
       </c>
       <c r="B4" t="n">
-        <v>95455</v>
+        <v>74577</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668450</v>
+        <v>668311</v>
       </c>
       <c r="R4" t="n">
-        <v>6696589</v>
+        <v>6696520</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120208740</v>
+        <v>120208705</v>
       </c>
       <c r="B5" t="n">
-        <v>57463</v>
+        <v>95455</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,42 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668357</v>
+        <v>668521</v>
       </c>
       <c r="R5" t="n">
-        <v>6696585</v>
+        <v>6696330</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,6 +1077,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1101,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120208819</v>
+        <v>120208854</v>
       </c>
       <c r="B6" t="n">
-        <v>105009</v>
+        <v>100171</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1124,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668579</v>
+        <v>668370</v>
       </c>
       <c r="R6" t="n">
-        <v>6696655</v>
+        <v>6696506</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120208861</v>
+        <v>120208684</v>
       </c>
       <c r="B7" t="n">
-        <v>100171</v>
+        <v>101074</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668567</v>
+        <v>668201</v>
       </c>
       <c r="R7" t="n">
-        <v>6696809</v>
+        <v>6696519</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1312,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120208683</v>
+        <v>120208682</v>
       </c>
       <c r="B8" t="n">
         <v>101074</v>
@@ -1345,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668188</v>
+        <v>668186</v>
       </c>
       <c r="R8" t="n">
-        <v>6696531</v>
+        <v>6696508</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120208721</v>
+        <v>120208713</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>95455</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668589</v>
+        <v>668379</v>
       </c>
       <c r="R9" t="n">
-        <v>6696866</v>
+        <v>6696528</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120208862</v>
+        <v>120208827</v>
       </c>
       <c r="B10" t="n">
-        <v>100171</v>
+        <v>4772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1525,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668572</v>
+        <v>668457</v>
       </c>
       <c r="R10" t="n">
-        <v>6696573</v>
+        <v>6696523</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120208828</v>
+        <v>120208759</v>
       </c>
       <c r="B11" t="n">
-        <v>4772</v>
+        <v>57326</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,38 +1630,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668595</v>
+        <v>668572</v>
       </c>
       <c r="R11" t="n">
-        <v>6696467</v>
+        <v>6696839</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1687,6 +1699,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1713,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120208857</v>
+        <v>120208812</v>
       </c>
       <c r="B12" t="n">
-        <v>100171</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,38 +1742,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668438</v>
+        <v>668568</v>
       </c>
       <c r="R12" t="n">
-        <v>6696512</v>
+        <v>6696851</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120208799</v>
+        <v>120208826</v>
       </c>
       <c r="B13" t="n">
-        <v>57679</v>
+        <v>4772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1831,39 +1857,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>102306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668558</v>
+        <v>668442</v>
       </c>
       <c r="R13" t="n">
-        <v>6696534</v>
+        <v>6696515</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,10 +1943,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120208686</v>
+        <v>120208785</v>
       </c>
       <c r="B14" t="n">
-        <v>101074</v>
+        <v>90846</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1934,25 +1955,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221235</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1962,10 +1983,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668242</v>
+        <v>668552</v>
       </c>
       <c r="R14" t="n">
-        <v>6696541</v>
+        <v>6696684</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,10 +2045,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120208823</v>
+        <v>120208735</v>
       </c>
       <c r="B15" t="n">
-        <v>57329</v>
+        <v>56522</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2040,16 +2061,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102977</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2057,25 +2078,26 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668565</v>
+        <v>668518</v>
       </c>
       <c r="R15" t="n">
-        <v>6696520</v>
+        <v>6696678</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,7 +2134,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Inom avverkningsanmälan</t>
+          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2139,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120208858</v>
+        <v>120208704</v>
       </c>
       <c r="B16" t="n">
-        <v>100171</v>
+        <v>95455</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2151,25 +2173,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2179,7 +2201,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668564</v>
+        <v>668571</v>
       </c>
       <c r="R16" t="n">
         <v>6696816</v>
@@ -2225,6 +2247,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2241,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120208814</v>
+        <v>120208800</v>
       </c>
       <c r="B17" t="n">
-        <v>74577</v>
+        <v>57679</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2257,34 +2294,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668296</v>
+        <v>668525</v>
       </c>
       <c r="R17" t="n">
-        <v>6696535</v>
+        <v>6696405</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2343,10 +2389,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120208777</v>
+        <v>120208716</v>
       </c>
       <c r="B18" t="n">
-        <v>97885</v>
+        <v>95455</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2355,25 +2401,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2383,10 +2429,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668188</v>
+        <v>668439</v>
       </c>
       <c r="R18" t="n">
-        <v>6696531</v>
+        <v>6696517</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,10 +2491,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120208784</v>
+        <v>120208782</v>
       </c>
       <c r="B19" t="n">
-        <v>91005</v>
+        <v>97885</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2457,25 +2503,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>219798</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2485,10 +2531,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668273</v>
+        <v>668279</v>
       </c>
       <c r="R19" t="n">
-        <v>6696531</v>
+        <v>6696528</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2547,7 +2593,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120208713</v>
+        <v>120208709</v>
       </c>
       <c r="B20" t="n">
         <v>95455</v>
@@ -2587,10 +2633,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668379</v>
+        <v>668362</v>
       </c>
       <c r="R20" t="n">
-        <v>6696528</v>
+        <v>6696599</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2649,10 +2695,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120208852</v>
+        <v>120208774</v>
       </c>
       <c r="B21" t="n">
-        <v>100171</v>
+        <v>97885</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2665,21 +2711,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2689,10 +2735,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668230</v>
+        <v>668365</v>
       </c>
       <c r="R21" t="n">
-        <v>6696502</v>
+        <v>6696575</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2751,10 +2797,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120208714</v>
+        <v>120208725</v>
       </c>
       <c r="B22" t="n">
-        <v>95455</v>
+        <v>90562</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2767,21 +2813,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2791,10 +2837,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668369</v>
+        <v>668551</v>
       </c>
       <c r="R22" t="n">
-        <v>6696540</v>
+        <v>6696304</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2853,10 +2899,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120208743</v>
+        <v>120208758</v>
       </c>
       <c r="B23" t="n">
-        <v>57463</v>
+        <v>57326</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2869,42 +2915,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668533</v>
+        <v>668240</v>
       </c>
       <c r="R23" t="n">
-        <v>6696366</v>
+        <v>6696522</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,6 +2980,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2963,10 +3011,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120208712</v>
+        <v>120208783</v>
       </c>
       <c r="B24" t="n">
-        <v>95455</v>
+        <v>90334</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2975,25 +3023,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3003,10 +3051,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668301</v>
+        <v>668281</v>
       </c>
       <c r="R24" t="n">
-        <v>6696522</v>
+        <v>6696528</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3065,10 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120208855</v>
+        <v>120208690</v>
       </c>
       <c r="B25" t="n">
-        <v>100171</v>
+        <v>101074</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3081,21 +3129,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3105,10 +3153,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668380</v>
+        <v>668564</v>
       </c>
       <c r="R25" t="n">
-        <v>6696528</v>
+        <v>6696811</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3167,10 +3215,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120208781</v>
+        <v>120208737</v>
       </c>
       <c r="B26" t="n">
-        <v>97885</v>
+        <v>56522</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3183,34 +3231,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668261</v>
+        <v>668566</v>
       </c>
       <c r="R26" t="n">
-        <v>6696558</v>
+        <v>6696455</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3243,6 +3296,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3269,10 +3327,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120208775</v>
+        <v>120208739</v>
       </c>
       <c r="B27" t="n">
-        <v>97885</v>
+        <v>103418</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3285,21 +3343,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3309,10 +3367,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668180</v>
+        <v>668166</v>
       </c>
       <c r="R27" t="n">
-        <v>6696501</v>
+        <v>6696498</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3371,10 +3429,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120208688</v>
+        <v>120208775</v>
       </c>
       <c r="B28" t="n">
-        <v>101074</v>
+        <v>97885</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3387,21 +3445,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3411,10 +3469,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668383</v>
+        <v>668180</v>
       </c>
       <c r="R28" t="n">
-        <v>6696524</v>
+        <v>6696501</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3473,10 +3531,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120208811</v>
+        <v>120208850</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>100171</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3485,47 +3543,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668524</v>
+        <v>668179</v>
       </c>
       <c r="R29" t="n">
-        <v>6696416</v>
+        <v>6696528</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3584,10 +3633,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120208711</v>
+        <v>120208799</v>
       </c>
       <c r="B30" t="n">
-        <v>95455</v>
+        <v>57679</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3596,38 +3645,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668345</v>
+        <v>668558</v>
       </c>
       <c r="R30" t="n">
-        <v>6696598</v>
+        <v>6696534</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3686,10 +3740,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120208800</v>
+        <v>120208856</v>
       </c>
       <c r="B31" t="n">
-        <v>57679</v>
+        <v>100171</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3702,43 +3756,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668525</v>
+        <v>668382</v>
       </c>
       <c r="R31" t="n">
-        <v>6696405</v>
+        <v>6696524</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3797,10 +3842,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120208812</v>
+        <v>120208718</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3809,47 +3854,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668568</v>
+        <v>668450</v>
       </c>
       <c r="R32" t="n">
-        <v>6696851</v>
+        <v>6696589</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3908,10 +3944,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120208744</v>
+        <v>120208724</v>
       </c>
       <c r="B33" t="n">
-        <v>57463</v>
+        <v>90562</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3924,39 +3960,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668602</v>
+        <v>668608</v>
       </c>
       <c r="R33" t="n">
-        <v>6696625</v>
+        <v>6696611</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4015,10 +4046,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120208725</v>
+        <v>120208720</v>
       </c>
       <c r="B34" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4027,25 +4058,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4055,10 +4086,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668551</v>
+        <v>668407</v>
       </c>
       <c r="R34" t="n">
-        <v>6696304</v>
+        <v>6696520</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4101,6 +4132,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4117,10 +4163,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120208779</v>
+        <v>120208741</v>
       </c>
       <c r="B35" t="n">
-        <v>97885</v>
+        <v>57463</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4129,38 +4175,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219798</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668212</v>
+        <v>668483</v>
       </c>
       <c r="R35" t="n">
-        <v>6696497</v>
+        <v>6696590</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4219,10 +4273,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120208691</v>
+        <v>120208816</v>
       </c>
       <c r="B36" t="n">
-        <v>101074</v>
+        <v>56514</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4231,25 +4285,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221235</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4259,10 +4313,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668509</v>
+        <v>668248</v>
       </c>
       <c r="R36" t="n">
-        <v>6696436</v>
+        <v>6696628</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4295,6 +4349,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>flög upp från marken</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4321,10 +4380,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120208706</v>
+        <v>120208862</v>
       </c>
       <c r="B37" t="n">
-        <v>95455</v>
+        <v>100171</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4333,25 +4392,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4361,10 +4420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668408</v>
+        <v>668572</v>
       </c>
       <c r="R37" t="n">
-        <v>6696562</v>
+        <v>6696573</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4423,10 +4482,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120208722</v>
+        <v>120208853</v>
       </c>
       <c r="B38" t="n">
-        <v>90562</v>
+        <v>100171</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4435,25 +4494,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4463,10 +4522,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668552</v>
+        <v>668241</v>
       </c>
       <c r="R38" t="n">
-        <v>6696684</v>
+        <v>6696541</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4525,10 +4584,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120208758</v>
+        <v>120208688</v>
       </c>
       <c r="B39" t="n">
-        <v>57326</v>
+        <v>101074</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4537,43 +4596,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668240</v>
+        <v>668383</v>
       </c>
       <c r="R39" t="n">
-        <v>6696522</v>
+        <v>6696524</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4606,11 +4660,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4637,10 +4686,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120208785</v>
+        <v>120208703</v>
       </c>
       <c r="B40" t="n">
-        <v>90846</v>
+        <v>95455</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4653,21 +4702,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4677,10 +4726,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668552</v>
+        <v>668451</v>
       </c>
       <c r="R40" t="n">
-        <v>6696684</v>
+        <v>6696602</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4723,6 +4772,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4739,10 +4803,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120208705</v>
+        <v>120208740</v>
       </c>
       <c r="B41" t="n">
-        <v>95455</v>
+        <v>57463</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4755,34 +4819,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668521</v>
+        <v>668357</v>
       </c>
       <c r="R41" t="n">
-        <v>6696330</v>
+        <v>6696585</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4825,21 +4897,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4856,10 +4913,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120208827</v>
+        <v>120208822</v>
       </c>
       <c r="B42" t="n">
-        <v>4772</v>
+        <v>57329</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4872,34 +4929,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102306</v>
+        <v>102977</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668457</v>
+        <v>668585</v>
       </c>
       <c r="R42" t="n">
-        <v>6696523</v>
+        <v>6696613</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4932,6 +4997,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4958,10 +5028,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120208717</v>
+        <v>120208851</v>
       </c>
       <c r="B43" t="n">
-        <v>95455</v>
+        <v>100171</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4970,25 +5040,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4998,10 +5068,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668468</v>
+        <v>668213</v>
       </c>
       <c r="R43" t="n">
-        <v>6696587</v>
+        <v>6696494</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5060,10 +5130,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120208813</v>
+        <v>120208855</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>100171</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5072,47 +5142,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668575</v>
+        <v>668380</v>
       </c>
       <c r="R44" t="n">
-        <v>6696701</v>
+        <v>6696528</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5171,10 +5232,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120208708</v>
+        <v>120208828</v>
       </c>
       <c r="B45" t="n">
-        <v>95455</v>
+        <v>4772</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5183,25 +5244,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5211,10 +5272,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668376</v>
+        <v>668595</v>
       </c>
       <c r="R45" t="n">
-        <v>6696595</v>
+        <v>6696467</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5273,10 +5334,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120208690</v>
+        <v>120208814</v>
       </c>
       <c r="B46" t="n">
-        <v>101074</v>
+        <v>74577</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5289,21 +5350,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221235</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5313,10 +5374,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668564</v>
+        <v>668296</v>
       </c>
       <c r="R46" t="n">
-        <v>6696811</v>
+        <v>6696535</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5375,10 +5436,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120208826</v>
+        <v>120208830</v>
       </c>
       <c r="B47" t="n">
-        <v>4772</v>
+        <v>78526</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5387,25 +5448,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102306</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5418,7 +5479,7 @@
         <v>668442</v>
       </c>
       <c r="R47" t="n">
-        <v>6696515</v>
+        <v>6696514</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5461,6 +5522,21 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5477,10 +5553,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120208856</v>
+        <v>120208722</v>
       </c>
       <c r="B48" t="n">
-        <v>100171</v>
+        <v>90562</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5489,25 +5565,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5517,10 +5593,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668382</v>
+        <v>668552</v>
       </c>
       <c r="R48" t="n">
-        <v>6696524</v>
+        <v>6696684</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5579,10 +5655,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120208776</v>
+        <v>120208686</v>
       </c>
       <c r="B49" t="n">
-        <v>97885</v>
+        <v>101074</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5595,21 +5671,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5619,10 +5695,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668186</v>
+        <v>668242</v>
       </c>
       <c r="R49" t="n">
-        <v>6696508</v>
+        <v>6696541</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5681,7 +5757,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120208710</v>
+        <v>120208707</v>
       </c>
       <c r="B50" t="n">
         <v>95455</v>
@@ -5721,10 +5797,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668362</v>
+        <v>668394</v>
       </c>
       <c r="R50" t="n">
-        <v>6696582</v>
+        <v>6696553</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5783,10 +5859,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120208704</v>
+        <v>120208860</v>
       </c>
       <c r="B51" t="n">
-        <v>95455</v>
+        <v>100171</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5795,25 +5871,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5823,10 +5899,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668571</v>
+        <v>668566</v>
       </c>
       <c r="R51" t="n">
-        <v>6696816</v>
+        <v>6696858</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5869,21 +5945,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -5900,10 +5961,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120208863</v>
+        <v>120208692</v>
       </c>
       <c r="B52" t="n">
-        <v>100171</v>
+        <v>101074</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5916,21 +5977,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5940,10 +6001,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668568</v>
+        <v>668538</v>
       </c>
       <c r="R52" t="n">
-        <v>6696542</v>
+        <v>6696322</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6002,10 +6063,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120208778</v>
+        <v>120208719</v>
       </c>
       <c r="B53" t="n">
-        <v>97885</v>
+        <v>95455</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6014,25 +6075,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6042,10 +6103,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668191</v>
+        <v>668514</v>
       </c>
       <c r="R53" t="n">
-        <v>6696527</v>
+        <v>6696439</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6211,10 +6272,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120208736</v>
+        <v>120208864</v>
       </c>
       <c r="B55" t="n">
-        <v>56522</v>
+        <v>100171</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6227,39 +6288,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668532</v>
+        <v>668527</v>
       </c>
       <c r="R55" t="n">
-        <v>6696689</v>
+        <v>6696351</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6292,11 +6348,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6323,7 +6374,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120208864</v>
+        <v>120208857</v>
       </c>
       <c r="B56" t="n">
         <v>100171</v>
@@ -6363,10 +6414,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668527</v>
+        <v>668438</v>
       </c>
       <c r="R56" t="n">
-        <v>6696351</v>
+        <v>6696512</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6425,10 +6476,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120208719</v>
+        <v>120208791</v>
       </c>
       <c r="B57" t="n">
-        <v>95455</v>
+        <v>57316</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6441,34 +6492,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>100048</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668514</v>
+        <v>668520</v>
       </c>
       <c r="R57" t="n">
-        <v>6696439</v>
+        <v>6696377</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6501,6 +6560,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6527,10 +6591,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120208849</v>
+        <v>120208757</v>
       </c>
       <c r="B58" t="n">
-        <v>100171</v>
+        <v>57326</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6539,38 +6603,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668362</v>
+        <v>668572</v>
       </c>
       <c r="R58" t="n">
-        <v>6696583</v>
+        <v>6696525</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6603,6 +6672,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6629,10 +6703,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120208724</v>
+        <v>120208714</v>
       </c>
       <c r="B59" t="n">
-        <v>90562</v>
+        <v>95455</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6645,21 +6719,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6669,10 +6743,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668608</v>
+        <v>668369</v>
       </c>
       <c r="R59" t="n">
-        <v>6696611</v>
+        <v>6696540</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6731,10 +6805,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120208756</v>
+        <v>120208778</v>
       </c>
       <c r="B60" t="n">
-        <v>57326</v>
+        <v>97885</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6743,43 +6817,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>668467</v>
+        <v>668191</v>
       </c>
       <c r="R60" t="n">
-        <v>6696630</v>
+        <v>6696527</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6812,11 +6881,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6843,10 +6907,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120208792</v>
+        <v>120208717</v>
       </c>
       <c r="B61" t="n">
-        <v>57316</v>
+        <v>95455</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6859,42 +6923,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100048</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>668517</v>
+        <v>668468</v>
       </c>
       <c r="R61" t="n">
-        <v>6696457</v>
+        <v>6696587</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6927,11 +6983,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6958,10 +7009,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120208851</v>
+        <v>120208683</v>
       </c>
       <c r="B62" t="n">
-        <v>100171</v>
+        <v>101074</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6974,21 +7025,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6998,10 +7049,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668213</v>
+        <v>668188</v>
       </c>
       <c r="R62" t="n">
-        <v>6696494</v>
+        <v>6696531</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7060,10 +7111,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120208791</v>
+        <v>120208819</v>
       </c>
       <c r="B63" t="n">
-        <v>57316</v>
+        <v>105009</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7072,46 +7123,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100048</v>
+        <v>221144</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668520</v>
+        <v>668579</v>
       </c>
       <c r="R63" t="n">
-        <v>6696377</v>
+        <v>6696655</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7144,11 +7187,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7175,10 +7213,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120208815</v>
+        <v>120208811</v>
       </c>
       <c r="B64" t="n">
-        <v>74577</v>
+        <v>97907</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7187,38 +7225,47 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668311</v>
+        <v>668524</v>
       </c>
       <c r="R64" t="n">
-        <v>6696520</v>
+        <v>6696416</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7277,10 +7324,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120208741</v>
+        <v>120208823</v>
       </c>
       <c r="B65" t="n">
-        <v>57463</v>
+        <v>57329</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7289,25 +7336,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7325,10 +7372,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668483</v>
+        <v>668565</v>
       </c>
       <c r="R65" t="n">
-        <v>6696590</v>
+        <v>6696520</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7361,6 +7408,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7387,10 +7439,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120208790</v>
+        <v>120208708</v>
       </c>
       <c r="B66" t="n">
-        <v>57316</v>
+        <v>95455</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7403,42 +7455,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100048</v>
+        <v>53</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668550</v>
+        <v>668376</v>
       </c>
       <c r="R66" t="n">
-        <v>6696605</v>
+        <v>6696595</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7471,11 +7515,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7502,10 +7541,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120208782</v>
+        <v>120208691</v>
       </c>
       <c r="B67" t="n">
-        <v>97885</v>
+        <v>101074</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7518,21 +7557,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7542,10 +7581,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>668279</v>
+        <v>668509</v>
       </c>
       <c r="R67" t="n">
-        <v>6696528</v>
+        <v>6696436</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7604,10 +7643,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120208682</v>
+        <v>120208792</v>
       </c>
       <c r="B68" t="n">
-        <v>101074</v>
+        <v>57316</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7616,38 +7655,46 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221235</v>
+        <v>100048</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>668186</v>
+        <v>668517</v>
       </c>
       <c r="R68" t="n">
-        <v>6696508</v>
+        <v>6696457</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7680,6 +7727,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7706,10 +7758,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120208853</v>
+        <v>120208781</v>
       </c>
       <c r="B69" t="n">
-        <v>100171</v>
+        <v>97885</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7722,21 +7774,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7746,10 +7798,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>668241</v>
+        <v>668261</v>
       </c>
       <c r="R69" t="n">
-        <v>6696541</v>
+        <v>6696558</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7808,10 +7860,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120208759</v>
+        <v>120208743</v>
       </c>
       <c r="B70" t="n">
-        <v>57326</v>
+        <v>57463</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7824,39 +7876,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>668572</v>
+        <v>668533</v>
       </c>
       <c r="R70" t="n">
-        <v>6696839</v>
+        <v>6696366</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7889,11 +7944,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7920,10 +7970,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120208684</v>
+        <v>120208744</v>
       </c>
       <c r="B71" t="n">
-        <v>101074</v>
+        <v>57463</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7932,38 +7982,43 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221235</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>668201</v>
+        <v>668602</v>
       </c>
       <c r="R71" t="n">
-        <v>6696519</v>
+        <v>6696625</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8022,10 +8077,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120208848</v>
+        <v>120208721</v>
       </c>
       <c r="B72" t="n">
-        <v>100171</v>
+        <v>90562</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8034,25 +8089,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8062,10 +8117,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>668419</v>
+        <v>668589</v>
       </c>
       <c r="R72" t="n">
-        <v>6696535</v>
+        <v>6696866</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8124,10 +8179,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120208735</v>
+        <v>120208859</v>
       </c>
       <c r="B73" t="n">
-        <v>56522</v>
+        <v>100171</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8140,43 +8195,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>668518</v>
+        <v>668581</v>
       </c>
       <c r="R73" t="n">
-        <v>6696678</v>
+        <v>6696848</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8209,11 +8255,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8240,10 +8281,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120208860</v>
+        <v>120208706</v>
       </c>
       <c r="B74" t="n">
-        <v>100171</v>
+        <v>95455</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8252,25 +8293,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8280,10 +8321,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>668566</v>
+        <v>668408</v>
       </c>
       <c r="R74" t="n">
-        <v>6696858</v>
+        <v>6696562</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8342,10 +8383,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120208720</v>
+        <v>120208779</v>
       </c>
       <c r="B75" t="n">
-        <v>90527</v>
+        <v>97885</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8358,21 +8399,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>219798</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8382,10 +8423,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>668407</v>
+        <v>668212</v>
       </c>
       <c r="R75" t="n">
-        <v>6696520</v>
+        <v>6696497</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8428,21 +8469,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8459,10 +8485,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120208739</v>
+        <v>120208848</v>
       </c>
       <c r="B76" t="n">
-        <v>103418</v>
+        <v>100171</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8475,21 +8501,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8499,10 +8525,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>668166</v>
+        <v>668419</v>
       </c>
       <c r="R76" t="n">
-        <v>6696498</v>
+        <v>6696535</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8561,10 +8587,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120208757</v>
+        <v>120208849</v>
       </c>
       <c r="B77" t="n">
-        <v>57326</v>
+        <v>100171</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8573,43 +8599,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>668572</v>
+        <v>668362</v>
       </c>
       <c r="R77" t="n">
-        <v>6696525</v>
+        <v>6696583</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8642,11 +8663,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8673,10 +8689,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120208818</v>
+        <v>120208784</v>
       </c>
       <c r="B78" t="n">
-        <v>105009</v>
+        <v>91005</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8685,25 +8701,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8713,10 +8729,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>668437</v>
+        <v>668273</v>
       </c>
       <c r="R78" t="n">
-        <v>6696501</v>
+        <v>6696531</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8775,10 +8791,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120208687</v>
+        <v>120208818</v>
       </c>
       <c r="B79" t="n">
-        <v>101074</v>
+        <v>105009</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8791,21 +8807,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8815,10 +8831,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>668382</v>
+        <v>668437</v>
       </c>
       <c r="R79" t="n">
-        <v>6696529</v>
+        <v>6696501</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8877,10 +8893,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120208774</v>
+        <v>120208710</v>
       </c>
       <c r="B80" t="n">
-        <v>97885</v>
+        <v>95455</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8889,25 +8905,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8917,10 +8933,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>668365</v>
+        <v>668362</v>
       </c>
       <c r="R80" t="n">
-        <v>6696575</v>
+        <v>6696582</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8979,7 +8995,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120208859</v>
+        <v>120208852</v>
       </c>
       <c r="B81" t="n">
         <v>100171</v>
@@ -9019,10 +9035,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>668581</v>
+        <v>668230</v>
       </c>
       <c r="R81" t="n">
-        <v>6696848</v>
+        <v>6696502</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9081,7 +9097,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120208854</v>
+        <v>120208863</v>
       </c>
       <c r="B82" t="n">
         <v>100171</v>
@@ -9121,10 +9137,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>668370</v>
+        <v>668568</v>
       </c>
       <c r="R82" t="n">
-        <v>6696506</v>
+        <v>6696542</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9183,10 +9199,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120208822</v>
+        <v>120208712</v>
       </c>
       <c r="B83" t="n">
-        <v>57329</v>
+        <v>95455</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9195,46 +9211,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>102977</v>
+        <v>53</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>668585</v>
+        <v>668301</v>
       </c>
       <c r="R83" t="n">
-        <v>6696613</v>
+        <v>6696522</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9267,11 +9275,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9298,10 +9301,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120208850</v>
+        <v>120208687</v>
       </c>
       <c r="B84" t="n">
-        <v>100171</v>
+        <v>101074</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9314,21 +9317,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9338,10 +9341,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>668179</v>
+        <v>668382</v>
       </c>
       <c r="R84" t="n">
-        <v>6696528</v>
+        <v>6696529</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9400,7 +9403,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120208716</v>
+        <v>120208711</v>
       </c>
       <c r="B85" t="n">
         <v>95455</v>
@@ -9440,10 +9443,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>668439</v>
+        <v>668345</v>
       </c>
       <c r="R85" t="n">
-        <v>6696517</v>
+        <v>6696598</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9502,10 +9505,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120208783</v>
+        <v>120208790</v>
       </c>
       <c r="B86" t="n">
-        <v>90334</v>
+        <v>57316</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9514,38 +9517,46 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3215</v>
+        <v>100048</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>668281</v>
+        <v>668550</v>
       </c>
       <c r="R86" t="n">
-        <v>6696528</v>
+        <v>6696605</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9578,6 +9589,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9604,10 +9620,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120208707</v>
+        <v>120208736</v>
       </c>
       <c r="B87" t="n">
-        <v>95455</v>
+        <v>56522</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9616,38 +9632,43 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>100138</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>668394</v>
+        <v>668532</v>
       </c>
       <c r="R87" t="n">
-        <v>6696553</v>
+        <v>6696689</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9680,6 +9701,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9706,10 +9732,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120208709</v>
+        <v>120208776</v>
       </c>
       <c r="B88" t="n">
-        <v>95455</v>
+        <v>97885</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9718,25 +9744,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9746,10 +9772,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>668362</v>
+        <v>668186</v>
       </c>
       <c r="R88" t="n">
-        <v>6696599</v>
+        <v>6696508</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9808,10 +9834,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120208816</v>
+        <v>120208813</v>
       </c>
       <c r="B89" t="n">
-        <v>56514</v>
+        <v>97907</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9820,38 +9846,47 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>668248</v>
+        <v>668575</v>
       </c>
       <c r="R89" t="n">
-        <v>6696628</v>
+        <v>6696701</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9884,11 +9919,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>flög upp från marken</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9915,10 +9945,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120208703</v>
+        <v>120208858</v>
       </c>
       <c r="B90" t="n">
-        <v>95455</v>
+        <v>100171</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9927,25 +9957,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9955,10 +9985,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>668451</v>
+        <v>668564</v>
       </c>
       <c r="R90" t="n">
-        <v>6696602</v>
+        <v>6696816</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10001,21 +10031,6 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -10032,10 +10047,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120208830</v>
+        <v>120208861</v>
       </c>
       <c r="B91" t="n">
-        <v>78526</v>
+        <v>100171</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10044,25 +10059,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10072,10 +10087,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>668442</v>
+        <v>668567</v>
       </c>
       <c r="R91" t="n">
-        <v>6696514</v>
+        <v>6696809</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10118,21 +10133,6 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -3740,10 +3740,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120208856</v>
+        <v>120208718</v>
       </c>
       <c r="B31" t="n">
-        <v>100171</v>
+        <v>95455</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3752,25 +3752,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668382</v>
+        <v>668450</v>
       </c>
       <c r="R31" t="n">
-        <v>6696524</v>
+        <v>6696589</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120208718</v>
+        <v>120208724</v>
       </c>
       <c r="B32" t="n">
-        <v>95455</v>
+        <v>90562</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3858,21 +3858,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668450</v>
+        <v>668608</v>
       </c>
       <c r="R32" t="n">
-        <v>6696589</v>
+        <v>6696611</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120208724</v>
+        <v>120208856</v>
       </c>
       <c r="B33" t="n">
-        <v>90562</v>
+        <v>100171</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3956,25 +3956,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668608</v>
+        <v>668382</v>
       </c>
       <c r="R33" t="n">
-        <v>6696611</v>
+        <v>6696524</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4584,10 +4584,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120208688</v>
+        <v>120208740</v>
       </c>
       <c r="B39" t="n">
-        <v>101074</v>
+        <v>57463</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4596,38 +4596,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221235</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668383</v>
+        <v>668357</v>
       </c>
       <c r="R39" t="n">
-        <v>6696524</v>
+        <v>6696585</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4686,10 +4694,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120208703</v>
+        <v>120208688</v>
       </c>
       <c r="B40" t="n">
-        <v>95455</v>
+        <v>101074</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4698,25 +4706,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4726,10 +4734,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668451</v>
+        <v>668383</v>
       </c>
       <c r="R40" t="n">
-        <v>6696602</v>
+        <v>6696524</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4772,21 +4780,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4803,10 +4796,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120208740</v>
+        <v>120208703</v>
       </c>
       <c r="B41" t="n">
-        <v>57463</v>
+        <v>95455</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4819,42 +4812,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668357</v>
+        <v>668451</v>
       </c>
       <c r="R41" t="n">
-        <v>6696585</v>
+        <v>6696602</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4897,6 +4882,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -6165,10 +6165,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120208798</v>
+        <v>120208791</v>
       </c>
       <c r="B54" t="n">
-        <v>57679</v>
+        <v>57316</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6177,20 +6177,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6199,21 +6199,24 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668342</v>
+        <v>668520</v>
       </c>
       <c r="R54" t="n">
-        <v>6696603</v>
+        <v>6696377</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6246,6 +6249,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6272,10 +6280,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120208864</v>
+        <v>120208798</v>
       </c>
       <c r="B55" t="n">
-        <v>100171</v>
+        <v>57679</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6288,34 +6296,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668527</v>
+        <v>668342</v>
       </c>
       <c r="R55" t="n">
-        <v>6696351</v>
+        <v>6696603</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6374,7 +6387,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120208857</v>
+        <v>120208864</v>
       </c>
       <c r="B56" t="n">
         <v>100171</v>
@@ -6414,10 +6427,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668438</v>
+        <v>668527</v>
       </c>
       <c r="R56" t="n">
-        <v>6696512</v>
+        <v>6696351</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6476,10 +6489,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120208791</v>
+        <v>120208857</v>
       </c>
       <c r="B57" t="n">
-        <v>57316</v>
+        <v>100171</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6488,46 +6501,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100048</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668520</v>
+        <v>668438</v>
       </c>
       <c r="R57" t="n">
-        <v>6696377</v>
+        <v>6696512</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6560,11 +6565,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7324,10 +7324,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120208823</v>
+        <v>120208708</v>
       </c>
       <c r="B65" t="n">
-        <v>57329</v>
+        <v>95455</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7336,46 +7336,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102977</v>
+        <v>53</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668565</v>
+        <v>668376</v>
       </c>
       <c r="R65" t="n">
-        <v>6696520</v>
+        <v>6696595</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7408,11 +7400,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7439,10 +7426,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120208708</v>
+        <v>120208691</v>
       </c>
       <c r="B66" t="n">
-        <v>95455</v>
+        <v>101074</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7451,25 +7438,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7479,10 +7466,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668376</v>
+        <v>668509</v>
       </c>
       <c r="R66" t="n">
-        <v>6696595</v>
+        <v>6696436</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7541,10 +7528,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120208691</v>
+        <v>120208823</v>
       </c>
       <c r="B67" t="n">
-        <v>101074</v>
+        <v>57329</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7557,34 +7544,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221235</v>
+        <v>102977</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>668509</v>
+        <v>668565</v>
       </c>
       <c r="R67" t="n">
-        <v>6696436</v>
+        <v>6696520</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7617,6 +7612,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8077,10 +8077,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120208721</v>
+        <v>120208849</v>
       </c>
       <c r="B72" t="n">
-        <v>90562</v>
+        <v>100171</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8089,25 +8089,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8117,10 +8117,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>668589</v>
+        <v>668362</v>
       </c>
       <c r="R72" t="n">
-        <v>6696866</v>
+        <v>6696583</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8281,10 +8281,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120208706</v>
+        <v>120208848</v>
       </c>
       <c r="B74" t="n">
-        <v>95455</v>
+        <v>100171</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8293,25 +8293,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8321,10 +8321,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>668408</v>
+        <v>668419</v>
       </c>
       <c r="R74" t="n">
-        <v>6696562</v>
+        <v>6696535</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8383,10 +8383,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120208779</v>
+        <v>120208818</v>
       </c>
       <c r="B75" t="n">
-        <v>97885</v>
+        <v>105009</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8399,21 +8399,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8423,10 +8423,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>668212</v>
+        <v>668437</v>
       </c>
       <c r="R75" t="n">
-        <v>6696497</v>
+        <v>6696501</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8485,10 +8485,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120208848</v>
+        <v>120208721</v>
       </c>
       <c r="B76" t="n">
-        <v>100171</v>
+        <v>90562</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8497,25 +8497,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8525,10 +8525,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>668419</v>
+        <v>668589</v>
       </c>
       <c r="R76" t="n">
-        <v>6696535</v>
+        <v>6696866</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8587,10 +8587,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120208849</v>
+        <v>120208784</v>
       </c>
       <c r="B77" t="n">
-        <v>100171</v>
+        <v>91005</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8599,25 +8599,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>668362</v>
+        <v>668273</v>
       </c>
       <c r="R77" t="n">
-        <v>6696583</v>
+        <v>6696531</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8689,10 +8689,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120208784</v>
+        <v>120208706</v>
       </c>
       <c r="B78" t="n">
-        <v>91005</v>
+        <v>95455</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8701,25 +8701,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8729,10 +8729,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>668273</v>
+        <v>668408</v>
       </c>
       <c r="R78" t="n">
-        <v>6696531</v>
+        <v>6696562</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8791,10 +8791,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120208818</v>
+        <v>120208779</v>
       </c>
       <c r="B79" t="n">
-        <v>105009</v>
+        <v>97885</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8807,21 +8807,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>668437</v>
+        <v>668212</v>
       </c>
       <c r="R79" t="n">
-        <v>6696501</v>
+        <v>6696497</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8893,10 +8893,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120208710</v>
+        <v>120208852</v>
       </c>
       <c r="B80" t="n">
-        <v>95455</v>
+        <v>100171</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8905,25 +8905,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8933,10 +8933,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>668362</v>
+        <v>668230</v>
       </c>
       <c r="R80" t="n">
-        <v>6696582</v>
+        <v>6696502</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8995,7 +8995,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120208852</v>
+        <v>120208863</v>
       </c>
       <c r="B81" t="n">
         <v>100171</v>
@@ -9035,10 +9035,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>668230</v>
+        <v>668568</v>
       </c>
       <c r="R81" t="n">
-        <v>6696502</v>
+        <v>6696542</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9097,10 +9097,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120208863</v>
+        <v>120208712</v>
       </c>
       <c r="B82" t="n">
-        <v>100171</v>
+        <v>95455</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9109,25 +9109,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9137,10 +9137,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>668568</v>
+        <v>668301</v>
       </c>
       <c r="R82" t="n">
-        <v>6696542</v>
+        <v>6696522</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9199,7 +9199,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120208712</v>
+        <v>120208710</v>
       </c>
       <c r="B83" t="n">
         <v>95455</v>
@@ -9239,10 +9239,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>668301</v>
+        <v>668362</v>
       </c>
       <c r="R83" t="n">
-        <v>6696522</v>
+        <v>6696582</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9620,10 +9620,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120208736</v>
+        <v>120208813</v>
       </c>
       <c r="B87" t="n">
-        <v>56522</v>
+        <v>97907</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9632,31 +9632,35 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9665,10 +9669,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>668532</v>
+        <v>668575</v>
       </c>
       <c r="R87" t="n">
-        <v>6696689</v>
+        <v>6696701</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9701,11 +9705,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9732,10 +9731,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120208776</v>
+        <v>120208736</v>
       </c>
       <c r="B88" t="n">
-        <v>97885</v>
+        <v>56522</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9748,34 +9747,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219798</v>
+        <v>100138</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>668186</v>
+        <v>668532</v>
       </c>
       <c r="R88" t="n">
-        <v>6696508</v>
+        <v>6696689</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9808,6 +9812,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9834,10 +9843,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120208813</v>
+        <v>120208776</v>
       </c>
       <c r="B89" t="n">
-        <v>97907</v>
+        <v>97885</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9846,47 +9855,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>668575</v>
+        <v>668186</v>
       </c>
       <c r="R89" t="n">
-        <v>6696701</v>
+        <v>6696508</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -6165,10 +6165,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120208791</v>
+        <v>120208798</v>
       </c>
       <c r="B54" t="n">
-        <v>57316</v>
+        <v>57679</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6177,20 +6177,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6199,24 +6199,21 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668520</v>
+        <v>668342</v>
       </c>
       <c r="R54" t="n">
-        <v>6696377</v>
+        <v>6696603</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6249,11 +6246,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6280,10 +6272,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120208798</v>
+        <v>120208864</v>
       </c>
       <c r="B55" t="n">
-        <v>57679</v>
+        <v>100171</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6296,39 +6288,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668342</v>
+        <v>668527</v>
       </c>
       <c r="R55" t="n">
-        <v>6696603</v>
+        <v>6696351</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6387,7 +6374,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120208864</v>
+        <v>120208857</v>
       </c>
       <c r="B56" t="n">
         <v>100171</v>
@@ -6427,10 +6414,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668527</v>
+        <v>668438</v>
       </c>
       <c r="R56" t="n">
-        <v>6696351</v>
+        <v>6696512</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6489,10 +6476,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120208857</v>
+        <v>120208791</v>
       </c>
       <c r="B57" t="n">
-        <v>100171</v>
+        <v>57316</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6501,38 +6488,46 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>100048</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668438</v>
+        <v>668520</v>
       </c>
       <c r="R57" t="n">
-        <v>6696512</v>
+        <v>6696377</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6565,6 +6560,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7324,10 +7324,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120208708</v>
+        <v>120208823</v>
       </c>
       <c r="B65" t="n">
-        <v>95455</v>
+        <v>57329</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7336,38 +7336,46 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>53</v>
+        <v>102977</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668376</v>
+        <v>668565</v>
       </c>
       <c r="R65" t="n">
-        <v>6696595</v>
+        <v>6696520</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7400,6 +7408,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7426,10 +7439,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120208691</v>
+        <v>120208708</v>
       </c>
       <c r="B66" t="n">
-        <v>101074</v>
+        <v>95455</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7438,25 +7451,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7466,10 +7479,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668509</v>
+        <v>668376</v>
       </c>
       <c r="R66" t="n">
-        <v>6696436</v>
+        <v>6696595</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7528,10 +7541,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120208823</v>
+        <v>120208691</v>
       </c>
       <c r="B67" t="n">
-        <v>57329</v>
+        <v>101074</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7544,42 +7557,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102977</v>
+        <v>221235</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>668565</v>
+        <v>668509</v>
       </c>
       <c r="R67" t="n">
-        <v>6696520</v>
+        <v>6696436</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7612,11 +7617,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8077,10 +8077,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120208849</v>
+        <v>120208721</v>
       </c>
       <c r="B72" t="n">
-        <v>100171</v>
+        <v>90562</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8089,25 +8089,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8117,10 +8117,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>668362</v>
+        <v>668589</v>
       </c>
       <c r="R72" t="n">
-        <v>6696583</v>
+        <v>6696866</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8281,10 +8281,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120208848</v>
+        <v>120208706</v>
       </c>
       <c r="B74" t="n">
-        <v>100171</v>
+        <v>95455</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8293,25 +8293,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8321,10 +8321,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>668419</v>
+        <v>668408</v>
       </c>
       <c r="R74" t="n">
-        <v>6696535</v>
+        <v>6696562</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8383,10 +8383,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120208818</v>
+        <v>120208779</v>
       </c>
       <c r="B75" t="n">
-        <v>105009</v>
+        <v>97885</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8399,21 +8399,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8423,10 +8423,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>668437</v>
+        <v>668212</v>
       </c>
       <c r="R75" t="n">
-        <v>6696501</v>
+        <v>6696497</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8485,10 +8485,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120208721</v>
+        <v>120208848</v>
       </c>
       <c r="B76" t="n">
-        <v>90562</v>
+        <v>100171</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8497,25 +8497,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8525,10 +8525,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>668589</v>
+        <v>668419</v>
       </c>
       <c r="R76" t="n">
-        <v>6696866</v>
+        <v>6696535</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8587,10 +8587,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120208784</v>
+        <v>120208849</v>
       </c>
       <c r="B77" t="n">
-        <v>91005</v>
+        <v>100171</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8599,25 +8599,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>668273</v>
+        <v>668362</v>
       </c>
       <c r="R77" t="n">
-        <v>6696531</v>
+        <v>6696583</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8689,10 +8689,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120208706</v>
+        <v>120208784</v>
       </c>
       <c r="B78" t="n">
-        <v>95455</v>
+        <v>91005</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8701,25 +8701,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8729,10 +8729,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>668408</v>
+        <v>668273</v>
       </c>
       <c r="R78" t="n">
-        <v>6696562</v>
+        <v>6696531</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8791,10 +8791,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120208779</v>
+        <v>120208818</v>
       </c>
       <c r="B79" t="n">
-        <v>97885</v>
+        <v>105009</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8807,21 +8807,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>668212</v>
+        <v>668437</v>
       </c>
       <c r="R79" t="n">
-        <v>6696497</v>
+        <v>6696501</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9620,10 +9620,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120208813</v>
+        <v>120208736</v>
       </c>
       <c r="B87" t="n">
-        <v>97907</v>
+        <v>56522</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9632,35 +9632,31 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9669,10 +9665,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>668575</v>
+        <v>668532</v>
       </c>
       <c r="R87" t="n">
-        <v>6696701</v>
+        <v>6696689</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9705,6 +9701,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9731,10 +9732,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120208736</v>
+        <v>120208776</v>
       </c>
       <c r="B88" t="n">
-        <v>56522</v>
+        <v>97885</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9747,39 +9748,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100138</v>
+        <v>219798</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>668532</v>
+        <v>668186</v>
       </c>
       <c r="R88" t="n">
-        <v>6696689</v>
+        <v>6696508</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9812,11 +9808,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9843,10 +9834,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120208776</v>
+        <v>120208813</v>
       </c>
       <c r="B89" t="n">
-        <v>97885</v>
+        <v>97907</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9855,38 +9846,47 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>668186</v>
+        <v>668575</v>
       </c>
       <c r="R89" t="n">
-        <v>6696508</v>
+        <v>6696701</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120208756</v>
+        <v>120208777</v>
       </c>
       <c r="B2" t="n">
-        <v>57326</v>
+        <v>97885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668467</v>
+        <v>668188</v>
       </c>
       <c r="R2" t="n">
-        <v>6696630</v>
+        <v>6696531</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120208777</v>
+        <v>120208815</v>
       </c>
       <c r="B3" t="n">
-        <v>97885</v>
+        <v>74577</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668188</v>
+        <v>668311</v>
       </c>
       <c r="R3" t="n">
-        <v>6696531</v>
+        <v>6696520</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120208815</v>
+        <v>120208705</v>
       </c>
       <c r="B4" t="n">
-        <v>74577</v>
+        <v>95455</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668311</v>
+        <v>668521</v>
       </c>
       <c r="R4" t="n">
-        <v>6696520</v>
+        <v>6696330</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,6 +965,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120208705</v>
+        <v>120208756</v>
       </c>
       <c r="B5" t="n">
-        <v>95455</v>
+        <v>57326</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,34 +1012,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668521</v>
+        <v>668467</v>
       </c>
       <c r="R5" t="n">
-        <v>6696330</v>
+        <v>6696630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,6 +1079,11 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1077,21 +1092,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -4584,10 +4584,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120208740</v>
+        <v>120208688</v>
       </c>
       <c r="B39" t="n">
-        <v>57463</v>
+        <v>101074</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4596,46 +4596,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>221235</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668357</v>
+        <v>668383</v>
       </c>
       <c r="R39" t="n">
-        <v>6696585</v>
+        <v>6696524</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4694,10 +4686,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120208688</v>
+        <v>120208703</v>
       </c>
       <c r="B40" t="n">
-        <v>101074</v>
+        <v>95455</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4706,25 +4698,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4734,10 +4726,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668383</v>
+        <v>668451</v>
       </c>
       <c r="R40" t="n">
-        <v>6696524</v>
+        <v>6696602</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4780,6 +4772,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4796,10 +4803,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120208703</v>
+        <v>120208740</v>
       </c>
       <c r="B41" t="n">
-        <v>95455</v>
+        <v>57463</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4812,34 +4819,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668451</v>
+        <v>668357</v>
       </c>
       <c r="R41" t="n">
-        <v>6696602</v>
+        <v>6696585</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4882,21 +4897,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5553,10 +5553,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120208722</v>
+        <v>120208686</v>
       </c>
       <c r="B48" t="n">
-        <v>90562</v>
+        <v>101074</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5565,25 +5565,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>221235</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668552</v>
+        <v>668242</v>
       </c>
       <c r="R48" t="n">
-        <v>6696684</v>
+        <v>6696541</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5655,10 +5655,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120208686</v>
+        <v>120208860</v>
       </c>
       <c r="B49" t="n">
-        <v>101074</v>
+        <v>100171</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668242</v>
+        <v>668566</v>
       </c>
       <c r="R49" t="n">
-        <v>6696541</v>
+        <v>6696858</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5757,10 +5757,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120208707</v>
+        <v>120208722</v>
       </c>
       <c r="B50" t="n">
-        <v>95455</v>
+        <v>90562</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5773,21 +5773,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5797,10 +5797,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668394</v>
+        <v>668552</v>
       </c>
       <c r="R50" t="n">
-        <v>6696553</v>
+        <v>6696684</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5859,10 +5859,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120208860</v>
+        <v>120208707</v>
       </c>
       <c r="B51" t="n">
-        <v>100171</v>
+        <v>95455</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5871,25 +5871,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668566</v>
+        <v>668394</v>
       </c>
       <c r="R51" t="n">
-        <v>6696858</v>
+        <v>6696553</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6165,10 +6165,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120208798</v>
+        <v>120208791</v>
       </c>
       <c r="B54" t="n">
-        <v>57679</v>
+        <v>57316</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6177,20 +6177,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6199,21 +6199,24 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668342</v>
+        <v>668520</v>
       </c>
       <c r="R54" t="n">
-        <v>6696603</v>
+        <v>6696377</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6246,6 +6249,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6272,10 +6280,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120208864</v>
+        <v>120208798</v>
       </c>
       <c r="B55" t="n">
-        <v>100171</v>
+        <v>57679</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6288,34 +6296,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668527</v>
+        <v>668342</v>
       </c>
       <c r="R55" t="n">
-        <v>6696351</v>
+        <v>6696603</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6374,7 +6387,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120208857</v>
+        <v>120208864</v>
       </c>
       <c r="B56" t="n">
         <v>100171</v>
@@ -6414,10 +6427,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668438</v>
+        <v>668527</v>
       </c>
       <c r="R56" t="n">
-        <v>6696512</v>
+        <v>6696351</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6476,10 +6489,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120208791</v>
+        <v>120208857</v>
       </c>
       <c r="B57" t="n">
-        <v>57316</v>
+        <v>100171</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6488,46 +6501,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100048</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668520</v>
+        <v>668438</v>
       </c>
       <c r="R57" t="n">
-        <v>6696377</v>
+        <v>6696512</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6560,11 +6565,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7643,10 +7643,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120208792</v>
+        <v>120208781</v>
       </c>
       <c r="B68" t="n">
-        <v>57316</v>
+        <v>97885</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7655,46 +7655,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100048</v>
+        <v>219798</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>668517</v>
+        <v>668261</v>
       </c>
       <c r="R68" t="n">
-        <v>6696457</v>
+        <v>6696558</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7727,11 +7719,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7758,10 +7745,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120208781</v>
+        <v>120208743</v>
       </c>
       <c r="B69" t="n">
-        <v>97885</v>
+        <v>57463</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7770,38 +7757,46 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>668261</v>
+        <v>668533</v>
       </c>
       <c r="R69" t="n">
-        <v>6696558</v>
+        <v>6696366</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7860,7 +7855,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120208743</v>
+        <v>120208744</v>
       </c>
       <c r="B70" t="n">
         <v>57463</v>
@@ -7894,24 +7889,21 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>668533</v>
+        <v>668602</v>
       </c>
       <c r="R70" t="n">
-        <v>6696366</v>
+        <v>6696625</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7970,10 +7962,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120208744</v>
+        <v>120208792</v>
       </c>
       <c r="B71" t="n">
-        <v>57463</v>
+        <v>57316</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7986,39 +7978,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>668602</v>
+        <v>668517</v>
       </c>
       <c r="R71" t="n">
-        <v>6696625</v>
+        <v>6696457</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8051,6 +8046,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120208777</v>
+        <v>120208756</v>
       </c>
       <c r="B2" t="n">
-        <v>97885</v>
+        <v>57326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668188</v>
+        <v>668467</v>
       </c>
       <c r="R2" t="n">
-        <v>6696531</v>
+        <v>6696630</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120208815</v>
+        <v>120208777</v>
       </c>
       <c r="B3" t="n">
-        <v>74577</v>
+        <v>97885</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668311</v>
+        <v>668188</v>
       </c>
       <c r="R3" t="n">
-        <v>6696520</v>
+        <v>6696531</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120208705</v>
+        <v>120208815</v>
       </c>
       <c r="B4" t="n">
-        <v>95455</v>
+        <v>74577</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668521</v>
+        <v>668311</v>
       </c>
       <c r="R4" t="n">
-        <v>6696330</v>
+        <v>6696520</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,21 +975,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120208756</v>
+        <v>120208705</v>
       </c>
       <c r="B5" t="n">
-        <v>57326</v>
+        <v>95455</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668467</v>
+        <v>668521</v>
       </c>
       <c r="R5" t="n">
-        <v>6696630</v>
+        <v>6696330</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,11 +1069,6 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1092,6 +1077,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120208854</v>
+        <v>120208682</v>
       </c>
       <c r="B6" t="n">
-        <v>100171</v>
+        <v>101074</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,21 +1124,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668370</v>
+        <v>668186</v>
       </c>
       <c r="R6" t="n">
-        <v>6696506</v>
+        <v>6696508</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120208684</v>
+        <v>120208713</v>
       </c>
       <c r="B7" t="n">
-        <v>101074</v>
+        <v>95455</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668201</v>
+        <v>668379</v>
       </c>
       <c r="R7" t="n">
-        <v>6696519</v>
+        <v>6696528</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120208682</v>
+        <v>120208759</v>
       </c>
       <c r="B8" t="n">
-        <v>101074</v>
+        <v>57326</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,38 +1324,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668186</v>
+        <v>668572</v>
       </c>
       <c r="R8" t="n">
-        <v>6696508</v>
+        <v>6696839</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1393,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120208713</v>
+        <v>120208684</v>
       </c>
       <c r="B9" t="n">
-        <v>95455</v>
+        <v>101074</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,25 +1436,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668379</v>
+        <v>668201</v>
       </c>
       <c r="R9" t="n">
-        <v>6696528</v>
+        <v>6696519</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1618,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120208759</v>
+        <v>120208854</v>
       </c>
       <c r="B11" t="n">
-        <v>57326</v>
+        <v>100171</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,43 +1640,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668572</v>
+        <v>668370</v>
       </c>
       <c r="R11" t="n">
-        <v>6696839</v>
+        <v>6696506</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2899,10 +2899,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120208758</v>
+        <v>120208783</v>
       </c>
       <c r="B23" t="n">
-        <v>57326</v>
+        <v>90334</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2911,43 +2911,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668240</v>
+        <v>668281</v>
       </c>
       <c r="R23" t="n">
-        <v>6696522</v>
+        <v>6696528</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,11 +2975,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3011,10 +3001,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120208783</v>
+        <v>120208690</v>
       </c>
       <c r="B24" t="n">
-        <v>90334</v>
+        <v>101074</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3027,21 +3017,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3215</v>
+        <v>221235</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3051,10 +3041,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668281</v>
+        <v>668564</v>
       </c>
       <c r="R24" t="n">
-        <v>6696528</v>
+        <v>6696811</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,10 +3103,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120208690</v>
+        <v>120208737</v>
       </c>
       <c r="B25" t="n">
-        <v>101074</v>
+        <v>56522</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3129,34 +3119,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221235</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668564</v>
+        <v>668566</v>
       </c>
       <c r="R25" t="n">
-        <v>6696811</v>
+        <v>6696455</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3189,6 +3184,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3215,10 +3215,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120208737</v>
+        <v>120208739</v>
       </c>
       <c r="B26" t="n">
-        <v>56522</v>
+        <v>103418</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3231,39 +3231,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>222412</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668566</v>
+        <v>668166</v>
       </c>
       <c r="R26" t="n">
-        <v>6696455</v>
+        <v>6696498</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3296,11 +3291,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3327,10 +3317,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120208739</v>
+        <v>120208775</v>
       </c>
       <c r="B27" t="n">
-        <v>103418</v>
+        <v>97885</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3343,21 +3333,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3367,10 +3357,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668166</v>
+        <v>668180</v>
       </c>
       <c r="R27" t="n">
-        <v>6696498</v>
+        <v>6696501</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,10 +3419,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120208775</v>
+        <v>120208758</v>
       </c>
       <c r="B28" t="n">
-        <v>97885</v>
+        <v>57326</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3441,38 +3431,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668180</v>
+        <v>668240</v>
       </c>
       <c r="R28" t="n">
-        <v>6696501</v>
+        <v>6696522</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3505,6 +3500,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -5553,10 +5553,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120208686</v>
+        <v>120208722</v>
       </c>
       <c r="B48" t="n">
-        <v>101074</v>
+        <v>90562</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5565,25 +5565,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221235</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668242</v>
+        <v>668552</v>
       </c>
       <c r="R48" t="n">
-        <v>6696541</v>
+        <v>6696684</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5655,10 +5655,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120208860</v>
+        <v>120208686</v>
       </c>
       <c r="B49" t="n">
-        <v>100171</v>
+        <v>101074</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5671,21 +5671,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5695,10 +5695,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668566</v>
+        <v>668242</v>
       </c>
       <c r="R49" t="n">
-        <v>6696858</v>
+        <v>6696541</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5757,10 +5757,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120208722</v>
+        <v>120208707</v>
       </c>
       <c r="B50" t="n">
-        <v>90562</v>
+        <v>95455</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5773,21 +5773,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5797,10 +5797,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668552</v>
+        <v>668394</v>
       </c>
       <c r="R50" t="n">
-        <v>6696684</v>
+        <v>6696553</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5859,10 +5859,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120208707</v>
+        <v>120208860</v>
       </c>
       <c r="B51" t="n">
-        <v>95455</v>
+        <v>100171</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5871,25 +5871,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5899,10 +5899,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668394</v>
+        <v>668566</v>
       </c>
       <c r="R51" t="n">
-        <v>6696553</v>
+        <v>6696858</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6165,10 +6165,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120208791</v>
+        <v>120208798</v>
       </c>
       <c r="B54" t="n">
-        <v>57316</v>
+        <v>57679</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6177,20 +6177,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6199,24 +6199,21 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668520</v>
+        <v>668342</v>
       </c>
       <c r="R54" t="n">
-        <v>6696377</v>
+        <v>6696603</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6249,11 +6246,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6280,10 +6272,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120208798</v>
+        <v>120208864</v>
       </c>
       <c r="B55" t="n">
-        <v>57679</v>
+        <v>100171</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6296,39 +6288,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668342</v>
+        <v>668527</v>
       </c>
       <c r="R55" t="n">
-        <v>6696603</v>
+        <v>6696351</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6387,7 +6374,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120208864</v>
+        <v>120208857</v>
       </c>
       <c r="B56" t="n">
         <v>100171</v>
@@ -6427,10 +6414,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668527</v>
+        <v>668438</v>
       </c>
       <c r="R56" t="n">
-        <v>6696351</v>
+        <v>6696512</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6489,10 +6476,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120208857</v>
+        <v>120208791</v>
       </c>
       <c r="B57" t="n">
-        <v>100171</v>
+        <v>57316</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6501,38 +6488,46 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>100048</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668438</v>
+        <v>668520</v>
       </c>
       <c r="R57" t="n">
-        <v>6696512</v>
+        <v>6696377</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6565,6 +6560,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7324,10 +7324,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120208823</v>
+        <v>120208708</v>
       </c>
       <c r="B65" t="n">
-        <v>57329</v>
+        <v>95455</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7336,46 +7336,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102977</v>
+        <v>53</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668565</v>
+        <v>668376</v>
       </c>
       <c r="R65" t="n">
-        <v>6696520</v>
+        <v>6696595</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7408,11 +7400,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7439,10 +7426,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120208708</v>
+        <v>120208691</v>
       </c>
       <c r="B66" t="n">
-        <v>95455</v>
+        <v>101074</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7451,25 +7438,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7479,10 +7466,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668376</v>
+        <v>668509</v>
       </c>
       <c r="R66" t="n">
-        <v>6696595</v>
+        <v>6696436</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7541,10 +7528,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120208691</v>
+        <v>120208823</v>
       </c>
       <c r="B67" t="n">
-        <v>101074</v>
+        <v>57329</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7557,34 +7544,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221235</v>
+        <v>102977</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>668509</v>
+        <v>668565</v>
       </c>
       <c r="R67" t="n">
-        <v>6696436</v>
+        <v>6696520</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7617,6 +7612,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7643,10 +7643,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120208781</v>
+        <v>120208792</v>
       </c>
       <c r="B68" t="n">
-        <v>97885</v>
+        <v>57316</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7655,38 +7655,46 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>219798</v>
+        <v>100048</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>668261</v>
+        <v>668517</v>
       </c>
       <c r="R68" t="n">
-        <v>6696558</v>
+        <v>6696457</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7719,6 +7727,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7745,10 +7758,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120208743</v>
+        <v>120208781</v>
       </c>
       <c r="B69" t="n">
-        <v>57463</v>
+        <v>97885</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7757,46 +7770,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>668533</v>
+        <v>668261</v>
       </c>
       <c r="R69" t="n">
-        <v>6696366</v>
+        <v>6696558</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7855,7 +7860,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120208744</v>
+        <v>120208743</v>
       </c>
       <c r="B70" t="n">
         <v>57463</v>
@@ -7889,21 +7894,24 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>668602</v>
+        <v>668533</v>
       </c>
       <c r="R70" t="n">
-        <v>6696625</v>
+        <v>6696366</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7962,10 +7970,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120208792</v>
+        <v>120208744</v>
       </c>
       <c r="B71" t="n">
-        <v>57316</v>
+        <v>57463</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7978,42 +7986,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>668517</v>
+        <v>668602</v>
       </c>
       <c r="R71" t="n">
-        <v>6696457</v>
+        <v>6696625</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8046,11 +8051,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8077,10 +8077,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120208721</v>
+        <v>120208849</v>
       </c>
       <c r="B72" t="n">
-        <v>90562</v>
+        <v>100171</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8089,25 +8089,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8117,10 +8117,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>668589</v>
+        <v>668362</v>
       </c>
       <c r="R72" t="n">
-        <v>6696866</v>
+        <v>6696583</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8281,10 +8281,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120208706</v>
+        <v>120208848</v>
       </c>
       <c r="B74" t="n">
-        <v>95455</v>
+        <v>100171</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8293,25 +8293,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8321,10 +8321,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>668408</v>
+        <v>668419</v>
       </c>
       <c r="R74" t="n">
-        <v>6696562</v>
+        <v>6696535</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8383,10 +8383,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120208779</v>
+        <v>120208818</v>
       </c>
       <c r="B75" t="n">
-        <v>97885</v>
+        <v>105009</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8399,21 +8399,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8423,10 +8423,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>668212</v>
+        <v>668437</v>
       </c>
       <c r="R75" t="n">
-        <v>6696497</v>
+        <v>6696501</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8485,10 +8485,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120208848</v>
+        <v>120208721</v>
       </c>
       <c r="B76" t="n">
-        <v>100171</v>
+        <v>90562</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8497,25 +8497,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8525,10 +8525,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>668419</v>
+        <v>668589</v>
       </c>
       <c r="R76" t="n">
-        <v>6696535</v>
+        <v>6696866</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8587,10 +8587,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120208849</v>
+        <v>120208784</v>
       </c>
       <c r="B77" t="n">
-        <v>100171</v>
+        <v>91005</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8599,25 +8599,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>668362</v>
+        <v>668273</v>
       </c>
       <c r="R77" t="n">
-        <v>6696583</v>
+        <v>6696531</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8689,10 +8689,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120208784</v>
+        <v>120208706</v>
       </c>
       <c r="B78" t="n">
-        <v>91005</v>
+        <v>95455</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8701,25 +8701,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8729,10 +8729,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>668273</v>
+        <v>668408</v>
       </c>
       <c r="R78" t="n">
-        <v>6696531</v>
+        <v>6696562</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8791,10 +8791,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120208818</v>
+        <v>120208779</v>
       </c>
       <c r="B79" t="n">
-        <v>105009</v>
+        <v>97885</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8807,21 +8807,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8831,10 +8831,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>668437</v>
+        <v>668212</v>
       </c>
       <c r="R79" t="n">
-        <v>6696501</v>
+        <v>6696497</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120208756</v>
+        <v>120208777</v>
       </c>
       <c r="B2" t="n">
-        <v>57326</v>
+        <v>97885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668467</v>
+        <v>668188</v>
       </c>
       <c r="R2" t="n">
-        <v>6696630</v>
+        <v>6696531</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120208777</v>
+        <v>120208815</v>
       </c>
       <c r="B3" t="n">
-        <v>97885</v>
+        <v>74577</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668188</v>
+        <v>668311</v>
       </c>
       <c r="R3" t="n">
-        <v>6696531</v>
+        <v>6696520</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120208815</v>
+        <v>120208705</v>
       </c>
       <c r="B4" t="n">
-        <v>74577</v>
+        <v>95455</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668311</v>
+        <v>668521</v>
       </c>
       <c r="R4" t="n">
-        <v>6696520</v>
+        <v>6696330</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -975,6 +965,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120208705</v>
+        <v>120208756</v>
       </c>
       <c r="B5" t="n">
-        <v>95455</v>
+        <v>57326</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,34 +1012,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668521</v>
+        <v>668467</v>
       </c>
       <c r="R5" t="n">
-        <v>6696330</v>
+        <v>6696630</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,6 +1079,11 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1077,21 +1092,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120208682</v>
+        <v>120208854</v>
       </c>
       <c r="B6" t="n">
-        <v>101074</v>
+        <v>100171</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,21 +1124,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668186</v>
+        <v>668370</v>
       </c>
       <c r="R6" t="n">
-        <v>6696508</v>
+        <v>6696506</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120208713</v>
+        <v>120208684</v>
       </c>
       <c r="B7" t="n">
-        <v>95455</v>
+        <v>101074</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668379</v>
+        <v>668201</v>
       </c>
       <c r="R7" t="n">
-        <v>6696528</v>
+        <v>6696519</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120208759</v>
+        <v>120208682</v>
       </c>
       <c r="B8" t="n">
-        <v>57326</v>
+        <v>101074</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,43 +1324,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668572</v>
+        <v>668186</v>
       </c>
       <c r="R8" t="n">
-        <v>6696839</v>
+        <v>6696508</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120208684</v>
+        <v>120208713</v>
       </c>
       <c r="B9" t="n">
-        <v>101074</v>
+        <v>95455</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668201</v>
+        <v>668379</v>
       </c>
       <c r="R9" t="n">
-        <v>6696519</v>
+        <v>6696528</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1628,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120208854</v>
+        <v>120208759</v>
       </c>
       <c r="B11" t="n">
-        <v>100171</v>
+        <v>57326</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1640,38 +1630,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668370</v>
+        <v>668572</v>
       </c>
       <c r="R11" t="n">
-        <v>6696506</v>
+        <v>6696839</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,6 +1699,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2278,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120208800</v>
+        <v>120208716</v>
       </c>
       <c r="B17" t="n">
-        <v>57679</v>
+        <v>95455</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2290,47 +2290,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668525</v>
+        <v>668439</v>
       </c>
       <c r="R17" t="n">
-        <v>6696405</v>
+        <v>6696517</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2389,10 +2380,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120208716</v>
+        <v>120208782</v>
       </c>
       <c r="B18" t="n">
-        <v>95455</v>
+        <v>97885</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2401,25 +2392,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2429,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668439</v>
+        <v>668279</v>
       </c>
       <c r="R18" t="n">
-        <v>6696517</v>
+        <v>6696528</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2491,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120208782</v>
+        <v>120208709</v>
       </c>
       <c r="B19" t="n">
-        <v>97885</v>
+        <v>95455</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2503,25 +2494,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2531,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668279</v>
+        <v>668362</v>
       </c>
       <c r="R19" t="n">
-        <v>6696528</v>
+        <v>6696599</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2593,10 +2584,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120208709</v>
+        <v>120208774</v>
       </c>
       <c r="B20" t="n">
-        <v>95455</v>
+        <v>97885</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2605,25 +2596,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2633,10 +2624,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668362</v>
+        <v>668365</v>
       </c>
       <c r="R20" t="n">
-        <v>6696599</v>
+        <v>6696575</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2695,10 +2686,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120208774</v>
+        <v>120208800</v>
       </c>
       <c r="B21" t="n">
-        <v>97885</v>
+        <v>57679</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2711,34 +2702,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219798</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668365</v>
+        <v>668525</v>
       </c>
       <c r="R21" t="n">
-        <v>6696575</v>
+        <v>6696405</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120208783</v>
+        <v>120208758</v>
       </c>
       <c r="B23" t="n">
-        <v>90334</v>
+        <v>57326</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2911,38 +2911,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668281</v>
+        <v>668240</v>
       </c>
       <c r="R23" t="n">
-        <v>6696528</v>
+        <v>6696522</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2975,6 +2980,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3001,10 +3011,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120208690</v>
+        <v>120208783</v>
       </c>
       <c r="B24" t="n">
-        <v>101074</v>
+        <v>90334</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3017,21 +3027,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221235</v>
+        <v>3215</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3041,10 +3051,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668564</v>
+        <v>668281</v>
       </c>
       <c r="R24" t="n">
-        <v>6696811</v>
+        <v>6696528</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3103,10 +3113,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120208737</v>
+        <v>120208690</v>
       </c>
       <c r="B25" t="n">
-        <v>56522</v>
+        <v>101074</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3119,39 +3129,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>221235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668566</v>
+        <v>668564</v>
       </c>
       <c r="R25" t="n">
-        <v>6696455</v>
+        <v>6696811</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3184,11 +3189,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3215,10 +3215,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120208739</v>
+        <v>120208737</v>
       </c>
       <c r="B26" t="n">
-        <v>103418</v>
+        <v>56522</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3231,34 +3231,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222412</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668166</v>
+        <v>668566</v>
       </c>
       <c r="R26" t="n">
-        <v>6696498</v>
+        <v>6696455</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3291,6 +3296,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3317,10 +3327,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120208775</v>
+        <v>120208739</v>
       </c>
       <c r="B27" t="n">
-        <v>97885</v>
+        <v>103418</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3333,21 +3343,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3357,10 +3367,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668180</v>
+        <v>668166</v>
       </c>
       <c r="R27" t="n">
-        <v>6696501</v>
+        <v>6696498</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3419,10 +3429,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120208758</v>
+        <v>120208775</v>
       </c>
       <c r="B28" t="n">
-        <v>57326</v>
+        <v>97885</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3431,43 +3441,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668240</v>
+        <v>668180</v>
       </c>
       <c r="R28" t="n">
-        <v>6696522</v>
+        <v>6696501</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3500,11 +3505,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4584,10 +4584,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120208688</v>
+        <v>120208740</v>
       </c>
       <c r="B39" t="n">
-        <v>101074</v>
+        <v>57463</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4596,38 +4596,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221235</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668383</v>
+        <v>668357</v>
       </c>
       <c r="R39" t="n">
-        <v>6696524</v>
+        <v>6696585</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4686,10 +4694,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120208703</v>
+        <v>120208688</v>
       </c>
       <c r="B40" t="n">
-        <v>95455</v>
+        <v>101074</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4698,25 +4706,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4726,10 +4734,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668451</v>
+        <v>668383</v>
       </c>
       <c r="R40" t="n">
-        <v>6696602</v>
+        <v>6696524</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4772,21 +4780,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4803,10 +4796,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120208740</v>
+        <v>120208703</v>
       </c>
       <c r="B41" t="n">
-        <v>57463</v>
+        <v>95455</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4819,42 +4812,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668357</v>
+        <v>668451</v>
       </c>
       <c r="R41" t="n">
-        <v>6696585</v>
+        <v>6696602</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4897,6 +4882,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -2899,10 +2899,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120208758</v>
+        <v>120208783</v>
       </c>
       <c r="B23" t="n">
-        <v>57326</v>
+        <v>90334</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2911,43 +2911,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668240</v>
+        <v>668281</v>
       </c>
       <c r="R23" t="n">
-        <v>6696522</v>
+        <v>6696528</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,11 +2975,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3011,10 +3001,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120208783</v>
+        <v>120208690</v>
       </c>
       <c r="B24" t="n">
-        <v>90334</v>
+        <v>101074</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3027,21 +3017,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3215</v>
+        <v>221235</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3051,10 +3041,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668281</v>
+        <v>668564</v>
       </c>
       <c r="R24" t="n">
-        <v>6696528</v>
+        <v>6696811</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,10 +3103,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120208690</v>
+        <v>120208737</v>
       </c>
       <c r="B25" t="n">
-        <v>101074</v>
+        <v>56522</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3129,34 +3119,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221235</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668564</v>
+        <v>668566</v>
       </c>
       <c r="R25" t="n">
-        <v>6696811</v>
+        <v>6696455</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3189,6 +3184,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3215,10 +3215,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120208737</v>
+        <v>120208739</v>
       </c>
       <c r="B26" t="n">
-        <v>56522</v>
+        <v>103418</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3231,39 +3231,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>222412</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668566</v>
+        <v>668166</v>
       </c>
       <c r="R26" t="n">
-        <v>6696455</v>
+        <v>6696498</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3296,11 +3291,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3327,10 +3317,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120208739</v>
+        <v>120208775</v>
       </c>
       <c r="B27" t="n">
-        <v>103418</v>
+        <v>97885</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3343,21 +3333,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3367,10 +3357,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668166</v>
+        <v>668180</v>
       </c>
       <c r="R27" t="n">
-        <v>6696498</v>
+        <v>6696501</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,10 +3419,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120208775</v>
+        <v>120208758</v>
       </c>
       <c r="B28" t="n">
-        <v>97885</v>
+        <v>57326</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3441,38 +3431,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668180</v>
+        <v>668240</v>
       </c>
       <c r="R28" t="n">
-        <v>6696501</v>
+        <v>6696522</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3505,6 +3500,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120208777</v>
+        <v>120208850</v>
       </c>
       <c r="B2" t="n">
-        <v>97885</v>
+        <v>100194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668188</v>
+        <v>668179</v>
       </c>
       <c r="R2" t="n">
-        <v>6696531</v>
+        <v>6696528</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120208815</v>
+        <v>120208743</v>
       </c>
       <c r="B3" t="n">
-        <v>74577</v>
+        <v>57473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668311</v>
+        <v>668533</v>
       </c>
       <c r="R3" t="n">
-        <v>6696520</v>
+        <v>6696366</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120208705</v>
+        <v>120208744</v>
       </c>
       <c r="B4" t="n">
-        <v>95455</v>
+        <v>57473</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +903,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668521</v>
+        <v>668602</v>
       </c>
       <c r="R4" t="n">
-        <v>6696330</v>
+        <v>6696625</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,21 +978,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -996,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120208756</v>
+        <v>120208705</v>
       </c>
       <c r="B5" t="n">
-        <v>57326</v>
+        <v>95478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,39 +1010,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668467</v>
+        <v>668521</v>
       </c>
       <c r="R5" t="n">
-        <v>6696630</v>
+        <v>6696330</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,11 +1072,6 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1092,6 +1080,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1108,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120208854</v>
+        <v>120208706</v>
       </c>
       <c r="B6" t="n">
-        <v>100171</v>
+        <v>95478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,25 +1123,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668370</v>
+        <v>668408</v>
       </c>
       <c r="R6" t="n">
-        <v>6696506</v>
+        <v>6696562</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120208684</v>
+        <v>120208758</v>
       </c>
       <c r="B7" t="n">
-        <v>101074</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,38 +1225,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668201</v>
+        <v>668240</v>
       </c>
       <c r="R7" t="n">
-        <v>6696519</v>
+        <v>6696522</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1294,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120208682</v>
+        <v>120208826</v>
       </c>
       <c r="B8" t="n">
-        <v>101074</v>
+        <v>4772</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1341,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>102306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668186</v>
+        <v>668442</v>
       </c>
       <c r="R8" t="n">
-        <v>6696508</v>
+        <v>6696515</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120208713</v>
+        <v>120208819</v>
       </c>
       <c r="B9" t="n">
-        <v>95455</v>
+        <v>105032</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,25 +1439,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668379</v>
+        <v>668579</v>
       </c>
       <c r="R9" t="n">
-        <v>6696528</v>
+        <v>6696655</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120208827</v>
+        <v>120208777</v>
       </c>
       <c r="B10" t="n">
-        <v>4772</v>
+        <v>97908</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1545,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102306</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668457</v>
+        <v>668188</v>
       </c>
       <c r="R10" t="n">
-        <v>6696523</v>
+        <v>6696531</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120208759</v>
+        <v>120208709</v>
       </c>
       <c r="B11" t="n">
-        <v>57326</v>
+        <v>95478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,39 +1647,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668572</v>
+        <v>668362</v>
       </c>
       <c r="R11" t="n">
-        <v>6696839</v>
+        <v>6696599</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1707,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1733,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120208812</v>
+        <v>120208739</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>103441</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1742,47 +1745,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668568</v>
+        <v>668166</v>
       </c>
       <c r="R12" t="n">
-        <v>6696851</v>
+        <v>6696498</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1835,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120208826</v>
+        <v>120208791</v>
       </c>
       <c r="B13" t="n">
-        <v>4772</v>
+        <v>57326</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,38 +1847,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102306</v>
+        <v>100048</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668442</v>
+        <v>668520</v>
       </c>
       <c r="R13" t="n">
-        <v>6696515</v>
+        <v>6696377</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,6 +1919,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1943,10 +1950,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120208785</v>
+        <v>120208724</v>
       </c>
       <c r="B14" t="n">
-        <v>90846</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1959,21 +1966,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1983,10 +1990,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668552</v>
+        <v>668608</v>
       </c>
       <c r="R14" t="n">
-        <v>6696684</v>
+        <v>6696611</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,10 +2052,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120208735</v>
+        <v>120208774</v>
       </c>
       <c r="B15" t="n">
-        <v>56522</v>
+        <v>97908</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2061,43 +2068,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668518</v>
+        <v>668365</v>
       </c>
       <c r="R15" t="n">
-        <v>6696678</v>
+        <v>6696575</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2130,11 +2128,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2161,10 +2154,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120208704</v>
+        <v>120208721</v>
       </c>
       <c r="B16" t="n">
-        <v>95455</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2177,21 +2170,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2201,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668571</v>
+        <v>668589</v>
       </c>
       <c r="R16" t="n">
-        <v>6696816</v>
+        <v>6696866</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2247,21 +2240,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2278,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120208716</v>
+        <v>120208687</v>
       </c>
       <c r="B17" t="n">
-        <v>95455</v>
+        <v>101097</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2290,25 +2268,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2318,10 +2296,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668439</v>
+        <v>668382</v>
       </c>
       <c r="R17" t="n">
-        <v>6696517</v>
+        <v>6696529</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2380,10 +2358,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120208782</v>
+        <v>120208859</v>
       </c>
       <c r="B18" t="n">
-        <v>97885</v>
+        <v>100194</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2396,21 +2374,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2420,10 +2398,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668279</v>
+        <v>668581</v>
       </c>
       <c r="R18" t="n">
-        <v>6696528</v>
+        <v>6696848</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2482,10 +2460,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120208709</v>
+        <v>120208856</v>
       </c>
       <c r="B19" t="n">
-        <v>95455</v>
+        <v>100194</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2494,25 +2472,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2522,10 +2500,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668362</v>
+        <v>668382</v>
       </c>
       <c r="R19" t="n">
-        <v>6696599</v>
+        <v>6696524</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,10 +2562,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120208774</v>
+        <v>120208851</v>
       </c>
       <c r="B20" t="n">
-        <v>97885</v>
+        <v>100194</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2600,21 +2578,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2624,10 +2602,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668365</v>
+        <v>668213</v>
       </c>
       <c r="R20" t="n">
-        <v>6696575</v>
+        <v>6696494</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2686,10 +2664,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120208800</v>
+        <v>120208818</v>
       </c>
       <c r="B21" t="n">
-        <v>57679</v>
+        <v>105032</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2702,43 +2680,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668525</v>
+        <v>668437</v>
       </c>
       <c r="R21" t="n">
-        <v>6696405</v>
+        <v>6696501</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,10 +2766,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120208725</v>
+        <v>120208827</v>
       </c>
       <c r="B22" t="n">
-        <v>90562</v>
+        <v>4772</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2809,25 +2778,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2837,10 +2806,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668551</v>
+        <v>668457</v>
       </c>
       <c r="R22" t="n">
-        <v>6696304</v>
+        <v>6696523</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2899,10 +2868,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120208783</v>
+        <v>120208822</v>
       </c>
       <c r="B23" t="n">
-        <v>90334</v>
+        <v>57339</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2915,34 +2884,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3215</v>
+        <v>102977</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668281</v>
+        <v>668585</v>
       </c>
       <c r="R23" t="n">
-        <v>6696528</v>
+        <v>6696613</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2975,6 +2952,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3001,10 +2983,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120208690</v>
+        <v>120208800</v>
       </c>
       <c r="B24" t="n">
-        <v>101074</v>
+        <v>57689</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3017,34 +2999,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221235</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668564</v>
+        <v>668525</v>
       </c>
       <c r="R24" t="n">
-        <v>6696811</v>
+        <v>6696405</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3103,10 +3094,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120208737</v>
+        <v>120208740</v>
       </c>
       <c r="B25" t="n">
-        <v>56522</v>
+        <v>57473</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3115,43 +3106,46 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668566</v>
+        <v>668357</v>
       </c>
       <c r="R25" t="n">
-        <v>6696455</v>
+        <v>6696585</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3184,11 +3178,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3215,10 +3204,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120208739</v>
+        <v>120208860</v>
       </c>
       <c r="B26" t="n">
-        <v>103418</v>
+        <v>100194</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3231,21 +3220,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3255,10 +3244,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668166</v>
+        <v>668566</v>
       </c>
       <c r="R26" t="n">
-        <v>6696498</v>
+        <v>6696858</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3317,10 +3306,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120208775</v>
+        <v>120208862</v>
       </c>
       <c r="B27" t="n">
-        <v>97885</v>
+        <v>100194</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3333,21 +3322,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3357,10 +3346,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668180</v>
+        <v>668572</v>
       </c>
       <c r="R27" t="n">
-        <v>6696501</v>
+        <v>6696573</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3419,10 +3408,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120208758</v>
+        <v>120208830</v>
       </c>
       <c r="B28" t="n">
-        <v>57326</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3435,39 +3424,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668240</v>
+        <v>668442</v>
       </c>
       <c r="R28" t="n">
-        <v>6696522</v>
+        <v>6696514</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3502,11 +3486,6 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3515,6 +3494,21 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3531,10 +3525,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120208850</v>
+        <v>120208707</v>
       </c>
       <c r="B29" t="n">
-        <v>100171</v>
+        <v>95478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3543,25 +3537,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3571,10 +3565,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668179</v>
+        <v>668394</v>
       </c>
       <c r="R29" t="n">
-        <v>6696528</v>
+        <v>6696553</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3633,10 +3627,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120208799</v>
+        <v>120208718</v>
       </c>
       <c r="B30" t="n">
-        <v>57679</v>
+        <v>95478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3645,43 +3639,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668558</v>
+        <v>668450</v>
       </c>
       <c r="R30" t="n">
-        <v>6696534</v>
+        <v>6696589</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3740,10 +3729,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120208718</v>
+        <v>120208852</v>
       </c>
       <c r="B31" t="n">
-        <v>95455</v>
+        <v>100194</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3752,25 +3741,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3780,10 +3769,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668450</v>
+        <v>668230</v>
       </c>
       <c r="R31" t="n">
-        <v>6696589</v>
+        <v>6696502</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3842,10 +3831,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120208724</v>
+        <v>120208828</v>
       </c>
       <c r="B32" t="n">
-        <v>90562</v>
+        <v>4772</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3854,25 +3843,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3882,10 +3871,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668608</v>
+        <v>668595</v>
       </c>
       <c r="R32" t="n">
-        <v>6696611</v>
+        <v>6696467</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3944,10 +3933,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120208856</v>
+        <v>120208711</v>
       </c>
       <c r="B33" t="n">
-        <v>100171</v>
+        <v>95478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3956,25 +3945,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3984,10 +3973,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668382</v>
+        <v>668345</v>
       </c>
       <c r="R33" t="n">
-        <v>6696524</v>
+        <v>6696598</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4046,10 +4035,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120208720</v>
+        <v>120208717</v>
       </c>
       <c r="B34" t="n">
-        <v>90527</v>
+        <v>95478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4058,25 +4047,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4086,10 +4075,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668407</v>
+        <v>668468</v>
       </c>
       <c r="R34" t="n">
-        <v>6696520</v>
+        <v>6696587</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4132,21 +4121,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4163,10 +4137,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120208741</v>
+        <v>120208719</v>
       </c>
       <c r="B35" t="n">
-        <v>57463</v>
+        <v>95478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4179,42 +4153,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668483</v>
+        <v>668514</v>
       </c>
       <c r="R35" t="n">
-        <v>6696590</v>
+        <v>6696439</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4273,10 +4239,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120208816</v>
+        <v>120208704</v>
       </c>
       <c r="B36" t="n">
-        <v>56514</v>
+        <v>95478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4289,21 +4255,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4313,10 +4279,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668248</v>
+        <v>668571</v>
       </c>
       <c r="R36" t="n">
-        <v>6696628</v>
+        <v>6696816</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4351,11 +4317,6 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>flög upp från marken</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4364,6 +4325,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4380,10 +4356,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120208862</v>
+        <v>120208811</v>
       </c>
       <c r="B37" t="n">
-        <v>100171</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4392,38 +4368,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668572</v>
+        <v>668524</v>
       </c>
       <c r="R37" t="n">
-        <v>6696573</v>
+        <v>6696416</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4482,10 +4467,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120208853</v>
+        <v>120208779</v>
       </c>
       <c r="B38" t="n">
-        <v>100171</v>
+        <v>97908</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4498,21 +4483,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4522,10 +4507,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668241</v>
+        <v>668212</v>
       </c>
       <c r="R38" t="n">
-        <v>6696541</v>
+        <v>6696497</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4584,10 +4569,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120208740</v>
+        <v>120208690</v>
       </c>
       <c r="B39" t="n">
-        <v>57463</v>
+        <v>101097</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4596,46 +4581,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>221235</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668357</v>
+        <v>668564</v>
       </c>
       <c r="R39" t="n">
-        <v>6696585</v>
+        <v>6696811</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4694,10 +4671,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120208688</v>
+        <v>120208857</v>
       </c>
       <c r="B40" t="n">
-        <v>101074</v>
+        <v>100194</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4710,21 +4687,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4734,10 +4711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668383</v>
+        <v>668438</v>
       </c>
       <c r="R40" t="n">
-        <v>6696524</v>
+        <v>6696512</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4796,10 +4773,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120208703</v>
+        <v>120208853</v>
       </c>
       <c r="B41" t="n">
-        <v>95455</v>
+        <v>100194</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4808,25 +4785,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4836,10 +4813,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668451</v>
+        <v>668241</v>
       </c>
       <c r="R41" t="n">
-        <v>6696602</v>
+        <v>6696541</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4882,21 +4859,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -4913,10 +4875,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120208822</v>
+        <v>120208782</v>
       </c>
       <c r="B42" t="n">
-        <v>57329</v>
+        <v>97908</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4929,42 +4891,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102977</v>
+        <v>219798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668585</v>
+        <v>668279</v>
       </c>
       <c r="R42" t="n">
-        <v>6696613</v>
+        <v>6696528</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4997,11 +4951,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5028,10 +4977,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120208851</v>
+        <v>120208778</v>
       </c>
       <c r="B43" t="n">
-        <v>100171</v>
+        <v>97908</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5044,21 +4993,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5068,10 +5017,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668213</v>
+        <v>668191</v>
       </c>
       <c r="R43" t="n">
-        <v>6696494</v>
+        <v>6696527</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5130,10 +5079,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120208855</v>
+        <v>120208858</v>
       </c>
       <c r="B44" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5170,10 +5119,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668380</v>
+        <v>668564</v>
       </c>
       <c r="R44" t="n">
-        <v>6696528</v>
+        <v>6696816</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5232,10 +5181,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120208828</v>
+        <v>120208854</v>
       </c>
       <c r="B45" t="n">
-        <v>4772</v>
+        <v>100194</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5248,21 +5197,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5272,10 +5221,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668595</v>
+        <v>668370</v>
       </c>
       <c r="R45" t="n">
-        <v>6696467</v>
+        <v>6696506</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5334,10 +5283,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120208814</v>
+        <v>120208682</v>
       </c>
       <c r="B46" t="n">
-        <v>74577</v>
+        <v>101097</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5350,21 +5299,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>221235</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5374,10 +5323,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668296</v>
+        <v>668186</v>
       </c>
       <c r="R46" t="n">
-        <v>6696535</v>
+        <v>6696508</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5436,10 +5385,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120208830</v>
+        <v>120208863</v>
       </c>
       <c r="B47" t="n">
-        <v>78526</v>
+        <v>100194</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5448,25 +5397,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5476,10 +5425,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>668442</v>
+        <v>668568</v>
       </c>
       <c r="R47" t="n">
-        <v>6696514</v>
+        <v>6696542</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5522,21 +5471,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5553,10 +5487,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120208722</v>
+        <v>120208684</v>
       </c>
       <c r="B48" t="n">
-        <v>90562</v>
+        <v>101097</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5565,25 +5499,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>221235</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5593,10 +5527,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668552</v>
+        <v>668201</v>
       </c>
       <c r="R48" t="n">
-        <v>6696684</v>
+        <v>6696519</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5655,10 +5589,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120208686</v>
+        <v>120208722</v>
       </c>
       <c r="B49" t="n">
-        <v>101074</v>
+        <v>90580</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5667,25 +5601,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221235</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5695,10 +5629,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668242</v>
+        <v>668552</v>
       </c>
       <c r="R49" t="n">
-        <v>6696541</v>
+        <v>6696684</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5757,10 +5691,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120208707</v>
+        <v>120208741</v>
       </c>
       <c r="B50" t="n">
-        <v>95455</v>
+        <v>57473</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5773,34 +5707,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668394</v>
+        <v>668483</v>
       </c>
       <c r="R50" t="n">
-        <v>6696553</v>
+        <v>6696590</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5859,10 +5801,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120208860</v>
+        <v>120208712</v>
       </c>
       <c r="B51" t="n">
-        <v>100171</v>
+        <v>95478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5871,25 +5813,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5899,10 +5841,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668566</v>
+        <v>668301</v>
       </c>
       <c r="R51" t="n">
-        <v>6696858</v>
+        <v>6696522</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5961,10 +5903,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120208692</v>
+        <v>120208713</v>
       </c>
       <c r="B52" t="n">
-        <v>101074</v>
+        <v>95478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5973,25 +5915,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6001,10 +5943,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668538</v>
+        <v>668379</v>
       </c>
       <c r="R52" t="n">
-        <v>6696322</v>
+        <v>6696528</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6063,10 +6005,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120208719</v>
+        <v>120208735</v>
       </c>
       <c r="B53" t="n">
-        <v>95455</v>
+        <v>56532</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6075,38 +6017,47 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668514</v>
+        <v>668518</v>
       </c>
       <c r="R53" t="n">
-        <v>6696439</v>
+        <v>6696678</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6139,6 +6090,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6165,10 +6121,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120208798</v>
+        <v>120208816</v>
       </c>
       <c r="B54" t="n">
-        <v>57679</v>
+        <v>56524</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6177,20 +6133,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6199,21 +6155,16 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668342</v>
+        <v>668248</v>
       </c>
       <c r="R54" t="n">
-        <v>6696603</v>
+        <v>6696628</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6246,6 +6197,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>flög upp från marken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6272,10 +6228,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120208864</v>
+        <v>120208691</v>
       </c>
       <c r="B55" t="n">
-        <v>100171</v>
+        <v>101097</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6288,21 +6244,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6312,10 +6268,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668527</v>
+        <v>668509</v>
       </c>
       <c r="R55" t="n">
-        <v>6696351</v>
+        <v>6696436</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6374,10 +6330,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120208857</v>
+        <v>120208781</v>
       </c>
       <c r="B56" t="n">
-        <v>100171</v>
+        <v>97908</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6390,21 +6346,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6414,10 +6370,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668438</v>
+        <v>668261</v>
       </c>
       <c r="R56" t="n">
-        <v>6696512</v>
+        <v>6696558</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6476,10 +6432,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120208791</v>
+        <v>120208823</v>
       </c>
       <c r="B57" t="n">
-        <v>57316</v>
+        <v>57339</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6488,25 +6444,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100048</v>
+        <v>102977</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6524,10 +6480,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668520</v>
+        <v>668565</v>
       </c>
       <c r="R57" t="n">
-        <v>6696377</v>
+        <v>6696520</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6591,10 +6547,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120208757</v>
+        <v>120208759</v>
       </c>
       <c r="B58" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6639,7 +6595,7 @@
         <v>668572</v>
       </c>
       <c r="R58" t="n">
-        <v>6696525</v>
+        <v>6696839</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6703,10 +6659,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120208714</v>
+        <v>120208686</v>
       </c>
       <c r="B59" t="n">
-        <v>95455</v>
+        <v>101097</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6715,25 +6671,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6743,10 +6699,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668369</v>
+        <v>668242</v>
       </c>
       <c r="R59" t="n">
-        <v>6696540</v>
+        <v>6696541</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6805,10 +6761,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120208778</v>
+        <v>120208848</v>
       </c>
       <c r="B60" t="n">
-        <v>97885</v>
+        <v>100194</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6821,21 +6777,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6845,10 +6801,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>668191</v>
+        <v>668419</v>
       </c>
       <c r="R60" t="n">
-        <v>6696527</v>
+        <v>6696535</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6907,10 +6863,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120208717</v>
+        <v>120208784</v>
       </c>
       <c r="B61" t="n">
-        <v>95455</v>
+        <v>91023</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6919,25 +6875,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6947,10 +6903,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>668468</v>
+        <v>668273</v>
       </c>
       <c r="R61" t="n">
-        <v>6696587</v>
+        <v>6696531</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7009,10 +6965,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120208683</v>
+        <v>120208783</v>
       </c>
       <c r="B62" t="n">
-        <v>101074</v>
+        <v>90351</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7025,21 +6981,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221235</v>
+        <v>3215</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7049,10 +7005,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668188</v>
+        <v>668281</v>
       </c>
       <c r="R62" t="n">
-        <v>6696531</v>
+        <v>6696528</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7111,10 +7067,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120208819</v>
+        <v>120208708</v>
       </c>
       <c r="B63" t="n">
-        <v>105009</v>
+        <v>95478</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7123,25 +7079,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7151,10 +7107,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668579</v>
+        <v>668376</v>
       </c>
       <c r="R63" t="n">
-        <v>6696655</v>
+        <v>6696595</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7213,10 +7169,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120208811</v>
+        <v>120208736</v>
       </c>
       <c r="B64" t="n">
-        <v>97907</v>
+        <v>56532</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7225,35 +7181,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7262,10 +7214,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668524</v>
+        <v>668532</v>
       </c>
       <c r="R64" t="n">
-        <v>6696416</v>
+        <v>6696689</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7298,6 +7250,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7324,10 +7281,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120208708</v>
+        <v>120208725</v>
       </c>
       <c r="B65" t="n">
-        <v>95455</v>
+        <v>90580</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7340,21 +7297,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7364,10 +7321,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668376</v>
+        <v>668551</v>
       </c>
       <c r="R65" t="n">
-        <v>6696595</v>
+        <v>6696304</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7426,10 +7383,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120208691</v>
+        <v>120208720</v>
       </c>
       <c r="B66" t="n">
-        <v>101074</v>
+        <v>90545</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7442,21 +7399,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221235</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7466,10 +7423,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668509</v>
+        <v>668407</v>
       </c>
       <c r="R66" t="n">
-        <v>6696436</v>
+        <v>6696520</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7512,6 +7469,21 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -7528,10 +7500,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120208823</v>
+        <v>120208757</v>
       </c>
       <c r="B67" t="n">
-        <v>57329</v>
+        <v>57336</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7540,46 +7512,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>668565</v>
+        <v>668572</v>
       </c>
       <c r="R67" t="n">
-        <v>6696520</v>
+        <v>6696525</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7616,7 +7585,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Inom avverkningsanmälan</t>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7643,10 +7612,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120208792</v>
+        <v>120208799</v>
       </c>
       <c r="B68" t="n">
-        <v>57316</v>
+        <v>57689</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7655,20 +7624,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7677,24 +7646,21 @@
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>668517</v>
+        <v>668558</v>
       </c>
       <c r="R68" t="n">
-        <v>6696457</v>
+        <v>6696534</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7727,11 +7693,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7758,10 +7719,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120208781</v>
+        <v>120208849</v>
       </c>
       <c r="B69" t="n">
-        <v>97885</v>
+        <v>100194</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7774,21 +7735,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7798,10 +7759,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>668261</v>
+        <v>668362</v>
       </c>
       <c r="R69" t="n">
-        <v>6696558</v>
+        <v>6696583</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7860,10 +7821,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120208743</v>
+        <v>120208861</v>
       </c>
       <c r="B70" t="n">
-        <v>57463</v>
+        <v>100194</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7872,46 +7833,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>668533</v>
+        <v>668567</v>
       </c>
       <c r="R70" t="n">
-        <v>6696366</v>
+        <v>6696809</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7970,10 +7923,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120208744</v>
+        <v>120208688</v>
       </c>
       <c r="B71" t="n">
-        <v>57463</v>
+        <v>101097</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7982,43 +7935,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>221235</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>668602</v>
+        <v>668383</v>
       </c>
       <c r="R71" t="n">
-        <v>6696625</v>
+        <v>6696524</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8077,10 +8025,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120208849</v>
+        <v>120208683</v>
       </c>
       <c r="B72" t="n">
-        <v>100171</v>
+        <v>101097</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8093,21 +8041,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8117,10 +8065,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>668362</v>
+        <v>668188</v>
       </c>
       <c r="R72" t="n">
-        <v>6696583</v>
+        <v>6696531</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8179,10 +8127,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120208859</v>
+        <v>120208812</v>
       </c>
       <c r="B73" t="n">
-        <v>100171</v>
+        <v>97930</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8191,38 +8139,47 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>668581</v>
+        <v>668568</v>
       </c>
       <c r="R73" t="n">
-        <v>6696848</v>
+        <v>6696851</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8281,10 +8238,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120208848</v>
+        <v>120208710</v>
       </c>
       <c r="B74" t="n">
-        <v>100171</v>
+        <v>95478</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8293,25 +8250,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8321,10 +8278,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>668419</v>
+        <v>668362</v>
       </c>
       <c r="R74" t="n">
-        <v>6696535</v>
+        <v>6696582</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8383,10 +8340,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120208818</v>
+        <v>120208714</v>
       </c>
       <c r="B75" t="n">
-        <v>105009</v>
+        <v>95478</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8395,25 +8352,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8423,10 +8380,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>668437</v>
+        <v>668369</v>
       </c>
       <c r="R75" t="n">
-        <v>6696501</v>
+        <v>6696540</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8485,10 +8442,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120208721</v>
+        <v>120208703</v>
       </c>
       <c r="B76" t="n">
-        <v>90562</v>
+        <v>95478</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8501,21 +8458,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8525,10 +8482,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>668589</v>
+        <v>668451</v>
       </c>
       <c r="R76" t="n">
-        <v>6696866</v>
+        <v>6696602</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8571,6 +8528,21 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8587,10 +8559,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120208784</v>
+        <v>120208737</v>
       </c>
       <c r="B77" t="n">
-        <v>91005</v>
+        <v>56532</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8599,38 +8571,43 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>668273</v>
+        <v>668566</v>
       </c>
       <c r="R77" t="n">
-        <v>6696531</v>
+        <v>6696455</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8663,6 +8640,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8689,10 +8671,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120208706</v>
+        <v>120208790</v>
       </c>
       <c r="B78" t="n">
-        <v>95455</v>
+        <v>57326</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8705,34 +8687,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>100048</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>668408</v>
+        <v>668550</v>
       </c>
       <c r="R78" t="n">
-        <v>6696562</v>
+        <v>6696605</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8765,6 +8755,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8791,10 +8786,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120208779</v>
+        <v>120208692</v>
       </c>
       <c r="B79" t="n">
-        <v>97885</v>
+        <v>101097</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8807,21 +8802,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8831,10 +8826,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>668212</v>
+        <v>668538</v>
       </c>
       <c r="R79" t="n">
-        <v>6696497</v>
+        <v>6696322</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8893,10 +8888,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120208852</v>
+        <v>120208855</v>
       </c>
       <c r="B80" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8933,10 +8928,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>668230</v>
+        <v>668380</v>
       </c>
       <c r="R80" t="n">
-        <v>6696502</v>
+        <v>6696528</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8995,10 +8990,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120208863</v>
+        <v>120208785</v>
       </c>
       <c r="B81" t="n">
-        <v>100171</v>
+        <v>90864</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9007,25 +9002,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>658</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9035,10 +9030,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>668568</v>
+        <v>668552</v>
       </c>
       <c r="R81" t="n">
-        <v>6696542</v>
+        <v>6696684</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9097,10 +9092,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120208712</v>
+        <v>120208815</v>
       </c>
       <c r="B82" t="n">
-        <v>95455</v>
+        <v>74593</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9109,25 +9104,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9137,10 +9132,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>668301</v>
+        <v>668311</v>
       </c>
       <c r="R82" t="n">
-        <v>6696522</v>
+        <v>6696520</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9199,10 +9194,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120208710</v>
+        <v>120208814</v>
       </c>
       <c r="B83" t="n">
-        <v>95455</v>
+        <v>74593</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9211,25 +9206,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9239,10 +9234,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>668362</v>
+        <v>668296</v>
       </c>
       <c r="R83" t="n">
-        <v>6696582</v>
+        <v>6696535</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9301,10 +9296,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120208687</v>
+        <v>120208775</v>
       </c>
       <c r="B84" t="n">
-        <v>101074</v>
+        <v>97908</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9317,21 +9312,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9341,10 +9336,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>668382</v>
+        <v>668180</v>
       </c>
       <c r="R84" t="n">
-        <v>6696529</v>
+        <v>6696501</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9403,10 +9398,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120208711</v>
+        <v>120208864</v>
       </c>
       <c r="B85" t="n">
-        <v>95455</v>
+        <v>100194</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9415,25 +9410,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9443,10 +9438,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>668345</v>
+        <v>668527</v>
       </c>
       <c r="R85" t="n">
-        <v>6696598</v>
+        <v>6696351</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9505,10 +9500,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120208790</v>
+        <v>120208716</v>
       </c>
       <c r="B86" t="n">
-        <v>57316</v>
+        <v>95478</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9521,42 +9516,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100048</v>
+        <v>53</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>668550</v>
+        <v>668439</v>
       </c>
       <c r="R86" t="n">
-        <v>6696605</v>
+        <v>6696517</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9589,11 +9576,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9620,10 +9602,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120208736</v>
+        <v>120208776</v>
       </c>
       <c r="B87" t="n">
-        <v>56522</v>
+        <v>97908</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9636,39 +9618,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100138</v>
+        <v>219798</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>668532</v>
+        <v>668186</v>
       </c>
       <c r="R87" t="n">
-        <v>6696689</v>
+        <v>6696508</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9701,11 +9678,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9732,10 +9704,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120208776</v>
+        <v>120208813</v>
       </c>
       <c r="B88" t="n">
-        <v>97885</v>
+        <v>97930</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9744,38 +9716,47 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>668186</v>
+        <v>668575</v>
       </c>
       <c r="R88" t="n">
-        <v>6696508</v>
+        <v>6696701</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9834,10 +9815,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120208813</v>
+        <v>120208798</v>
       </c>
       <c r="B89" t="n">
-        <v>97907</v>
+        <v>57689</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9846,35 +9827,31 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -9883,10 +9860,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>668575</v>
+        <v>668342</v>
       </c>
       <c r="R89" t="n">
-        <v>6696701</v>
+        <v>6696603</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9945,10 +9922,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120208858</v>
+        <v>120208756</v>
       </c>
       <c r="B90" t="n">
-        <v>100171</v>
+        <v>57336</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9957,38 +9934,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>668564</v>
+        <v>668467</v>
       </c>
       <c r="R90" t="n">
-        <v>6696816</v>
+        <v>6696630</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10021,6 +10003,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10047,10 +10034,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120208861</v>
+        <v>120208792</v>
       </c>
       <c r="B91" t="n">
-        <v>100171</v>
+        <v>57326</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10059,38 +10046,46 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222498</v>
+        <v>100048</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>668567</v>
+        <v>668517</v>
       </c>
       <c r="R91" t="n">
-        <v>6696809</v>
+        <v>6696457</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10123,6 +10118,11 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -2154,10 +2154,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120208721</v>
+        <v>120208687</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>101097</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2166,25 +2166,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>221235</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668589</v>
+        <v>668382</v>
       </c>
       <c r="R16" t="n">
-        <v>6696866</v>
+        <v>6696529</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120208687</v>
+        <v>120208859</v>
       </c>
       <c r="B17" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2272,21 +2272,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668382</v>
+        <v>668581</v>
       </c>
       <c r="R17" t="n">
-        <v>6696529</v>
+        <v>6696848</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120208859</v>
+        <v>120208856</v>
       </c>
       <c r="B18" t="n">
         <v>100194</v>
@@ -2398,10 +2398,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668581</v>
+        <v>668382</v>
       </c>
       <c r="R18" t="n">
-        <v>6696848</v>
+        <v>6696524</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120208856</v>
+        <v>120208851</v>
       </c>
       <c r="B19" t="n">
         <v>100194</v>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668382</v>
+        <v>668213</v>
       </c>
       <c r="R19" t="n">
-        <v>6696524</v>
+        <v>6696494</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120208851</v>
+        <v>120208818</v>
       </c>
       <c r="B20" t="n">
-        <v>100194</v>
+        <v>105032</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2578,21 +2578,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2602,10 +2602,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668213</v>
+        <v>668437</v>
       </c>
       <c r="R20" t="n">
-        <v>6696494</v>
+        <v>6696501</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,10 +2664,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120208818</v>
+        <v>120208822</v>
       </c>
       <c r="B21" t="n">
-        <v>105032</v>
+        <v>57339</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2680,34 +2680,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>102977</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668437</v>
+        <v>668585</v>
       </c>
       <c r="R21" t="n">
-        <v>6696501</v>
+        <v>6696613</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,6 +2748,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2766,10 +2779,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120208827</v>
+        <v>120208800</v>
       </c>
       <c r="B22" t="n">
-        <v>4772</v>
+        <v>57689</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2782,34 +2795,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102306</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668457</v>
+        <v>668525</v>
       </c>
       <c r="R22" t="n">
-        <v>6696523</v>
+        <v>6696405</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2868,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120208822</v>
+        <v>120208721</v>
       </c>
       <c r="B23" t="n">
-        <v>57339</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2880,46 +2902,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102977</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668585</v>
+        <v>668589</v>
       </c>
       <c r="R23" t="n">
-        <v>6696613</v>
+        <v>6696866</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2952,11 +2966,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2983,10 +2992,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120208800</v>
+        <v>120208827</v>
       </c>
       <c r="B24" t="n">
-        <v>57689</v>
+        <v>4772</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2999,43 +3008,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>102306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668525</v>
+        <v>668457</v>
       </c>
       <c r="R24" t="n">
-        <v>6696405</v>
+        <v>6696523</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3306,10 +3306,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120208862</v>
+        <v>120208830</v>
       </c>
       <c r="B27" t="n">
-        <v>100194</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3318,25 +3318,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668572</v>
+        <v>668442</v>
       </c>
       <c r="R27" t="n">
-        <v>6696573</v>
+        <v>6696514</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3392,6 +3392,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3408,10 +3423,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120208830</v>
+        <v>120208862</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>100194</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3420,25 +3435,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3448,10 +3463,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668442</v>
+        <v>668572</v>
       </c>
       <c r="R28" t="n">
-        <v>6696514</v>
+        <v>6696573</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3494,21 +3509,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3933,10 +3933,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120208711</v>
+        <v>120208690</v>
       </c>
       <c r="B33" t="n">
-        <v>95478</v>
+        <v>101097</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3945,25 +3945,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3973,10 +3973,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668345</v>
+        <v>668564</v>
       </c>
       <c r="R33" t="n">
-        <v>6696598</v>
+        <v>6696811</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4035,10 +4035,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120208717</v>
+        <v>120208857</v>
       </c>
       <c r="B34" t="n">
-        <v>95478</v>
+        <v>100194</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4047,25 +4047,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4075,10 +4075,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668468</v>
+        <v>668438</v>
       </c>
       <c r="R34" t="n">
-        <v>6696587</v>
+        <v>6696512</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4137,7 +4137,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120208719</v>
+        <v>120208711</v>
       </c>
       <c r="B35" t="n">
         <v>95478</v>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668514</v>
+        <v>668345</v>
       </c>
       <c r="R35" t="n">
-        <v>6696439</v>
+        <v>6696598</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4239,7 +4239,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120208704</v>
+        <v>120208717</v>
       </c>
       <c r="B36" t="n">
         <v>95478</v>
@@ -4279,10 +4279,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668571</v>
+        <v>668468</v>
       </c>
       <c r="R36" t="n">
-        <v>6696816</v>
+        <v>6696587</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4325,21 +4325,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4356,10 +4341,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120208811</v>
+        <v>120208719</v>
       </c>
       <c r="B37" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4368,47 +4353,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668524</v>
+        <v>668514</v>
       </c>
       <c r="R37" t="n">
-        <v>6696416</v>
+        <v>6696439</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4467,10 +4443,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120208779</v>
+        <v>120208704</v>
       </c>
       <c r="B38" t="n">
-        <v>97908</v>
+        <v>95478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4479,25 +4455,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4507,10 +4483,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668212</v>
+        <v>668571</v>
       </c>
       <c r="R38" t="n">
-        <v>6696497</v>
+        <v>6696816</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4553,6 +4529,21 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4569,10 +4560,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120208690</v>
+        <v>120208811</v>
       </c>
       <c r="B39" t="n">
-        <v>101097</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4581,38 +4572,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668564</v>
+        <v>668524</v>
       </c>
       <c r="R39" t="n">
-        <v>6696811</v>
+        <v>6696416</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4671,10 +4671,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120208857</v>
+        <v>120208779</v>
       </c>
       <c r="B40" t="n">
-        <v>100194</v>
+        <v>97908</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4687,21 +4687,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4711,10 +4711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668438</v>
+        <v>668212</v>
       </c>
       <c r="R40" t="n">
-        <v>6696512</v>
+        <v>6696497</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -7281,10 +7281,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120208725</v>
+        <v>120208710</v>
       </c>
       <c r="B65" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7297,21 +7297,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7321,10 +7321,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668551</v>
+        <v>668362</v>
       </c>
       <c r="R65" t="n">
-        <v>6696304</v>
+        <v>6696582</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7383,10 +7383,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120208720</v>
+        <v>120208714</v>
       </c>
       <c r="B66" t="n">
-        <v>90545</v>
+        <v>95478</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7395,25 +7395,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7423,10 +7423,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668407</v>
+        <v>668369</v>
       </c>
       <c r="R66" t="n">
-        <v>6696520</v>
+        <v>6696540</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7469,21 +7469,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -7500,10 +7485,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120208757</v>
+        <v>120208725</v>
       </c>
       <c r="B67" t="n">
-        <v>57336</v>
+        <v>90580</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7516,39 +7501,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>668572</v>
+        <v>668551</v>
       </c>
       <c r="R67" t="n">
-        <v>6696525</v>
+        <v>6696304</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7581,11 +7561,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7612,10 +7587,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120208799</v>
+        <v>120208720</v>
       </c>
       <c r="B68" t="n">
-        <v>57689</v>
+        <v>90545</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7628,39 +7603,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>668558</v>
+        <v>668407</v>
       </c>
       <c r="R68" t="n">
-        <v>6696534</v>
+        <v>6696520</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7703,6 +7673,21 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -7719,10 +7704,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120208849</v>
+        <v>120208757</v>
       </c>
       <c r="B69" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7731,38 +7716,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>668362</v>
+        <v>668572</v>
       </c>
       <c r="R69" t="n">
-        <v>6696583</v>
+        <v>6696525</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7795,6 +7785,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7821,10 +7816,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120208861</v>
+        <v>120208799</v>
       </c>
       <c r="B70" t="n">
-        <v>100194</v>
+        <v>57689</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7837,34 +7832,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>668567</v>
+        <v>668558</v>
       </c>
       <c r="R70" t="n">
-        <v>6696809</v>
+        <v>6696534</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7923,10 +7923,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120208688</v>
+        <v>120208849</v>
       </c>
       <c r="B71" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7939,21 +7939,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7963,10 +7963,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>668383</v>
+        <v>668362</v>
       </c>
       <c r="R71" t="n">
-        <v>6696524</v>
+        <v>6696583</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8025,10 +8025,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120208683</v>
+        <v>120208861</v>
       </c>
       <c r="B72" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8041,21 +8041,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8065,10 +8065,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>668188</v>
+        <v>668567</v>
       </c>
       <c r="R72" t="n">
-        <v>6696531</v>
+        <v>6696809</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8127,10 +8127,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120208812</v>
+        <v>120208688</v>
       </c>
       <c r="B73" t="n">
-        <v>97930</v>
+        <v>101097</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8139,47 +8139,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>221235</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>668568</v>
+        <v>668383</v>
       </c>
       <c r="R73" t="n">
-        <v>6696851</v>
+        <v>6696524</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8238,10 +8229,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120208710</v>
+        <v>120208683</v>
       </c>
       <c r="B74" t="n">
-        <v>95478</v>
+        <v>101097</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8250,25 +8241,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8278,10 +8269,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>668362</v>
+        <v>668188</v>
       </c>
       <c r="R74" t="n">
-        <v>6696582</v>
+        <v>6696531</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8340,10 +8331,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120208714</v>
+        <v>120208812</v>
       </c>
       <c r="B75" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8352,38 +8343,47 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>668369</v>
+        <v>668568</v>
       </c>
       <c r="R75" t="n">
-        <v>6696540</v>
+        <v>6696851</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8442,10 +8442,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120208703</v>
+        <v>120208692</v>
       </c>
       <c r="B76" t="n">
-        <v>95478</v>
+        <v>101097</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8454,25 +8454,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8482,10 +8482,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>668451</v>
+        <v>668538</v>
       </c>
       <c r="R76" t="n">
-        <v>6696602</v>
+        <v>6696322</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8528,21 +8528,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -8559,10 +8544,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120208737</v>
+        <v>120208855</v>
       </c>
       <c r="B77" t="n">
-        <v>56532</v>
+        <v>100194</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8575,39 +8560,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>668566</v>
+        <v>668380</v>
       </c>
       <c r="R77" t="n">
-        <v>6696455</v>
+        <v>6696528</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8640,11 +8620,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8671,10 +8646,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120208790</v>
+        <v>120208703</v>
       </c>
       <c r="B78" t="n">
-        <v>57326</v>
+        <v>95478</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8687,42 +8662,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100048</v>
+        <v>53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>668550</v>
+        <v>668451</v>
       </c>
       <c r="R78" t="n">
-        <v>6696605</v>
+        <v>6696602</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8757,11 +8724,6 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8770,6 +8732,21 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -8786,10 +8763,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120208692</v>
+        <v>120208737</v>
       </c>
       <c r="B79" t="n">
-        <v>101097</v>
+        <v>56532</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8802,34 +8779,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221235</v>
+        <v>100138</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>668538</v>
+        <v>668566</v>
       </c>
       <c r="R79" t="n">
-        <v>6696322</v>
+        <v>6696455</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8862,6 +8844,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8888,10 +8875,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120208855</v>
+        <v>120208790</v>
       </c>
       <c r="B80" t="n">
-        <v>100194</v>
+        <v>57326</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8900,38 +8887,46 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>100048</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>668380</v>
+        <v>668550</v>
       </c>
       <c r="R80" t="n">
-        <v>6696528</v>
+        <v>6696605</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8964,6 +8959,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8990,10 +8990,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120208785</v>
+        <v>120208815</v>
       </c>
       <c r="B81" t="n">
-        <v>90864</v>
+        <v>74593</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9002,25 +9002,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9030,10 +9030,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>668552</v>
+        <v>668311</v>
       </c>
       <c r="R81" t="n">
-        <v>6696684</v>
+        <v>6696520</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9092,7 +9092,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120208815</v>
+        <v>120208814</v>
       </c>
       <c r="B82" t="n">
         <v>74593</v>
@@ -9132,10 +9132,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>668311</v>
+        <v>668296</v>
       </c>
       <c r="R82" t="n">
-        <v>6696520</v>
+        <v>6696535</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9194,10 +9194,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120208814</v>
+        <v>120208785</v>
       </c>
       <c r="B83" t="n">
-        <v>74593</v>
+        <v>90864</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9206,25 +9206,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9234,10 +9234,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>668296</v>
+        <v>668552</v>
       </c>
       <c r="R83" t="n">
-        <v>6696535</v>
+        <v>6696684</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9296,10 +9296,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120208775</v>
+        <v>120208716</v>
       </c>
       <c r="B84" t="n">
-        <v>97908</v>
+        <v>95478</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9308,25 +9308,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9336,10 +9336,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>668180</v>
+        <v>668439</v>
       </c>
       <c r="R84" t="n">
-        <v>6696501</v>
+        <v>6696517</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9398,10 +9398,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120208864</v>
+        <v>120208775</v>
       </c>
       <c r="B85" t="n">
-        <v>100194</v>
+        <v>97908</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9414,21 +9414,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9438,10 +9438,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>668527</v>
+        <v>668180</v>
       </c>
       <c r="R85" t="n">
-        <v>6696351</v>
+        <v>6696501</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9500,10 +9500,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120208716</v>
+        <v>120208864</v>
       </c>
       <c r="B86" t="n">
-        <v>95478</v>
+        <v>100194</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9512,25 +9512,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9540,10 +9540,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>668439</v>
+        <v>668527</v>
       </c>
       <c r="R86" t="n">
-        <v>6696517</v>
+        <v>6696351</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9815,10 +9815,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120208798</v>
+        <v>120208756</v>
       </c>
       <c r="B89" t="n">
-        <v>57689</v>
+        <v>57336</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9827,20 +9827,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -9851,7 +9851,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -9860,10 +9860,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>668342</v>
+        <v>668467</v>
       </c>
       <c r="R89" t="n">
-        <v>6696603</v>
+        <v>6696630</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9896,6 +9896,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9922,10 +9927,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120208756</v>
+        <v>120208792</v>
       </c>
       <c r="B90" t="n">
-        <v>57336</v>
+        <v>57326</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9938,16 +9943,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -9956,21 +9961,24 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>668467</v>
+        <v>668517</v>
       </c>
       <c r="R90" t="n">
-        <v>6696630</v>
+        <v>6696457</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10007,7 +10015,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>hackmärken i död ved</t>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10034,10 +10042,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120208792</v>
+        <v>120208798</v>
       </c>
       <c r="B91" t="n">
-        <v>57326</v>
+        <v>57689</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10046,20 +10054,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100048</v>
+        <v>103015</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -10068,24 +10076,21 @@
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>668517</v>
+        <v>668342</v>
       </c>
       <c r="R91" t="n">
-        <v>6696457</v>
+        <v>6696603</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10118,11 +10123,6 @@
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120208850</v>
+        <v>120208828</v>
       </c>
       <c r="B2" t="n">
-        <v>100194</v>
+        <v>4772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668179</v>
+        <v>668595</v>
       </c>
       <c r="R2" t="n">
-        <v>6696528</v>
+        <v>6696467</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120208743</v>
+        <v>120208744</v>
       </c>
       <c r="B3" t="n">
         <v>57473</v>
@@ -811,24 +811,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668533</v>
+        <v>668602</v>
       </c>
       <c r="R3" t="n">
-        <v>6696366</v>
+        <v>6696625</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120208744</v>
+        <v>120208705</v>
       </c>
       <c r="B4" t="n">
-        <v>57473</v>
+        <v>95478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668602</v>
+        <v>668521</v>
       </c>
       <c r="R4" t="n">
-        <v>6696625</v>
+        <v>6696330</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,6 +970,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -994,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120208705</v>
+        <v>120208718</v>
       </c>
       <c r="B5" t="n">
         <v>95478</v>
@@ -1034,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668521</v>
+        <v>668450</v>
       </c>
       <c r="R5" t="n">
-        <v>6696330</v>
+        <v>6696589</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,21 +1087,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1111,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120208706</v>
+        <v>120208722</v>
       </c>
       <c r="B6" t="n">
-        <v>95478</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1151,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668408</v>
+        <v>668552</v>
       </c>
       <c r="R6" t="n">
-        <v>6696562</v>
+        <v>6696684</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120208758</v>
+        <v>120208816</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
+        <v>56524</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,16 +1221,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1247,21 +1239,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668240</v>
+        <v>668248</v>
       </c>
       <c r="R7" t="n">
-        <v>6696522</v>
+        <v>6696628</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>hackmärken i död ved</t>
+          <t>flög upp från marken</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120208826</v>
+        <v>120208688</v>
       </c>
       <c r="B8" t="n">
-        <v>4772</v>
+        <v>101097</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>221235</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1365,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668442</v>
+        <v>668383</v>
       </c>
       <c r="R8" t="n">
-        <v>6696515</v>
+        <v>6696524</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120208819</v>
+        <v>120208690</v>
       </c>
       <c r="B9" t="n">
-        <v>105032</v>
+        <v>101097</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668579</v>
+        <v>668564</v>
       </c>
       <c r="R9" t="n">
-        <v>6696655</v>
+        <v>6696811</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120208777</v>
+        <v>120208710</v>
       </c>
       <c r="B10" t="n">
-        <v>97908</v>
+        <v>95478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,25 +1528,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1569,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668188</v>
+        <v>668362</v>
       </c>
       <c r="R10" t="n">
-        <v>6696531</v>
+        <v>6696582</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120208709</v>
+        <v>120208737</v>
       </c>
       <c r="B11" t="n">
-        <v>95478</v>
+        <v>56532</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1643,38 +1630,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668362</v>
+        <v>668566</v>
       </c>
       <c r="R11" t="n">
-        <v>6696599</v>
+        <v>6696455</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,6 +1699,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1733,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120208739</v>
+        <v>120208735</v>
       </c>
       <c r="B12" t="n">
-        <v>103441</v>
+        <v>56532</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1749,34 +1746,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222412</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668166</v>
+        <v>668518</v>
       </c>
       <c r="R12" t="n">
-        <v>6696498</v>
+        <v>6696678</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1809,6 +1815,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1835,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120208791</v>
+        <v>120208823</v>
       </c>
       <c r="B13" t="n">
-        <v>57326</v>
+        <v>57339</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1847,25 +1858,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100048</v>
+        <v>102977</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1883,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668520</v>
+        <v>668565</v>
       </c>
       <c r="R13" t="n">
-        <v>6696377</v>
+        <v>6696520</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1950,10 +1961,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120208724</v>
+        <v>120208798</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>57689</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1962,38 +1973,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668608</v>
+        <v>668342</v>
       </c>
       <c r="R14" t="n">
-        <v>6696611</v>
+        <v>6696603</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120208774</v>
+        <v>120208830</v>
       </c>
       <c r="B15" t="n">
-        <v>97908</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2064,25 +2080,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2092,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668365</v>
+        <v>668442</v>
       </c>
       <c r="R15" t="n">
-        <v>6696575</v>
+        <v>6696514</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,6 +2154,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2154,10 +2185,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120208687</v>
+        <v>120208775</v>
       </c>
       <c r="B16" t="n">
-        <v>101097</v>
+        <v>97908</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2170,21 +2201,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2194,10 +2225,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668382</v>
+        <v>668180</v>
       </c>
       <c r="R16" t="n">
-        <v>6696529</v>
+        <v>6696501</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,10 +2287,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120208859</v>
+        <v>120208756</v>
       </c>
       <c r="B17" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2268,38 +2299,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668581</v>
+        <v>668467</v>
       </c>
       <c r="R17" t="n">
-        <v>6696848</v>
+        <v>6696630</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,6 +2368,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2358,10 +2399,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120208856</v>
+        <v>120208774</v>
       </c>
       <c r="B18" t="n">
-        <v>100194</v>
+        <v>97908</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2374,21 +2415,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2398,10 +2439,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668382</v>
+        <v>668365</v>
       </c>
       <c r="R18" t="n">
-        <v>6696524</v>
+        <v>6696575</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2460,7 +2501,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120208851</v>
+        <v>120208849</v>
       </c>
       <c r="B19" t="n">
         <v>100194</v>
@@ -2500,10 +2541,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668213</v>
+        <v>668362</v>
       </c>
       <c r="R19" t="n">
-        <v>6696494</v>
+        <v>6696583</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2562,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120208818</v>
+        <v>120208851</v>
       </c>
       <c r="B20" t="n">
-        <v>105032</v>
+        <v>100194</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2578,21 +2619,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2602,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668437</v>
+        <v>668213</v>
       </c>
       <c r="R20" t="n">
-        <v>6696501</v>
+        <v>6696494</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2664,10 +2705,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120208822</v>
+        <v>120208861</v>
       </c>
       <c r="B21" t="n">
-        <v>57339</v>
+        <v>100194</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2680,42 +2721,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102977</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668585</v>
+        <v>668567</v>
       </c>
       <c r="R21" t="n">
-        <v>6696613</v>
+        <v>6696809</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2748,11 +2781,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2779,10 +2807,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120208800</v>
+        <v>120208704</v>
       </c>
       <c r="B22" t="n">
-        <v>57689</v>
+        <v>95478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2791,47 +2819,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668525</v>
+        <v>668571</v>
       </c>
       <c r="R22" t="n">
-        <v>6696405</v>
+        <v>6696816</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2874,6 +2893,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2890,10 +2924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120208721</v>
+        <v>120208858</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>100194</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2902,25 +2936,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2930,10 +2964,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668589</v>
+        <v>668564</v>
       </c>
       <c r="R23" t="n">
-        <v>6696866</v>
+        <v>6696816</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2992,10 +3026,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120208827</v>
+        <v>120208864</v>
       </c>
       <c r="B24" t="n">
-        <v>4772</v>
+        <v>100194</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3008,21 +3042,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3032,10 +3066,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668457</v>
+        <v>668527</v>
       </c>
       <c r="R24" t="n">
-        <v>6696523</v>
+        <v>6696351</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3094,10 +3128,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120208740</v>
+        <v>120208853</v>
       </c>
       <c r="B25" t="n">
-        <v>57473</v>
+        <v>100194</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3106,46 +3140,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668357</v>
+        <v>668241</v>
       </c>
       <c r="R25" t="n">
-        <v>6696585</v>
+        <v>6696541</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3204,10 +3230,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120208860</v>
+        <v>120208783</v>
       </c>
       <c r="B26" t="n">
-        <v>100194</v>
+        <v>90351</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3220,21 +3246,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3244,10 +3270,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668566</v>
+        <v>668281</v>
       </c>
       <c r="R26" t="n">
-        <v>6696858</v>
+        <v>6696528</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3306,10 +3332,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120208830</v>
+        <v>120208706</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>95478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3322,21 +3348,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3346,10 +3372,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668442</v>
+        <v>668408</v>
       </c>
       <c r="R27" t="n">
-        <v>6696514</v>
+        <v>6696562</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3392,21 +3418,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3423,10 +3434,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120208862</v>
+        <v>120208683</v>
       </c>
       <c r="B28" t="n">
-        <v>100194</v>
+        <v>101097</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3439,21 +3450,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3463,10 +3474,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668572</v>
+        <v>668188</v>
       </c>
       <c r="R28" t="n">
-        <v>6696573</v>
+        <v>6696531</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3525,10 +3536,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120208707</v>
+        <v>120208811</v>
       </c>
       <c r="B29" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3537,38 +3548,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668394</v>
+        <v>668524</v>
       </c>
       <c r="R29" t="n">
-        <v>6696553</v>
+        <v>6696416</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3627,10 +3647,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120208718</v>
+        <v>120208812</v>
       </c>
       <c r="B30" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3639,38 +3659,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668450</v>
+        <v>668568</v>
       </c>
       <c r="R30" t="n">
-        <v>6696589</v>
+        <v>6696851</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3729,10 +3758,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120208852</v>
+        <v>120208682</v>
       </c>
       <c r="B31" t="n">
-        <v>100194</v>
+        <v>101097</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3745,21 +3774,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3769,10 +3798,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668230</v>
+        <v>668186</v>
       </c>
       <c r="R31" t="n">
-        <v>6696502</v>
+        <v>6696508</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3831,10 +3860,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120208828</v>
+        <v>120208818</v>
       </c>
       <c r="B32" t="n">
-        <v>4772</v>
+        <v>105032</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3847,21 +3876,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102306</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3871,10 +3900,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668595</v>
+        <v>668437</v>
       </c>
       <c r="R32" t="n">
-        <v>6696467</v>
+        <v>6696501</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3933,10 +3962,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120208690</v>
+        <v>120208757</v>
       </c>
       <c r="B33" t="n">
-        <v>101097</v>
+        <v>57336</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3945,38 +3974,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668564</v>
+        <v>668572</v>
       </c>
       <c r="R33" t="n">
-        <v>6696811</v>
+        <v>6696525</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4009,6 +4043,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4035,10 +4074,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120208857</v>
+        <v>120208826</v>
       </c>
       <c r="B34" t="n">
-        <v>100194</v>
+        <v>4772</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4051,21 +4090,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4075,10 +4114,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668438</v>
+        <v>668442</v>
       </c>
       <c r="R34" t="n">
-        <v>6696512</v>
+        <v>6696515</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4137,10 +4176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120208711</v>
+        <v>120208736</v>
       </c>
       <c r="B35" t="n">
-        <v>95478</v>
+        <v>56532</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4149,38 +4188,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668345</v>
+        <v>668532</v>
       </c>
       <c r="R35" t="n">
-        <v>6696598</v>
+        <v>6696689</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4213,6 +4257,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4239,10 +4288,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120208717</v>
+        <v>120208819</v>
       </c>
       <c r="B36" t="n">
-        <v>95478</v>
+        <v>105032</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4251,25 +4300,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4279,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668468</v>
+        <v>668579</v>
       </c>
       <c r="R36" t="n">
-        <v>6696587</v>
+        <v>6696655</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4341,10 +4390,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120208719</v>
+        <v>120208759</v>
       </c>
       <c r="B37" t="n">
-        <v>95478</v>
+        <v>57336</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4357,34 +4406,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668514</v>
+        <v>668572</v>
       </c>
       <c r="R37" t="n">
-        <v>6696439</v>
+        <v>6696839</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4417,6 +4471,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4443,10 +4502,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120208704</v>
+        <v>120208800</v>
       </c>
       <c r="B38" t="n">
-        <v>95478</v>
+        <v>57689</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4455,38 +4514,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668571</v>
+        <v>668525</v>
       </c>
       <c r="R38" t="n">
-        <v>6696816</v>
+        <v>6696405</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4529,21 +4597,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4560,10 +4613,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120208811</v>
+        <v>120208776</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
+        <v>97908</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4572,47 +4625,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668524</v>
+        <v>668186</v>
       </c>
       <c r="R39" t="n">
-        <v>6696416</v>
+        <v>6696508</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4671,10 +4715,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120208779</v>
+        <v>120208863</v>
       </c>
       <c r="B40" t="n">
-        <v>97908</v>
+        <v>100194</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4687,21 +4731,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4711,10 +4755,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668212</v>
+        <v>668568</v>
       </c>
       <c r="R40" t="n">
-        <v>6696497</v>
+        <v>6696542</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4773,10 +4817,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120208853</v>
+        <v>120208724</v>
       </c>
       <c r="B41" t="n">
-        <v>100194</v>
+        <v>90580</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4785,25 +4829,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4813,10 +4857,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668241</v>
+        <v>668608</v>
       </c>
       <c r="R41" t="n">
-        <v>6696541</v>
+        <v>6696611</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4875,10 +4919,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120208782</v>
+        <v>120208827</v>
       </c>
       <c r="B42" t="n">
-        <v>97908</v>
+        <v>4772</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4891,21 +4935,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219798</v>
+        <v>102306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4915,10 +4959,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668279</v>
+        <v>668457</v>
       </c>
       <c r="R42" t="n">
-        <v>6696528</v>
+        <v>6696523</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4977,10 +5021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120208778</v>
+        <v>120208784</v>
       </c>
       <c r="B43" t="n">
-        <v>97908</v>
+        <v>91023</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4989,25 +5033,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219798</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5017,10 +5061,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668191</v>
+        <v>668273</v>
       </c>
       <c r="R43" t="n">
-        <v>6696527</v>
+        <v>6696531</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5079,10 +5123,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120208858</v>
+        <v>120208720</v>
       </c>
       <c r="B44" t="n">
-        <v>100194</v>
+        <v>90545</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5095,21 +5139,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5119,10 +5163,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668564</v>
+        <v>668407</v>
       </c>
       <c r="R44" t="n">
-        <v>6696816</v>
+        <v>6696520</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5165,6 +5209,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5181,7 +5240,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120208854</v>
+        <v>120208856</v>
       </c>
       <c r="B45" t="n">
         <v>100194</v>
@@ -5221,10 +5280,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668370</v>
+        <v>668382</v>
       </c>
       <c r="R45" t="n">
-        <v>6696506</v>
+        <v>6696524</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5283,10 +5342,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120208682</v>
+        <v>120208860</v>
       </c>
       <c r="B46" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5299,21 +5358,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5323,10 +5382,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668186</v>
+        <v>668566</v>
       </c>
       <c r="R46" t="n">
-        <v>6696508</v>
+        <v>6696858</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5385,10 +5444,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120208863</v>
+        <v>120208703</v>
       </c>
       <c r="B47" t="n">
-        <v>100194</v>
+        <v>95478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5397,25 +5456,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5425,10 +5484,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>668568</v>
+        <v>668451</v>
       </c>
       <c r="R47" t="n">
-        <v>6696542</v>
+        <v>6696602</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5471,6 +5530,21 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5487,10 +5561,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120208684</v>
+        <v>120208717</v>
       </c>
       <c r="B48" t="n">
-        <v>101097</v>
+        <v>95478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5499,25 +5573,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5527,10 +5601,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668201</v>
+        <v>668468</v>
       </c>
       <c r="R48" t="n">
-        <v>6696519</v>
+        <v>6696587</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5589,10 +5663,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120208722</v>
+        <v>120208709</v>
       </c>
       <c r="B49" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5605,21 +5679,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5629,10 +5703,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668552</v>
+        <v>668362</v>
       </c>
       <c r="R49" t="n">
-        <v>6696684</v>
+        <v>6696599</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5691,10 +5765,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120208741</v>
+        <v>120208815</v>
       </c>
       <c r="B50" t="n">
-        <v>57473</v>
+        <v>74593</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5703,46 +5777,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6426</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668483</v>
+        <v>668311</v>
       </c>
       <c r="R50" t="n">
-        <v>6696590</v>
+        <v>6696520</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5801,10 +5867,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120208712</v>
+        <v>120208782</v>
       </c>
       <c r="B51" t="n">
-        <v>95478</v>
+        <v>97908</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5813,25 +5879,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5841,10 +5907,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668301</v>
+        <v>668279</v>
       </c>
       <c r="R51" t="n">
-        <v>6696522</v>
+        <v>6696528</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5903,10 +5969,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120208713</v>
+        <v>120208779</v>
       </c>
       <c r="B52" t="n">
-        <v>95478</v>
+        <v>97908</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5915,25 +5981,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5943,10 +6009,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668379</v>
+        <v>668212</v>
       </c>
       <c r="R52" t="n">
-        <v>6696528</v>
+        <v>6696497</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6005,10 +6071,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120208735</v>
+        <v>120208790</v>
       </c>
       <c r="B53" t="n">
-        <v>56532</v>
+        <v>57326</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6017,47 +6083,46 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>100048</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668518</v>
+        <v>668550</v>
       </c>
       <c r="R53" t="n">
-        <v>6696678</v>
+        <v>6696605</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6094,7 +6159,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Stötte upp</t>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6121,10 +6186,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120208816</v>
+        <v>120208712</v>
       </c>
       <c r="B54" t="n">
-        <v>56524</v>
+        <v>95478</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6137,21 +6202,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102612</v>
+        <v>53</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6161,10 +6226,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668248</v>
+        <v>668301</v>
       </c>
       <c r="R54" t="n">
-        <v>6696628</v>
+        <v>6696522</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6197,11 +6262,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>flög upp från marken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6228,10 +6288,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120208691</v>
+        <v>120208850</v>
       </c>
       <c r="B55" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6244,21 +6304,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6268,10 +6328,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668509</v>
+        <v>668179</v>
       </c>
       <c r="R55" t="n">
-        <v>6696436</v>
+        <v>6696528</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6330,10 +6390,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120208781</v>
+        <v>120208739</v>
       </c>
       <c r="B56" t="n">
-        <v>97908</v>
+        <v>103441</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6346,21 +6406,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6370,10 +6430,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668261</v>
+        <v>668166</v>
       </c>
       <c r="R56" t="n">
-        <v>6696558</v>
+        <v>6696498</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6432,10 +6492,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120208823</v>
+        <v>120208777</v>
       </c>
       <c r="B57" t="n">
-        <v>57339</v>
+        <v>97908</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6448,42 +6508,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102977</v>
+        <v>219798</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668565</v>
+        <v>668188</v>
       </c>
       <c r="R57" t="n">
-        <v>6696520</v>
+        <v>6696531</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6516,11 +6568,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6547,10 +6594,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120208759</v>
+        <v>120208848</v>
       </c>
       <c r="B58" t="n">
-        <v>57336</v>
+        <v>100194</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6559,43 +6606,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668572</v>
+        <v>668419</v>
       </c>
       <c r="R58" t="n">
-        <v>6696839</v>
+        <v>6696535</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6628,11 +6670,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6659,10 +6696,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120208686</v>
+        <v>120208854</v>
       </c>
       <c r="B59" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6675,21 +6712,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6699,10 +6736,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668242</v>
+        <v>668370</v>
       </c>
       <c r="R59" t="n">
-        <v>6696541</v>
+        <v>6696506</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6761,10 +6798,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120208848</v>
+        <v>120208714</v>
       </c>
       <c r="B60" t="n">
-        <v>100194</v>
+        <v>95478</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6773,25 +6810,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6801,10 +6838,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>668419</v>
+        <v>668369</v>
       </c>
       <c r="R60" t="n">
-        <v>6696535</v>
+        <v>6696540</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6863,10 +6900,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120208784</v>
+        <v>120208813</v>
       </c>
       <c r="B61" t="n">
-        <v>91023</v>
+        <v>97930</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6879,34 +6916,43 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>668273</v>
+        <v>668575</v>
       </c>
       <c r="R61" t="n">
-        <v>6696531</v>
+        <v>6696701</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6965,10 +7011,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120208783</v>
+        <v>120208781</v>
       </c>
       <c r="B62" t="n">
-        <v>90351</v>
+        <v>97908</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6981,21 +7027,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3215</v>
+        <v>219798</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7005,10 +7051,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668281</v>
+        <v>668261</v>
       </c>
       <c r="R62" t="n">
-        <v>6696528</v>
+        <v>6696558</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7067,10 +7113,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120208708</v>
+        <v>120208799</v>
       </c>
       <c r="B63" t="n">
-        <v>95478</v>
+        <v>57689</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7079,38 +7125,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668376</v>
+        <v>668558</v>
       </c>
       <c r="R63" t="n">
-        <v>6696595</v>
+        <v>6696534</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7169,10 +7220,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120208736</v>
+        <v>120208687</v>
       </c>
       <c r="B64" t="n">
-        <v>56532</v>
+        <v>101097</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7185,39 +7236,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>221235</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668532</v>
+        <v>668382</v>
       </c>
       <c r="R64" t="n">
-        <v>6696689</v>
+        <v>6696529</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7250,11 +7296,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7281,7 +7322,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120208710</v>
+        <v>120208719</v>
       </c>
       <c r="B65" t="n">
         <v>95478</v>
@@ -7321,10 +7362,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668362</v>
+        <v>668514</v>
       </c>
       <c r="R65" t="n">
-        <v>6696582</v>
+        <v>6696439</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7383,10 +7424,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120208714</v>
+        <v>120208740</v>
       </c>
       <c r="B66" t="n">
-        <v>95478</v>
+        <v>57473</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7399,34 +7440,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668369</v>
+        <v>668357</v>
       </c>
       <c r="R66" t="n">
-        <v>6696540</v>
+        <v>6696585</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7485,10 +7534,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120208725</v>
+        <v>120208741</v>
       </c>
       <c r="B67" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7501,34 +7550,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>668551</v>
+        <v>668483</v>
       </c>
       <c r="R67" t="n">
-        <v>6696304</v>
+        <v>6696590</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7587,10 +7644,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120208720</v>
+        <v>120208791</v>
       </c>
       <c r="B68" t="n">
-        <v>90545</v>
+        <v>57326</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7599,38 +7656,46 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>100048</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>668407</v>
+        <v>668520</v>
       </c>
       <c r="R68" t="n">
-        <v>6696520</v>
+        <v>6696377</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7665,6 +7730,11 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7673,21 +7743,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -7704,10 +7759,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120208757</v>
+        <v>120208692</v>
       </c>
       <c r="B69" t="n">
-        <v>57336</v>
+        <v>101097</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7716,43 +7771,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>668572</v>
+        <v>668538</v>
       </c>
       <c r="R69" t="n">
-        <v>6696525</v>
+        <v>6696322</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7785,11 +7835,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7816,10 +7861,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120208799</v>
+        <v>120208686</v>
       </c>
       <c r="B70" t="n">
-        <v>57689</v>
+        <v>101097</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7832,39 +7877,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103015</v>
+        <v>221235</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>668558</v>
+        <v>668242</v>
       </c>
       <c r="R70" t="n">
-        <v>6696534</v>
+        <v>6696541</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7923,10 +7963,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120208849</v>
+        <v>120208716</v>
       </c>
       <c r="B71" t="n">
-        <v>100194</v>
+        <v>95478</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7935,25 +7975,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7963,10 +8003,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>668362</v>
+        <v>668439</v>
       </c>
       <c r="R71" t="n">
-        <v>6696583</v>
+        <v>6696517</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8025,10 +8065,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120208861</v>
+        <v>120208713</v>
       </c>
       <c r="B72" t="n">
-        <v>100194</v>
+        <v>95478</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8037,25 +8077,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8065,10 +8105,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>668567</v>
+        <v>668379</v>
       </c>
       <c r="R72" t="n">
-        <v>6696809</v>
+        <v>6696528</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8127,10 +8167,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120208688</v>
+        <v>120208857</v>
       </c>
       <c r="B73" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8143,21 +8183,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8167,10 +8207,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>668383</v>
+        <v>668438</v>
       </c>
       <c r="R73" t="n">
-        <v>6696524</v>
+        <v>6696512</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8229,10 +8269,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120208683</v>
+        <v>120208855</v>
       </c>
       <c r="B74" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8245,21 +8285,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8269,10 +8309,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>668188</v>
+        <v>668380</v>
       </c>
       <c r="R74" t="n">
-        <v>6696531</v>
+        <v>6696528</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8331,10 +8371,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120208812</v>
+        <v>120208711</v>
       </c>
       <c r="B75" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8343,47 +8383,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>668568</v>
+        <v>668345</v>
       </c>
       <c r="R75" t="n">
-        <v>6696851</v>
+        <v>6696598</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8442,10 +8473,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120208692</v>
+        <v>120208721</v>
       </c>
       <c r="B76" t="n">
-        <v>101097</v>
+        <v>90580</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8454,25 +8485,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221235</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8482,10 +8513,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>668538</v>
+        <v>668589</v>
       </c>
       <c r="R76" t="n">
-        <v>6696322</v>
+        <v>6696866</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8544,10 +8575,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120208855</v>
+        <v>120208707</v>
       </c>
       <c r="B77" t="n">
-        <v>100194</v>
+        <v>95478</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8556,25 +8587,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8584,10 +8615,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>668380</v>
+        <v>668394</v>
       </c>
       <c r="R77" t="n">
-        <v>6696528</v>
+        <v>6696553</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8646,10 +8677,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120208703</v>
+        <v>120208792</v>
       </c>
       <c r="B78" t="n">
-        <v>95478</v>
+        <v>57326</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8662,34 +8693,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>100048</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>668451</v>
+        <v>668517</v>
       </c>
       <c r="R78" t="n">
-        <v>6696602</v>
+        <v>6696457</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8724,6 +8763,11 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8732,21 +8776,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -8763,10 +8792,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120208737</v>
+        <v>120208822</v>
       </c>
       <c r="B79" t="n">
-        <v>56532</v>
+        <v>57339</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8779,16 +8808,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100138</v>
+        <v>102977</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8797,21 +8826,24 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>668566</v>
+        <v>668585</v>
       </c>
       <c r="R79" t="n">
-        <v>6696455</v>
+        <v>6696613</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8848,7 +8880,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Fjädrar efter en slagen tjäder</t>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8875,10 +8907,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120208790</v>
+        <v>120208684</v>
       </c>
       <c r="B80" t="n">
-        <v>57326</v>
+        <v>101097</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8887,46 +8919,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100048</v>
+        <v>221235</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>668550</v>
+        <v>668201</v>
       </c>
       <c r="R80" t="n">
-        <v>6696605</v>
+        <v>6696519</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8959,11 +8983,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8990,10 +9009,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120208815</v>
+        <v>120208778</v>
       </c>
       <c r="B81" t="n">
-        <v>74593</v>
+        <v>97908</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9006,21 +9025,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6426</v>
+        <v>219798</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9030,10 +9049,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>668311</v>
+        <v>668191</v>
       </c>
       <c r="R81" t="n">
-        <v>6696520</v>
+        <v>6696527</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9092,10 +9111,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120208814</v>
+        <v>120208785</v>
       </c>
       <c r="B82" t="n">
-        <v>74593</v>
+        <v>90864</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9104,25 +9123,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9132,10 +9151,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>668296</v>
+        <v>668552</v>
       </c>
       <c r="R82" t="n">
-        <v>6696535</v>
+        <v>6696684</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9194,10 +9213,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120208785</v>
+        <v>120208814</v>
       </c>
       <c r="B83" t="n">
-        <v>90864</v>
+        <v>74593</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9206,25 +9225,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>6426</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9234,10 +9253,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>668552</v>
+        <v>668296</v>
       </c>
       <c r="R83" t="n">
-        <v>6696684</v>
+        <v>6696535</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9296,10 +9315,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120208716</v>
+        <v>120208691</v>
       </c>
       <c r="B84" t="n">
-        <v>95478</v>
+        <v>101097</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9308,25 +9327,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9336,10 +9355,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>668439</v>
+        <v>668509</v>
       </c>
       <c r="R84" t="n">
-        <v>6696517</v>
+        <v>6696436</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9398,10 +9417,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120208775</v>
+        <v>120208758</v>
       </c>
       <c r="B85" t="n">
-        <v>97908</v>
+        <v>57336</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9410,38 +9429,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>668180</v>
+        <v>668240</v>
       </c>
       <c r="R85" t="n">
-        <v>6696501</v>
+        <v>6696522</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9474,6 +9498,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9500,7 +9529,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120208864</v>
+        <v>120208852</v>
       </c>
       <c r="B86" t="n">
         <v>100194</v>
@@ -9540,10 +9569,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>668527</v>
+        <v>668230</v>
       </c>
       <c r="R86" t="n">
-        <v>6696351</v>
+        <v>6696502</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9602,10 +9631,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120208776</v>
+        <v>120208859</v>
       </c>
       <c r="B87" t="n">
-        <v>97908</v>
+        <v>100194</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9618,21 +9647,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9642,10 +9671,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>668186</v>
+        <v>668581</v>
       </c>
       <c r="R87" t="n">
-        <v>6696508</v>
+        <v>6696848</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9704,10 +9733,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120208813</v>
+        <v>120208862</v>
       </c>
       <c r="B88" t="n">
-        <v>97930</v>
+        <v>100194</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9716,47 +9745,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>668575</v>
+        <v>668572</v>
       </c>
       <c r="R88" t="n">
-        <v>6696701</v>
+        <v>6696573</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9815,10 +9835,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120208756</v>
+        <v>120208743</v>
       </c>
       <c r="B89" t="n">
-        <v>57336</v>
+        <v>57473</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9831,39 +9851,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>668467</v>
+        <v>668533</v>
       </c>
       <c r="R89" t="n">
-        <v>6696630</v>
+        <v>6696366</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9896,11 +9919,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9927,10 +9945,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120208792</v>
+        <v>120208725</v>
       </c>
       <c r="B90" t="n">
-        <v>57326</v>
+        <v>90580</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9943,42 +9961,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100048</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>668517</v>
+        <v>668551</v>
       </c>
       <c r="R90" t="n">
-        <v>6696457</v>
+        <v>6696304</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10011,11 +10021,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10042,10 +10047,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120208798</v>
+        <v>120208708</v>
       </c>
       <c r="B91" t="n">
-        <v>57689</v>
+        <v>95478</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10054,43 +10059,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103015</v>
+        <v>53</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>668342</v>
+        <v>668376</v>
       </c>
       <c r="R91" t="n">
-        <v>6696603</v>
+        <v>6696595</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120208722</v>
+        <v>120208816</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>56524</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668552</v>
+        <v>668248</v>
       </c>
       <c r="R6" t="n">
-        <v>6696684</v>
+        <v>6696628</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1179,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>flög upp från marken</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120208816</v>
+        <v>120208722</v>
       </c>
       <c r="B7" t="n">
-        <v>56524</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668248</v>
+        <v>668552</v>
       </c>
       <c r="R7" t="n">
-        <v>6696628</v>
+        <v>6696684</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>flög upp från marken</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120208710</v>
+        <v>120208737</v>
       </c>
       <c r="B10" t="n">
-        <v>95478</v>
+        <v>56532</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1528,38 +1528,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668362</v>
+        <v>668566</v>
       </c>
       <c r="R10" t="n">
-        <v>6696582</v>
+        <v>6696455</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,6 +1597,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120208737</v>
+        <v>120208735</v>
       </c>
       <c r="B11" t="n">
         <v>56532</v>
@@ -1651,10 +1661,14 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1663,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668566</v>
+        <v>668518</v>
       </c>
       <c r="R11" t="n">
-        <v>6696455</v>
+        <v>6696678</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1717,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Fjädrar efter en slagen tjäder</t>
+          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120208735</v>
+        <v>120208798</v>
       </c>
       <c r="B12" t="n">
-        <v>56532</v>
+        <v>57689</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,31 +1760,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1779,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668518</v>
+        <v>668342</v>
       </c>
       <c r="R12" t="n">
-        <v>6696678</v>
+        <v>6696603</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,11 +1825,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,10 +1966,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120208798</v>
+        <v>120208775</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>97908</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1977,39 +1982,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668342</v>
+        <v>668180</v>
       </c>
       <c r="R14" t="n">
-        <v>6696603</v>
+        <v>6696501</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120208830</v>
+        <v>120208710</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>95478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2084,21 +2084,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668442</v>
+        <v>668362</v>
       </c>
       <c r="R15" t="n">
-        <v>6696514</v>
+        <v>6696582</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2154,21 +2154,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2185,10 +2170,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120208775</v>
+        <v>120208830</v>
       </c>
       <c r="B16" t="n">
-        <v>97908</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2197,25 +2182,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2225,10 +2210,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668180</v>
+        <v>668442</v>
       </c>
       <c r="R16" t="n">
-        <v>6696501</v>
+        <v>6696514</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,6 +2256,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -4288,10 +4288,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120208819</v>
+        <v>120208776</v>
       </c>
       <c r="B36" t="n">
-        <v>105032</v>
+        <v>97908</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4304,21 +4304,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668579</v>
+        <v>668186</v>
       </c>
       <c r="R36" t="n">
-        <v>6696655</v>
+        <v>6696508</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4390,10 +4390,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120208759</v>
+        <v>120208863</v>
       </c>
       <c r="B37" t="n">
-        <v>57336</v>
+        <v>100194</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4402,43 +4402,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668572</v>
+        <v>668568</v>
       </c>
       <c r="R37" t="n">
-        <v>6696839</v>
+        <v>6696542</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4471,11 +4466,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4502,10 +4492,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120208800</v>
+        <v>120208819</v>
       </c>
       <c r="B38" t="n">
-        <v>57689</v>
+        <v>105032</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4518,43 +4508,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668525</v>
+        <v>668579</v>
       </c>
       <c r="R38" t="n">
-        <v>6696405</v>
+        <v>6696655</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4613,10 +4594,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120208776</v>
+        <v>120208759</v>
       </c>
       <c r="B39" t="n">
-        <v>97908</v>
+        <v>57336</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4625,38 +4606,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668186</v>
+        <v>668572</v>
       </c>
       <c r="R39" t="n">
-        <v>6696508</v>
+        <v>6696839</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4689,6 +4675,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4715,10 +4706,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120208863</v>
+        <v>120208800</v>
       </c>
       <c r="B40" t="n">
-        <v>100194</v>
+        <v>57689</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4731,34 +4722,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668568</v>
+        <v>668525</v>
       </c>
       <c r="R40" t="n">
-        <v>6696542</v>
+        <v>6696405</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5123,10 +5123,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120208720</v>
+        <v>120208815</v>
       </c>
       <c r="B44" t="n">
-        <v>90545</v>
+        <v>74593</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5139,21 +5139,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>6426</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668407</v>
+        <v>668311</v>
       </c>
       <c r="R44" t="n">
         <v>6696520</v>
@@ -5209,21 +5209,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5240,10 +5225,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120208856</v>
+        <v>120208782</v>
       </c>
       <c r="B45" t="n">
-        <v>100194</v>
+        <v>97908</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5256,21 +5241,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5280,10 +5265,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668382</v>
+        <v>668279</v>
       </c>
       <c r="R45" t="n">
-        <v>6696524</v>
+        <v>6696528</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5342,10 +5327,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120208860</v>
+        <v>120208779</v>
       </c>
       <c r="B46" t="n">
-        <v>100194</v>
+        <v>97908</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5358,21 +5343,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5382,10 +5367,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668566</v>
+        <v>668212</v>
       </c>
       <c r="R46" t="n">
-        <v>6696858</v>
+        <v>6696497</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5765,10 +5750,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120208815</v>
+        <v>120208720</v>
       </c>
       <c r="B50" t="n">
-        <v>74593</v>
+        <v>90545</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5781,21 +5766,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5805,7 +5790,7 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668311</v>
+        <v>668407</v>
       </c>
       <c r="R50" t="n">
         <v>6696520</v>
@@ -5851,6 +5836,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5867,10 +5867,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120208782</v>
+        <v>120208856</v>
       </c>
       <c r="B51" t="n">
-        <v>97908</v>
+        <v>100194</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5883,21 +5883,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5907,10 +5907,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668279</v>
+        <v>668382</v>
       </c>
       <c r="R51" t="n">
-        <v>6696528</v>
+        <v>6696524</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5969,10 +5969,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120208779</v>
+        <v>120208860</v>
       </c>
       <c r="B52" t="n">
-        <v>97908</v>
+        <v>100194</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5985,21 +5985,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6009,10 +6009,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668212</v>
+        <v>668566</v>
       </c>
       <c r="R52" t="n">
-        <v>6696497</v>
+        <v>6696858</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6071,10 +6071,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120208790</v>
+        <v>120208850</v>
       </c>
       <c r="B53" t="n">
-        <v>57326</v>
+        <v>100194</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6083,46 +6083,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100048</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668550</v>
+        <v>668179</v>
       </c>
       <c r="R53" t="n">
-        <v>6696605</v>
+        <v>6696528</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6155,11 +6147,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6186,10 +6173,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120208712</v>
+        <v>120208739</v>
       </c>
       <c r="B54" t="n">
-        <v>95478</v>
+        <v>103441</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6198,25 +6185,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>53</v>
+        <v>222412</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6226,10 +6213,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668301</v>
+        <v>668166</v>
       </c>
       <c r="R54" t="n">
-        <v>6696522</v>
+        <v>6696498</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6288,10 +6275,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120208850</v>
+        <v>120208790</v>
       </c>
       <c r="B55" t="n">
-        <v>100194</v>
+        <v>57326</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6300,38 +6287,46 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>100048</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668179</v>
+        <v>668550</v>
       </c>
       <c r="R55" t="n">
-        <v>6696528</v>
+        <v>6696605</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6364,6 +6359,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6390,10 +6390,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120208739</v>
+        <v>120208712</v>
       </c>
       <c r="B56" t="n">
-        <v>103441</v>
+        <v>95478</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6402,25 +6402,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222412</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6430,10 +6430,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668166</v>
+        <v>668301</v>
       </c>
       <c r="R56" t="n">
-        <v>6696498</v>
+        <v>6696522</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7534,10 +7534,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120208741</v>
+        <v>120208791</v>
       </c>
       <c r="B67" t="n">
-        <v>57473</v>
+        <v>57326</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7550,21 +7550,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7582,10 +7582,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>668483</v>
+        <v>668520</v>
       </c>
       <c r="R67" t="n">
-        <v>6696590</v>
+        <v>6696377</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7618,6 +7618,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7644,10 +7649,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120208791</v>
+        <v>120208741</v>
       </c>
       <c r="B68" t="n">
-        <v>57326</v>
+        <v>57473</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7660,21 +7665,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7692,10 +7697,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>668520</v>
+        <v>668483</v>
       </c>
       <c r="R68" t="n">
-        <v>6696377</v>
+        <v>6696590</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7728,11 +7733,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8473,10 +8473,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120208721</v>
+        <v>120208684</v>
       </c>
       <c r="B76" t="n">
-        <v>90580</v>
+        <v>101097</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8485,25 +8485,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>221235</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>668589</v>
+        <v>668201</v>
       </c>
       <c r="R76" t="n">
-        <v>6696866</v>
+        <v>6696519</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8575,10 +8575,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120208707</v>
+        <v>120208778</v>
       </c>
       <c r="B77" t="n">
-        <v>95478</v>
+        <v>97908</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8587,25 +8587,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8615,10 +8615,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>668394</v>
+        <v>668191</v>
       </c>
       <c r="R77" t="n">
-        <v>6696553</v>
+        <v>6696527</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8677,10 +8677,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120208792</v>
+        <v>120208721</v>
       </c>
       <c r="B78" t="n">
-        <v>57326</v>
+        <v>90580</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8693,42 +8693,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100048</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>668517</v>
+        <v>668589</v>
       </c>
       <c r="R78" t="n">
-        <v>6696457</v>
+        <v>6696866</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8761,11 +8753,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8792,10 +8779,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120208822</v>
+        <v>120208707</v>
       </c>
       <c r="B79" t="n">
-        <v>57339</v>
+        <v>95478</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8804,46 +8791,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>102977</v>
+        <v>53</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>668585</v>
+        <v>668394</v>
       </c>
       <c r="R79" t="n">
-        <v>6696613</v>
+        <v>6696553</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8876,11 +8855,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8907,10 +8881,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120208684</v>
+        <v>120208792</v>
       </c>
       <c r="B80" t="n">
-        <v>101097</v>
+        <v>57326</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8919,38 +8893,46 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221235</v>
+        <v>100048</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>668201</v>
+        <v>668517</v>
       </c>
       <c r="R80" t="n">
-        <v>6696519</v>
+        <v>6696457</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8983,6 +8965,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9009,10 +8996,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120208778</v>
+        <v>120208822</v>
       </c>
       <c r="B81" t="n">
-        <v>97908</v>
+        <v>57339</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9025,34 +9012,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>219798</v>
+        <v>102977</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>668191</v>
+        <v>668585</v>
       </c>
       <c r="R81" t="n">
-        <v>6696527</v>
+        <v>6696613</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9085,6 +9080,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9733,10 +9733,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120208862</v>
+        <v>120208743</v>
       </c>
       <c r="B88" t="n">
-        <v>100194</v>
+        <v>57473</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9745,38 +9745,46 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>668572</v>
+        <v>668533</v>
       </c>
       <c r="R88" t="n">
-        <v>6696573</v>
+        <v>6696366</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9835,10 +9843,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120208743</v>
+        <v>120208725</v>
       </c>
       <c r="B89" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9851,42 +9859,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>668533</v>
+        <v>668551</v>
       </c>
       <c r="R89" t="n">
-        <v>6696366</v>
+        <v>6696304</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9945,10 +9945,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120208725</v>
+        <v>120208708</v>
       </c>
       <c r="B90" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9961,21 +9961,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9985,10 +9985,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>668551</v>
+        <v>668376</v>
       </c>
       <c r="R90" t="n">
-        <v>6696304</v>
+        <v>6696595</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10047,10 +10047,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120208708</v>
+        <v>120208862</v>
       </c>
       <c r="B91" t="n">
-        <v>95478</v>
+        <v>100194</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10059,25 +10059,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10087,10 +10087,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>668376</v>
+        <v>668572</v>
       </c>
       <c r="R91" t="n">
-        <v>6696595</v>
+        <v>6696573</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120208828</v>
+        <v>120208707</v>
       </c>
       <c r="B2" t="n">
-        <v>4772</v>
+        <v>95478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668595</v>
+        <v>668394</v>
       </c>
       <c r="R2" t="n">
-        <v>6696467</v>
+        <v>6696553</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120208744</v>
+        <v>120208722</v>
       </c>
       <c r="B3" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668602</v>
+        <v>668552</v>
       </c>
       <c r="R3" t="n">
-        <v>6696625</v>
+        <v>6696684</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120208705</v>
+        <v>120208856</v>
       </c>
       <c r="B4" t="n">
-        <v>95478</v>
+        <v>100194</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668521</v>
+        <v>668382</v>
       </c>
       <c r="R4" t="n">
-        <v>6696330</v>
+        <v>6696524</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,21 +965,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1001,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120208718</v>
+        <v>120208858</v>
       </c>
       <c r="B5" t="n">
-        <v>95478</v>
+        <v>100194</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668450</v>
+        <v>668564</v>
       </c>
       <c r="R5" t="n">
-        <v>6696589</v>
+        <v>6696816</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120208816</v>
+        <v>120208857</v>
       </c>
       <c r="B6" t="n">
-        <v>56524</v>
+        <v>100194</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668248</v>
+        <v>668438</v>
       </c>
       <c r="R6" t="n">
-        <v>6696628</v>
+        <v>6696512</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,11 +1159,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>flög upp från marken</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120208722</v>
+        <v>120208683</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>101097</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>221235</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668552</v>
+        <v>668188</v>
       </c>
       <c r="R7" t="n">
-        <v>6696684</v>
+        <v>6696531</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1312,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120208688</v>
+        <v>120208724</v>
       </c>
       <c r="B8" t="n">
-        <v>101097</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668383</v>
+        <v>668608</v>
       </c>
       <c r="R8" t="n">
-        <v>6696524</v>
+        <v>6696611</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120208690</v>
+        <v>120208759</v>
       </c>
       <c r="B9" t="n">
-        <v>101097</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,38 +1401,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668564</v>
+        <v>668572</v>
       </c>
       <c r="R9" t="n">
-        <v>6696811</v>
+        <v>6696839</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1470,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120208737</v>
+        <v>120208823</v>
       </c>
       <c r="B10" t="n">
-        <v>56532</v>
+        <v>57339</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,16 +1517,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>102977</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1550,21 +1535,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668566</v>
+        <v>668565</v>
       </c>
       <c r="R10" t="n">
-        <v>6696455</v>
+        <v>6696520</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1589,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Fjädrar efter en slagen tjäder</t>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,10 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120208735</v>
+        <v>120208815</v>
       </c>
       <c r="B11" t="n">
-        <v>56532</v>
+        <v>74593</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,43 +1632,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668518</v>
+        <v>668311</v>
       </c>
       <c r="R11" t="n">
-        <v>6696678</v>
+        <v>6696520</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,11 +1692,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1744,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120208798</v>
+        <v>120208814</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>74593</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,39 +1734,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668342</v>
+        <v>668296</v>
       </c>
       <c r="R12" t="n">
-        <v>6696603</v>
+        <v>6696535</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,10 +1820,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120208823</v>
+        <v>120208790</v>
       </c>
       <c r="B13" t="n">
-        <v>57339</v>
+        <v>57326</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,25 +1832,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102977</v>
+        <v>100048</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1899,10 +1868,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668565</v>
+        <v>668550</v>
       </c>
       <c r="R13" t="n">
-        <v>6696520</v>
+        <v>6696605</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120208775</v>
+        <v>120208798</v>
       </c>
       <c r="B14" t="n">
-        <v>97908</v>
+        <v>57689</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1982,34 +1951,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668180</v>
+        <v>668342</v>
       </c>
       <c r="R14" t="n">
-        <v>6696501</v>
+        <v>6696603</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120208710</v>
+        <v>120208692</v>
       </c>
       <c r="B15" t="n">
-        <v>95478</v>
+        <v>101097</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,25 +2054,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2082,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668362</v>
+        <v>668538</v>
       </c>
       <c r="R15" t="n">
-        <v>6696582</v>
+        <v>6696322</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2170,10 +2144,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120208830</v>
+        <v>120208712</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>95478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2186,21 +2160,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2210,10 +2184,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668442</v>
+        <v>668301</v>
       </c>
       <c r="R16" t="n">
-        <v>6696514</v>
+        <v>6696522</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,21 +2230,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2287,10 +2246,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120208756</v>
+        <v>120208816</v>
       </c>
       <c r="B17" t="n">
-        <v>57336</v>
+        <v>56524</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2303,16 +2262,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2321,21 +2280,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668467</v>
+        <v>668248</v>
       </c>
       <c r="R17" t="n">
-        <v>6696630</v>
+        <v>6696628</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2326,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>hackmärken i död ved</t>
+          <t>flög upp från marken</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2399,10 +2353,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120208774</v>
+        <v>120208684</v>
       </c>
       <c r="B18" t="n">
-        <v>97908</v>
+        <v>101097</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2415,21 +2369,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2439,10 +2393,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668365</v>
+        <v>668201</v>
       </c>
       <c r="R18" t="n">
-        <v>6696575</v>
+        <v>6696519</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2501,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120208849</v>
+        <v>120208719</v>
       </c>
       <c r="B19" t="n">
-        <v>100194</v>
+        <v>95478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,25 +2467,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2541,10 +2495,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668362</v>
+        <v>668514</v>
       </c>
       <c r="R19" t="n">
-        <v>6696583</v>
+        <v>6696439</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2603,10 +2557,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120208851</v>
+        <v>120208758</v>
       </c>
       <c r="B20" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,38 +2569,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668213</v>
+        <v>668240</v>
       </c>
       <c r="R20" t="n">
-        <v>6696494</v>
+        <v>6696522</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2679,6 +2638,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2705,10 +2669,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120208861</v>
+        <v>120208744</v>
       </c>
       <c r="B21" t="n">
-        <v>100194</v>
+        <v>57473</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2717,38 +2681,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668567</v>
+        <v>668602</v>
       </c>
       <c r="R21" t="n">
-        <v>6696809</v>
+        <v>6696625</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2807,10 +2776,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120208704</v>
+        <v>120208784</v>
       </c>
       <c r="B22" t="n">
-        <v>95478</v>
+        <v>91023</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2819,25 +2788,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2847,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668571</v>
+        <v>668273</v>
       </c>
       <c r="R22" t="n">
-        <v>6696816</v>
+        <v>6696531</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2893,21 +2862,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -2924,10 +2878,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120208858</v>
+        <v>120208725</v>
       </c>
       <c r="B23" t="n">
-        <v>100194</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2936,25 +2890,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2964,10 +2918,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668564</v>
+        <v>668551</v>
       </c>
       <c r="R23" t="n">
-        <v>6696816</v>
+        <v>6696304</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3026,10 +2980,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120208864</v>
+        <v>120208830</v>
       </c>
       <c r="B24" t="n">
-        <v>100194</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3038,25 +2992,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3066,10 +3020,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668527</v>
+        <v>668442</v>
       </c>
       <c r="R24" t="n">
-        <v>6696351</v>
+        <v>6696514</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3112,6 +3066,21 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3128,7 +3097,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120208853</v>
+        <v>120208860</v>
       </c>
       <c r="B25" t="n">
         <v>100194</v>
@@ -3168,10 +3137,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668241</v>
+        <v>668566</v>
       </c>
       <c r="R25" t="n">
-        <v>6696541</v>
+        <v>6696858</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3230,10 +3199,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120208783</v>
+        <v>120208714</v>
       </c>
       <c r="B26" t="n">
-        <v>90351</v>
+        <v>95478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3242,25 +3211,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3270,10 +3239,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668281</v>
+        <v>668369</v>
       </c>
       <c r="R26" t="n">
-        <v>6696528</v>
+        <v>6696540</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3332,10 +3301,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120208706</v>
+        <v>120208721</v>
       </c>
       <c r="B27" t="n">
-        <v>95478</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3348,21 +3317,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3372,10 +3341,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668408</v>
+        <v>668589</v>
       </c>
       <c r="R27" t="n">
-        <v>6696562</v>
+        <v>6696866</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3434,10 +3403,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120208683</v>
+        <v>120208800</v>
       </c>
       <c r="B28" t="n">
-        <v>101097</v>
+        <v>57689</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3450,34 +3419,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221235</v>
+        <v>103015</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668188</v>
+        <v>668525</v>
       </c>
       <c r="R28" t="n">
-        <v>6696531</v>
+        <v>6696405</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3536,10 +3514,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120208811</v>
+        <v>120208709</v>
       </c>
       <c r="B29" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3548,47 +3526,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668524</v>
+        <v>668362</v>
       </c>
       <c r="R29" t="n">
-        <v>6696416</v>
+        <v>6696599</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3647,10 +3616,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120208812</v>
+        <v>120208736</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3659,35 +3628,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3696,10 +3661,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668568</v>
+        <v>668532</v>
       </c>
       <c r="R30" t="n">
-        <v>6696851</v>
+        <v>6696689</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3732,6 +3697,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3758,10 +3728,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120208682</v>
+        <v>120208782</v>
       </c>
       <c r="B31" t="n">
-        <v>101097</v>
+        <v>97908</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3774,21 +3744,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3798,10 +3768,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668186</v>
+        <v>668279</v>
       </c>
       <c r="R31" t="n">
-        <v>6696508</v>
+        <v>6696528</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3860,10 +3830,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120208818</v>
+        <v>120208776</v>
       </c>
       <c r="B32" t="n">
-        <v>105032</v>
+        <v>97908</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3876,21 +3846,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3900,10 +3870,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668437</v>
+        <v>668186</v>
       </c>
       <c r="R32" t="n">
-        <v>6696501</v>
+        <v>6696508</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3962,10 +3932,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120208757</v>
+        <v>120208813</v>
       </c>
       <c r="B33" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3974,31 +3944,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4007,10 +3981,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668572</v>
+        <v>668575</v>
       </c>
       <c r="R33" t="n">
-        <v>6696525</v>
+        <v>6696701</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4043,11 +4017,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4074,10 +4043,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120208826</v>
+        <v>120208792</v>
       </c>
       <c r="B34" t="n">
-        <v>4772</v>
+        <v>57326</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4086,38 +4055,46 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102306</v>
+        <v>100048</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668442</v>
+        <v>668517</v>
       </c>
       <c r="R34" t="n">
-        <v>6696515</v>
+        <v>6696457</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4150,6 +4127,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4176,10 +4158,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120208736</v>
+        <v>120208687</v>
       </c>
       <c r="B35" t="n">
-        <v>56532</v>
+        <v>101097</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4192,39 +4174,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>221235</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668532</v>
+        <v>668382</v>
       </c>
       <c r="R35" t="n">
-        <v>6696689</v>
+        <v>6696529</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4257,11 +4234,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4288,10 +4260,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120208776</v>
+        <v>120208819</v>
       </c>
       <c r="B36" t="n">
-        <v>97908</v>
+        <v>105032</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4304,21 +4276,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219798</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4328,10 +4300,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668186</v>
+        <v>668579</v>
       </c>
       <c r="R36" t="n">
-        <v>6696508</v>
+        <v>6696655</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4390,7 +4362,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120208863</v>
+        <v>120208850</v>
       </c>
       <c r="B37" t="n">
         <v>100194</v>
@@ -4430,10 +4402,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668568</v>
+        <v>668179</v>
       </c>
       <c r="R37" t="n">
-        <v>6696542</v>
+        <v>6696528</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4492,10 +4464,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120208819</v>
+        <v>120208774</v>
       </c>
       <c r="B38" t="n">
-        <v>105032</v>
+        <v>97908</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4508,21 +4480,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>219798</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4532,10 +4504,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668579</v>
+        <v>668365</v>
       </c>
       <c r="R38" t="n">
-        <v>6696655</v>
+        <v>6696575</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4594,10 +4566,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120208759</v>
+        <v>120208811</v>
       </c>
       <c r="B39" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4606,31 +4578,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4639,10 +4615,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668572</v>
+        <v>668524</v>
       </c>
       <c r="R39" t="n">
-        <v>6696839</v>
+        <v>6696416</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4675,11 +4651,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4706,10 +4677,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120208800</v>
+        <v>120208717</v>
       </c>
       <c r="B40" t="n">
-        <v>57689</v>
+        <v>95478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4718,47 +4689,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668525</v>
+        <v>668468</v>
       </c>
       <c r="R40" t="n">
-        <v>6696405</v>
+        <v>6696587</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4817,10 +4779,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120208724</v>
+        <v>120208735</v>
       </c>
       <c r="B41" t="n">
-        <v>90580</v>
+        <v>56532</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4829,38 +4791,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668608</v>
+        <v>668518</v>
       </c>
       <c r="R41" t="n">
-        <v>6696611</v>
+        <v>6696678</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4893,6 +4864,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4919,10 +4895,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120208827</v>
+        <v>120208691</v>
       </c>
       <c r="B42" t="n">
-        <v>4772</v>
+        <v>101097</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4935,21 +4911,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102306</v>
+        <v>221235</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4959,10 +4935,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668457</v>
+        <v>668509</v>
       </c>
       <c r="R42" t="n">
-        <v>6696523</v>
+        <v>6696436</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5021,10 +4997,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120208784</v>
+        <v>120208849</v>
       </c>
       <c r="B43" t="n">
-        <v>91023</v>
+        <v>100194</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5033,25 +5009,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5061,10 +5037,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668273</v>
+        <v>668362</v>
       </c>
       <c r="R43" t="n">
-        <v>6696531</v>
+        <v>6696583</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5123,10 +5099,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120208815</v>
+        <v>120208848</v>
       </c>
       <c r="B44" t="n">
-        <v>74593</v>
+        <v>100194</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5139,21 +5115,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6426</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5163,10 +5139,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668311</v>
+        <v>668419</v>
       </c>
       <c r="R44" t="n">
-        <v>6696520</v>
+        <v>6696535</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5225,10 +5201,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120208782</v>
+        <v>120208706</v>
       </c>
       <c r="B45" t="n">
-        <v>97908</v>
+        <v>95478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5237,25 +5213,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5265,10 +5241,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668279</v>
+        <v>668408</v>
       </c>
       <c r="R45" t="n">
-        <v>6696528</v>
+        <v>6696562</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5327,10 +5303,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120208779</v>
+        <v>120208708</v>
       </c>
       <c r="B46" t="n">
-        <v>97908</v>
+        <v>95478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5339,25 +5315,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5367,10 +5343,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668212</v>
+        <v>668376</v>
       </c>
       <c r="R46" t="n">
-        <v>6696497</v>
+        <v>6696595</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5429,7 +5405,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120208703</v>
+        <v>120208710</v>
       </c>
       <c r="B47" t="n">
         <v>95478</v>
@@ -5469,10 +5445,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>668451</v>
+        <v>668362</v>
       </c>
       <c r="R47" t="n">
-        <v>6696602</v>
+        <v>6696582</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5515,21 +5491,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5546,7 +5507,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120208717</v>
+        <v>120208704</v>
       </c>
       <c r="B48" t="n">
         <v>95478</v>
@@ -5586,10 +5547,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668468</v>
+        <v>668571</v>
       </c>
       <c r="R48" t="n">
-        <v>6696587</v>
+        <v>6696816</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5632,6 +5593,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5648,10 +5624,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120208709</v>
+        <v>120208757</v>
       </c>
       <c r="B49" t="n">
-        <v>95478</v>
+        <v>57336</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5664,34 +5640,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668362</v>
+        <v>668572</v>
       </c>
       <c r="R49" t="n">
-        <v>6696599</v>
+        <v>6696525</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5724,6 +5705,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5750,10 +5736,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120208720</v>
+        <v>120208682</v>
       </c>
       <c r="B50" t="n">
-        <v>90545</v>
+        <v>101097</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5766,21 +5752,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>221235</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5790,10 +5776,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668407</v>
+        <v>668186</v>
       </c>
       <c r="R50" t="n">
-        <v>6696520</v>
+        <v>6696508</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5836,21 +5822,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -5867,10 +5838,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120208856</v>
+        <v>120208741</v>
       </c>
       <c r="B51" t="n">
-        <v>100194</v>
+        <v>57473</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5879,38 +5850,46 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668382</v>
+        <v>668483</v>
       </c>
       <c r="R51" t="n">
-        <v>6696524</v>
+        <v>6696590</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5969,10 +5948,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120208860</v>
+        <v>120208690</v>
       </c>
       <c r="B52" t="n">
-        <v>100194</v>
+        <v>101097</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5985,21 +5964,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6009,10 +5988,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668566</v>
+        <v>668564</v>
       </c>
       <c r="R52" t="n">
-        <v>6696858</v>
+        <v>6696811</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6071,7 +6050,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120208850</v>
+        <v>120208851</v>
       </c>
       <c r="B53" t="n">
         <v>100194</v>
@@ -6111,10 +6090,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668179</v>
+        <v>668213</v>
       </c>
       <c r="R53" t="n">
-        <v>6696528</v>
+        <v>6696494</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6173,10 +6152,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120208739</v>
+        <v>120208783</v>
       </c>
       <c r="B54" t="n">
-        <v>103441</v>
+        <v>90351</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6189,21 +6168,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222412</v>
+        <v>3215</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6213,10 +6192,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668166</v>
+        <v>668281</v>
       </c>
       <c r="R54" t="n">
-        <v>6696498</v>
+        <v>6696528</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6275,10 +6254,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120208790</v>
+        <v>120208713</v>
       </c>
       <c r="B55" t="n">
-        <v>57326</v>
+        <v>95478</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6291,42 +6270,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100048</v>
+        <v>53</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668550</v>
+        <v>668379</v>
       </c>
       <c r="R55" t="n">
-        <v>6696605</v>
+        <v>6696528</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6359,11 +6330,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6390,7 +6356,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120208712</v>
+        <v>120208711</v>
       </c>
       <c r="B56" t="n">
         <v>95478</v>
@@ -6430,10 +6396,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668301</v>
+        <v>668345</v>
       </c>
       <c r="R56" t="n">
-        <v>6696522</v>
+        <v>6696598</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6492,10 +6458,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120208777</v>
+        <v>120208756</v>
       </c>
       <c r="B57" t="n">
-        <v>97908</v>
+        <v>57336</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6504,38 +6470,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668188</v>
+        <v>668467</v>
       </c>
       <c r="R57" t="n">
-        <v>6696531</v>
+        <v>6696630</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6568,6 +6539,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6594,7 +6570,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120208848</v>
+        <v>120208862</v>
       </c>
       <c r="B58" t="n">
         <v>100194</v>
@@ -6634,10 +6610,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668419</v>
+        <v>668572</v>
       </c>
       <c r="R58" t="n">
-        <v>6696535</v>
+        <v>6696573</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6798,10 +6774,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120208714</v>
+        <v>120208864</v>
       </c>
       <c r="B60" t="n">
-        <v>95478</v>
+        <v>100194</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6810,25 +6786,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6838,10 +6814,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>668369</v>
+        <v>668527</v>
       </c>
       <c r="R60" t="n">
-        <v>6696540</v>
+        <v>6696351</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6900,7 +6876,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120208813</v>
+        <v>120208812</v>
       </c>
       <c r="B61" t="n">
         <v>97930</v>
@@ -6935,7 +6911,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6949,10 +6925,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>668575</v>
+        <v>668568</v>
       </c>
       <c r="R61" t="n">
-        <v>6696701</v>
+        <v>6696851</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7011,10 +6987,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120208781</v>
+        <v>120208705</v>
       </c>
       <c r="B62" t="n">
-        <v>97908</v>
+        <v>95478</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7023,25 +6999,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7051,10 +7027,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668261</v>
+        <v>668521</v>
       </c>
       <c r="R62" t="n">
-        <v>6696558</v>
+        <v>6696330</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7097,6 +7073,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7113,10 +7104,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120208799</v>
+        <v>120208791</v>
       </c>
       <c r="B63" t="n">
-        <v>57689</v>
+        <v>57326</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7125,20 +7116,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>100048</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7147,21 +7138,24 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668558</v>
+        <v>668520</v>
       </c>
       <c r="R63" t="n">
-        <v>6696534</v>
+        <v>6696377</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7194,6 +7188,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7220,10 +7219,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120208687</v>
+        <v>120208737</v>
       </c>
       <c r="B64" t="n">
-        <v>101097</v>
+        <v>56532</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7236,34 +7235,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221235</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668382</v>
+        <v>668566</v>
       </c>
       <c r="R64" t="n">
-        <v>6696529</v>
+        <v>6696455</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7296,6 +7300,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7322,10 +7331,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120208719</v>
+        <v>120208828</v>
       </c>
       <c r="B65" t="n">
-        <v>95478</v>
+        <v>4772</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7334,25 +7343,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7362,10 +7371,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668514</v>
+        <v>668595</v>
       </c>
       <c r="R65" t="n">
-        <v>6696439</v>
+        <v>6696467</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7424,10 +7433,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120208740</v>
+        <v>120208720</v>
       </c>
       <c r="B66" t="n">
-        <v>57473</v>
+        <v>90545</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7436,46 +7445,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668357</v>
+        <v>668407</v>
       </c>
       <c r="R66" t="n">
-        <v>6696585</v>
+        <v>6696520</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7518,6 +7519,21 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -7534,10 +7550,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120208791</v>
+        <v>120208852</v>
       </c>
       <c r="B67" t="n">
-        <v>57326</v>
+        <v>100194</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7546,46 +7562,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100048</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>668520</v>
+        <v>668230</v>
       </c>
       <c r="R67" t="n">
-        <v>6696377</v>
+        <v>6696502</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7618,11 +7626,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7649,10 +7652,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120208741</v>
+        <v>120208855</v>
       </c>
       <c r="B68" t="n">
-        <v>57473</v>
+        <v>100194</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7661,46 +7664,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>668483</v>
+        <v>668380</v>
       </c>
       <c r="R68" t="n">
-        <v>6696590</v>
+        <v>6696528</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7759,10 +7754,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120208692</v>
+        <v>120208853</v>
       </c>
       <c r="B69" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7775,21 +7770,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7799,10 +7794,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>668538</v>
+        <v>668241</v>
       </c>
       <c r="R69" t="n">
-        <v>6696322</v>
+        <v>6696541</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7861,10 +7856,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120208686</v>
+        <v>120208781</v>
       </c>
       <c r="B70" t="n">
-        <v>101097</v>
+        <v>97908</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7877,21 +7872,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7901,10 +7896,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>668242</v>
+        <v>668261</v>
       </c>
       <c r="R70" t="n">
-        <v>6696541</v>
+        <v>6696558</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7963,10 +7958,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120208716</v>
+        <v>120208778</v>
       </c>
       <c r="B71" t="n">
-        <v>95478</v>
+        <v>97908</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7975,25 +7970,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8003,10 +7998,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>668439</v>
+        <v>668191</v>
       </c>
       <c r="R71" t="n">
-        <v>6696517</v>
+        <v>6696527</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8065,7 +8060,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120208713</v>
+        <v>120208703</v>
       </c>
       <c r="B72" t="n">
         <v>95478</v>
@@ -8105,10 +8100,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>668379</v>
+        <v>668451</v>
       </c>
       <c r="R72" t="n">
-        <v>6696528</v>
+        <v>6696602</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8151,6 +8146,21 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8167,10 +8177,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120208857</v>
+        <v>120208822</v>
       </c>
       <c r="B73" t="n">
-        <v>100194</v>
+        <v>57339</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8183,34 +8193,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>102977</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>668438</v>
+        <v>668585</v>
       </c>
       <c r="R73" t="n">
-        <v>6696512</v>
+        <v>6696613</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8243,6 +8261,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8269,7 +8292,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120208855</v>
+        <v>120208859</v>
       </c>
       <c r="B74" t="n">
         <v>100194</v>
@@ -8309,10 +8332,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>668380</v>
+        <v>668581</v>
       </c>
       <c r="R74" t="n">
-        <v>6696528</v>
+        <v>6696848</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8371,10 +8394,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120208711</v>
+        <v>120208863</v>
       </c>
       <c r="B75" t="n">
-        <v>95478</v>
+        <v>100194</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8383,25 +8406,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8411,10 +8434,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>668345</v>
+        <v>668568</v>
       </c>
       <c r="R75" t="n">
-        <v>6696598</v>
+        <v>6696542</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8473,10 +8496,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120208684</v>
+        <v>120208827</v>
       </c>
       <c r="B76" t="n">
-        <v>101097</v>
+        <v>4772</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8489,21 +8512,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221235</v>
+        <v>102306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8513,10 +8536,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>668201</v>
+        <v>668457</v>
       </c>
       <c r="R76" t="n">
-        <v>6696519</v>
+        <v>6696523</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8575,10 +8598,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120208778</v>
+        <v>120208716</v>
       </c>
       <c r="B77" t="n">
-        <v>97908</v>
+        <v>95478</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8587,25 +8610,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8615,10 +8638,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>668191</v>
+        <v>668439</v>
       </c>
       <c r="R77" t="n">
-        <v>6696527</v>
+        <v>6696517</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8677,10 +8700,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120208721</v>
+        <v>120208718</v>
       </c>
       <c r="B78" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8693,21 +8716,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8717,10 +8740,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>668589</v>
+        <v>668450</v>
       </c>
       <c r="R78" t="n">
-        <v>6696866</v>
+        <v>6696589</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8779,10 +8802,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120208707</v>
+        <v>120208740</v>
       </c>
       <c r="B79" t="n">
-        <v>95478</v>
+        <v>57473</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8795,34 +8818,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>668394</v>
+        <v>668357</v>
       </c>
       <c r="R79" t="n">
-        <v>6696553</v>
+        <v>6696585</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8881,10 +8912,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120208792</v>
+        <v>120208775</v>
       </c>
       <c r="B80" t="n">
-        <v>57326</v>
+        <v>97908</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8893,46 +8924,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100048</v>
+        <v>219798</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>668517</v>
+        <v>668180</v>
       </c>
       <c r="R80" t="n">
-        <v>6696457</v>
+        <v>6696501</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8965,11 +8988,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8996,10 +9014,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120208822</v>
+        <v>120208826</v>
       </c>
       <c r="B81" t="n">
-        <v>57339</v>
+        <v>4772</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9012,42 +9030,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>102977</v>
+        <v>102306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>668585</v>
+        <v>668442</v>
       </c>
       <c r="R81" t="n">
-        <v>6696613</v>
+        <v>6696515</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9080,11 +9090,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9111,10 +9116,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120208785</v>
+        <v>120208739</v>
       </c>
       <c r="B82" t="n">
-        <v>90864</v>
+        <v>103441</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9123,25 +9128,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>222412</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9151,10 +9156,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>668552</v>
+        <v>668166</v>
       </c>
       <c r="R82" t="n">
-        <v>6696684</v>
+        <v>6696498</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9213,10 +9218,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120208814</v>
+        <v>120208785</v>
       </c>
       <c r="B83" t="n">
-        <v>74593</v>
+        <v>90864</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9225,25 +9230,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6426</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9253,10 +9258,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>668296</v>
+        <v>668552</v>
       </c>
       <c r="R83" t="n">
-        <v>6696535</v>
+        <v>6696684</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9315,7 +9320,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120208691</v>
+        <v>120208688</v>
       </c>
       <c r="B84" t="n">
         <v>101097</v>
@@ -9355,10 +9360,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>668509</v>
+        <v>668383</v>
       </c>
       <c r="R84" t="n">
-        <v>6696436</v>
+        <v>6696524</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9417,10 +9422,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120208758</v>
+        <v>120208818</v>
       </c>
       <c r="B85" t="n">
-        <v>57336</v>
+        <v>105032</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9429,43 +9434,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>668240</v>
+        <v>668437</v>
       </c>
       <c r="R85" t="n">
-        <v>6696522</v>
+        <v>6696501</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9498,11 +9498,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9529,10 +9524,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120208852</v>
+        <v>120208743</v>
       </c>
       <c r="B86" t="n">
-        <v>100194</v>
+        <v>57473</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9541,38 +9536,46 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>668230</v>
+        <v>668533</v>
       </c>
       <c r="R86" t="n">
-        <v>6696502</v>
+        <v>6696366</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9631,7 +9634,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120208859</v>
+        <v>120208861</v>
       </c>
       <c r="B87" t="n">
         <v>100194</v>
@@ -9671,10 +9674,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>668581</v>
+        <v>668567</v>
       </c>
       <c r="R87" t="n">
-        <v>6696848</v>
+        <v>6696809</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9733,10 +9736,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120208743</v>
+        <v>120208779</v>
       </c>
       <c r="B88" t="n">
-        <v>57473</v>
+        <v>97908</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9745,46 +9748,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>103021</v>
+        <v>219798</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>668533</v>
+        <v>668212</v>
       </c>
       <c r="R88" t="n">
-        <v>6696366</v>
+        <v>6696497</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9843,10 +9838,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120208725</v>
+        <v>120208777</v>
       </c>
       <c r="B89" t="n">
-        <v>90580</v>
+        <v>97908</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9855,25 +9850,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>219798</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9883,10 +9878,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>668551</v>
+        <v>668188</v>
       </c>
       <c r="R89" t="n">
-        <v>6696304</v>
+        <v>6696531</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9945,10 +9940,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120208708</v>
+        <v>120208799</v>
       </c>
       <c r="B90" t="n">
-        <v>95478</v>
+        <v>57689</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9957,38 +9952,43 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>53</v>
+        <v>103015</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>668376</v>
+        <v>668558</v>
       </c>
       <c r="R90" t="n">
-        <v>6696595</v>
+        <v>6696534</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10047,10 +10047,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120208862</v>
+        <v>120208686</v>
       </c>
       <c r="B91" t="n">
-        <v>100194</v>
+        <v>101097</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10063,21 +10063,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10087,10 +10087,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>668572</v>
+        <v>668242</v>
       </c>
       <c r="R91" t="n">
-        <v>6696573</v>
+        <v>6696541</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10146,6 +10146,561 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>120434321</v>
+      </c>
+      <c r="B92" t="n">
+        <v>94550</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>210</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>668380</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6696576</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>120434323</v>
+      </c>
+      <c r="B93" t="n">
+        <v>74593</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>668320</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6696515</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>120434325</v>
+      </c>
+      <c r="B94" t="n">
+        <v>95478</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>53</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>668456</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6696470</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>120434322</v>
+      </c>
+      <c r="B95" t="n">
+        <v>95478</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>53</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>668377</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6696572</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>120434326</v>
+      </c>
+      <c r="B96" t="n">
+        <v>95478</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>53</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>668475</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6696461</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -3514,10 +3514,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120208709</v>
+        <v>120208736</v>
       </c>
       <c r="B29" t="n">
-        <v>95478</v>
+        <v>56532</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3526,38 +3526,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668362</v>
+        <v>668532</v>
       </c>
       <c r="R29" t="n">
-        <v>6696599</v>
+        <v>6696689</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3590,6 +3595,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3616,10 +3626,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120208736</v>
+        <v>120208813</v>
       </c>
       <c r="B30" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3628,31 +3638,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3661,10 +3675,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668532</v>
+        <v>668575</v>
       </c>
       <c r="R30" t="n">
-        <v>6696689</v>
+        <v>6696701</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3697,11 +3711,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3932,10 +3941,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120208813</v>
+        <v>120208709</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3944,47 +3953,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668575</v>
+        <v>668362</v>
       </c>
       <c r="R33" t="n">
-        <v>6696701</v>
+        <v>6696599</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4464,10 +4464,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120208774</v>
+        <v>120208717</v>
       </c>
       <c r="B38" t="n">
-        <v>97908</v>
+        <v>95478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4476,25 +4476,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668365</v>
+        <v>668468</v>
       </c>
       <c r="R38" t="n">
-        <v>6696575</v>
+        <v>6696587</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,10 +4566,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120208811</v>
+        <v>120208735</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4578,35 +4578,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4615,10 +4615,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668524</v>
+        <v>668518</v>
       </c>
       <c r="R39" t="n">
-        <v>6696416</v>
+        <v>6696678</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4651,6 +4651,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4677,10 +4682,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120208717</v>
+        <v>120208774</v>
       </c>
       <c r="B40" t="n">
-        <v>95478</v>
+        <v>97908</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4689,25 +4694,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4717,10 +4722,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668468</v>
+        <v>668365</v>
       </c>
       <c r="R40" t="n">
-        <v>6696587</v>
+        <v>6696575</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,10 +4784,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120208735</v>
+        <v>120208811</v>
       </c>
       <c r="B41" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4791,35 +4796,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4828,10 +4833,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668518</v>
+        <v>668524</v>
       </c>
       <c r="R41" t="n">
-        <v>6696678</v>
+        <v>6696416</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4864,11 +4869,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -8496,10 +8496,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120208827</v>
+        <v>120208716</v>
       </c>
       <c r="B76" t="n">
-        <v>4772</v>
+        <v>95478</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8508,25 +8508,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8536,10 +8536,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>668457</v>
+        <v>668439</v>
       </c>
       <c r="R76" t="n">
-        <v>6696523</v>
+        <v>6696517</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8598,7 +8598,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120208716</v>
+        <v>120208718</v>
       </c>
       <c r="B77" t="n">
         <v>95478</v>
@@ -8638,10 +8638,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>668439</v>
+        <v>668450</v>
       </c>
       <c r="R77" t="n">
-        <v>6696517</v>
+        <v>6696589</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8700,10 +8700,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120208718</v>
+        <v>120208827</v>
       </c>
       <c r="B78" t="n">
-        <v>95478</v>
+        <v>4772</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8712,25 +8712,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8740,10 +8740,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>668450</v>
+        <v>668457</v>
       </c>
       <c r="R78" t="n">
-        <v>6696589</v>
+        <v>6696523</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9838,10 +9838,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120208777</v>
+        <v>120208799</v>
       </c>
       <c r="B89" t="n">
-        <v>97908</v>
+        <v>57689</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9854,34 +9854,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219798</v>
+        <v>103015</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>668188</v>
+        <v>668558</v>
       </c>
       <c r="R89" t="n">
-        <v>6696531</v>
+        <v>6696534</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9940,10 +9945,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120208799</v>
+        <v>120208777</v>
       </c>
       <c r="B90" t="n">
-        <v>57689</v>
+        <v>97908</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9956,39 +9961,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103015</v>
+        <v>219798</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>668558</v>
+        <v>668188</v>
       </c>
       <c r="R90" t="n">
-        <v>6696534</v>
+        <v>6696531</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120208707</v>
+        <v>120208719</v>
       </c>
       <c r="B2" t="n">
         <v>95478</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668394</v>
+        <v>668514</v>
       </c>
       <c r="R2" t="n">
-        <v>6696553</v>
+        <v>6696439</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120208722</v>
+        <v>120208827</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>4772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>102306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668552</v>
+        <v>668457</v>
       </c>
       <c r="R3" t="n">
-        <v>6696684</v>
+        <v>6696523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120208856</v>
+        <v>120208740</v>
       </c>
       <c r="B4" t="n">
-        <v>100194</v>
+        <v>57473</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668382</v>
+        <v>668357</v>
       </c>
       <c r="R4" t="n">
-        <v>6696524</v>
+        <v>6696585</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120208858</v>
+        <v>120208798</v>
       </c>
       <c r="B5" t="n">
-        <v>100194</v>
+        <v>57689</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +1005,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668564</v>
+        <v>668342</v>
       </c>
       <c r="R5" t="n">
-        <v>6696816</v>
+        <v>6696603</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120208857</v>
+        <v>120208800</v>
       </c>
       <c r="B6" t="n">
-        <v>100194</v>
+        <v>57689</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1112,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668438</v>
+        <v>668525</v>
       </c>
       <c r="R6" t="n">
-        <v>6696512</v>
+        <v>6696405</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120208683</v>
+        <v>120208776</v>
       </c>
       <c r="B7" t="n">
-        <v>101097</v>
+        <v>97908</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1223,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668188</v>
+        <v>668186</v>
       </c>
       <c r="R7" t="n">
-        <v>6696531</v>
+        <v>6696508</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120208724</v>
+        <v>120208777</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>97908</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1321,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668608</v>
+        <v>668188</v>
       </c>
       <c r="R8" t="n">
-        <v>6696611</v>
+        <v>6696531</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120208759</v>
+        <v>120208813</v>
       </c>
       <c r="B9" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,31 +1423,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1434,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668572</v>
+        <v>668575</v>
       </c>
       <c r="R9" t="n">
-        <v>6696839</v>
+        <v>6696701</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1470,11 +1496,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120208823</v>
+        <v>120208857</v>
       </c>
       <c r="B10" t="n">
-        <v>57339</v>
+        <v>100194</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,42 +1538,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102977</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668565</v>
+        <v>668438</v>
       </c>
       <c r="R10" t="n">
-        <v>6696520</v>
+        <v>6696512</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,11 +1598,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1616,10 +1624,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120208815</v>
+        <v>120208741</v>
       </c>
       <c r="B11" t="n">
-        <v>74593</v>
+        <v>57473</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1628,38 +1636,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668311</v>
+        <v>668483</v>
       </c>
       <c r="R11" t="n">
-        <v>6696520</v>
+        <v>6696590</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,10 +1734,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120208814</v>
+        <v>120208850</v>
       </c>
       <c r="B12" t="n">
-        <v>74593</v>
+        <v>100194</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1734,21 +1750,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1758,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668296</v>
+        <v>668179</v>
       </c>
       <c r="R12" t="n">
-        <v>6696535</v>
+        <v>6696528</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120208790</v>
+        <v>120208830</v>
       </c>
       <c r="B13" t="n">
-        <v>57326</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1836,42 +1852,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100048</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668550</v>
+        <v>668442</v>
       </c>
       <c r="R13" t="n">
-        <v>6696605</v>
+        <v>6696514</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1906,11 +1914,6 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1919,6 +1922,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1935,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120208798</v>
+        <v>120208706</v>
       </c>
       <c r="B14" t="n">
-        <v>57689</v>
+        <v>95478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1947,43 +1965,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668342</v>
+        <v>668408</v>
       </c>
       <c r="R14" t="n">
-        <v>6696603</v>
+        <v>6696562</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2042,10 +2055,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120208692</v>
+        <v>120208826</v>
       </c>
       <c r="B15" t="n">
-        <v>101097</v>
+        <v>4772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2058,21 +2071,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221235</v>
+        <v>102306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2082,10 +2095,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668538</v>
+        <v>668442</v>
       </c>
       <c r="R15" t="n">
-        <v>6696322</v>
+        <v>6696515</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2144,10 +2157,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120208712</v>
+        <v>120208849</v>
       </c>
       <c r="B16" t="n">
-        <v>95478</v>
+        <v>100194</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2156,25 +2169,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2184,10 +2197,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668301</v>
+        <v>668362</v>
       </c>
       <c r="R16" t="n">
-        <v>6696522</v>
+        <v>6696583</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2246,10 +2259,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120208816</v>
+        <v>120208779</v>
       </c>
       <c r="B17" t="n">
-        <v>56524</v>
+        <v>97908</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2258,25 +2271,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>219798</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2286,10 +2299,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668248</v>
+        <v>668212</v>
       </c>
       <c r="R17" t="n">
-        <v>6696628</v>
+        <v>6696497</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,11 +2335,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>flög upp från marken</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2353,7 +2361,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120208684</v>
+        <v>120208688</v>
       </c>
       <c r="B18" t="n">
         <v>101097</v>
@@ -2393,10 +2401,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668201</v>
+        <v>668383</v>
       </c>
       <c r="R18" t="n">
-        <v>6696519</v>
+        <v>6696524</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,10 +2463,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120208719</v>
+        <v>120208853</v>
       </c>
       <c r="B19" t="n">
-        <v>95478</v>
+        <v>100194</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2467,25 +2475,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2495,10 +2503,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668514</v>
+        <v>668241</v>
       </c>
       <c r="R19" t="n">
-        <v>6696439</v>
+        <v>6696541</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,10 +2565,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120208758</v>
+        <v>120208703</v>
       </c>
       <c r="B20" t="n">
-        <v>57336</v>
+        <v>95478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2573,39 +2581,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668240</v>
+        <v>668451</v>
       </c>
       <c r="R20" t="n">
-        <v>6696522</v>
+        <v>6696602</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2640,11 +2643,6 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2653,6 +2651,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2669,10 +2682,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120208744</v>
+        <v>120208713</v>
       </c>
       <c r="B21" t="n">
-        <v>57473</v>
+        <v>95478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2685,39 +2698,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668602</v>
+        <v>668379</v>
       </c>
       <c r="R21" t="n">
-        <v>6696625</v>
+        <v>6696528</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2776,10 +2784,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120208784</v>
+        <v>120208686</v>
       </c>
       <c r="B22" t="n">
-        <v>91023</v>
+        <v>101097</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2788,25 +2796,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>221235</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2816,10 +2824,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668273</v>
+        <v>668242</v>
       </c>
       <c r="R22" t="n">
-        <v>6696531</v>
+        <v>6696541</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2878,10 +2886,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120208725</v>
+        <v>120208739</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>103441</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2890,25 +2898,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>222412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2918,10 +2926,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668551</v>
+        <v>668166</v>
       </c>
       <c r="R23" t="n">
-        <v>6696304</v>
+        <v>6696498</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,10 +2988,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120208830</v>
+        <v>120208717</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>95478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2996,21 +3004,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3020,10 +3028,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668442</v>
+        <v>668468</v>
       </c>
       <c r="R24" t="n">
-        <v>6696514</v>
+        <v>6696587</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3066,21 +3074,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3097,10 +3090,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120208860</v>
+        <v>120208687</v>
       </c>
       <c r="B25" t="n">
-        <v>100194</v>
+        <v>101097</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3113,21 +3106,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3137,10 +3130,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668566</v>
+        <v>668382</v>
       </c>
       <c r="R25" t="n">
-        <v>6696858</v>
+        <v>6696529</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3199,10 +3192,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120208714</v>
+        <v>120208811</v>
       </c>
       <c r="B26" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3211,38 +3204,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668369</v>
+        <v>668524</v>
       </c>
       <c r="R26" t="n">
-        <v>6696540</v>
+        <v>6696416</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3301,10 +3303,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120208721</v>
+        <v>120208785</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3317,21 +3319,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3341,10 +3343,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668589</v>
+        <v>668552</v>
       </c>
       <c r="R27" t="n">
-        <v>6696866</v>
+        <v>6696684</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3403,10 +3405,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120208800</v>
+        <v>120208757</v>
       </c>
       <c r="B28" t="n">
-        <v>57689</v>
+        <v>57336</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3415,20 +3417,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3436,14 +3438,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3452,10 +3450,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668525</v>
+        <v>668572</v>
       </c>
       <c r="R28" t="n">
-        <v>6696405</v>
+        <v>6696525</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3488,6 +3486,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3514,10 +3517,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120208736</v>
+        <v>120208759</v>
       </c>
       <c r="B29" t="n">
-        <v>56532</v>
+        <v>57336</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3526,31 +3529,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3559,10 +3562,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668532</v>
+        <v>668572</v>
       </c>
       <c r="R29" t="n">
-        <v>6696689</v>
+        <v>6696839</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3599,7 +3602,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3626,10 +3629,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120208813</v>
+        <v>120208814</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>74593</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3638,47 +3641,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668575</v>
+        <v>668296</v>
       </c>
       <c r="R30" t="n">
-        <v>6696701</v>
+        <v>6696535</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3737,10 +3731,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120208782</v>
+        <v>120208756</v>
       </c>
       <c r="B31" t="n">
-        <v>97908</v>
+        <v>57336</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3749,38 +3743,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668279</v>
+        <v>668467</v>
       </c>
       <c r="R31" t="n">
-        <v>6696528</v>
+        <v>6696630</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3813,6 +3812,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3839,10 +3843,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120208776</v>
+        <v>120208792</v>
       </c>
       <c r="B32" t="n">
-        <v>97908</v>
+        <v>57326</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3851,38 +3855,46 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219798</v>
+        <v>100048</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668186</v>
+        <v>668517</v>
       </c>
       <c r="R32" t="n">
-        <v>6696508</v>
+        <v>6696457</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3915,6 +3927,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3941,10 +3958,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120208709</v>
+        <v>120208683</v>
       </c>
       <c r="B33" t="n">
-        <v>95478</v>
+        <v>101097</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3953,25 +3970,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3981,10 +3998,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668362</v>
+        <v>668188</v>
       </c>
       <c r="R33" t="n">
-        <v>6696599</v>
+        <v>6696531</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4043,10 +4060,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120208792</v>
+        <v>120208691</v>
       </c>
       <c r="B34" t="n">
-        <v>57326</v>
+        <v>101097</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4055,46 +4072,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100048</v>
+        <v>221235</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668517</v>
+        <v>668509</v>
       </c>
       <c r="R34" t="n">
-        <v>6696457</v>
+        <v>6696436</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4127,11 +4136,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4158,7 +4162,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120208687</v>
+        <v>120208684</v>
       </c>
       <c r="B35" t="n">
         <v>101097</v>
@@ -4198,10 +4202,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668382</v>
+        <v>668201</v>
       </c>
       <c r="R35" t="n">
-        <v>6696529</v>
+        <v>6696519</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4260,10 +4264,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120208819</v>
+        <v>120208710</v>
       </c>
       <c r="B36" t="n">
-        <v>105032</v>
+        <v>95478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4272,25 +4276,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4300,10 +4304,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668579</v>
+        <v>668362</v>
       </c>
       <c r="R36" t="n">
-        <v>6696655</v>
+        <v>6696582</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4362,10 +4366,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120208850</v>
+        <v>120208744</v>
       </c>
       <c r="B37" t="n">
-        <v>100194</v>
+        <v>57473</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4374,38 +4378,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668179</v>
+        <v>668602</v>
       </c>
       <c r="R37" t="n">
-        <v>6696528</v>
+        <v>6696625</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4464,10 +4473,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120208717</v>
+        <v>120208781</v>
       </c>
       <c r="B38" t="n">
-        <v>95478</v>
+        <v>97908</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4476,25 +4485,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4504,10 +4513,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668468</v>
+        <v>668261</v>
       </c>
       <c r="R38" t="n">
-        <v>6696587</v>
+        <v>6696558</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,10 +4575,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120208735</v>
+        <v>120208854</v>
       </c>
       <c r="B39" t="n">
-        <v>56532</v>
+        <v>100194</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4582,43 +4591,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668518</v>
+        <v>668370</v>
       </c>
       <c r="R39" t="n">
-        <v>6696678</v>
+        <v>6696506</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4651,11 +4651,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4682,10 +4677,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120208774</v>
+        <v>120208863</v>
       </c>
       <c r="B40" t="n">
-        <v>97908</v>
+        <v>100194</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4698,21 +4693,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4722,10 +4717,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668365</v>
+        <v>668568</v>
       </c>
       <c r="R40" t="n">
-        <v>6696575</v>
+        <v>6696542</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4784,10 +4779,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120208811</v>
+        <v>120208735</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4796,35 +4791,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4833,10 +4828,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668524</v>
+        <v>668518</v>
       </c>
       <c r="R41" t="n">
-        <v>6696416</v>
+        <v>6696678</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4869,6 +4864,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4895,10 +4895,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120208691</v>
+        <v>120208799</v>
       </c>
       <c r="B42" t="n">
-        <v>101097</v>
+        <v>57689</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4911,34 +4911,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221235</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668509</v>
+        <v>668558</v>
       </c>
       <c r="R42" t="n">
-        <v>6696436</v>
+        <v>6696534</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4997,10 +5002,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120208849</v>
+        <v>120208716</v>
       </c>
       <c r="B43" t="n">
-        <v>100194</v>
+        <v>95478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5009,25 +5014,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5037,10 +5042,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668362</v>
+        <v>668439</v>
       </c>
       <c r="R43" t="n">
-        <v>6696583</v>
+        <v>6696517</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5099,10 +5104,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120208848</v>
+        <v>120208707</v>
       </c>
       <c r="B44" t="n">
-        <v>100194</v>
+        <v>95478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5111,25 +5116,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5139,10 +5144,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668419</v>
+        <v>668394</v>
       </c>
       <c r="R44" t="n">
-        <v>6696535</v>
+        <v>6696553</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5201,10 +5206,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120208706</v>
+        <v>120208758</v>
       </c>
       <c r="B45" t="n">
-        <v>95478</v>
+        <v>57336</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5217,34 +5222,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668408</v>
+        <v>668240</v>
       </c>
       <c r="R45" t="n">
-        <v>6696562</v>
+        <v>6696522</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5277,6 +5287,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5303,10 +5318,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120208708</v>
+        <v>120208737</v>
       </c>
       <c r="B46" t="n">
-        <v>95478</v>
+        <v>56532</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5315,38 +5330,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668376</v>
+        <v>668566</v>
       </c>
       <c r="R46" t="n">
-        <v>6696595</v>
+        <v>6696455</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5379,6 +5399,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5405,10 +5430,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120208710</v>
+        <v>120208816</v>
       </c>
       <c r="B47" t="n">
-        <v>95478</v>
+        <v>56524</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5421,21 +5446,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53</v>
+        <v>102612</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5445,10 +5470,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>668362</v>
+        <v>668248</v>
       </c>
       <c r="R47" t="n">
-        <v>6696582</v>
+        <v>6696628</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5481,6 +5506,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>flög upp från marken</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5507,10 +5537,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120208704</v>
+        <v>120208774</v>
       </c>
       <c r="B48" t="n">
-        <v>95478</v>
+        <v>97908</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5519,25 +5549,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5547,10 +5577,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668571</v>
+        <v>668365</v>
       </c>
       <c r="R48" t="n">
-        <v>6696816</v>
+        <v>6696575</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5593,21 +5623,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -5624,10 +5639,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120208757</v>
+        <v>120208862</v>
       </c>
       <c r="B49" t="n">
-        <v>57336</v>
+        <v>100194</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5636,33 +5651,28 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
@@ -5672,7 +5682,7 @@
         <v>668572</v>
       </c>
       <c r="R49" t="n">
-        <v>6696525</v>
+        <v>6696573</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5705,11 +5715,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5736,10 +5741,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120208682</v>
+        <v>120208856</v>
       </c>
       <c r="B50" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5752,21 +5757,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5776,10 +5781,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668186</v>
+        <v>668382</v>
       </c>
       <c r="R50" t="n">
-        <v>6696508</v>
+        <v>6696524</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5838,10 +5843,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120208741</v>
+        <v>120208823</v>
       </c>
       <c r="B51" t="n">
-        <v>57473</v>
+        <v>57339</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5850,25 +5855,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5886,10 +5891,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668483</v>
+        <v>668565</v>
       </c>
       <c r="R51" t="n">
-        <v>6696590</v>
+        <v>6696520</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5922,6 +5927,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5948,10 +5958,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120208690</v>
+        <v>120208783</v>
       </c>
       <c r="B52" t="n">
-        <v>101097</v>
+        <v>90351</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5964,21 +5974,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221235</v>
+        <v>3215</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5988,10 +5998,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668564</v>
+        <v>668281</v>
       </c>
       <c r="R52" t="n">
-        <v>6696811</v>
+        <v>6696528</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6050,10 +6060,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120208851</v>
+        <v>120208828</v>
       </c>
       <c r="B53" t="n">
-        <v>100194</v>
+        <v>4772</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6066,21 +6076,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>102306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6090,10 +6100,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668213</v>
+        <v>668595</v>
       </c>
       <c r="R53" t="n">
-        <v>6696494</v>
+        <v>6696467</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6152,10 +6162,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120208783</v>
+        <v>120208778</v>
       </c>
       <c r="B54" t="n">
-        <v>90351</v>
+        <v>97908</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6168,21 +6178,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3215</v>
+        <v>219798</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6192,10 +6202,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668281</v>
+        <v>668191</v>
       </c>
       <c r="R54" t="n">
-        <v>6696528</v>
+        <v>6696527</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6254,10 +6264,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120208713</v>
+        <v>120208784</v>
       </c>
       <c r="B55" t="n">
-        <v>95478</v>
+        <v>91023</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6266,25 +6276,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>53</v>
+        <v>1209</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6294,10 +6304,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668379</v>
+        <v>668273</v>
       </c>
       <c r="R55" t="n">
-        <v>6696528</v>
+        <v>6696531</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6356,7 +6366,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120208711</v>
+        <v>120208712</v>
       </c>
       <c r="B56" t="n">
         <v>95478</v>
@@ -6396,10 +6406,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668345</v>
+        <v>668301</v>
       </c>
       <c r="R56" t="n">
-        <v>6696598</v>
+        <v>6696522</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6458,10 +6468,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120208756</v>
+        <v>120208718</v>
       </c>
       <c r="B57" t="n">
-        <v>57336</v>
+        <v>95478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6474,39 +6484,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668467</v>
+        <v>668450</v>
       </c>
       <c r="R57" t="n">
-        <v>6696630</v>
+        <v>6696589</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6539,11 +6544,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6570,10 +6570,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120208862</v>
+        <v>120208708</v>
       </c>
       <c r="B58" t="n">
-        <v>100194</v>
+        <v>95478</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6582,25 +6582,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668572</v>
+        <v>668376</v>
       </c>
       <c r="R58" t="n">
-        <v>6696573</v>
+        <v>6696595</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6672,7 +6672,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120208854</v>
+        <v>120208861</v>
       </c>
       <c r="B59" t="n">
         <v>100194</v>
@@ -6712,10 +6712,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668370</v>
+        <v>668567</v>
       </c>
       <c r="R59" t="n">
-        <v>6696506</v>
+        <v>6696809</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6774,7 +6774,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120208864</v>
+        <v>120208848</v>
       </c>
       <c r="B60" t="n">
         <v>100194</v>
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>668527</v>
+        <v>668419</v>
       </c>
       <c r="R60" t="n">
-        <v>6696351</v>
+        <v>6696535</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6876,10 +6876,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120208812</v>
+        <v>120208705</v>
       </c>
       <c r="B61" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6888,47 +6888,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>668568</v>
+        <v>668521</v>
       </c>
       <c r="R61" t="n">
-        <v>6696851</v>
+        <v>6696330</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6971,6 +6962,21 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -6987,10 +6993,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120208705</v>
+        <v>120208721</v>
       </c>
       <c r="B62" t="n">
-        <v>95478</v>
+        <v>90580</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7003,21 +7009,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7027,10 +7033,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668521</v>
+        <v>668589</v>
       </c>
       <c r="R62" t="n">
-        <v>6696330</v>
+        <v>6696866</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7073,21 +7079,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7104,10 +7095,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120208791</v>
+        <v>120208782</v>
       </c>
       <c r="B63" t="n">
-        <v>57326</v>
+        <v>97908</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7116,46 +7107,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100048</v>
+        <v>219798</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668520</v>
+        <v>668279</v>
       </c>
       <c r="R63" t="n">
-        <v>6696377</v>
+        <v>6696528</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7188,11 +7171,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7219,10 +7197,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120208737</v>
+        <v>120208860</v>
       </c>
       <c r="B64" t="n">
-        <v>56532</v>
+        <v>100194</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7235,29 +7213,24 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
@@ -7267,7 +7240,7 @@
         <v>668566</v>
       </c>
       <c r="R64" t="n">
-        <v>6696455</v>
+        <v>6696858</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7300,11 +7273,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7331,10 +7299,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120208828</v>
+        <v>120208743</v>
       </c>
       <c r="B65" t="n">
-        <v>4772</v>
+        <v>57473</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7343,38 +7311,46 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668595</v>
+        <v>668533</v>
       </c>
       <c r="R65" t="n">
-        <v>6696467</v>
+        <v>6696366</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7433,10 +7409,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120208720</v>
+        <v>120208725</v>
       </c>
       <c r="B66" t="n">
-        <v>90545</v>
+        <v>90580</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7445,25 +7421,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7473,10 +7449,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668407</v>
+        <v>668551</v>
       </c>
       <c r="R66" t="n">
-        <v>6696520</v>
+        <v>6696304</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7519,21 +7495,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -7550,7 +7511,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120208852</v>
+        <v>120208858</v>
       </c>
       <c r="B67" t="n">
         <v>100194</v>
@@ -7590,10 +7551,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>668230</v>
+        <v>668564</v>
       </c>
       <c r="R67" t="n">
-        <v>6696502</v>
+        <v>6696816</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7652,10 +7613,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120208855</v>
+        <v>120208818</v>
       </c>
       <c r="B68" t="n">
-        <v>100194</v>
+        <v>105032</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7668,21 +7629,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7692,10 +7653,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>668380</v>
+        <v>668437</v>
       </c>
       <c r="R68" t="n">
-        <v>6696528</v>
+        <v>6696501</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7754,10 +7715,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120208853</v>
+        <v>120208775</v>
       </c>
       <c r="B69" t="n">
-        <v>100194</v>
+        <v>97908</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7770,21 +7731,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7794,10 +7755,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>668241</v>
+        <v>668180</v>
       </c>
       <c r="R69" t="n">
-        <v>6696541</v>
+        <v>6696501</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7856,10 +7817,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120208781</v>
+        <v>120208815</v>
       </c>
       <c r="B70" t="n">
-        <v>97908</v>
+        <v>74593</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7872,21 +7833,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219798</v>
+        <v>6426</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7896,10 +7857,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>668261</v>
+        <v>668311</v>
       </c>
       <c r="R70" t="n">
-        <v>6696558</v>
+        <v>6696520</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7958,10 +7919,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120208778</v>
+        <v>120208711</v>
       </c>
       <c r="B71" t="n">
-        <v>97908</v>
+        <v>95478</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7970,25 +7931,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7998,10 +7959,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>668191</v>
+        <v>668345</v>
       </c>
       <c r="R71" t="n">
-        <v>6696527</v>
+        <v>6696598</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8060,7 +8021,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120208703</v>
+        <v>120208714</v>
       </c>
       <c r="B72" t="n">
         <v>95478</v>
@@ -8100,10 +8061,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>668451</v>
+        <v>668369</v>
       </c>
       <c r="R72" t="n">
-        <v>6696602</v>
+        <v>6696540</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8146,21 +8107,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8177,10 +8123,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120208822</v>
+        <v>120208790</v>
       </c>
       <c r="B73" t="n">
-        <v>57339</v>
+        <v>57326</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8189,25 +8135,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>102977</v>
+        <v>100048</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8225,10 +8171,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>668585</v>
+        <v>668550</v>
       </c>
       <c r="R73" t="n">
-        <v>6696613</v>
+        <v>6696605</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8292,10 +8238,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120208859</v>
+        <v>120208822</v>
       </c>
       <c r="B74" t="n">
-        <v>100194</v>
+        <v>57339</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8308,34 +8254,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>102977</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>668581</v>
+        <v>668585</v>
       </c>
       <c r="R74" t="n">
-        <v>6696848</v>
+        <v>6696613</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8368,6 +8322,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8394,10 +8353,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120208863</v>
+        <v>120208819</v>
       </c>
       <c r="B75" t="n">
-        <v>100194</v>
+        <v>105032</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8410,21 +8369,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8434,10 +8393,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>668568</v>
+        <v>668579</v>
       </c>
       <c r="R75" t="n">
-        <v>6696542</v>
+        <v>6696655</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8496,10 +8455,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120208716</v>
+        <v>120208692</v>
       </c>
       <c r="B76" t="n">
-        <v>95478</v>
+        <v>101097</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8508,25 +8467,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8536,10 +8495,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>668439</v>
+        <v>668538</v>
       </c>
       <c r="R76" t="n">
-        <v>6696517</v>
+        <v>6696322</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8598,10 +8557,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120208718</v>
+        <v>120208682</v>
       </c>
       <c r="B77" t="n">
-        <v>95478</v>
+        <v>101097</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8610,25 +8569,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8638,10 +8597,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>668450</v>
+        <v>668186</v>
       </c>
       <c r="R77" t="n">
-        <v>6696589</v>
+        <v>6696508</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8700,10 +8659,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120208827</v>
+        <v>120208720</v>
       </c>
       <c r="B78" t="n">
-        <v>4772</v>
+        <v>90545</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8716,21 +8675,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8740,10 +8699,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>668457</v>
+        <v>668407</v>
       </c>
       <c r="R78" t="n">
-        <v>6696523</v>
+        <v>6696520</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8786,6 +8745,21 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -8802,10 +8776,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120208740</v>
+        <v>120208852</v>
       </c>
       <c r="B79" t="n">
-        <v>57473</v>
+        <v>100194</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8814,46 +8788,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>668357</v>
+        <v>668230</v>
       </c>
       <c r="R79" t="n">
-        <v>6696585</v>
+        <v>6696502</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8912,10 +8878,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120208775</v>
+        <v>120208690</v>
       </c>
       <c r="B80" t="n">
-        <v>97908</v>
+        <v>101097</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8928,21 +8894,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8952,10 +8918,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>668180</v>
+        <v>668564</v>
       </c>
       <c r="R80" t="n">
-        <v>6696501</v>
+        <v>6696811</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9014,10 +8980,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120208826</v>
+        <v>120208724</v>
       </c>
       <c r="B81" t="n">
-        <v>4772</v>
+        <v>90580</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9026,25 +8992,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9054,10 +9020,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>668442</v>
+        <v>668608</v>
       </c>
       <c r="R81" t="n">
-        <v>6696515</v>
+        <v>6696611</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9116,10 +9082,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120208739</v>
+        <v>120208791</v>
       </c>
       <c r="B82" t="n">
-        <v>103441</v>
+        <v>57326</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9128,38 +9094,46 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222412</v>
+        <v>100048</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>668166</v>
+        <v>668520</v>
       </c>
       <c r="R82" t="n">
-        <v>6696498</v>
+        <v>6696377</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9192,6 +9166,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9218,10 +9197,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120208785</v>
+        <v>120208851</v>
       </c>
       <c r="B83" t="n">
-        <v>90864</v>
+        <v>100194</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9230,25 +9209,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9258,10 +9237,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>668552</v>
+        <v>668213</v>
       </c>
       <c r="R83" t="n">
-        <v>6696684</v>
+        <v>6696494</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9320,10 +9299,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120208688</v>
+        <v>120208855</v>
       </c>
       <c r="B84" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9336,21 +9315,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9360,10 +9339,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>668383</v>
+        <v>668380</v>
       </c>
       <c r="R84" t="n">
-        <v>6696524</v>
+        <v>6696528</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9422,10 +9401,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120208818</v>
+        <v>120208709</v>
       </c>
       <c r="B85" t="n">
-        <v>105032</v>
+        <v>95478</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9434,25 +9413,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9462,10 +9441,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>668437</v>
+        <v>668362</v>
       </c>
       <c r="R85" t="n">
-        <v>6696501</v>
+        <v>6696599</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9524,10 +9503,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120208743</v>
+        <v>120208722</v>
       </c>
       <c r="B86" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9540,42 +9519,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>668533</v>
+        <v>668552</v>
       </c>
       <c r="R86" t="n">
-        <v>6696366</v>
+        <v>6696684</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9634,10 +9605,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120208861</v>
+        <v>120208704</v>
       </c>
       <c r="B87" t="n">
-        <v>100194</v>
+        <v>95478</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9646,25 +9617,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9674,10 +9645,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>668567</v>
+        <v>668571</v>
       </c>
       <c r="R87" t="n">
-        <v>6696809</v>
+        <v>6696816</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9720,6 +9691,21 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -9736,10 +9722,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120208779</v>
+        <v>120208736</v>
       </c>
       <c r="B88" t="n">
-        <v>97908</v>
+        <v>56532</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9752,34 +9738,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219798</v>
+        <v>100138</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>668212</v>
+        <v>668532</v>
       </c>
       <c r="R88" t="n">
-        <v>6696497</v>
+        <v>6696689</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9812,6 +9803,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9838,10 +9834,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120208799</v>
+        <v>120208812</v>
       </c>
       <c r="B89" t="n">
-        <v>57689</v>
+        <v>97930</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9850,31 +9846,35 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>668558</v>
+        <v>668568</v>
       </c>
       <c r="R89" t="n">
-        <v>6696534</v>
+        <v>6696851</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9945,10 +9945,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120208777</v>
+        <v>120208859</v>
       </c>
       <c r="B90" t="n">
-        <v>97908</v>
+        <v>100194</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9961,21 +9961,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9985,10 +9985,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>668188</v>
+        <v>668581</v>
       </c>
       <c r="R90" t="n">
-        <v>6696531</v>
+        <v>6696848</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10047,10 +10047,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120208686</v>
+        <v>120208864</v>
       </c>
       <c r="B91" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10063,21 +10063,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10087,10 +10087,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>668242</v>
+        <v>668527</v>
       </c>
       <c r="R91" t="n">
-        <v>6696541</v>
+        <v>6696351</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10149,10 +10149,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120434321</v>
+        <v>120434326</v>
       </c>
       <c r="B92" t="n">
-        <v>94550</v>
+        <v>95478</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10161,25 +10161,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10189,10 +10189,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>668380</v>
+        <v>668475</v>
       </c>
       <c r="R92" t="n">
-        <v>6696576</v>
+        <v>6696461</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10235,6 +10235,21 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10368,10 +10383,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120434325</v>
+        <v>120434321</v>
       </c>
       <c r="B94" t="n">
-        <v>95478</v>
+        <v>94550</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10380,25 +10395,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10408,10 +10423,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>668456</v>
+        <v>668380</v>
       </c>
       <c r="R94" t="n">
-        <v>6696470</v>
+        <v>6696576</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10454,21 +10469,6 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -10587,7 +10587,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120434326</v>
+        <v>120434325</v>
       </c>
       <c r="B96" t="n">
         <v>95478</v>
@@ -10627,10 +10627,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>668475</v>
+        <v>668456</v>
       </c>
       <c r="R96" t="n">
-        <v>6696461</v>
+        <v>6696470</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120208719</v>
+        <v>120208830</v>
       </c>
       <c r="B2" t="n">
-        <v>95478</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668514</v>
+        <v>668442</v>
       </c>
       <c r="R2" t="n">
-        <v>6696439</v>
+        <v>6696514</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,6 +761,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120208827</v>
+        <v>120208822</v>
       </c>
       <c r="B3" t="n">
-        <v>4772</v>
+        <v>57339</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +808,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102306</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668457</v>
+        <v>668585</v>
       </c>
       <c r="R3" t="n">
-        <v>6696523</v>
+        <v>6696613</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +876,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120208740</v>
+        <v>120208741</v>
       </c>
       <c r="B4" t="n">
         <v>57473</v>
@@ -927,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668357</v>
+        <v>668483</v>
       </c>
       <c r="R4" t="n">
-        <v>6696585</v>
+        <v>6696590</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120208798</v>
+        <v>120208812</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,31 +1029,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1034,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668342</v>
+        <v>668568</v>
       </c>
       <c r="R5" t="n">
-        <v>6696603</v>
+        <v>6696851</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120208800</v>
+        <v>120208815</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>74593</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,43 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668525</v>
+        <v>668311</v>
       </c>
       <c r="R6" t="n">
-        <v>6696405</v>
+        <v>6696520</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120208776</v>
+        <v>120208784</v>
       </c>
       <c r="B7" t="n">
-        <v>97908</v>
+        <v>91023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1247,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668186</v>
+        <v>668273</v>
       </c>
       <c r="R7" t="n">
-        <v>6696508</v>
+        <v>6696531</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120208777</v>
+        <v>120208851</v>
       </c>
       <c r="B8" t="n">
-        <v>97908</v>
+        <v>100194</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1349,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668188</v>
+        <v>668213</v>
       </c>
       <c r="R8" t="n">
-        <v>6696531</v>
+        <v>6696494</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120208813</v>
+        <v>120208774</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>97908</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,47 +1446,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668575</v>
+        <v>668365</v>
       </c>
       <c r="R9" t="n">
-        <v>6696701</v>
+        <v>6696575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120208857</v>
+        <v>120208779</v>
       </c>
       <c r="B10" t="n">
-        <v>100194</v>
+        <v>97908</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1538,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668438</v>
+        <v>668212</v>
       </c>
       <c r="R10" t="n">
-        <v>6696512</v>
+        <v>6696497</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120208741</v>
+        <v>120208777</v>
       </c>
       <c r="B11" t="n">
-        <v>57473</v>
+        <v>97908</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1636,46 +1650,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668483</v>
+        <v>668188</v>
       </c>
       <c r="R11" t="n">
-        <v>6696590</v>
+        <v>6696531</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1734,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120208850</v>
+        <v>120208782</v>
       </c>
       <c r="B12" t="n">
-        <v>100194</v>
+        <v>97908</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1750,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1774,7 +1780,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668179</v>
+        <v>668279</v>
       </c>
       <c r="R12" t="n">
         <v>6696528</v>
@@ -1836,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120208830</v>
+        <v>120208781</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>97908</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,25 +1854,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1876,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668442</v>
+        <v>668261</v>
       </c>
       <c r="R13" t="n">
-        <v>6696514</v>
+        <v>6696558</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,21 +1928,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1953,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120208706</v>
+        <v>120208853</v>
       </c>
       <c r="B14" t="n">
-        <v>95478</v>
+        <v>100194</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,25 +1956,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1993,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668408</v>
+        <v>668241</v>
       </c>
       <c r="R14" t="n">
-        <v>6696562</v>
+        <v>6696541</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120208826</v>
+        <v>120208827</v>
       </c>
       <c r="B15" t="n">
         <v>4772</v>
@@ -2095,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668442</v>
+        <v>668457</v>
       </c>
       <c r="R15" t="n">
-        <v>6696515</v>
+        <v>6696523</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120208849</v>
+        <v>120208722</v>
       </c>
       <c r="B16" t="n">
-        <v>100194</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,25 +2160,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2197,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668362</v>
+        <v>668552</v>
       </c>
       <c r="R16" t="n">
-        <v>6696583</v>
+        <v>6696684</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2259,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120208779</v>
+        <v>120208716</v>
       </c>
       <c r="B17" t="n">
-        <v>97908</v>
+        <v>95478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,25 +2262,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2299,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668212</v>
+        <v>668439</v>
       </c>
       <c r="R17" t="n">
-        <v>6696497</v>
+        <v>6696517</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2361,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120208688</v>
+        <v>120208705</v>
       </c>
       <c r="B18" t="n">
-        <v>101097</v>
+        <v>95478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2373,25 +2364,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2401,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668383</v>
+        <v>668521</v>
       </c>
       <c r="R18" t="n">
-        <v>6696524</v>
+        <v>6696330</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,6 +2438,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2463,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120208853</v>
+        <v>120208736</v>
       </c>
       <c r="B19" t="n">
-        <v>100194</v>
+        <v>56532</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2479,34 +2485,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668241</v>
+        <v>668532</v>
       </c>
       <c r="R19" t="n">
-        <v>6696541</v>
+        <v>6696689</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2539,6 +2550,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2565,10 +2581,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120208703</v>
+        <v>120208775</v>
       </c>
       <c r="B20" t="n">
-        <v>95478</v>
+        <v>97908</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2577,25 +2593,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2605,10 +2621,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668451</v>
+        <v>668180</v>
       </c>
       <c r="R20" t="n">
-        <v>6696602</v>
+        <v>6696501</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,21 +2667,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2682,10 +2683,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120208713</v>
+        <v>120208686</v>
       </c>
       <c r="B21" t="n">
-        <v>95478</v>
+        <v>101097</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2694,25 +2695,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2722,10 +2723,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668379</v>
+        <v>668242</v>
       </c>
       <c r="R21" t="n">
-        <v>6696528</v>
+        <v>6696541</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2784,10 +2785,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120208686</v>
+        <v>120208710</v>
       </c>
       <c r="B22" t="n">
-        <v>101097</v>
+        <v>95478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2796,25 +2797,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2824,10 +2825,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668242</v>
+        <v>668362</v>
       </c>
       <c r="R22" t="n">
-        <v>6696541</v>
+        <v>6696582</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2886,10 +2887,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120208739</v>
+        <v>120208724</v>
       </c>
       <c r="B23" t="n">
-        <v>103441</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2898,25 +2899,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222412</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2926,10 +2927,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668166</v>
+        <v>668608</v>
       </c>
       <c r="R23" t="n">
-        <v>6696498</v>
+        <v>6696611</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2988,10 +2989,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120208717</v>
+        <v>120208783</v>
       </c>
       <c r="B24" t="n">
-        <v>95478</v>
+        <v>90351</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3000,25 +3001,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3028,10 +3029,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668468</v>
+        <v>668281</v>
       </c>
       <c r="R24" t="n">
-        <v>6696587</v>
+        <v>6696528</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3090,10 +3091,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120208687</v>
+        <v>120208778</v>
       </c>
       <c r="B25" t="n">
-        <v>101097</v>
+        <v>97908</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3106,21 +3107,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3130,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668382</v>
+        <v>668191</v>
       </c>
       <c r="R25" t="n">
-        <v>6696529</v>
+        <v>6696527</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3192,10 +3193,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120208811</v>
+        <v>120208711</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3204,47 +3205,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668524</v>
+        <v>668345</v>
       </c>
       <c r="R26" t="n">
-        <v>6696416</v>
+        <v>6696598</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120208785</v>
+        <v>120208707</v>
       </c>
       <c r="B27" t="n">
-        <v>90864</v>
+        <v>95478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3319,21 +3311,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3343,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668552</v>
+        <v>668394</v>
       </c>
       <c r="R27" t="n">
-        <v>6696684</v>
+        <v>6696553</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3405,10 +3397,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120208757</v>
+        <v>120208719</v>
       </c>
       <c r="B28" t="n">
-        <v>57336</v>
+        <v>95478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3421,39 +3413,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668572</v>
+        <v>668514</v>
       </c>
       <c r="R28" t="n">
-        <v>6696525</v>
+        <v>6696439</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3486,11 +3473,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3517,10 +3499,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120208759</v>
+        <v>120208863</v>
       </c>
       <c r="B29" t="n">
-        <v>57336</v>
+        <v>100194</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3529,43 +3511,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668572</v>
+        <v>668568</v>
       </c>
       <c r="R29" t="n">
-        <v>6696839</v>
+        <v>6696542</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3598,11 +3575,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3629,10 +3601,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120208814</v>
+        <v>120208757</v>
       </c>
       <c r="B30" t="n">
-        <v>74593</v>
+        <v>57336</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3641,38 +3613,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668296</v>
+        <v>668572</v>
       </c>
       <c r="R30" t="n">
-        <v>6696535</v>
+        <v>6696525</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3705,6 +3682,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3731,10 +3713,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120208756</v>
+        <v>120208714</v>
       </c>
       <c r="B31" t="n">
-        <v>57336</v>
+        <v>95478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3747,39 +3729,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668467</v>
+        <v>668369</v>
       </c>
       <c r="R31" t="n">
-        <v>6696630</v>
+        <v>6696540</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3812,11 +3789,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3843,7 +3815,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120208792</v>
+        <v>120208790</v>
       </c>
       <c r="B32" t="n">
         <v>57326</v>
@@ -3891,10 +3863,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668517</v>
+        <v>668550</v>
       </c>
       <c r="R32" t="n">
-        <v>6696457</v>
+        <v>6696605</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3958,10 +3930,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120208683</v>
+        <v>120208811</v>
       </c>
       <c r="B33" t="n">
-        <v>101097</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3970,38 +3942,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668188</v>
+        <v>668524</v>
       </c>
       <c r="R33" t="n">
-        <v>6696531</v>
+        <v>6696416</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4060,10 +4041,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120208691</v>
+        <v>120208856</v>
       </c>
       <c r="B34" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4076,21 +4057,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4100,10 +4081,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668509</v>
+        <v>668382</v>
       </c>
       <c r="R34" t="n">
-        <v>6696436</v>
+        <v>6696524</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4162,7 +4143,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120208684</v>
+        <v>120208688</v>
       </c>
       <c r="B35" t="n">
         <v>101097</v>
@@ -4202,10 +4183,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668201</v>
+        <v>668383</v>
       </c>
       <c r="R35" t="n">
-        <v>6696519</v>
+        <v>6696524</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4264,10 +4245,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120208710</v>
+        <v>120208691</v>
       </c>
       <c r="B36" t="n">
-        <v>95478</v>
+        <v>101097</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4276,25 +4257,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4304,10 +4285,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668362</v>
+        <v>668509</v>
       </c>
       <c r="R36" t="n">
-        <v>6696582</v>
+        <v>6696436</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4366,10 +4347,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120208744</v>
+        <v>120208706</v>
       </c>
       <c r="B37" t="n">
-        <v>57473</v>
+        <v>95478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4382,39 +4363,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668602</v>
+        <v>668408</v>
       </c>
       <c r="R37" t="n">
-        <v>6696625</v>
+        <v>6696562</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4473,10 +4449,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120208781</v>
+        <v>120208816</v>
       </c>
       <c r="B38" t="n">
-        <v>97908</v>
+        <v>56524</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4485,25 +4461,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>219798</v>
+        <v>102612</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4513,10 +4489,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668261</v>
+        <v>668248</v>
       </c>
       <c r="R38" t="n">
-        <v>6696558</v>
+        <v>6696628</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4549,6 +4525,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>flög upp från marken</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4575,10 +4556,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120208854</v>
+        <v>120208718</v>
       </c>
       <c r="B39" t="n">
-        <v>100194</v>
+        <v>95478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4587,25 +4568,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4615,10 +4596,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668370</v>
+        <v>668450</v>
       </c>
       <c r="R39" t="n">
-        <v>6696506</v>
+        <v>6696589</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4677,10 +4658,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120208863</v>
+        <v>120208704</v>
       </c>
       <c r="B40" t="n">
-        <v>100194</v>
+        <v>95478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4689,25 +4670,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4717,10 +4698,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668568</v>
+        <v>668571</v>
       </c>
       <c r="R40" t="n">
-        <v>6696542</v>
+        <v>6696816</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4763,6 +4744,21 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4779,10 +4775,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120208735</v>
+        <v>120208799</v>
       </c>
       <c r="B41" t="n">
-        <v>56532</v>
+        <v>57689</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4795,31 +4791,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4828,10 +4820,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668518</v>
+        <v>668558</v>
       </c>
       <c r="R41" t="n">
-        <v>6696678</v>
+        <v>6696534</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4864,11 +4856,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4895,7 +4882,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120208799</v>
+        <v>120208800</v>
       </c>
       <c r="B42" t="n">
         <v>57689</v>
@@ -4928,10 +4915,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4940,10 +4931,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668558</v>
+        <v>668525</v>
       </c>
       <c r="R42" t="n">
-        <v>6696534</v>
+        <v>6696405</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5002,10 +4993,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120208716</v>
+        <v>120208743</v>
       </c>
       <c r="B43" t="n">
-        <v>95478</v>
+        <v>57473</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5018,34 +5009,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668439</v>
+        <v>668533</v>
       </c>
       <c r="R43" t="n">
-        <v>6696517</v>
+        <v>6696366</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5104,10 +5103,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120208707</v>
+        <v>120208828</v>
       </c>
       <c r="B44" t="n">
-        <v>95478</v>
+        <v>4772</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5116,25 +5115,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5144,10 +5143,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668394</v>
+        <v>668595</v>
       </c>
       <c r="R44" t="n">
-        <v>6696553</v>
+        <v>6696467</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5318,10 +5317,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120208737</v>
+        <v>120208785</v>
       </c>
       <c r="B46" t="n">
-        <v>56532</v>
+        <v>90864</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5330,43 +5329,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668566</v>
+        <v>668552</v>
       </c>
       <c r="R46" t="n">
-        <v>6696455</v>
+        <v>6696684</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5399,11 +5393,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5430,10 +5419,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120208816</v>
+        <v>120208720</v>
       </c>
       <c r="B47" t="n">
-        <v>56524</v>
+        <v>90545</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5442,25 +5431,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5470,10 +5459,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>668248</v>
+        <v>668407</v>
       </c>
       <c r="R47" t="n">
-        <v>6696628</v>
+        <v>6696520</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5508,11 +5497,6 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>flög upp från marken</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5521,6 +5505,21 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5537,10 +5536,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120208774</v>
+        <v>120208798</v>
       </c>
       <c r="B48" t="n">
-        <v>97908</v>
+        <v>57689</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5553,34 +5552,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219798</v>
+        <v>103015</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668365</v>
+        <v>668342</v>
       </c>
       <c r="R48" t="n">
-        <v>6696575</v>
+        <v>6696603</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5639,7 +5643,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120208862</v>
+        <v>120208852</v>
       </c>
       <c r="B49" t="n">
         <v>100194</v>
@@ -5679,10 +5683,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668572</v>
+        <v>668230</v>
       </c>
       <c r="R49" t="n">
-        <v>6696573</v>
+        <v>6696502</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5741,7 +5745,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120208856</v>
+        <v>120208855</v>
       </c>
       <c r="B50" t="n">
         <v>100194</v>
@@ -5781,10 +5785,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668382</v>
+        <v>668380</v>
       </c>
       <c r="R50" t="n">
-        <v>6696524</v>
+        <v>6696528</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5843,10 +5847,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120208823</v>
+        <v>120208692</v>
       </c>
       <c r="B51" t="n">
-        <v>57339</v>
+        <v>101097</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5859,42 +5863,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102977</v>
+        <v>221235</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668565</v>
+        <v>668538</v>
       </c>
       <c r="R51" t="n">
-        <v>6696520</v>
+        <v>6696322</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5927,11 +5923,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5958,10 +5949,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120208783</v>
+        <v>120208713</v>
       </c>
       <c r="B52" t="n">
-        <v>90351</v>
+        <v>95478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5970,25 +5961,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3215</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5998,7 +5989,7 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668281</v>
+        <v>668379</v>
       </c>
       <c r="R52" t="n">
         <v>6696528</v>
@@ -6060,10 +6051,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120208828</v>
+        <v>120208709</v>
       </c>
       <c r="B53" t="n">
-        <v>4772</v>
+        <v>95478</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6072,25 +6063,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6100,10 +6091,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668595</v>
+        <v>668362</v>
       </c>
       <c r="R53" t="n">
-        <v>6696467</v>
+        <v>6696599</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6162,10 +6153,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120208778</v>
+        <v>120208813</v>
       </c>
       <c r="B54" t="n">
-        <v>97908</v>
+        <v>97930</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6174,38 +6165,47 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219798</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668191</v>
+        <v>668575</v>
       </c>
       <c r="R54" t="n">
-        <v>6696527</v>
+        <v>6696701</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6264,10 +6264,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120208784</v>
+        <v>120208857</v>
       </c>
       <c r="B55" t="n">
-        <v>91023</v>
+        <v>100194</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6276,25 +6276,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668273</v>
+        <v>668438</v>
       </c>
       <c r="R55" t="n">
-        <v>6696531</v>
+        <v>6696512</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120208712</v>
+        <v>120208792</v>
       </c>
       <c r="B56" t="n">
-        <v>95478</v>
+        <v>57326</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6382,34 +6382,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>100048</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668301</v>
+        <v>668517</v>
       </c>
       <c r="R56" t="n">
-        <v>6696522</v>
+        <v>6696457</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6442,6 +6450,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6468,10 +6481,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120208718</v>
+        <v>120208848</v>
       </c>
       <c r="B57" t="n">
-        <v>95478</v>
+        <v>100194</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6480,25 +6493,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6508,10 +6521,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668450</v>
+        <v>668419</v>
       </c>
       <c r="R57" t="n">
-        <v>6696589</v>
+        <v>6696535</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6570,10 +6583,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120208708</v>
+        <v>120208823</v>
       </c>
       <c r="B58" t="n">
-        <v>95478</v>
+        <v>57339</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6582,38 +6595,46 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>102977</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668376</v>
+        <v>668565</v>
       </c>
       <c r="R58" t="n">
-        <v>6696595</v>
+        <v>6696520</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6646,6 +6667,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6672,10 +6698,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120208861</v>
+        <v>120208818</v>
       </c>
       <c r="B59" t="n">
-        <v>100194</v>
+        <v>105032</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6688,21 +6714,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6712,10 +6738,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668567</v>
+        <v>668437</v>
       </c>
       <c r="R59" t="n">
-        <v>6696809</v>
+        <v>6696501</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6774,10 +6800,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120208848</v>
+        <v>120208739</v>
       </c>
       <c r="B60" t="n">
-        <v>100194</v>
+        <v>103441</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6790,21 +6816,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6814,10 +6840,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>668419</v>
+        <v>668166</v>
       </c>
       <c r="R60" t="n">
-        <v>6696535</v>
+        <v>6696498</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6876,10 +6902,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120208705</v>
+        <v>120208826</v>
       </c>
       <c r="B61" t="n">
-        <v>95478</v>
+        <v>4772</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6888,25 +6914,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6916,10 +6942,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>668521</v>
+        <v>668442</v>
       </c>
       <c r="R61" t="n">
-        <v>6696330</v>
+        <v>6696515</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6962,21 +6988,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7095,10 +7106,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120208782</v>
+        <v>120208717</v>
       </c>
       <c r="B63" t="n">
-        <v>97908</v>
+        <v>95478</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7107,25 +7118,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7135,10 +7146,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668279</v>
+        <v>668468</v>
       </c>
       <c r="R63" t="n">
-        <v>6696528</v>
+        <v>6696587</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7197,10 +7208,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120208860</v>
+        <v>120208740</v>
       </c>
       <c r="B64" t="n">
-        <v>100194</v>
+        <v>57473</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7209,38 +7220,46 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668566</v>
+        <v>668357</v>
       </c>
       <c r="R64" t="n">
-        <v>6696858</v>
+        <v>6696585</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7299,10 +7318,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120208743</v>
+        <v>120208859</v>
       </c>
       <c r="B65" t="n">
-        <v>57473</v>
+        <v>100194</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7311,46 +7330,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668533</v>
+        <v>668581</v>
       </c>
       <c r="R65" t="n">
-        <v>6696366</v>
+        <v>6696848</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7409,10 +7420,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120208725</v>
+        <v>120208776</v>
       </c>
       <c r="B66" t="n">
-        <v>90580</v>
+        <v>97908</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7421,25 +7432,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>219798</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7449,10 +7460,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668551</v>
+        <v>668186</v>
       </c>
       <c r="R66" t="n">
-        <v>6696304</v>
+        <v>6696508</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7511,7 +7522,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120208858</v>
+        <v>120208850</v>
       </c>
       <c r="B67" t="n">
         <v>100194</v>
@@ -7551,10 +7562,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>668564</v>
+        <v>668179</v>
       </c>
       <c r="R67" t="n">
-        <v>6696816</v>
+        <v>6696528</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7613,10 +7624,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120208818</v>
+        <v>120208791</v>
       </c>
       <c r="B68" t="n">
-        <v>105032</v>
+        <v>57326</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7625,38 +7636,46 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221144</v>
+        <v>100048</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>668437</v>
+        <v>668520</v>
       </c>
       <c r="R68" t="n">
-        <v>6696501</v>
+        <v>6696377</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7689,6 +7708,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7715,10 +7739,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120208775</v>
+        <v>120208712</v>
       </c>
       <c r="B69" t="n">
-        <v>97908</v>
+        <v>95478</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7727,25 +7751,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7755,10 +7779,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>668180</v>
+        <v>668301</v>
       </c>
       <c r="R69" t="n">
-        <v>6696501</v>
+        <v>6696522</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7817,10 +7841,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120208815</v>
+        <v>120208708</v>
       </c>
       <c r="B70" t="n">
-        <v>74593</v>
+        <v>95478</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7829,25 +7853,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7857,10 +7881,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>668311</v>
+        <v>668376</v>
       </c>
       <c r="R70" t="n">
-        <v>6696520</v>
+        <v>6696595</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7919,10 +7943,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120208711</v>
+        <v>120208819</v>
       </c>
       <c r="B71" t="n">
-        <v>95478</v>
+        <v>105032</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7931,25 +7955,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7959,10 +7983,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>668345</v>
+        <v>668579</v>
       </c>
       <c r="R71" t="n">
-        <v>6696598</v>
+        <v>6696655</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8021,10 +8045,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120208714</v>
+        <v>120208682</v>
       </c>
       <c r="B72" t="n">
-        <v>95478</v>
+        <v>101097</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8033,25 +8057,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8061,10 +8085,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>668369</v>
+        <v>668186</v>
       </c>
       <c r="R72" t="n">
-        <v>6696540</v>
+        <v>6696508</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8123,10 +8147,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120208790</v>
+        <v>120208684</v>
       </c>
       <c r="B73" t="n">
-        <v>57326</v>
+        <v>101097</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8135,46 +8159,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100048</v>
+        <v>221235</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>668550</v>
+        <v>668201</v>
       </c>
       <c r="R73" t="n">
-        <v>6696605</v>
+        <v>6696519</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8207,11 +8223,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8238,10 +8249,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120208822</v>
+        <v>120208683</v>
       </c>
       <c r="B74" t="n">
-        <v>57339</v>
+        <v>101097</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8254,42 +8265,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>102977</v>
+        <v>221235</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>668585</v>
+        <v>668188</v>
       </c>
       <c r="R74" t="n">
-        <v>6696613</v>
+        <v>6696531</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8322,11 +8325,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8353,10 +8351,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120208819</v>
+        <v>120208861</v>
       </c>
       <c r="B75" t="n">
-        <v>105032</v>
+        <v>100194</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8369,21 +8367,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8393,10 +8391,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>668579</v>
+        <v>668567</v>
       </c>
       <c r="R75" t="n">
-        <v>6696655</v>
+        <v>6696809</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8455,10 +8453,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120208692</v>
+        <v>120208860</v>
       </c>
       <c r="B76" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8471,21 +8469,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8495,10 +8493,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>668538</v>
+        <v>668566</v>
       </c>
       <c r="R76" t="n">
-        <v>6696322</v>
+        <v>6696858</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8557,7 +8555,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120208682</v>
+        <v>120208687</v>
       </c>
       <c r="B77" t="n">
         <v>101097</v>
@@ -8597,10 +8595,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>668186</v>
+        <v>668382</v>
       </c>
       <c r="R77" t="n">
-        <v>6696508</v>
+        <v>6696529</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8659,10 +8657,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120208720</v>
+        <v>120208756</v>
       </c>
       <c r="B78" t="n">
-        <v>90545</v>
+        <v>57336</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8671,38 +8669,43 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>668407</v>
+        <v>668467</v>
       </c>
       <c r="R78" t="n">
-        <v>6696520</v>
+        <v>6696630</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8737,6 +8740,11 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8745,21 +8753,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -8776,10 +8769,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120208852</v>
+        <v>120208737</v>
       </c>
       <c r="B79" t="n">
-        <v>100194</v>
+        <v>56532</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8792,34 +8785,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>668230</v>
+        <v>668566</v>
       </c>
       <c r="R79" t="n">
-        <v>6696502</v>
+        <v>6696455</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8852,6 +8850,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8878,10 +8881,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120208690</v>
+        <v>120208849</v>
       </c>
       <c r="B80" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8894,21 +8897,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8918,10 +8921,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>668564</v>
+        <v>668362</v>
       </c>
       <c r="R80" t="n">
-        <v>6696811</v>
+        <v>6696583</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8980,10 +8983,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120208724</v>
+        <v>120208854</v>
       </c>
       <c r="B81" t="n">
-        <v>90580</v>
+        <v>100194</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8992,25 +8995,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9020,10 +9023,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>668608</v>
+        <v>668370</v>
       </c>
       <c r="R81" t="n">
-        <v>6696611</v>
+        <v>6696506</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9082,10 +9085,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120208791</v>
+        <v>120208864</v>
       </c>
       <c r="B82" t="n">
-        <v>57326</v>
+        <v>100194</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9094,46 +9097,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100048</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>668520</v>
+        <v>668527</v>
       </c>
       <c r="R82" t="n">
-        <v>6696377</v>
+        <v>6696351</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9166,11 +9161,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9197,10 +9187,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120208851</v>
+        <v>120208725</v>
       </c>
       <c r="B83" t="n">
-        <v>100194</v>
+        <v>90580</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9209,25 +9199,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9237,10 +9227,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>668213</v>
+        <v>668551</v>
       </c>
       <c r="R83" t="n">
-        <v>6696494</v>
+        <v>6696304</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9299,10 +9289,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120208855</v>
+        <v>120208759</v>
       </c>
       <c r="B84" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9311,38 +9301,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>668380</v>
+        <v>668572</v>
       </c>
       <c r="R84" t="n">
-        <v>6696528</v>
+        <v>6696839</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9375,6 +9370,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9401,10 +9401,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120208709</v>
+        <v>120208690</v>
       </c>
       <c r="B85" t="n">
-        <v>95478</v>
+        <v>101097</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9413,25 +9413,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9441,10 +9441,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>668362</v>
+        <v>668564</v>
       </c>
       <c r="R85" t="n">
-        <v>6696599</v>
+        <v>6696811</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9503,10 +9503,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120208722</v>
+        <v>120208744</v>
       </c>
       <c r="B86" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9519,34 +9519,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>668552</v>
+        <v>668602</v>
       </c>
       <c r="R86" t="n">
-        <v>6696684</v>
+        <v>6696625</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9605,7 +9610,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120208704</v>
+        <v>120208703</v>
       </c>
       <c r="B87" t="n">
         <v>95478</v>
@@ -9645,10 +9650,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>668571</v>
+        <v>668451</v>
       </c>
       <c r="R87" t="n">
-        <v>6696816</v>
+        <v>6696602</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9722,10 +9727,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120208736</v>
+        <v>120208814</v>
       </c>
       <c r="B88" t="n">
-        <v>56532</v>
+        <v>74593</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9738,39 +9743,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>668532</v>
+        <v>668296</v>
       </c>
       <c r="R88" t="n">
-        <v>6696689</v>
+        <v>6696535</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9803,11 +9803,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9834,10 +9829,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120208812</v>
+        <v>120208735</v>
       </c>
       <c r="B89" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9846,35 +9841,35 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -9883,10 +9878,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>668568</v>
+        <v>668518</v>
       </c>
       <c r="R89" t="n">
-        <v>6696851</v>
+        <v>6696678</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9919,6 +9914,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9945,7 +9945,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120208859</v>
+        <v>120208862</v>
       </c>
       <c r="B90" t="n">
         <v>100194</v>
@@ -9985,10 +9985,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>668581</v>
+        <v>668572</v>
       </c>
       <c r="R90" t="n">
-        <v>6696848</v>
+        <v>6696573</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10047,7 +10047,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120208864</v>
+        <v>120208858</v>
       </c>
       <c r="B91" t="n">
         <v>100194</v>
@@ -10087,10 +10087,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>668527</v>
+        <v>668564</v>
       </c>
       <c r="R91" t="n">
-        <v>6696351</v>
+        <v>6696816</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10149,10 +10149,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120434326</v>
+        <v>120434323</v>
       </c>
       <c r="B92" t="n">
-        <v>95478</v>
+        <v>74593</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10161,25 +10161,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10189,10 +10189,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>668475</v>
+        <v>668320</v>
       </c>
       <c r="R92" t="n">
-        <v>6696461</v>
+        <v>6696515</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10238,17 +10238,17 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK92" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10266,10 +10266,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120434323</v>
+        <v>120434326</v>
       </c>
       <c r="B93" t="n">
-        <v>74593</v>
+        <v>95478</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10278,25 +10278,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10306,10 +10306,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>668320</v>
+        <v>668475</v>
       </c>
       <c r="R93" t="n">
-        <v>6696515</v>
+        <v>6696461</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10355,17 +10355,17 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -10383,10 +10383,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120434321</v>
+        <v>120434325</v>
       </c>
       <c r="B94" t="n">
-        <v>94550</v>
+        <v>95478</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10395,25 +10395,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10423,10 +10423,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>668380</v>
+        <v>668456</v>
       </c>
       <c r="R94" t="n">
-        <v>6696576</v>
+        <v>6696470</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10469,6 +10469,21 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -10485,10 +10500,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120434322</v>
+        <v>120434321</v>
       </c>
       <c r="B95" t="n">
-        <v>95478</v>
+        <v>94550</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10497,25 +10512,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>53</v>
+        <v>210</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10525,10 +10540,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>668377</v>
+        <v>668380</v>
       </c>
       <c r="R95" t="n">
-        <v>6696572</v>
+        <v>6696576</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10587,7 +10602,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120434325</v>
+        <v>120434322</v>
       </c>
       <c r="B96" t="n">
         <v>95478</v>
@@ -10627,10 +10642,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>668456</v>
+        <v>668377</v>
       </c>
       <c r="R96" t="n">
-        <v>6696470</v>
+        <v>6696572</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10673,21 +10688,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120208822</v>
+        <v>120208741</v>
       </c>
       <c r="B3" t="n">
-        <v>57339</v>
+        <v>57473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668585</v>
+        <v>668483</v>
       </c>
       <c r="R3" t="n">
-        <v>6696613</v>
+        <v>6696590</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,11 +876,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120208741</v>
+        <v>120208822</v>
       </c>
       <c r="B4" t="n">
-        <v>57473</v>
+        <v>57339</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +914,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668483</v>
+        <v>668585</v>
       </c>
       <c r="R4" t="n">
-        <v>6696590</v>
+        <v>6696613</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,6 +986,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1638,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120208777</v>
+        <v>120208722</v>
       </c>
       <c r="B11" t="n">
-        <v>97908</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,25 +1650,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668188</v>
+        <v>668552</v>
       </c>
       <c r="R11" t="n">
-        <v>6696531</v>
+        <v>6696684</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120208782</v>
+        <v>120208716</v>
       </c>
       <c r="B12" t="n">
-        <v>97908</v>
+        <v>95478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668279</v>
+        <v>668439</v>
       </c>
       <c r="R12" t="n">
-        <v>6696528</v>
+        <v>6696517</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120208781</v>
+        <v>120208827</v>
       </c>
       <c r="B13" t="n">
-        <v>97908</v>
+        <v>4772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1858,21 +1858,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>102306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668261</v>
+        <v>668457</v>
       </c>
       <c r="R13" t="n">
-        <v>6696558</v>
+        <v>6696523</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120208853</v>
+        <v>120208777</v>
       </c>
       <c r="B14" t="n">
-        <v>100194</v>
+        <v>97908</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668241</v>
+        <v>668188</v>
       </c>
       <c r="R14" t="n">
-        <v>6696541</v>
+        <v>6696531</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120208827</v>
+        <v>120208782</v>
       </c>
       <c r="B15" t="n">
-        <v>4772</v>
+        <v>97908</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102306</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668457</v>
+        <v>668279</v>
       </c>
       <c r="R15" t="n">
-        <v>6696523</v>
+        <v>6696528</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120208722</v>
+        <v>120208781</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>97908</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2160,25 +2160,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>219798</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668552</v>
+        <v>668261</v>
       </c>
       <c r="R16" t="n">
-        <v>6696684</v>
+        <v>6696558</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2250,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120208716</v>
+        <v>120208853</v>
       </c>
       <c r="B17" t="n">
-        <v>95478</v>
+        <v>100194</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2262,25 +2262,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2290,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668439</v>
+        <v>668241</v>
       </c>
       <c r="R17" t="n">
-        <v>6696517</v>
+        <v>6696541</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3091,10 +3091,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120208778</v>
+        <v>120208711</v>
       </c>
       <c r="B25" t="n">
-        <v>97908</v>
+        <v>95478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3103,25 +3103,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668191</v>
+        <v>668345</v>
       </c>
       <c r="R25" t="n">
-        <v>6696527</v>
+        <v>6696598</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3193,7 +3193,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120208711</v>
+        <v>120208707</v>
       </c>
       <c r="B26" t="n">
         <v>95478</v>
@@ -3233,10 +3233,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668345</v>
+        <v>668394</v>
       </c>
       <c r="R26" t="n">
-        <v>6696598</v>
+        <v>6696553</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,7 +3295,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120208707</v>
+        <v>120208719</v>
       </c>
       <c r="B27" t="n">
         <v>95478</v>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668394</v>
+        <v>668514</v>
       </c>
       <c r="R27" t="n">
-        <v>6696553</v>
+        <v>6696439</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3397,10 +3397,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120208719</v>
+        <v>120208778</v>
       </c>
       <c r="B28" t="n">
-        <v>95478</v>
+        <v>97908</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3409,25 +3409,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668514</v>
+        <v>668191</v>
       </c>
       <c r="R28" t="n">
-        <v>6696439</v>
+        <v>6696527</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -6153,10 +6153,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120208813</v>
+        <v>120208848</v>
       </c>
       <c r="B54" t="n">
-        <v>97930</v>
+        <v>100194</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6165,47 +6165,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668575</v>
+        <v>668419</v>
       </c>
       <c r="R54" t="n">
-        <v>6696701</v>
+        <v>6696535</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6264,10 +6255,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120208857</v>
+        <v>120208792</v>
       </c>
       <c r="B55" t="n">
-        <v>100194</v>
+        <v>57326</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6276,38 +6267,46 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>100048</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668438</v>
+        <v>668517</v>
       </c>
       <c r="R55" t="n">
-        <v>6696512</v>
+        <v>6696457</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6340,6 +6339,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6366,10 +6370,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120208792</v>
+        <v>120208813</v>
       </c>
       <c r="B56" t="n">
-        <v>57326</v>
+        <v>97930</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6378,46 +6382,47 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668517</v>
+        <v>668575</v>
       </c>
       <c r="R56" t="n">
-        <v>6696457</v>
+        <v>6696701</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6450,11 +6455,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6481,7 +6481,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120208848</v>
+        <v>120208857</v>
       </c>
       <c r="B57" t="n">
         <v>100194</v>
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668419</v>
+        <v>668438</v>
       </c>
       <c r="R57" t="n">
-        <v>6696535</v>
+        <v>6696512</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7004,10 +7004,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120208721</v>
+        <v>120208740</v>
       </c>
       <c r="B62" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7020,34 +7020,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668589</v>
+        <v>668357</v>
       </c>
       <c r="R62" t="n">
-        <v>6696866</v>
+        <v>6696585</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7106,10 +7114,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120208717</v>
+        <v>120208721</v>
       </c>
       <c r="B63" t="n">
-        <v>95478</v>
+        <v>90580</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7122,21 +7130,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7146,10 +7154,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668468</v>
+        <v>668589</v>
       </c>
       <c r="R63" t="n">
-        <v>6696587</v>
+        <v>6696866</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7208,10 +7216,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120208740</v>
+        <v>120208717</v>
       </c>
       <c r="B64" t="n">
-        <v>57473</v>
+        <v>95478</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7224,42 +7232,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668357</v>
+        <v>668468</v>
       </c>
       <c r="R64" t="n">
-        <v>6696585</v>
+        <v>6696587</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120208830</v>
+        <v>120208777</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>97908</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668442</v>
+        <v>668188</v>
       </c>
       <c r="R2" t="n">
-        <v>6696514</v>
+        <v>6696531</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,21 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120208741</v>
+        <v>120208716</v>
       </c>
       <c r="B3" t="n">
-        <v>57473</v>
+        <v>95478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668483</v>
+        <v>668439</v>
       </c>
       <c r="R3" t="n">
-        <v>6696590</v>
+        <v>6696517</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120208822</v>
+        <v>120208692</v>
       </c>
       <c r="B4" t="n">
-        <v>57339</v>
+        <v>101097</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,42 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102977</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668585</v>
+        <v>668538</v>
       </c>
       <c r="R4" t="n">
-        <v>6696613</v>
+        <v>6696322</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120208812</v>
+        <v>120208785</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,47 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668568</v>
+        <v>668552</v>
       </c>
       <c r="R5" t="n">
-        <v>6696851</v>
+        <v>6696684</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120208815</v>
+        <v>120208705</v>
       </c>
       <c r="B6" t="n">
-        <v>74593</v>
+        <v>95478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668311</v>
+        <v>668521</v>
       </c>
       <c r="R6" t="n">
-        <v>6696520</v>
+        <v>6696330</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,6 +1169,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1230,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120208784</v>
+        <v>120208714</v>
       </c>
       <c r="B7" t="n">
-        <v>91023</v>
+        <v>95478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668273</v>
+        <v>668369</v>
       </c>
       <c r="R7" t="n">
-        <v>6696531</v>
+        <v>6696540</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120208851</v>
+        <v>120208736</v>
       </c>
       <c r="B8" t="n">
-        <v>100194</v>
+        <v>56532</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,34 +1318,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668213</v>
+        <v>668532</v>
       </c>
       <c r="R8" t="n">
-        <v>6696494</v>
+        <v>6696689</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120208774</v>
+        <v>120208706</v>
       </c>
       <c r="B9" t="n">
-        <v>97908</v>
+        <v>95478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,25 +1426,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668365</v>
+        <v>668408</v>
       </c>
       <c r="R9" t="n">
-        <v>6696575</v>
+        <v>6696562</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120208779</v>
+        <v>120208713</v>
       </c>
       <c r="B10" t="n">
-        <v>97908</v>
+        <v>95478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,25 +1528,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668212</v>
+        <v>668379</v>
       </c>
       <c r="R10" t="n">
-        <v>6696497</v>
+        <v>6696528</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120208722</v>
+        <v>120208775</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>97908</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,25 +1630,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>219798</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668552</v>
+        <v>668180</v>
       </c>
       <c r="R11" t="n">
-        <v>6696684</v>
+        <v>6696501</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120208716</v>
+        <v>120208856</v>
       </c>
       <c r="B12" t="n">
-        <v>95478</v>
+        <v>100194</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,25 +1732,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668439</v>
+        <v>668382</v>
       </c>
       <c r="R12" t="n">
-        <v>6696517</v>
+        <v>6696524</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120208827</v>
+        <v>120208711</v>
       </c>
       <c r="B13" t="n">
-        <v>4772</v>
+        <v>95478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1854,25 +1834,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102306</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668457</v>
+        <v>668345</v>
       </c>
       <c r="R13" t="n">
-        <v>6696523</v>
+        <v>6696598</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120208777</v>
+        <v>120208792</v>
       </c>
       <c r="B14" t="n">
-        <v>97908</v>
+        <v>57326</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1956,38 +1936,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>100048</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668188</v>
+        <v>668517</v>
       </c>
       <c r="R14" t="n">
-        <v>6696531</v>
+        <v>6696457</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,6 +2008,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,10 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120208782</v>
+        <v>120208724</v>
       </c>
       <c r="B15" t="n">
-        <v>97908</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2058,25 +2051,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2079,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668279</v>
+        <v>668608</v>
       </c>
       <c r="R15" t="n">
-        <v>6696528</v>
+        <v>6696611</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,10 +2141,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120208781</v>
+        <v>120208827</v>
       </c>
       <c r="B16" t="n">
-        <v>97908</v>
+        <v>4772</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2164,21 +2157,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219798</v>
+        <v>102306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2188,10 +2181,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668261</v>
+        <v>668457</v>
       </c>
       <c r="R16" t="n">
-        <v>6696558</v>
+        <v>6696523</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2250,10 +2243,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120208853</v>
+        <v>120208743</v>
       </c>
       <c r="B17" t="n">
-        <v>100194</v>
+        <v>57473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2262,38 +2255,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668241</v>
+        <v>668533</v>
       </c>
       <c r="R17" t="n">
-        <v>6696541</v>
+        <v>6696366</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2352,10 +2353,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120208705</v>
+        <v>120208741</v>
       </c>
       <c r="B18" t="n">
-        <v>95478</v>
+        <v>57473</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2368,34 +2369,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668521</v>
+        <v>668483</v>
       </c>
       <c r="R18" t="n">
-        <v>6696330</v>
+        <v>6696590</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,21 +2447,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2469,10 +2463,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120208736</v>
+        <v>120208852</v>
       </c>
       <c r="B19" t="n">
-        <v>56532</v>
+        <v>100194</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,39 +2479,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668532</v>
+        <v>668230</v>
       </c>
       <c r="R19" t="n">
-        <v>6696689</v>
+        <v>6696502</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2550,11 +2539,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2581,10 +2565,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120208775</v>
+        <v>120208862</v>
       </c>
       <c r="B20" t="n">
-        <v>97908</v>
+        <v>100194</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2597,21 +2581,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2621,10 +2605,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668180</v>
+        <v>668572</v>
       </c>
       <c r="R20" t="n">
-        <v>6696501</v>
+        <v>6696573</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2683,10 +2667,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120208686</v>
+        <v>120208718</v>
       </c>
       <c r="B21" t="n">
-        <v>101097</v>
+        <v>95478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2695,25 +2679,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2723,10 +2707,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668242</v>
+        <v>668450</v>
       </c>
       <c r="R21" t="n">
-        <v>6696541</v>
+        <v>6696589</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2785,10 +2769,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120208710</v>
+        <v>120208819</v>
       </c>
       <c r="B22" t="n">
-        <v>95478</v>
+        <v>105032</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2797,25 +2781,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2825,10 +2809,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668362</v>
+        <v>668579</v>
       </c>
       <c r="R22" t="n">
-        <v>6696582</v>
+        <v>6696655</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2887,10 +2871,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120208724</v>
+        <v>120208739</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>103441</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2899,25 +2883,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>222412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2927,10 +2911,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668608</v>
+        <v>668166</v>
       </c>
       <c r="R23" t="n">
-        <v>6696611</v>
+        <v>6696498</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2989,10 +2973,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120208783</v>
+        <v>120208740</v>
       </c>
       <c r="B24" t="n">
-        <v>90351</v>
+        <v>57473</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3001,38 +2985,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3215</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668281</v>
+        <v>668357</v>
       </c>
       <c r="R24" t="n">
-        <v>6696528</v>
+        <v>6696585</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3091,10 +3083,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120208711</v>
+        <v>120208779</v>
       </c>
       <c r="B25" t="n">
-        <v>95478</v>
+        <v>97908</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3103,25 +3095,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3131,10 +3123,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668345</v>
+        <v>668212</v>
       </c>
       <c r="R25" t="n">
-        <v>6696598</v>
+        <v>6696497</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3193,10 +3185,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120208707</v>
+        <v>120208778</v>
       </c>
       <c r="B26" t="n">
-        <v>95478</v>
+        <v>97908</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3205,25 +3197,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3233,10 +3225,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668394</v>
+        <v>668191</v>
       </c>
       <c r="R26" t="n">
-        <v>6696553</v>
+        <v>6696527</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,7 +3287,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120208719</v>
+        <v>120208704</v>
       </c>
       <c r="B27" t="n">
         <v>95478</v>
@@ -3335,10 +3327,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668514</v>
+        <v>668571</v>
       </c>
       <c r="R27" t="n">
-        <v>6696439</v>
+        <v>6696816</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3381,6 +3373,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3397,10 +3404,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120208778</v>
+        <v>120208756</v>
       </c>
       <c r="B28" t="n">
-        <v>97908</v>
+        <v>57336</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3409,38 +3416,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668191</v>
+        <v>668467</v>
       </c>
       <c r="R28" t="n">
-        <v>6696527</v>
+        <v>6696630</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3473,6 +3485,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3499,10 +3516,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120208863</v>
+        <v>120208782</v>
       </c>
       <c r="B29" t="n">
-        <v>100194</v>
+        <v>97908</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3515,21 +3532,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3539,10 +3556,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668568</v>
+        <v>668279</v>
       </c>
       <c r="R29" t="n">
-        <v>6696542</v>
+        <v>6696528</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3601,10 +3618,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120208757</v>
+        <v>120208683</v>
       </c>
       <c r="B30" t="n">
-        <v>57336</v>
+        <v>101097</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3613,43 +3630,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668572</v>
+        <v>668188</v>
       </c>
       <c r="R30" t="n">
-        <v>6696525</v>
+        <v>6696531</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3682,11 +3694,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3713,10 +3720,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120208714</v>
+        <v>120208860</v>
       </c>
       <c r="B31" t="n">
-        <v>95478</v>
+        <v>100194</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3725,25 +3732,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3753,10 +3760,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668369</v>
+        <v>668566</v>
       </c>
       <c r="R31" t="n">
-        <v>6696540</v>
+        <v>6696858</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3815,10 +3822,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120208790</v>
+        <v>120208781</v>
       </c>
       <c r="B32" t="n">
-        <v>57326</v>
+        <v>97908</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3827,46 +3834,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100048</v>
+        <v>219798</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668550</v>
+        <v>668261</v>
       </c>
       <c r="R32" t="n">
-        <v>6696605</v>
+        <v>6696558</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3899,11 +3898,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3930,10 +3924,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120208811</v>
+        <v>120208818</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3942,47 +3936,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668524</v>
+        <v>668437</v>
       </c>
       <c r="R33" t="n">
-        <v>6696416</v>
+        <v>6696501</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4041,10 +4026,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120208856</v>
+        <v>120208758</v>
       </c>
       <c r="B34" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4053,38 +4038,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668382</v>
+        <v>668240</v>
       </c>
       <c r="R34" t="n">
-        <v>6696524</v>
+        <v>6696522</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4117,6 +4107,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4143,10 +4138,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120208688</v>
+        <v>120208737</v>
       </c>
       <c r="B35" t="n">
-        <v>101097</v>
+        <v>56532</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4159,34 +4154,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221235</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668383</v>
+        <v>668566</v>
       </c>
       <c r="R35" t="n">
-        <v>6696524</v>
+        <v>6696455</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4219,6 +4219,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4245,10 +4250,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120208691</v>
+        <v>120208735</v>
       </c>
       <c r="B36" t="n">
-        <v>101097</v>
+        <v>56532</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4261,34 +4266,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221235</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668509</v>
+        <v>668518</v>
       </c>
       <c r="R36" t="n">
-        <v>6696436</v>
+        <v>6696678</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4321,6 +4335,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4347,10 +4366,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120208706</v>
+        <v>120208828</v>
       </c>
       <c r="B37" t="n">
-        <v>95478</v>
+        <v>4772</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4359,25 +4378,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4387,10 +4406,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668408</v>
+        <v>668595</v>
       </c>
       <c r="R37" t="n">
-        <v>6696562</v>
+        <v>6696467</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4449,10 +4468,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120208816</v>
+        <v>120208708</v>
       </c>
       <c r="B38" t="n">
-        <v>56524</v>
+        <v>95478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4465,21 +4484,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102612</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4489,10 +4508,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668248</v>
+        <v>668376</v>
       </c>
       <c r="R38" t="n">
-        <v>6696628</v>
+        <v>6696595</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4525,11 +4544,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>flög upp från marken</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4556,10 +4570,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120208718</v>
+        <v>120208687</v>
       </c>
       <c r="B39" t="n">
-        <v>95478</v>
+        <v>101097</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4568,25 +4582,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4596,10 +4610,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668450</v>
+        <v>668382</v>
       </c>
       <c r="R39" t="n">
-        <v>6696589</v>
+        <v>6696529</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4658,10 +4672,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120208704</v>
+        <v>120208774</v>
       </c>
       <c r="B40" t="n">
-        <v>95478</v>
+        <v>97908</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4670,25 +4684,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4698,10 +4712,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668571</v>
+        <v>668365</v>
       </c>
       <c r="R40" t="n">
-        <v>6696816</v>
+        <v>6696575</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4744,21 +4758,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -4775,10 +4774,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120208799</v>
+        <v>120208855</v>
       </c>
       <c r="B41" t="n">
-        <v>57689</v>
+        <v>100194</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4791,39 +4790,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668558</v>
+        <v>668380</v>
       </c>
       <c r="R41" t="n">
-        <v>6696534</v>
+        <v>6696528</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4882,10 +4876,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120208800</v>
+        <v>120208864</v>
       </c>
       <c r="B42" t="n">
-        <v>57689</v>
+        <v>100194</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4898,43 +4892,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668525</v>
+        <v>668527</v>
       </c>
       <c r="R42" t="n">
-        <v>6696405</v>
+        <v>6696351</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4993,10 +4978,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120208743</v>
+        <v>120208853</v>
       </c>
       <c r="B43" t="n">
-        <v>57473</v>
+        <v>100194</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5005,46 +4990,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668533</v>
+        <v>668241</v>
       </c>
       <c r="R43" t="n">
-        <v>6696366</v>
+        <v>6696541</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5103,10 +5080,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120208828</v>
+        <v>120208863</v>
       </c>
       <c r="B44" t="n">
-        <v>4772</v>
+        <v>100194</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5119,21 +5096,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5143,10 +5120,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668595</v>
+        <v>668568</v>
       </c>
       <c r="R44" t="n">
-        <v>6696467</v>
+        <v>6696542</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5205,10 +5182,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120208758</v>
+        <v>120208721</v>
       </c>
       <c r="B45" t="n">
-        <v>57336</v>
+        <v>90580</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5221,39 +5198,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668240</v>
+        <v>668589</v>
       </c>
       <c r="R45" t="n">
-        <v>6696522</v>
+        <v>6696866</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5286,11 +5258,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5317,10 +5284,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120208785</v>
+        <v>120208800</v>
       </c>
       <c r="B46" t="n">
-        <v>90864</v>
+        <v>57689</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5329,38 +5296,47 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668552</v>
+        <v>668525</v>
       </c>
       <c r="R46" t="n">
-        <v>6696684</v>
+        <v>6696405</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5419,10 +5395,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120208720</v>
+        <v>120208791</v>
       </c>
       <c r="B47" t="n">
-        <v>90545</v>
+        <v>57326</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5431,38 +5407,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>100048</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>668407</v>
+        <v>668520</v>
       </c>
       <c r="R47" t="n">
-        <v>6696520</v>
+        <v>6696377</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5497,6 +5481,11 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5505,21 +5494,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5536,10 +5510,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120208798</v>
+        <v>120208682</v>
       </c>
       <c r="B48" t="n">
-        <v>57689</v>
+        <v>101097</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5552,39 +5526,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103015</v>
+        <v>221235</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668342</v>
+        <v>668186</v>
       </c>
       <c r="R48" t="n">
-        <v>6696603</v>
+        <v>6696508</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5643,7 +5612,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120208852</v>
+        <v>120208849</v>
       </c>
       <c r="B49" t="n">
         <v>100194</v>
@@ -5683,10 +5652,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668230</v>
+        <v>668362</v>
       </c>
       <c r="R49" t="n">
-        <v>6696502</v>
+        <v>6696583</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5745,7 +5714,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120208855</v>
+        <v>120208858</v>
       </c>
       <c r="B50" t="n">
         <v>100194</v>
@@ -5785,10 +5754,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668380</v>
+        <v>668564</v>
       </c>
       <c r="R50" t="n">
-        <v>6696528</v>
+        <v>6696816</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5847,7 +5816,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120208692</v>
+        <v>120208691</v>
       </c>
       <c r="B51" t="n">
         <v>101097</v>
@@ -5887,10 +5856,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668538</v>
+        <v>668509</v>
       </c>
       <c r="R51" t="n">
-        <v>6696322</v>
+        <v>6696436</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5949,10 +5918,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120208713</v>
+        <v>120208813</v>
       </c>
       <c r="B52" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5961,38 +5930,47 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668379</v>
+        <v>668575</v>
       </c>
       <c r="R52" t="n">
-        <v>6696528</v>
+        <v>6696701</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6051,10 +6029,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120208709</v>
+        <v>120208722</v>
       </c>
       <c r="B53" t="n">
-        <v>95478</v>
+        <v>90580</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6067,21 +6045,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6091,10 +6069,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668362</v>
+        <v>668552</v>
       </c>
       <c r="R53" t="n">
-        <v>6696599</v>
+        <v>6696684</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6153,10 +6131,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120208848</v>
+        <v>120208790</v>
       </c>
       <c r="B54" t="n">
-        <v>100194</v>
+        <v>57326</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6165,38 +6143,46 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>100048</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668419</v>
+        <v>668550</v>
       </c>
       <c r="R54" t="n">
-        <v>6696535</v>
+        <v>6696605</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6229,6 +6215,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6255,10 +6246,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120208792</v>
+        <v>120208712</v>
       </c>
       <c r="B55" t="n">
-        <v>57326</v>
+        <v>95478</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6271,42 +6262,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100048</v>
+        <v>53</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668517</v>
+        <v>668301</v>
       </c>
       <c r="R55" t="n">
-        <v>6696457</v>
+        <v>6696522</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6339,11 +6322,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6370,10 +6348,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120208813</v>
+        <v>120208725</v>
       </c>
       <c r="B56" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6382,47 +6360,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668575</v>
+        <v>668551</v>
       </c>
       <c r="R56" t="n">
-        <v>6696701</v>
+        <v>6696304</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6481,10 +6450,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120208857</v>
+        <v>120208720</v>
       </c>
       <c r="B57" t="n">
-        <v>100194</v>
+        <v>90545</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6497,21 +6466,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6521,10 +6490,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668438</v>
+        <v>668407</v>
       </c>
       <c r="R57" t="n">
-        <v>6696512</v>
+        <v>6696520</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6567,6 +6536,21 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -6583,10 +6567,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120208823</v>
+        <v>120208757</v>
       </c>
       <c r="B58" t="n">
-        <v>57339</v>
+        <v>57336</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6595,46 +6579,43 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668565</v>
+        <v>668572</v>
       </c>
       <c r="R58" t="n">
-        <v>6696520</v>
+        <v>6696525</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6671,7 +6652,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Inom avverkningsanmälan</t>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6698,10 +6679,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120208818</v>
+        <v>120208684</v>
       </c>
       <c r="B59" t="n">
-        <v>105032</v>
+        <v>101097</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6714,21 +6695,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221144</v>
+        <v>221235</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6738,10 +6719,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668437</v>
+        <v>668201</v>
       </c>
       <c r="R59" t="n">
-        <v>6696501</v>
+        <v>6696519</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6800,10 +6781,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120208739</v>
+        <v>120208861</v>
       </c>
       <c r="B60" t="n">
-        <v>103441</v>
+        <v>100194</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6816,21 +6797,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6840,10 +6821,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>668166</v>
+        <v>668567</v>
       </c>
       <c r="R60" t="n">
-        <v>6696498</v>
+        <v>6696809</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6902,10 +6883,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120208826</v>
+        <v>120208857</v>
       </c>
       <c r="B61" t="n">
-        <v>4772</v>
+        <v>100194</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6918,21 +6899,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6942,10 +6923,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>668442</v>
+        <v>668438</v>
       </c>
       <c r="R61" t="n">
-        <v>6696515</v>
+        <v>6696512</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7004,10 +6985,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120208740</v>
+        <v>120208703</v>
       </c>
       <c r="B62" t="n">
-        <v>57473</v>
+        <v>95478</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7020,42 +7001,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668357</v>
+        <v>668451</v>
       </c>
       <c r="R62" t="n">
-        <v>6696585</v>
+        <v>6696602</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7098,6 +7071,21 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7114,10 +7102,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120208721</v>
+        <v>120208707</v>
       </c>
       <c r="B63" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7130,21 +7118,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7154,10 +7142,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668589</v>
+        <v>668394</v>
       </c>
       <c r="R63" t="n">
-        <v>6696866</v>
+        <v>6696553</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7216,10 +7204,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120208717</v>
+        <v>120208744</v>
       </c>
       <c r="B64" t="n">
-        <v>95478</v>
+        <v>57473</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7232,34 +7220,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668468</v>
+        <v>668602</v>
       </c>
       <c r="R64" t="n">
-        <v>6696587</v>
+        <v>6696625</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7318,10 +7311,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120208859</v>
+        <v>120208812</v>
       </c>
       <c r="B65" t="n">
-        <v>100194</v>
+        <v>97930</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7330,38 +7323,47 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668581</v>
+        <v>668568</v>
       </c>
       <c r="R65" t="n">
-        <v>6696848</v>
+        <v>6696851</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7420,10 +7422,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120208776</v>
+        <v>120208719</v>
       </c>
       <c r="B66" t="n">
-        <v>97908</v>
+        <v>95478</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7432,25 +7434,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7460,10 +7462,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668186</v>
+        <v>668514</v>
       </c>
       <c r="R66" t="n">
-        <v>6696508</v>
+        <v>6696439</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7522,10 +7524,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120208850</v>
+        <v>120208759</v>
       </c>
       <c r="B67" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7534,38 +7536,43 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>668179</v>
+        <v>668572</v>
       </c>
       <c r="R67" t="n">
-        <v>6696528</v>
+        <v>6696839</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7598,6 +7605,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7624,10 +7636,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120208791</v>
+        <v>120208830</v>
       </c>
       <c r="B68" t="n">
-        <v>57326</v>
+        <v>78542</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7640,42 +7652,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100048</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>668520</v>
+        <v>668442</v>
       </c>
       <c r="R68" t="n">
-        <v>6696377</v>
+        <v>6696514</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7710,11 +7714,6 @@
           <t>2024-10-04</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7723,6 +7722,21 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -7739,10 +7753,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120208712</v>
+        <v>120208854</v>
       </c>
       <c r="B69" t="n">
-        <v>95478</v>
+        <v>100194</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7751,25 +7765,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7779,10 +7793,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>668301</v>
+        <v>668370</v>
       </c>
       <c r="R69" t="n">
-        <v>6696522</v>
+        <v>6696506</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7841,7 +7855,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120208708</v>
+        <v>120208717</v>
       </c>
       <c r="B70" t="n">
         <v>95478</v>
@@ -7881,10 +7895,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>668376</v>
+        <v>668468</v>
       </c>
       <c r="R70" t="n">
-        <v>6696595</v>
+        <v>6696587</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7943,10 +7957,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120208819</v>
+        <v>120208784</v>
       </c>
       <c r="B71" t="n">
-        <v>105032</v>
+        <v>91023</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7955,25 +7969,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7983,10 +7997,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>668579</v>
+        <v>668273</v>
       </c>
       <c r="R71" t="n">
-        <v>6696655</v>
+        <v>6696531</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8045,10 +8059,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120208682</v>
+        <v>120208823</v>
       </c>
       <c r="B72" t="n">
-        <v>101097</v>
+        <v>57339</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8061,34 +8075,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221235</v>
+        <v>102977</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>668186</v>
+        <v>668565</v>
       </c>
       <c r="R72" t="n">
-        <v>6696508</v>
+        <v>6696520</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8121,6 +8143,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8147,10 +8174,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120208684</v>
+        <v>120208811</v>
       </c>
       <c r="B73" t="n">
-        <v>101097</v>
+        <v>97930</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8159,38 +8186,47 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221235</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>668201</v>
+        <v>668524</v>
       </c>
       <c r="R73" t="n">
-        <v>6696519</v>
+        <v>6696416</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8249,10 +8285,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120208683</v>
+        <v>120208798</v>
       </c>
       <c r="B74" t="n">
-        <v>101097</v>
+        <v>57689</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8265,34 +8301,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221235</v>
+        <v>103015</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>668188</v>
+        <v>668342</v>
       </c>
       <c r="R74" t="n">
-        <v>6696531</v>
+        <v>6696603</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8351,10 +8392,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120208861</v>
+        <v>120208814</v>
       </c>
       <c r="B75" t="n">
-        <v>100194</v>
+        <v>74593</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8367,21 +8408,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8391,10 +8432,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>668567</v>
+        <v>668296</v>
       </c>
       <c r="R75" t="n">
-        <v>6696809</v>
+        <v>6696535</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8453,10 +8494,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120208860</v>
+        <v>120208816</v>
       </c>
       <c r="B76" t="n">
-        <v>100194</v>
+        <v>56524</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8465,25 +8506,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>102612</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8493,10 +8534,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>668566</v>
+        <v>668248</v>
       </c>
       <c r="R76" t="n">
-        <v>6696858</v>
+        <v>6696628</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8529,6 +8570,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>flög upp från marken</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8555,10 +8601,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120208687</v>
+        <v>120208822</v>
       </c>
       <c r="B77" t="n">
-        <v>101097</v>
+        <v>57339</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8571,34 +8617,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221235</v>
+        <v>102977</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>668382</v>
+        <v>668585</v>
       </c>
       <c r="R77" t="n">
-        <v>6696529</v>
+        <v>6696613</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8631,6 +8685,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8657,10 +8716,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120208756</v>
+        <v>120208690</v>
       </c>
       <c r="B78" t="n">
-        <v>57336</v>
+        <v>101097</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8669,43 +8728,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>221235</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>668467</v>
+        <v>668564</v>
       </c>
       <c r="R78" t="n">
-        <v>6696630</v>
+        <v>6696811</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8738,11 +8792,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8769,10 +8818,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120208737</v>
+        <v>120208688</v>
       </c>
       <c r="B79" t="n">
-        <v>56532</v>
+        <v>101097</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8785,39 +8834,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100138</v>
+        <v>221235</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>668566</v>
+        <v>668383</v>
       </c>
       <c r="R79" t="n">
-        <v>6696455</v>
+        <v>6696524</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8850,11 +8894,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8881,10 +8920,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120208849</v>
+        <v>120208799</v>
       </c>
       <c r="B80" t="n">
-        <v>100194</v>
+        <v>57689</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8897,34 +8936,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>668362</v>
+        <v>668558</v>
       </c>
       <c r="R80" t="n">
-        <v>6696583</v>
+        <v>6696534</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8983,7 +9027,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120208854</v>
+        <v>120208848</v>
       </c>
       <c r="B81" t="n">
         <v>100194</v>
@@ -9023,10 +9067,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>668370</v>
+        <v>668419</v>
       </c>
       <c r="R81" t="n">
-        <v>6696506</v>
+        <v>6696535</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9085,10 +9129,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120208864</v>
+        <v>120208776</v>
       </c>
       <c r="B82" t="n">
-        <v>100194</v>
+        <v>97908</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9101,21 +9145,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9125,10 +9169,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>668527</v>
+        <v>668186</v>
       </c>
       <c r="R82" t="n">
-        <v>6696351</v>
+        <v>6696508</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9187,10 +9231,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120208725</v>
+        <v>120208710</v>
       </c>
       <c r="B83" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9203,21 +9247,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9227,10 +9271,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>668551</v>
+        <v>668362</v>
       </c>
       <c r="R83" t="n">
-        <v>6696304</v>
+        <v>6696582</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9289,10 +9333,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120208759</v>
+        <v>120208709</v>
       </c>
       <c r="B84" t="n">
-        <v>57336</v>
+        <v>95478</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9305,39 +9349,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>668572</v>
+        <v>668362</v>
       </c>
       <c r="R84" t="n">
-        <v>6696839</v>
+        <v>6696599</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9370,11 +9409,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9401,10 +9435,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120208690</v>
+        <v>120208851</v>
       </c>
       <c r="B85" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9417,21 +9451,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9441,10 +9475,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>668564</v>
+        <v>668213</v>
       </c>
       <c r="R85" t="n">
-        <v>6696811</v>
+        <v>6696494</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9503,10 +9537,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120208744</v>
+        <v>120208850</v>
       </c>
       <c r="B86" t="n">
-        <v>57473</v>
+        <v>100194</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9515,43 +9549,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>668602</v>
+        <v>668179</v>
       </c>
       <c r="R86" t="n">
-        <v>6696625</v>
+        <v>6696528</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9610,10 +9639,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120208703</v>
+        <v>120208826</v>
       </c>
       <c r="B87" t="n">
-        <v>95478</v>
+        <v>4772</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9622,25 +9651,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>102306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9650,10 +9679,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>668451</v>
+        <v>668442</v>
       </c>
       <c r="R87" t="n">
-        <v>6696602</v>
+        <v>6696515</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9696,21 +9725,6 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -9727,10 +9741,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120208814</v>
+        <v>120208859</v>
       </c>
       <c r="B88" t="n">
-        <v>74593</v>
+        <v>100194</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9743,21 +9757,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6426</v>
+        <v>222498</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9767,10 +9781,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>668296</v>
+        <v>668581</v>
       </c>
       <c r="R88" t="n">
-        <v>6696535</v>
+        <v>6696848</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9829,10 +9843,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120208735</v>
+        <v>120208686</v>
       </c>
       <c r="B89" t="n">
-        <v>56532</v>
+        <v>101097</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9845,43 +9859,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100138</v>
+        <v>221235</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>668518</v>
+        <v>668242</v>
       </c>
       <c r="R89" t="n">
-        <v>6696678</v>
+        <v>6696541</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9914,11 +9919,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9945,10 +9945,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120208862</v>
+        <v>120208783</v>
       </c>
       <c r="B90" t="n">
-        <v>100194</v>
+        <v>90351</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9961,21 +9961,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9985,10 +9985,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>668572</v>
+        <v>668281</v>
       </c>
       <c r="R90" t="n">
-        <v>6696573</v>
+        <v>6696528</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10047,10 +10047,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120208858</v>
+        <v>120208815</v>
       </c>
       <c r="B91" t="n">
-        <v>100194</v>
+        <v>74593</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10063,21 +10063,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10087,10 +10087,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>668564</v>
+        <v>668311</v>
       </c>
       <c r="R91" t="n">
-        <v>6696816</v>
+        <v>6696520</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10149,10 +10149,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120434323</v>
+        <v>120434321</v>
       </c>
       <c r="B92" t="n">
-        <v>74593</v>
+        <v>94550</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10165,21 +10165,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6426</v>
+        <v>210</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10189,10 +10189,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>668320</v>
+        <v>668380</v>
       </c>
       <c r="R92" t="n">
-        <v>6696515</v>
+        <v>6696576</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10235,21 +10235,6 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
@@ -10383,10 +10368,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120434325</v>
+        <v>120434323</v>
       </c>
       <c r="B94" t="n">
-        <v>95478</v>
+        <v>74593</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10395,25 +10380,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10423,10 +10408,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>668456</v>
+        <v>668320</v>
       </c>
       <c r="R94" t="n">
-        <v>6696470</v>
+        <v>6696515</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10472,17 +10457,17 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -10500,10 +10485,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120434321</v>
+        <v>120434322</v>
       </c>
       <c r="B95" t="n">
-        <v>94550</v>
+        <v>95478</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10512,25 +10497,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10540,10 +10525,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>668380</v>
+        <v>668377</v>
       </c>
       <c r="R95" t="n">
-        <v>6696576</v>
+        <v>6696572</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10602,7 +10587,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120434322</v>
+        <v>120434325</v>
       </c>
       <c r="B96" t="n">
         <v>95478</v>
@@ -10642,10 +10627,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>668377</v>
+        <v>668456</v>
       </c>
       <c r="R96" t="n">
-        <v>6696572</v>
+        <v>6696470</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10688,6 +10673,21 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120208777</v>
+        <v>120208814</v>
       </c>
       <c r="B2" t="n">
-        <v>97908</v>
+        <v>74593</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668188</v>
+        <v>668296</v>
       </c>
       <c r="R2" t="n">
-        <v>6696531</v>
+        <v>6696535</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120208716</v>
+        <v>120208736</v>
       </c>
       <c r="B3" t="n">
-        <v>95478</v>
+        <v>56532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668439</v>
+        <v>668532</v>
       </c>
       <c r="R3" t="n">
-        <v>6696517</v>
+        <v>6696689</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120208692</v>
+        <v>120208713</v>
       </c>
       <c r="B4" t="n">
-        <v>101097</v>
+        <v>95478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668538</v>
+        <v>668379</v>
       </c>
       <c r="R4" t="n">
-        <v>6696322</v>
+        <v>6696528</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120208785</v>
+        <v>120208709</v>
       </c>
       <c r="B5" t="n">
-        <v>90864</v>
+        <v>95478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>668552</v>
+        <v>668362</v>
       </c>
       <c r="R5" t="n">
-        <v>6696684</v>
+        <v>6696599</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120208705</v>
+        <v>120208799</v>
       </c>
       <c r="B6" t="n">
-        <v>95478</v>
+        <v>57689</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1105,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>668521</v>
+        <v>668558</v>
       </c>
       <c r="R6" t="n">
-        <v>6696330</v>
+        <v>6696534</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,21 +1184,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120208714</v>
+        <v>120208783</v>
       </c>
       <c r="B7" t="n">
-        <v>95478</v>
+        <v>90351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>3215</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>668369</v>
+        <v>668281</v>
       </c>
       <c r="R7" t="n">
-        <v>6696540</v>
+        <v>6696528</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120208736</v>
+        <v>120208823</v>
       </c>
       <c r="B8" t="n">
-        <v>56532</v>
+        <v>57339</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,16 +1318,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>102977</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1336,21 +1336,24 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>668532</v>
+        <v>668565</v>
       </c>
       <c r="R8" t="n">
-        <v>6696689</v>
+        <v>6696520</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1390,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120208706</v>
+        <v>120208811</v>
       </c>
       <c r="B9" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,38 +1429,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668408</v>
+        <v>668524</v>
       </c>
       <c r="R9" t="n">
-        <v>6696562</v>
+        <v>6696416</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1528,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120208713</v>
+        <v>120208684</v>
       </c>
       <c r="B10" t="n">
-        <v>95478</v>
+        <v>101097</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1528,25 +1540,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668379</v>
+        <v>668201</v>
       </c>
       <c r="R10" t="n">
-        <v>6696528</v>
+        <v>6696519</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120208775</v>
+        <v>120208851</v>
       </c>
       <c r="B11" t="n">
-        <v>97908</v>
+        <v>100194</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1646,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1670,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668180</v>
+        <v>668213</v>
       </c>
       <c r="R11" t="n">
-        <v>6696501</v>
+        <v>6696494</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,7 +1732,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120208856</v>
+        <v>120208855</v>
       </c>
       <c r="B12" t="n">
         <v>100194</v>
@@ -1760,10 +1772,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668382</v>
+        <v>668380</v>
       </c>
       <c r="R12" t="n">
-        <v>6696524</v>
+        <v>6696528</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1834,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120208711</v>
+        <v>120208719</v>
       </c>
       <c r="B13" t="n">
         <v>95478</v>
@@ -1862,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668345</v>
+        <v>668514</v>
       </c>
       <c r="R13" t="n">
-        <v>6696598</v>
+        <v>6696439</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,10 +1936,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120208792</v>
+        <v>120208737</v>
       </c>
       <c r="B14" t="n">
-        <v>57326</v>
+        <v>56532</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,46 +1948,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100048</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668517</v>
+        <v>668566</v>
       </c>
       <c r="R14" t="n">
-        <v>6696457</v>
+        <v>6696455</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2012,7 +2021,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Inom avverkningsanmälan</t>
+          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2039,10 +2048,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120208724</v>
+        <v>120208784</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2051,25 +2060,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2079,10 +2088,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>668608</v>
+        <v>668273</v>
       </c>
       <c r="R15" t="n">
-        <v>6696611</v>
+        <v>6696531</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,10 +2150,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120208827</v>
+        <v>120208759</v>
       </c>
       <c r="B16" t="n">
-        <v>4772</v>
+        <v>57336</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2153,38 +2162,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668457</v>
+        <v>668572</v>
       </c>
       <c r="R16" t="n">
-        <v>6696523</v>
+        <v>6696839</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2217,6 +2231,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2243,10 +2262,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120208743</v>
+        <v>120208827</v>
       </c>
       <c r="B17" t="n">
-        <v>57473</v>
+        <v>4772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2255,46 +2274,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>102306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>668533</v>
+        <v>668457</v>
       </c>
       <c r="R17" t="n">
-        <v>6696366</v>
+        <v>6696523</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2353,10 +2364,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120208741</v>
+        <v>120208864</v>
       </c>
       <c r="B18" t="n">
-        <v>57473</v>
+        <v>100194</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2365,46 +2376,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>668483</v>
+        <v>668527</v>
       </c>
       <c r="R18" t="n">
-        <v>6696590</v>
+        <v>6696351</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2463,10 +2466,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120208852</v>
+        <v>120208687</v>
       </c>
       <c r="B19" t="n">
-        <v>100194</v>
+        <v>101097</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2479,21 +2482,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2503,10 +2506,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>668230</v>
+        <v>668382</v>
       </c>
       <c r="R19" t="n">
-        <v>6696502</v>
+        <v>6696529</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2565,10 +2568,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120208862</v>
+        <v>120208690</v>
       </c>
       <c r="B20" t="n">
-        <v>100194</v>
+        <v>101097</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2581,21 +2584,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2605,10 +2608,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>668572</v>
+        <v>668564</v>
       </c>
       <c r="R20" t="n">
-        <v>6696573</v>
+        <v>6696811</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2667,10 +2670,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120208718</v>
+        <v>120208785</v>
       </c>
       <c r="B21" t="n">
-        <v>95478</v>
+        <v>90864</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2683,21 +2686,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2707,10 +2710,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>668450</v>
+        <v>668552</v>
       </c>
       <c r="R21" t="n">
-        <v>6696589</v>
+        <v>6696684</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2769,10 +2772,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120208819</v>
+        <v>120208712</v>
       </c>
       <c r="B22" t="n">
-        <v>105032</v>
+        <v>95478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2781,25 +2784,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2809,10 +2812,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>668579</v>
+        <v>668301</v>
       </c>
       <c r="R22" t="n">
-        <v>6696655</v>
+        <v>6696522</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2871,10 +2874,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120208739</v>
+        <v>120208707</v>
       </c>
       <c r="B23" t="n">
-        <v>103441</v>
+        <v>95478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2883,25 +2886,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222412</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2911,10 +2914,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>668166</v>
+        <v>668394</v>
       </c>
       <c r="R23" t="n">
-        <v>6696498</v>
+        <v>6696553</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,10 +2976,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120208740</v>
+        <v>120208710</v>
       </c>
       <c r="B24" t="n">
-        <v>57473</v>
+        <v>95478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2989,42 +2992,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>668357</v>
+        <v>668362</v>
       </c>
       <c r="R24" t="n">
-        <v>6696585</v>
+        <v>6696582</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3083,10 +3078,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120208779</v>
+        <v>120208756</v>
       </c>
       <c r="B25" t="n">
-        <v>97908</v>
+        <v>57336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3095,38 +3090,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668212</v>
+        <v>668467</v>
       </c>
       <c r="R25" t="n">
-        <v>6696497</v>
+        <v>6696630</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3159,6 +3159,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3185,10 +3190,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120208778</v>
+        <v>120208798</v>
       </c>
       <c r="B26" t="n">
-        <v>97908</v>
+        <v>57689</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3201,34 +3206,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219798</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668191</v>
+        <v>668342</v>
       </c>
       <c r="R26" t="n">
-        <v>6696527</v>
+        <v>6696603</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3287,10 +3297,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120208704</v>
+        <v>120208848</v>
       </c>
       <c r="B27" t="n">
-        <v>95478</v>
+        <v>100194</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3299,25 +3309,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3327,10 +3337,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>668571</v>
+        <v>668419</v>
       </c>
       <c r="R27" t="n">
-        <v>6696816</v>
+        <v>6696535</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3373,21 +3383,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3404,10 +3399,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120208756</v>
+        <v>120208725</v>
       </c>
       <c r="B28" t="n">
-        <v>57336</v>
+        <v>90580</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3420,39 +3415,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>668467</v>
+        <v>668551</v>
       </c>
       <c r="R28" t="n">
-        <v>6696630</v>
+        <v>6696304</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3485,11 +3475,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3516,10 +3501,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120208782</v>
+        <v>120208758</v>
       </c>
       <c r="B29" t="n">
-        <v>97908</v>
+        <v>57336</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3528,38 +3513,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>668279</v>
+        <v>668240</v>
       </c>
       <c r="R29" t="n">
-        <v>6696528</v>
+        <v>6696522</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3592,6 +3582,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3618,7 +3613,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120208683</v>
+        <v>120208686</v>
       </c>
       <c r="B30" t="n">
         <v>101097</v>
@@ -3658,10 +3653,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>668188</v>
+        <v>668242</v>
       </c>
       <c r="R30" t="n">
-        <v>6696531</v>
+        <v>6696541</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3720,10 +3715,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120208860</v>
+        <v>120208688</v>
       </c>
       <c r="B31" t="n">
-        <v>100194</v>
+        <v>101097</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3736,21 +3731,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3760,10 +3755,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>668566</v>
+        <v>668383</v>
       </c>
       <c r="R31" t="n">
-        <v>6696858</v>
+        <v>6696524</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,10 +3817,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120208781</v>
+        <v>120208691</v>
       </c>
       <c r="B32" t="n">
-        <v>97908</v>
+        <v>101097</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3838,21 +3833,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3862,10 +3857,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>668261</v>
+        <v>668509</v>
       </c>
       <c r="R32" t="n">
-        <v>6696558</v>
+        <v>6696436</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3924,10 +3919,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120208818</v>
+        <v>120208849</v>
       </c>
       <c r="B33" t="n">
-        <v>105032</v>
+        <v>100194</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3940,21 +3935,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3964,10 +3959,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>668437</v>
+        <v>668362</v>
       </c>
       <c r="R33" t="n">
-        <v>6696501</v>
+        <v>6696583</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4026,10 +4021,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120208758</v>
+        <v>120208781</v>
       </c>
       <c r="B34" t="n">
-        <v>57336</v>
+        <v>97908</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4038,43 +4033,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>219798</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>668240</v>
+        <v>668261</v>
       </c>
       <c r="R34" t="n">
-        <v>6696522</v>
+        <v>6696558</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4107,11 +4097,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4138,10 +4123,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120208737</v>
+        <v>120208682</v>
       </c>
       <c r="B35" t="n">
-        <v>56532</v>
+        <v>101097</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4154,39 +4139,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>221235</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>668566</v>
+        <v>668186</v>
       </c>
       <c r="R35" t="n">
-        <v>6696455</v>
+        <v>6696508</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4219,11 +4199,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4250,10 +4225,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120208735</v>
+        <v>120208683</v>
       </c>
       <c r="B36" t="n">
-        <v>56532</v>
+        <v>101097</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4266,43 +4241,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>221235</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>668518</v>
+        <v>668188</v>
       </c>
       <c r="R36" t="n">
-        <v>6696678</v>
+        <v>6696531</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4335,11 +4301,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4366,10 +4327,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120208828</v>
+        <v>120208720</v>
       </c>
       <c r="B37" t="n">
-        <v>4772</v>
+        <v>90545</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4382,21 +4343,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102306</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4406,10 +4367,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>668595</v>
+        <v>668407</v>
       </c>
       <c r="R37" t="n">
-        <v>6696467</v>
+        <v>6696520</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4452,6 +4413,21 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4468,10 +4444,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120208708</v>
+        <v>120208790</v>
       </c>
       <c r="B38" t="n">
-        <v>95478</v>
+        <v>57326</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4484,34 +4460,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>100048</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>668376</v>
+        <v>668550</v>
       </c>
       <c r="R38" t="n">
-        <v>6696595</v>
+        <v>6696605</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4544,6 +4528,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4570,10 +4559,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120208687</v>
+        <v>120208757</v>
       </c>
       <c r="B39" t="n">
-        <v>101097</v>
+        <v>57336</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4582,38 +4571,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221235</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>668382</v>
+        <v>668572</v>
       </c>
       <c r="R39" t="n">
-        <v>6696529</v>
+        <v>6696525</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4646,6 +4640,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4672,7 +4671,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120208774</v>
+        <v>120208777</v>
       </c>
       <c r="B40" t="n">
         <v>97908</v>
@@ -4712,10 +4711,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>668365</v>
+        <v>668188</v>
       </c>
       <c r="R40" t="n">
-        <v>6696575</v>
+        <v>6696531</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4774,10 +4773,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120208855</v>
+        <v>120208692</v>
       </c>
       <c r="B41" t="n">
-        <v>100194</v>
+        <v>101097</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4790,21 +4789,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4814,10 +4813,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>668380</v>
+        <v>668538</v>
       </c>
       <c r="R41" t="n">
-        <v>6696528</v>
+        <v>6696322</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4876,10 +4875,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120208864</v>
+        <v>120208706</v>
       </c>
       <c r="B42" t="n">
-        <v>100194</v>
+        <v>95478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4888,25 +4887,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4916,10 +4915,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668527</v>
+        <v>668408</v>
       </c>
       <c r="R42" t="n">
-        <v>6696351</v>
+        <v>6696562</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4978,10 +4977,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120208853</v>
+        <v>120208717</v>
       </c>
       <c r="B43" t="n">
-        <v>100194</v>
+        <v>95478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4990,25 +4989,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5018,10 +5017,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668241</v>
+        <v>668468</v>
       </c>
       <c r="R43" t="n">
-        <v>6696541</v>
+        <v>6696587</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5080,10 +5079,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120208863</v>
+        <v>120208704</v>
       </c>
       <c r="B44" t="n">
-        <v>100194</v>
+        <v>95478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5092,25 +5091,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5120,10 +5119,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668568</v>
+        <v>668571</v>
       </c>
       <c r="R44" t="n">
-        <v>6696542</v>
+        <v>6696816</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5166,6 +5165,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5182,7 +5196,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120208721</v>
+        <v>120208722</v>
       </c>
       <c r="B45" t="n">
         <v>90580</v>
@@ -5222,10 +5236,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668589</v>
+        <v>668552</v>
       </c>
       <c r="R45" t="n">
-        <v>6696866</v>
+        <v>6696684</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5284,10 +5298,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120208800</v>
+        <v>120208711</v>
       </c>
       <c r="B46" t="n">
-        <v>57689</v>
+        <v>95478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5296,47 +5310,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103015</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668525</v>
+        <v>668345</v>
       </c>
       <c r="R46" t="n">
-        <v>6696405</v>
+        <v>6696598</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5395,10 +5400,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120208791</v>
+        <v>120208782</v>
       </c>
       <c r="B47" t="n">
-        <v>57326</v>
+        <v>97908</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5407,46 +5412,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100048</v>
+        <v>219798</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>668520</v>
+        <v>668279</v>
       </c>
       <c r="R47" t="n">
-        <v>6696377</v>
+        <v>6696528</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5479,11 +5476,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5510,10 +5502,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120208682</v>
+        <v>120208791</v>
       </c>
       <c r="B48" t="n">
-        <v>101097</v>
+        <v>57326</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5522,38 +5514,46 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221235</v>
+        <v>100048</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668186</v>
+        <v>668520</v>
       </c>
       <c r="R48" t="n">
-        <v>6696508</v>
+        <v>6696377</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5586,6 +5586,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5612,10 +5617,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120208849</v>
+        <v>120208813</v>
       </c>
       <c r="B49" t="n">
-        <v>100194</v>
+        <v>97930</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5624,38 +5629,47 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668362</v>
+        <v>668575</v>
       </c>
       <c r="R49" t="n">
-        <v>6696583</v>
+        <v>6696701</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5714,10 +5728,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120208858</v>
+        <v>120208778</v>
       </c>
       <c r="B50" t="n">
-        <v>100194</v>
+        <v>97908</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5730,21 +5744,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5754,10 +5768,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668564</v>
+        <v>668191</v>
       </c>
       <c r="R50" t="n">
-        <v>6696816</v>
+        <v>6696527</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5816,10 +5830,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120208691</v>
+        <v>120208714</v>
       </c>
       <c r="B51" t="n">
-        <v>101097</v>
+        <v>95478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5828,25 +5842,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221235</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5856,10 +5870,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668509</v>
+        <v>668369</v>
       </c>
       <c r="R51" t="n">
-        <v>6696436</v>
+        <v>6696540</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5918,10 +5932,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120208813</v>
+        <v>120208815</v>
       </c>
       <c r="B52" t="n">
-        <v>97930</v>
+        <v>74593</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5930,47 +5944,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668575</v>
+        <v>668311</v>
       </c>
       <c r="R52" t="n">
-        <v>6696701</v>
+        <v>6696520</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6029,10 +6034,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120208722</v>
+        <v>120208735</v>
       </c>
       <c r="B53" t="n">
-        <v>90580</v>
+        <v>56532</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6041,38 +6046,47 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668552</v>
+        <v>668518</v>
       </c>
       <c r="R53" t="n">
-        <v>6696684</v>
+        <v>6696678</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6105,6 +6119,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6131,10 +6150,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120208790</v>
+        <v>120208743</v>
       </c>
       <c r="B54" t="n">
-        <v>57326</v>
+        <v>57473</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6147,21 +6166,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6179,10 +6198,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668550</v>
+        <v>668533</v>
       </c>
       <c r="R54" t="n">
-        <v>6696605</v>
+        <v>6696366</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6215,11 +6234,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6246,10 +6260,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120208712</v>
+        <v>120208744</v>
       </c>
       <c r="B55" t="n">
-        <v>95478</v>
+        <v>57473</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6262,34 +6276,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668301</v>
+        <v>668602</v>
       </c>
       <c r="R55" t="n">
-        <v>6696522</v>
+        <v>6696625</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6348,10 +6367,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120208725</v>
+        <v>120208858</v>
       </c>
       <c r="B56" t="n">
-        <v>90580</v>
+        <v>100194</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6360,25 +6379,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6388,10 +6407,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668551</v>
+        <v>668564</v>
       </c>
       <c r="R56" t="n">
-        <v>6696304</v>
+        <v>6696816</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6450,10 +6469,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120208720</v>
+        <v>120208816</v>
       </c>
       <c r="B57" t="n">
-        <v>90545</v>
+        <v>56524</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6462,25 +6481,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6490,10 +6509,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668407</v>
+        <v>668248</v>
       </c>
       <c r="R57" t="n">
-        <v>6696520</v>
+        <v>6696628</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6528,6 +6547,11 @@
           <t>2024-10-04</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>flög upp från marken</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6536,21 +6560,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -6567,10 +6576,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120208757</v>
+        <v>120208826</v>
       </c>
       <c r="B58" t="n">
-        <v>57336</v>
+        <v>4772</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6579,43 +6588,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>102306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668572</v>
+        <v>668442</v>
       </c>
       <c r="R58" t="n">
-        <v>6696525</v>
+        <v>6696515</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6648,11 +6652,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6679,10 +6678,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120208684</v>
+        <v>120208828</v>
       </c>
       <c r="B59" t="n">
-        <v>101097</v>
+        <v>4772</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6695,21 +6694,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221235</v>
+        <v>102306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6719,10 +6718,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668201</v>
+        <v>668595</v>
       </c>
       <c r="R59" t="n">
-        <v>6696519</v>
+        <v>6696467</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6781,10 +6780,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120208861</v>
+        <v>120208708</v>
       </c>
       <c r="B60" t="n">
-        <v>100194</v>
+        <v>95478</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6793,25 +6792,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6821,10 +6820,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>668567</v>
+        <v>668376</v>
       </c>
       <c r="R60" t="n">
-        <v>6696809</v>
+        <v>6696595</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6883,7 +6882,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120208857</v>
+        <v>120208861</v>
       </c>
       <c r="B61" t="n">
         <v>100194</v>
@@ -6923,10 +6922,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>668438</v>
+        <v>668567</v>
       </c>
       <c r="R61" t="n">
-        <v>6696512</v>
+        <v>6696809</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6985,10 +6984,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120208703</v>
+        <v>120208860</v>
       </c>
       <c r="B62" t="n">
-        <v>95478</v>
+        <v>100194</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6997,25 +6996,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7025,10 +7024,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>668451</v>
+        <v>668566</v>
       </c>
       <c r="R62" t="n">
-        <v>6696602</v>
+        <v>6696858</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7071,21 +7070,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7102,10 +7086,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120208707</v>
+        <v>120208863</v>
       </c>
       <c r="B63" t="n">
-        <v>95478</v>
+        <v>100194</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7114,25 +7098,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7142,10 +7126,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>668394</v>
+        <v>668568</v>
       </c>
       <c r="R63" t="n">
-        <v>6696553</v>
+        <v>6696542</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7204,10 +7188,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120208744</v>
+        <v>120208812</v>
       </c>
       <c r="B64" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7216,31 +7200,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7249,10 +7237,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>668602</v>
+        <v>668568</v>
       </c>
       <c r="R64" t="n">
-        <v>6696625</v>
+        <v>6696851</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7311,10 +7299,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120208812</v>
+        <v>120208818</v>
       </c>
       <c r="B65" t="n">
-        <v>97930</v>
+        <v>105032</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7323,47 +7311,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>668568</v>
+        <v>668437</v>
       </c>
       <c r="R65" t="n">
-        <v>6696851</v>
+        <v>6696501</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7422,10 +7401,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120208719</v>
+        <v>120208819</v>
       </c>
       <c r="B66" t="n">
-        <v>95478</v>
+        <v>105032</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7434,25 +7413,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7462,10 +7441,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>668514</v>
+        <v>668579</v>
       </c>
       <c r="R66" t="n">
-        <v>6696439</v>
+        <v>6696655</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7524,10 +7503,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120208759</v>
+        <v>120208854</v>
       </c>
       <c r="B67" t="n">
-        <v>57336</v>
+        <v>100194</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7536,43 +7515,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>668572</v>
+        <v>668370</v>
       </c>
       <c r="R67" t="n">
-        <v>6696839</v>
+        <v>6696506</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7605,11 +7579,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7636,10 +7605,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120208830</v>
+        <v>120208705</v>
       </c>
       <c r="B68" t="n">
-        <v>78542</v>
+        <v>95478</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7652,21 +7621,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7676,10 +7645,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>668442</v>
+        <v>668521</v>
       </c>
       <c r="R68" t="n">
-        <v>6696514</v>
+        <v>6696330</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7725,17 +7694,17 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -7753,10 +7722,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120208854</v>
+        <v>120208740</v>
       </c>
       <c r="B69" t="n">
-        <v>100194</v>
+        <v>57473</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7765,38 +7734,46 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>668370</v>
+        <v>668357</v>
       </c>
       <c r="R69" t="n">
-        <v>6696506</v>
+        <v>6696585</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7855,10 +7832,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120208717</v>
+        <v>120208779</v>
       </c>
       <c r="B70" t="n">
-        <v>95478</v>
+        <v>97908</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7867,25 +7844,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7895,10 +7872,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>668468</v>
+        <v>668212</v>
       </c>
       <c r="R70" t="n">
-        <v>6696587</v>
+        <v>6696497</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7957,10 +7934,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120208784</v>
+        <v>120208822</v>
       </c>
       <c r="B71" t="n">
-        <v>91023</v>
+        <v>57339</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7969,38 +7946,46 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1209</v>
+        <v>102977</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>668273</v>
+        <v>668585</v>
       </c>
       <c r="R71" t="n">
-        <v>6696531</v>
+        <v>6696613</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8033,6 +8018,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8059,10 +8049,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120208823</v>
+        <v>120208852</v>
       </c>
       <c r="B72" t="n">
-        <v>57339</v>
+        <v>100194</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8075,42 +8065,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102977</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>668565</v>
+        <v>668230</v>
       </c>
       <c r="R72" t="n">
-        <v>6696520</v>
+        <v>6696502</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8143,11 +8125,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8174,10 +8151,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120208811</v>
+        <v>120208853</v>
       </c>
       <c r="B73" t="n">
-        <v>97930</v>
+        <v>100194</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8186,47 +8163,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>668524</v>
+        <v>668241</v>
       </c>
       <c r="R73" t="n">
-        <v>6696416</v>
+        <v>6696541</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8285,7 +8253,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120208798</v>
+        <v>120208800</v>
       </c>
       <c r="B74" t="n">
         <v>57689</v>
@@ -8318,10 +8286,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8330,10 +8302,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>668342</v>
+        <v>668525</v>
       </c>
       <c r="R74" t="n">
-        <v>6696603</v>
+        <v>6696405</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8392,10 +8364,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120208814</v>
+        <v>120208792</v>
       </c>
       <c r="B75" t="n">
-        <v>74593</v>
+        <v>57326</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8404,38 +8376,46 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6426</v>
+        <v>100048</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>668296</v>
+        <v>668517</v>
       </c>
       <c r="R75" t="n">
-        <v>6696535</v>
+        <v>6696457</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8468,6 +8448,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8494,10 +8479,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120208816</v>
+        <v>120208716</v>
       </c>
       <c r="B76" t="n">
-        <v>56524</v>
+        <v>95478</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8510,21 +8495,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>102612</v>
+        <v>53</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8534,10 +8519,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>668248</v>
+        <v>668439</v>
       </c>
       <c r="R76" t="n">
-        <v>6696628</v>
+        <v>6696517</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8570,11 +8555,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>flög upp från marken</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8601,10 +8581,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120208822</v>
+        <v>120208721</v>
       </c>
       <c r="B77" t="n">
-        <v>57339</v>
+        <v>90580</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8613,46 +8593,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>102977</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>668585</v>
+        <v>668589</v>
       </c>
       <c r="R77" t="n">
-        <v>6696613</v>
+        <v>6696866</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8685,11 +8657,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8716,10 +8683,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120208690</v>
+        <v>120208724</v>
       </c>
       <c r="B78" t="n">
-        <v>101097</v>
+        <v>90580</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8728,25 +8695,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221235</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8756,10 +8723,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>668564</v>
+        <v>668608</v>
       </c>
       <c r="R78" t="n">
-        <v>6696811</v>
+        <v>6696611</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8818,10 +8785,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120208688</v>
+        <v>120208741</v>
       </c>
       <c r="B79" t="n">
-        <v>101097</v>
+        <v>57473</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8830,38 +8797,46 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221235</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>668383</v>
+        <v>668483</v>
       </c>
       <c r="R79" t="n">
-        <v>6696524</v>
+        <v>6696590</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8920,10 +8895,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120208799</v>
+        <v>120208850</v>
       </c>
       <c r="B80" t="n">
-        <v>57689</v>
+        <v>100194</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8936,39 +8911,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>668558</v>
+        <v>668179</v>
       </c>
       <c r="R80" t="n">
-        <v>6696534</v>
+        <v>6696528</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9027,10 +8997,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120208848</v>
+        <v>120208739</v>
       </c>
       <c r="B81" t="n">
-        <v>100194</v>
+        <v>103441</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9043,21 +9013,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9067,10 +9037,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>668419</v>
+        <v>668166</v>
       </c>
       <c r="R81" t="n">
-        <v>6696535</v>
+        <v>6696498</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9129,10 +9099,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120208776</v>
+        <v>120208857</v>
       </c>
       <c r="B82" t="n">
-        <v>97908</v>
+        <v>100194</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9145,21 +9115,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9169,10 +9139,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>668186</v>
+        <v>668438</v>
       </c>
       <c r="R82" t="n">
-        <v>6696508</v>
+        <v>6696512</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9231,10 +9201,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120208710</v>
+        <v>120208776</v>
       </c>
       <c r="B83" t="n">
-        <v>95478</v>
+        <v>97908</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9243,25 +9213,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9271,10 +9241,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>668362</v>
+        <v>668186</v>
       </c>
       <c r="R83" t="n">
-        <v>6696582</v>
+        <v>6696508</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9333,10 +9303,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120208709</v>
+        <v>120208774</v>
       </c>
       <c r="B84" t="n">
-        <v>95478</v>
+        <v>97908</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9345,25 +9315,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9373,10 +9343,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>668362</v>
+        <v>668365</v>
       </c>
       <c r="R84" t="n">
-        <v>6696599</v>
+        <v>6696575</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9435,10 +9405,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120208851</v>
+        <v>120208703</v>
       </c>
       <c r="B85" t="n">
-        <v>100194</v>
+        <v>95478</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9447,25 +9417,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9475,10 +9445,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>668213</v>
+        <v>668451</v>
       </c>
       <c r="R85" t="n">
-        <v>6696494</v>
+        <v>6696602</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9521,6 +9491,21 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -9537,10 +9522,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120208850</v>
+        <v>120208718</v>
       </c>
       <c r="B86" t="n">
-        <v>100194</v>
+        <v>95478</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9549,25 +9534,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9577,10 +9562,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>668179</v>
+        <v>668450</v>
       </c>
       <c r="R86" t="n">
-        <v>6696528</v>
+        <v>6696589</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9639,10 +9624,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120208826</v>
+        <v>120208862</v>
       </c>
       <c r="B87" t="n">
-        <v>4772</v>
+        <v>100194</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9655,21 +9640,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>102306</v>
+        <v>222498</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9679,10 +9664,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>668442</v>
+        <v>668572</v>
       </c>
       <c r="R87" t="n">
-        <v>6696515</v>
+        <v>6696573</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9843,10 +9828,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120208686</v>
+        <v>120208856</v>
       </c>
       <c r="B89" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9859,21 +9844,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9883,10 +9868,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>668242</v>
+        <v>668382</v>
       </c>
       <c r="R89" t="n">
-        <v>6696541</v>
+        <v>6696524</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9945,10 +9930,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120208783</v>
+        <v>120208775</v>
       </c>
       <c r="B90" t="n">
-        <v>90351</v>
+        <v>97908</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9961,21 +9946,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3215</v>
+        <v>219798</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9985,10 +9970,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>668281</v>
+        <v>668180</v>
       </c>
       <c r="R90" t="n">
-        <v>6696528</v>
+        <v>6696501</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10047,10 +10032,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120208815</v>
+        <v>120208830</v>
       </c>
       <c r="B91" t="n">
-        <v>74593</v>
+        <v>78542</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10059,25 +10044,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10087,10 +10072,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>668311</v>
+        <v>668442</v>
       </c>
       <c r="R91" t="n">
-        <v>6696520</v>
+        <v>6696514</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10133,6 +10118,21 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
@@ -10149,10 +10149,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120434321</v>
+        <v>120434322</v>
       </c>
       <c r="B92" t="n">
-        <v>94550</v>
+        <v>95478</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10161,25 +10161,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10189,10 +10189,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>668380</v>
+        <v>668377</v>
       </c>
       <c r="R92" t="n">
-        <v>6696576</v>
+        <v>6696572</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10251,7 +10251,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120434326</v>
+        <v>120434325</v>
       </c>
       <c r="B93" t="n">
         <v>95478</v>
@@ -10291,10 +10291,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>668475</v>
+        <v>668456</v>
       </c>
       <c r="R93" t="n">
-        <v>6696461</v>
+        <v>6696470</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10368,10 +10368,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120434323</v>
+        <v>120434321</v>
       </c>
       <c r="B94" t="n">
-        <v>74593</v>
+        <v>94550</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10384,21 +10384,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6426</v>
+        <v>210</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>668320</v>
+        <v>668380</v>
       </c>
       <c r="R94" t="n">
-        <v>6696515</v>
+        <v>6696576</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10454,21 +10454,6 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -10485,10 +10470,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120434322</v>
+        <v>120434323</v>
       </c>
       <c r="B95" t="n">
-        <v>95478</v>
+        <v>74593</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10497,25 +10482,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10525,10 +10510,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>668377</v>
+        <v>668320</v>
       </c>
       <c r="R95" t="n">
-        <v>6696572</v>
+        <v>6696515</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10571,6 +10556,21 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -10587,7 +10587,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120434325</v>
+        <v>120434326</v>
       </c>
       <c r="B96" t="n">
         <v>95478</v>
@@ -10627,10 +10627,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>668456</v>
+        <v>668475</v>
       </c>
       <c r="R96" t="n">
-        <v>6696470</v>
+        <v>6696461</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120208811</v>
+        <v>120208759</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,35 +1429,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1466,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>668524</v>
+        <v>668572</v>
       </c>
       <c r="R9" t="n">
-        <v>6696416</v>
+        <v>6696839</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,6 +1498,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120208684</v>
+        <v>120208851</v>
       </c>
       <c r="B10" t="n">
-        <v>101097</v>
+        <v>100194</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,21 +1545,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>668201</v>
+        <v>668213</v>
       </c>
       <c r="R10" t="n">
-        <v>6696519</v>
+        <v>6696494</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1630,7 +1631,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120208851</v>
+        <v>120208855</v>
       </c>
       <c r="B11" t="n">
         <v>100194</v>
@@ -1670,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>668213</v>
+        <v>668380</v>
       </c>
       <c r="R11" t="n">
-        <v>6696494</v>
+        <v>6696528</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,10 +1733,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120208855</v>
+        <v>120208811</v>
       </c>
       <c r="B12" t="n">
-        <v>100194</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1744,38 +1745,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>668380</v>
+        <v>668524</v>
       </c>
       <c r="R12" t="n">
-        <v>6696528</v>
+        <v>6696416</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,10 +1844,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120208719</v>
+        <v>120208684</v>
       </c>
       <c r="B13" t="n">
-        <v>95478</v>
+        <v>101097</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1846,25 +1856,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>221235</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1874,10 +1884,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>668514</v>
+        <v>668201</v>
       </c>
       <c r="R13" t="n">
-        <v>6696439</v>
+        <v>6696519</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1936,10 +1946,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120208737</v>
+        <v>120208719</v>
       </c>
       <c r="B14" t="n">
-        <v>56532</v>
+        <v>95478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1948,43 +1958,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>668566</v>
+        <v>668514</v>
       </c>
       <c r="R14" t="n">
-        <v>6696455</v>
+        <v>6696439</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2017,11 +2022,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,10 +2150,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120208759</v>
+        <v>120208737</v>
       </c>
       <c r="B16" t="n">
-        <v>57336</v>
+        <v>56532</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2162,31 +2162,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>668572</v>
+        <v>668566</v>
       </c>
       <c r="R16" t="n">
-        <v>6696839</v>
+        <v>6696455</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>hackmärken i död ved</t>
+          <t>Fjädrar efter en slagen tjäder</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3078,10 +3078,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120208756</v>
+        <v>120208798</v>
       </c>
       <c r="B25" t="n">
-        <v>57336</v>
+        <v>57689</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3090,20 +3090,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3114,7 +3114,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3123,10 +3123,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>668467</v>
+        <v>668342</v>
       </c>
       <c r="R25" t="n">
-        <v>6696630</v>
+        <v>6696603</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3159,11 +3159,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3190,10 +3185,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120208798</v>
+        <v>120208756</v>
       </c>
       <c r="B26" t="n">
-        <v>57689</v>
+        <v>57336</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3202,20 +3197,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3226,7 +3221,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3235,10 +3230,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>668342</v>
+        <v>668467</v>
       </c>
       <c r="R26" t="n">
-        <v>6696603</v>
+        <v>6696630</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3271,6 +3266,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>hackmärken i död ved</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4875,10 +4875,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120208706</v>
+        <v>120208782</v>
       </c>
       <c r="B42" t="n">
-        <v>95478</v>
+        <v>97908</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4887,25 +4887,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>219798</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>668408</v>
+        <v>668279</v>
       </c>
       <c r="R42" t="n">
-        <v>6696562</v>
+        <v>6696528</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4977,7 +4977,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120208717</v>
+        <v>120208706</v>
       </c>
       <c r="B43" t="n">
         <v>95478</v>
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>668468</v>
+        <v>668408</v>
       </c>
       <c r="R43" t="n">
-        <v>6696587</v>
+        <v>6696562</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5079,7 +5079,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120208704</v>
+        <v>120208717</v>
       </c>
       <c r="B44" t="n">
         <v>95478</v>
@@ -5119,10 +5119,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>668571</v>
+        <v>668468</v>
       </c>
       <c r="R44" t="n">
-        <v>6696816</v>
+        <v>6696587</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5165,21 +5165,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5196,10 +5181,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120208722</v>
+        <v>120208704</v>
       </c>
       <c r="B45" t="n">
-        <v>90580</v>
+        <v>95478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5212,21 +5197,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5236,10 +5221,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>668552</v>
+        <v>668571</v>
       </c>
       <c r="R45" t="n">
-        <v>6696684</v>
+        <v>6696816</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5282,6 +5267,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5298,10 +5298,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120208711</v>
+        <v>120208722</v>
       </c>
       <c r="B46" t="n">
-        <v>95478</v>
+        <v>90580</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5314,21 +5314,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5338,10 +5338,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>668345</v>
+        <v>668552</v>
       </c>
       <c r="R46" t="n">
-        <v>6696598</v>
+        <v>6696684</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5400,10 +5400,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120208782</v>
+        <v>120208711</v>
       </c>
       <c r="B47" t="n">
-        <v>97908</v>
+        <v>95478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5412,25 +5412,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219798</v>
+        <v>53</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5440,10 +5440,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>668279</v>
+        <v>668345</v>
       </c>
       <c r="R47" t="n">
-        <v>6696528</v>
+        <v>6696598</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5502,10 +5502,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120208791</v>
+        <v>120208813</v>
       </c>
       <c r="B48" t="n">
-        <v>57326</v>
+        <v>97930</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5514,46 +5514,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100048</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>668520</v>
+        <v>668575</v>
       </c>
       <c r="R48" t="n">
-        <v>6696377</v>
+        <v>6696701</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5586,11 +5587,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5617,10 +5613,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120208813</v>
+        <v>120208778</v>
       </c>
       <c r="B49" t="n">
-        <v>97930</v>
+        <v>97908</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5629,47 +5625,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>219798</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>668575</v>
+        <v>668191</v>
       </c>
       <c r="R49" t="n">
-        <v>6696701</v>
+        <v>6696527</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5728,10 +5715,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120208778</v>
+        <v>120208791</v>
       </c>
       <c r="B50" t="n">
-        <v>97908</v>
+        <v>57326</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5740,38 +5727,46 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219798</v>
+        <v>100048</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>668191</v>
+        <v>668520</v>
       </c>
       <c r="R50" t="n">
-        <v>6696527</v>
+        <v>6696377</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5804,6 +5799,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5830,10 +5830,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120208714</v>
+        <v>120208735</v>
       </c>
       <c r="B51" t="n">
-        <v>95478</v>
+        <v>56532</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5842,38 +5842,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>668369</v>
+        <v>668518</v>
       </c>
       <c r="R51" t="n">
-        <v>6696540</v>
+        <v>6696678</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5906,6 +5915,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5932,10 +5946,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120208815</v>
+        <v>120208743</v>
       </c>
       <c r="B52" t="n">
-        <v>74593</v>
+        <v>57473</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5944,38 +5958,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>668311</v>
+        <v>668533</v>
       </c>
       <c r="R52" t="n">
-        <v>6696520</v>
+        <v>6696366</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6034,10 +6056,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120208735</v>
+        <v>120208815</v>
       </c>
       <c r="B53" t="n">
-        <v>56532</v>
+        <v>74593</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6050,43 +6072,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>668518</v>
+        <v>668311</v>
       </c>
       <c r="R53" t="n">
-        <v>6696678</v>
+        <v>6696520</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6119,11 +6132,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Stötte upp</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6150,10 +6158,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120208743</v>
+        <v>120208714</v>
       </c>
       <c r="B54" t="n">
-        <v>57473</v>
+        <v>95478</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6166,42 +6174,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>668533</v>
+        <v>668369</v>
       </c>
       <c r="R54" t="n">
-        <v>6696366</v>
+        <v>6696540</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6260,10 +6260,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120208744</v>
+        <v>120208858</v>
       </c>
       <c r="B55" t="n">
-        <v>57473</v>
+        <v>100194</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6272,43 +6272,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>668602</v>
+        <v>668564</v>
       </c>
       <c r="R55" t="n">
-        <v>6696625</v>
+        <v>6696816</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6367,10 +6362,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120208858</v>
+        <v>120208816</v>
       </c>
       <c r="B56" t="n">
-        <v>100194</v>
+        <v>56524</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6379,25 +6374,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>102612</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6407,10 +6402,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>668564</v>
+        <v>668248</v>
       </c>
       <c r="R56" t="n">
-        <v>6696816</v>
+        <v>6696628</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6443,6 +6438,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>flög upp från marken</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6469,10 +6469,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120208816</v>
+        <v>120208826</v>
       </c>
       <c r="B57" t="n">
-        <v>56524</v>
+        <v>4772</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6481,25 +6481,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102612</v>
+        <v>102306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6509,10 +6509,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>668248</v>
+        <v>668442</v>
       </c>
       <c r="R57" t="n">
-        <v>6696628</v>
+        <v>6696515</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6545,11 +6545,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-10-04</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>flög upp från marken</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6576,7 +6571,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120208826</v>
+        <v>120208828</v>
       </c>
       <c r="B58" t="n">
         <v>4772</v>
@@ -6616,10 +6611,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>668442</v>
+        <v>668595</v>
       </c>
       <c r="R58" t="n">
-        <v>6696515</v>
+        <v>6696467</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6678,10 +6673,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120208828</v>
+        <v>120208744</v>
       </c>
       <c r="B59" t="n">
-        <v>4772</v>
+        <v>57473</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6690,38 +6685,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102306</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Södra Västermarken, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>668595</v>
+        <v>668602</v>
       </c>
       <c r="R59" t="n">
-        <v>6696467</v>
+        <v>6696625</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -10704,10 +10704,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124393169</v>
+        <v>124393186</v>
       </c>
       <c r="B97" t="n">
-        <v>95455</v>
+        <v>74840</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10720,21 +10720,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10744,10 +10744,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>668156</v>
+        <v>668224</v>
       </c>
       <c r="R97" t="n">
-        <v>6696531</v>
+        <v>6696606</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10821,10 +10821,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124393186</v>
+        <v>124393191</v>
       </c>
       <c r="B98" t="n">
-        <v>74840</v>
+        <v>78810</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10833,25 +10833,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10861,10 +10861,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>668224</v>
+        <v>668413</v>
       </c>
       <c r="R98" t="n">
-        <v>6696606</v>
+        <v>6696637</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124393191</v>
+        <v>124393169</v>
       </c>
       <c r="B100" t="n">
-        <v>78810</v>
+        <v>95455</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11067,25 +11067,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>2818</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11095,10 +11095,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>668413</v>
+        <v>668156</v>
       </c>
       <c r="R100" t="n">
-        <v>6696637</v>
+        <v>6696531</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -10704,10 +10704,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124393186</v>
+        <v>124393187</v>
       </c>
       <c r="B97" t="n">
-        <v>74840</v>
+        <v>95551</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10720,21 +10720,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6426</v>
+        <v>210</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10744,10 +10744,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>668224</v>
+        <v>668151</v>
       </c>
       <c r="R97" t="n">
-        <v>6696606</v>
+        <v>6696537</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10821,10 +10821,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124393191</v>
+        <v>124393169</v>
       </c>
       <c r="B98" t="n">
-        <v>78810</v>
+        <v>95455</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10833,25 +10833,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>2818</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10861,10 +10861,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>668413</v>
+        <v>668156</v>
       </c>
       <c r="R98" t="n">
-        <v>6696637</v>
+        <v>6696531</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10938,10 +10938,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124393187</v>
+        <v>124393191</v>
       </c>
       <c r="B99" t="n">
-        <v>95551</v>
+        <v>78810</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10950,25 +10950,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>210</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>668151</v>
+        <v>668413</v>
       </c>
       <c r="R99" t="n">
-        <v>6696537</v>
+        <v>6696637</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124393169</v>
+        <v>124393186</v>
       </c>
       <c r="B100" t="n">
-        <v>95455</v>
+        <v>74840</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11071,21 +11071,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11095,10 +11095,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>668156</v>
+        <v>668224</v>
       </c>
       <c r="R100" t="n">
-        <v>6696531</v>
+        <v>6696606</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -10704,10 +10704,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124393187</v>
+        <v>124393191</v>
       </c>
       <c r="B97" t="n">
-        <v>95551</v>
+        <v>78810</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10716,25 +10716,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>210</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10744,10 +10744,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>668151</v>
+        <v>668413</v>
       </c>
       <c r="R97" t="n">
-        <v>6696537</v>
+        <v>6696637</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10821,10 +10821,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124393169</v>
+        <v>124393186</v>
       </c>
       <c r="B98" t="n">
-        <v>95455</v>
+        <v>74840</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10837,21 +10837,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10861,10 +10861,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>668156</v>
+        <v>668224</v>
       </c>
       <c r="R98" t="n">
-        <v>6696531</v>
+        <v>6696606</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10938,10 +10938,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124393191</v>
+        <v>124393169</v>
       </c>
       <c r="B99" t="n">
-        <v>78810</v>
+        <v>95455</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10950,25 +10950,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>2818</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>668413</v>
+        <v>668156</v>
       </c>
       <c r="R99" t="n">
-        <v>6696637</v>
+        <v>6696531</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124393186</v>
+        <v>124393187</v>
       </c>
       <c r="B100" t="n">
-        <v>74840</v>
+        <v>95551</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11071,21 +11071,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6426</v>
+        <v>210</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11095,10 +11095,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>668224</v>
+        <v>668151</v>
       </c>
       <c r="R100" t="n">
-        <v>6696606</v>
+        <v>6696537</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -10938,10 +10938,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124393169</v>
+        <v>124393187</v>
       </c>
       <c r="B99" t="n">
-        <v>95455</v>
+        <v>95551</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10954,21 +10954,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>668156</v>
+        <v>668151</v>
       </c>
       <c r="R99" t="n">
-        <v>6696531</v>
+        <v>6696537</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124393187</v>
+        <v>124393169</v>
       </c>
       <c r="B100" t="n">
-        <v>95551</v>
+        <v>95455</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11071,21 +11071,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11095,10 +11095,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>668151</v>
+        <v>668156</v>
       </c>
       <c r="R100" t="n">
-        <v>6696537</v>
+        <v>6696531</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -10704,10 +10704,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124393191</v>
+        <v>124393169</v>
       </c>
       <c r="B97" t="n">
-        <v>78810</v>
+        <v>95455</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10716,25 +10716,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>2818</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10744,10 +10744,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>668413</v>
+        <v>668156</v>
       </c>
       <c r="R97" t="n">
-        <v>6696637</v>
+        <v>6696531</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10821,10 +10821,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124393186</v>
+        <v>124393187</v>
       </c>
       <c r="B98" t="n">
-        <v>74840</v>
+        <v>95551</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10837,21 +10837,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6426</v>
+        <v>210</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10861,10 +10861,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>668224</v>
+        <v>668151</v>
       </c>
       <c r="R98" t="n">
-        <v>6696606</v>
+        <v>6696537</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10938,10 +10938,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124393187</v>
+        <v>124393186</v>
       </c>
       <c r="B99" t="n">
-        <v>95551</v>
+        <v>74840</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10954,21 +10954,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>210</v>
+        <v>6426</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>668151</v>
+        <v>668224</v>
       </c>
       <c r="R99" t="n">
-        <v>6696537</v>
+        <v>6696606</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124393169</v>
+        <v>124393191</v>
       </c>
       <c r="B100" t="n">
-        <v>95455</v>
+        <v>78810</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11067,25 +11067,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2818</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11095,10 +11095,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>668156</v>
+        <v>668413</v>
       </c>
       <c r="R100" t="n">
-        <v>6696531</v>
+        <v>6696637</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -10704,10 +10704,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124393169</v>
+        <v>124393186</v>
       </c>
       <c r="B97" t="n">
-        <v>95455</v>
+        <v>74840</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10720,21 +10720,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10744,10 +10744,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>668156</v>
+        <v>668224</v>
       </c>
       <c r="R97" t="n">
-        <v>6696531</v>
+        <v>6696606</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10938,10 +10938,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124393186</v>
+        <v>124393169</v>
       </c>
       <c r="B99" t="n">
-        <v>74840</v>
+        <v>95455</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10954,21 +10954,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>668224</v>
+        <v>668156</v>
       </c>
       <c r="R99" t="n">
-        <v>6696606</v>
+        <v>6696531</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -10704,10 +10704,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124393186</v>
+        <v>124393191</v>
       </c>
       <c r="B97" t="n">
-        <v>74840</v>
+        <v>78810</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10716,25 +10716,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10744,10 +10744,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>668224</v>
+        <v>668413</v>
       </c>
       <c r="R97" t="n">
-        <v>6696606</v>
+        <v>6696637</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10821,10 +10821,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124393187</v>
+        <v>124393169</v>
       </c>
       <c r="B98" t="n">
-        <v>95551</v>
+        <v>95455</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10837,21 +10837,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10861,10 +10861,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>668151</v>
+        <v>668156</v>
       </c>
       <c r="R98" t="n">
-        <v>6696537</v>
+        <v>6696531</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10938,10 +10938,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124393169</v>
+        <v>124393187</v>
       </c>
       <c r="B99" t="n">
-        <v>95455</v>
+        <v>95551</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10954,21 +10954,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>668156</v>
+        <v>668151</v>
       </c>
       <c r="R99" t="n">
-        <v>6696531</v>
+        <v>6696537</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124393191</v>
+        <v>124393186</v>
       </c>
       <c r="B100" t="n">
-        <v>78810</v>
+        <v>74840</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11067,25 +11067,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11095,10 +11095,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>668413</v>
+        <v>668224</v>
       </c>
       <c r="R100" t="n">
-        <v>6696637</v>
+        <v>6696606</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -10704,10 +10704,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124393191</v>
+        <v>124393186</v>
       </c>
       <c r="B97" t="n">
-        <v>78810</v>
+        <v>74840</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10716,25 +10716,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10744,10 +10744,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>668413</v>
+        <v>668224</v>
       </c>
       <c r="R97" t="n">
-        <v>6696637</v>
+        <v>6696606</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10821,10 +10821,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124393169</v>
+        <v>124393187</v>
       </c>
       <c r="B98" t="n">
-        <v>95455</v>
+        <v>95551</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10837,21 +10837,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10861,10 +10861,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>668156</v>
+        <v>668151</v>
       </c>
       <c r="R98" t="n">
-        <v>6696531</v>
+        <v>6696537</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10938,10 +10938,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124393187</v>
+        <v>124393169</v>
       </c>
       <c r="B99" t="n">
-        <v>95551</v>
+        <v>95455</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10954,21 +10954,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>668151</v>
+        <v>668156</v>
       </c>
       <c r="R99" t="n">
-        <v>6696537</v>
+        <v>6696531</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124393186</v>
+        <v>124393191</v>
       </c>
       <c r="B100" t="n">
-        <v>74840</v>
+        <v>78810</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11067,25 +11067,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11095,10 +11095,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>668224</v>
+        <v>668413</v>
       </c>
       <c r="R100" t="n">
-        <v>6696606</v>
+        <v>6696637</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -10821,10 +10821,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124393187</v>
+        <v>124393191</v>
       </c>
       <c r="B98" t="n">
-        <v>95551</v>
+        <v>78810</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10833,25 +10833,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>210</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10861,10 +10861,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>668151</v>
+        <v>668413</v>
       </c>
       <c r="R98" t="n">
-        <v>6696537</v>
+        <v>6696637</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10938,10 +10938,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124393169</v>
+        <v>124393187</v>
       </c>
       <c r="B99" t="n">
-        <v>95455</v>
+        <v>95551</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10954,21 +10954,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>668156</v>
+        <v>668151</v>
       </c>
       <c r="R99" t="n">
-        <v>6696531</v>
+        <v>6696537</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124393191</v>
+        <v>124393169</v>
       </c>
       <c r="B100" t="n">
-        <v>78810</v>
+        <v>95455</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11067,25 +11067,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>2818</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11095,10 +11095,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>668413</v>
+        <v>668156</v>
       </c>
       <c r="R100" t="n">
-        <v>6696637</v>
+        <v>6696531</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -10704,10 +10704,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124393186</v>
+        <v>124393187</v>
       </c>
       <c r="B97" t="n">
-        <v>74840</v>
+        <v>95551</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10720,21 +10720,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6426</v>
+        <v>210</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10744,10 +10744,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>668224</v>
+        <v>668151</v>
       </c>
       <c r="R97" t="n">
-        <v>6696606</v>
+        <v>6696537</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10821,10 +10821,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124393191</v>
+        <v>124393186</v>
       </c>
       <c r="B98" t="n">
-        <v>78810</v>
+        <v>74840</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10833,25 +10833,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10861,10 +10861,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>668413</v>
+        <v>668224</v>
       </c>
       <c r="R98" t="n">
-        <v>6696637</v>
+        <v>6696606</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10938,10 +10938,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124393187</v>
+        <v>124393169</v>
       </c>
       <c r="B99" t="n">
-        <v>95551</v>
+        <v>95455</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10954,21 +10954,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>668151</v>
+        <v>668156</v>
       </c>
       <c r="R99" t="n">
-        <v>6696537</v>
+        <v>6696531</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124393169</v>
+        <v>124393191</v>
       </c>
       <c r="B100" t="n">
-        <v>95455</v>
+        <v>78810</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11067,25 +11067,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2818</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11095,10 +11095,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>668156</v>
+        <v>668413</v>
       </c>
       <c r="R100" t="n">
-        <v>6696531</v>
+        <v>6696637</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -10821,10 +10821,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124393186</v>
+        <v>124393169</v>
       </c>
       <c r="B98" t="n">
-        <v>74840</v>
+        <v>95455</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10837,21 +10837,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10861,10 +10861,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>668224</v>
+        <v>668156</v>
       </c>
       <c r="R98" t="n">
-        <v>6696606</v>
+        <v>6696531</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10938,10 +10938,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124393169</v>
+        <v>124393186</v>
       </c>
       <c r="B99" t="n">
-        <v>95455</v>
+        <v>74840</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10954,21 +10954,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>668156</v>
+        <v>668224</v>
       </c>
       <c r="R99" t="n">
-        <v>6696531</v>
+        <v>6696606</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -10704,10 +10704,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124393187</v>
+        <v>124393169</v>
       </c>
       <c r="B97" t="n">
-        <v>95551</v>
+        <v>95455</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10720,21 +10720,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10744,10 +10744,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>668151</v>
+        <v>668156</v>
       </c>
       <c r="R97" t="n">
-        <v>6696537</v>
+        <v>6696531</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10821,10 +10821,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124393169</v>
+        <v>124393191</v>
       </c>
       <c r="B98" t="n">
-        <v>95455</v>
+        <v>78810</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10833,25 +10833,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2818</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10861,10 +10861,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>668156</v>
+        <v>668413</v>
       </c>
       <c r="R98" t="n">
-        <v>6696531</v>
+        <v>6696637</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -10938,10 +10938,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124393186</v>
+        <v>124393187</v>
       </c>
       <c r="B99" t="n">
-        <v>74840</v>
+        <v>95551</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10954,21 +10954,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6426</v>
+        <v>210</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>668224</v>
+        <v>668151</v>
       </c>
       <c r="R99" t="n">
-        <v>6696606</v>
+        <v>6696537</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124393191</v>
+        <v>124393186</v>
       </c>
       <c r="B100" t="n">
-        <v>78810</v>
+        <v>74840</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11067,25 +11067,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11095,10 +11095,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>668413</v>
+        <v>668224</v>
       </c>
       <c r="R100" t="n">
-        <v>6696637</v>
+        <v>6696606</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -10704,10 +10704,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124393169</v>
+        <v>124393186</v>
       </c>
       <c r="B97" t="n">
-        <v>95455</v>
+        <v>74840</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10720,21 +10720,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10744,10 +10744,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>668156</v>
+        <v>668224</v>
       </c>
       <c r="R97" t="n">
-        <v>6696531</v>
+        <v>6696606</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -10938,10 +10938,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124393187</v>
+        <v>124393169</v>
       </c>
       <c r="B99" t="n">
-        <v>95551</v>
+        <v>95455</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10954,21 +10954,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>668151</v>
+        <v>668156</v>
       </c>
       <c r="R99" t="n">
-        <v>6696537</v>
+        <v>6696531</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124393186</v>
+        <v>124393187</v>
       </c>
       <c r="B100" t="n">
-        <v>74840</v>
+        <v>95551</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11071,21 +11071,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6426</v>
+        <v>210</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11095,10 +11095,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>668224</v>
+        <v>668151</v>
       </c>
       <c r="R100" t="n">
-        <v>6696606</v>
+        <v>6696537</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -10821,10 +10821,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124393191</v>
+        <v>124393187</v>
       </c>
       <c r="B98" t="n">
-        <v>78810</v>
+        <v>95551</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10833,25 +10833,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>210</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10861,10 +10861,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>668413</v>
+        <v>668151</v>
       </c>
       <c r="R98" t="n">
-        <v>6696637</v>
+        <v>6696537</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -11055,10 +11055,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124393187</v>
+        <v>124393191</v>
       </c>
       <c r="B100" t="n">
-        <v>95551</v>
+        <v>78810</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11067,25 +11067,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>210</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11095,10 +11095,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>668151</v>
+        <v>668413</v>
       </c>
       <c r="R100" t="n">
-        <v>6696537</v>
+        <v>6696637</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY100"/>
+  <dimension ref="A1:AY167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11170,6 +11170,7154 @@
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>129528815</v>
+      </c>
+      <c r="B101" t="n">
+        <v>101823</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>668434</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6696572</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>129617873</v>
+      </c>
+      <c r="B102" t="n">
+        <v>92871</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>668264</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6696500</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>129609957</v>
+      </c>
+      <c r="B103" t="n">
+        <v>88740</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>4379</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Toppvaxing</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Hygrocybe conica</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>668194</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6696543</v>
+      </c>
+      <c r="S103" t="n">
+        <v>5</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>129610638</v>
+      </c>
+      <c r="B104" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>668314</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6696563</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>129610538</v>
+      </c>
+      <c r="B105" t="n">
+        <v>101823</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>668247</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6696545</v>
+      </c>
+      <c r="S105" t="n">
+        <v>5</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>129527202</v>
+      </c>
+      <c r="B106" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>668552</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6696416</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>129528876</v>
+      </c>
+      <c r="B107" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>668483</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6696587</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>129662449</v>
+      </c>
+      <c r="B108" t="n">
+        <v>91081</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>668437</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6696515</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Växer in 2-3 m ø ring runt smultronkantarell</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; gran intill men med tall inom rotavstånd.</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>129528780</v>
+      </c>
+      <c r="B109" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>668449</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6696572</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>129610545</v>
+      </c>
+      <c r="B110" t="n">
+        <v>92871</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>668300</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6696555</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>129527352</v>
+      </c>
+      <c r="B111" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>668516</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6696461</v>
+      </c>
+      <c r="S111" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>129528869</v>
+      </c>
+      <c r="B112" t="n">
+        <v>98761</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>668470</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6696562</v>
+      </c>
+      <c r="S112" t="n">
+        <v>5</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>129528987</v>
+      </c>
+      <c r="B113" t="n">
+        <v>98647</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>668525</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6696572</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>129617663</v>
+      </c>
+      <c r="B114" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>668387</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6696641</v>
+      </c>
+      <c r="S114" t="n">
+        <v>5</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>129609831</v>
+      </c>
+      <c r="B115" t="n">
+        <v>92508</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>668186</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6696475</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>129528857</v>
+      </c>
+      <c r="B116" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>668474</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6696557</v>
+      </c>
+      <c r="S116" t="n">
+        <v>25</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>129525668</v>
+      </c>
+      <c r="B117" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>668562</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6696327</v>
+      </c>
+      <c r="S117" t="n">
+        <v>5</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>129617669</v>
+      </c>
+      <c r="B118" t="n">
+        <v>58558</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>668387</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6696641</v>
+      </c>
+      <c r="S118" t="n">
+        <v>5</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>129610357</v>
+      </c>
+      <c r="B119" t="n">
+        <v>92871</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>668132</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6696568</v>
+      </c>
+      <c r="S119" t="n">
+        <v>5</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>129610493</v>
+      </c>
+      <c r="B120" t="n">
+        <v>92508</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>668244</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6696585</v>
+      </c>
+      <c r="S120" t="n">
+        <v>5</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>129528940</v>
+      </c>
+      <c r="B121" t="n">
+        <v>92508</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>668489</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6696575</v>
+      </c>
+      <c r="S121" t="n">
+        <v>5</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>129610650</v>
+      </c>
+      <c r="B122" t="n">
+        <v>92508</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>668349</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6696573</v>
+      </c>
+      <c r="S122" t="n">
+        <v>5</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>129610554</v>
+      </c>
+      <c r="B123" t="n">
+        <v>92508</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>668301</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6696575</v>
+      </c>
+      <c r="S123" t="n">
+        <v>5</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>129610501</v>
+      </c>
+      <c r="B124" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>668257</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6696575</v>
+      </c>
+      <c r="S124" t="n">
+        <v>5</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>129610447</v>
+      </c>
+      <c r="B125" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>668177</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6696570</v>
+      </c>
+      <c r="S125" t="n">
+        <v>5</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>129609949</v>
+      </c>
+      <c r="B126" t="n">
+        <v>104198</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>668189</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6696541</v>
+      </c>
+      <c r="S126" t="n">
+        <v>5</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>129529116</v>
+      </c>
+      <c r="B127" t="n">
+        <v>92847</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>668541</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6696479</v>
+      </c>
+      <c r="S127" t="n">
+        <v>5</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>129528822</v>
+      </c>
+      <c r="B128" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>668431</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6696579</v>
+      </c>
+      <c r="S128" t="n">
+        <v>5</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>129609938</v>
+      </c>
+      <c r="B129" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>668185</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6696506</v>
+      </c>
+      <c r="S129" t="n">
+        <v>5</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129617642</v>
+      </c>
+      <c r="B130" t="n">
+        <v>92871</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>668384</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6696663</v>
+      </c>
+      <c r="S130" t="n">
+        <v>5</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>129609966</v>
+      </c>
+      <c r="B131" t="n">
+        <v>92871</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>668187</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6696536</v>
+      </c>
+      <c r="S131" t="n">
+        <v>5</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF131" t="inlineStr"/>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>129617840</v>
+      </c>
+      <c r="B132" t="n">
+        <v>98761</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>668276</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6696503</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>129610655</v>
+      </c>
+      <c r="B133" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>668355</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6696569</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>129528897</v>
+      </c>
+      <c r="B134" t="n">
+        <v>101823</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>668488</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6696584</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>129610602</v>
+      </c>
+      <c r="B135" t="n">
+        <v>91098</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>6039940</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Mandarinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Ramaria tridentina</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Schild</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>668293</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6696561</v>
+      </c>
+      <c r="S135" t="n">
+        <v>5</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog under gran</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>129609920</v>
+      </c>
+      <c r="B136" t="n">
+        <v>92508</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>668179</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6696523</v>
+      </c>
+      <c r="S136" t="n">
+        <v>25</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF136" t="inlineStr"/>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>129610462</v>
+      </c>
+      <c r="B137" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>668179</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6696587</v>
+      </c>
+      <c r="S137" t="n">
+        <v>5</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF137" t="inlineStr"/>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>129528814</v>
+      </c>
+      <c r="B138" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>668434</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6696572</v>
+      </c>
+      <c r="S138" t="n">
+        <v>5</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>129528947</v>
+      </c>
+      <c r="B139" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>668522</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6696581</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF139" t="inlineStr"/>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>129527256</v>
+      </c>
+      <c r="B140" t="n">
+        <v>58586</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>668515</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6696421</v>
+      </c>
+      <c r="S140" t="n">
+        <v>5</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>129528723</v>
+      </c>
+      <c r="B141" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>668464</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6696569</v>
+      </c>
+      <c r="S141" t="n">
+        <v>5</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF141" t="inlineStr"/>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>129528546</v>
+      </c>
+      <c r="B142" t="n">
+        <v>88853</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>816</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Smultronkantarell</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Aphroditeola olida</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>668437</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6696515</v>
+      </c>
+      <c r="S142" t="n">
+        <v>5</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>Med gran och tall, omgiven av en Ramaria pallida. Kalk</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>129609795</v>
+      </c>
+      <c r="B143" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>668206</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6696477</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>129524780</v>
+      </c>
+      <c r="B144" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>668560</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6696304</v>
+      </c>
+      <c r="S144" t="n">
+        <v>5</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>129528853</v>
+      </c>
+      <c r="B145" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>668474</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6696547</v>
+      </c>
+      <c r="S145" t="n">
+        <v>25</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>129610679</v>
+      </c>
+      <c r="B146" t="n">
+        <v>91088</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>668330</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6696584</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>Gran, men finns tall; kalk</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>129528840</v>
+      </c>
+      <c r="B147" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>668462</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6696584</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>129610551</v>
+      </c>
+      <c r="B148" t="n">
+        <v>92871</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>668301</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6696575</v>
+      </c>
+      <c r="S148" t="n">
+        <v>5</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>129610013</v>
+      </c>
+      <c r="B149" t="n">
+        <v>92847</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>668130</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6696576</v>
+      </c>
+      <c r="S149" t="n">
+        <v>5</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF149" t="inlineStr"/>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>129609952</v>
+      </c>
+      <c r="B150" t="n">
+        <v>101823</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>668194</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6696543</v>
+      </c>
+      <c r="S150" t="n">
+        <v>5</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF150" t="inlineStr"/>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>129528942</v>
+      </c>
+      <c r="B151" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>668496</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6696582</v>
+      </c>
+      <c r="S151" t="n">
+        <v>5</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>129529126</v>
+      </c>
+      <c r="B152" t="n">
+        <v>100916</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>668512</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6696456</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>129526765</v>
+      </c>
+      <c r="B153" t="n">
+        <v>97598</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>668522</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6696350</v>
+      </c>
+      <c r="S153" t="n">
+        <v>5</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF153" t="inlineStr"/>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>129610394</v>
+      </c>
+      <c r="B154" t="n">
+        <v>92847</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>668132</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6696568</v>
+      </c>
+      <c r="S154" t="n">
+        <v>5</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF154" t="inlineStr"/>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>129528072</v>
+      </c>
+      <c r="B155" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>668498</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6696426</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>129609794</v>
+      </c>
+      <c r="B156" t="n">
+        <v>92508</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>668206</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6696477</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF156" t="inlineStr"/>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>129610543</v>
+      </c>
+      <c r="B157" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>668294</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6696541</v>
+      </c>
+      <c r="S157" t="n">
+        <v>5</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF157" t="inlineStr"/>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>129609986</v>
+      </c>
+      <c r="B158" t="n">
+        <v>92508</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>668169</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6696511</v>
+      </c>
+      <c r="S158" t="n">
+        <v>5</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF158" t="inlineStr"/>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>129610547</v>
+      </c>
+      <c r="B159" t="n">
+        <v>104198</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>668304</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6696565</v>
+      </c>
+      <c r="S159" t="n">
+        <v>5</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF159" t="inlineStr"/>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>129610541</v>
+      </c>
+      <c r="B160" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>668266</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6696524</v>
+      </c>
+      <c r="S160" t="n">
+        <v>5</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF160" t="inlineStr"/>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>129610475</v>
+      </c>
+      <c r="B161" t="n">
+        <v>92508</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>668225</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6696609</v>
+      </c>
+      <c r="S161" t="n">
+        <v>5</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF161" t="inlineStr"/>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>129528930</v>
+      </c>
+      <c r="B162" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>668489</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6696575</v>
+      </c>
+      <c r="S162" t="n">
+        <v>5</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF162" t="inlineStr"/>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>129609969</v>
+      </c>
+      <c r="B163" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>668169</v>
+      </c>
+      <c r="R163" t="n">
+        <v>6696511</v>
+      </c>
+      <c r="S163" t="n">
+        <v>5</v>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF163" t="inlineStr"/>
+      <c r="AG163" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="inlineStr"/>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>129610636</v>
+      </c>
+      <c r="B164" t="n">
+        <v>87005</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>668306</v>
+      </c>
+      <c r="R164" t="n">
+        <v>6696570</v>
+      </c>
+      <c r="S164" t="n">
+        <v>5</v>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF164" t="inlineStr"/>
+      <c r="AG164" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
+      </c>
+      <c r="AT164" t="inlineStr"/>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>129528721</v>
+      </c>
+      <c r="B165" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>668471</v>
+      </c>
+      <c r="R165" t="n">
+        <v>6696556</v>
+      </c>
+      <c r="S165" t="n">
+        <v>5</v>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF165" t="inlineStr"/>
+      <c r="AG165" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="inlineStr"/>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>129529111</v>
+      </c>
+      <c r="B166" t="n">
+        <v>92871</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>668539</v>
+      </c>
+      <c r="R166" t="n">
+        <v>6696478</v>
+      </c>
+      <c r="S166" t="n">
+        <v>5</v>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF166" t="inlineStr"/>
+      <c r="AG166" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT166" t="inlineStr"/>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>129526608</v>
+      </c>
+      <c r="B167" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Södra Västermarken, Upl</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>668515</v>
+      </c>
+      <c r="R167" t="n">
+        <v>6696327</v>
+      </c>
+      <c r="S167" t="n">
+        <v>5</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF167" t="inlineStr"/>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Björn Bråvander</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -11172,10 +11172,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129528815</v>
+        <v>129617873</v>
       </c>
       <c r="B101" t="n">
-        <v>101823</v>
+        <v>92871</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11183,27 +11183,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11211,10 +11218,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>668434</v>
+        <v>668264</v>
       </c>
       <c r="R101" t="n">
-        <v>6696572</v>
+        <v>6696500</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11241,12 +11248,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11274,10 +11281,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129617873</v>
+        <v>129528815</v>
       </c>
       <c r="B102" t="n">
-        <v>92871</v>
+        <v>101823</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11285,34 +11292,27 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -11320,10 +11320,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>668264</v>
+        <v>668434</v>
       </c>
       <c r="R102" t="n">
-        <v>6696500</v>
+        <v>6696572</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11383,37 +11383,37 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129609957</v>
+        <v>129662449</v>
       </c>
       <c r="B103" t="n">
-        <v>88740</v>
+        <v>91081</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4379</v>
+        <v>256756</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -11429,10 +11429,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>668194</v>
+        <v>668437</v>
       </c>
       <c r="R103" t="n">
-        <v>6696543</v>
+        <v>6696515</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11459,12 +11459,27 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Växer in 2-3 m ø ring runt smultronkantarell</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11473,9 +11488,23 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; gran intill men med tall inom rotavstånd.</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11492,7 +11521,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129610638</v>
+        <v>129527202</v>
       </c>
       <c r="B104" t="n">
         <v>91326</v>
@@ -11530,10 +11559,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>668314</v>
+        <v>668552</v>
       </c>
       <c r="R104" t="n">
-        <v>6696563</v>
+        <v>6696416</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11560,12 +11589,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11593,10 +11622,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129610538</v>
+        <v>129528876</v>
       </c>
       <c r="B105" t="n">
-        <v>101823</v>
+        <v>91326</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11604,27 +11633,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221235</v>
+        <v>3215</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -11632,13 +11660,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>668247</v>
+        <v>668483</v>
       </c>
       <c r="R105" t="n">
-        <v>6696545</v>
+        <v>6696587</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11662,12 +11690,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11695,10 +11723,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129527202</v>
+        <v>129610538</v>
       </c>
       <c r="B106" t="n">
-        <v>91326</v>
+        <v>101823</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11706,26 +11734,27 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3215</v>
+        <v>221235</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -11733,13 +11762,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>668552</v>
+        <v>668247</v>
       </c>
       <c r="R106" t="n">
-        <v>6696416</v>
+        <v>6696545</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11763,12 +11792,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11796,10 +11825,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129528876</v>
+        <v>129609957</v>
       </c>
       <c r="B107" t="n">
-        <v>91326</v>
+        <v>88740</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11807,25 +11836,33 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3215</v>
+        <v>4379</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
@@ -11834,13 +11871,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>668483</v>
+        <v>668194</v>
       </c>
       <c r="R107" t="n">
-        <v>6696587</v>
+        <v>6696543</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11864,12 +11901,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11897,44 +11934,36 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129662449</v>
+        <v>129610638</v>
       </c>
       <c r="B108" t="n">
-        <v>91081</v>
+        <v>91326</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>256756</v>
+        <v>3215</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
@@ -11943,13 +11972,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>668437</v>
+        <v>668314</v>
       </c>
       <c r="R108" t="n">
-        <v>6696515</v>
+        <v>6696563</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11973,27 +12002,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>14:26</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Växer in 2-3 m ø ring runt smultronkantarell</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12002,23 +12016,9 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; gran intill men med tall inom rotavstånd.</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -12136,10 +12136,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129610545</v>
+        <v>129528869</v>
       </c>
       <c r="B110" t="n">
-        <v>92871</v>
+        <v>98761</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12147,34 +12147,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5964</v>
+        <v>219874</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -12182,13 +12187,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>668300</v>
+        <v>668470</v>
       </c>
       <c r="R110" t="n">
-        <v>6696555</v>
+        <v>6696562</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12212,12 +12217,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12245,10 +12250,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129527352</v>
+        <v>129528987</v>
       </c>
       <c r="B111" t="n">
-        <v>91326</v>
+        <v>98647</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12256,26 +12261,31 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3215</v>
+        <v>223597</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12283,10 +12293,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>668516</v>
+        <v>668525</v>
       </c>
       <c r="R111" t="n">
-        <v>6696461</v>
+        <v>6696572</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12346,10 +12356,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129528869</v>
+        <v>129610545</v>
       </c>
       <c r="B112" t="n">
-        <v>98761</v>
+        <v>92871</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12357,39 +12367,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219874</v>
+        <v>5964</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -12397,13 +12402,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>668470</v>
+        <v>668300</v>
       </c>
       <c r="R112" t="n">
-        <v>6696562</v>
+        <v>6696555</v>
       </c>
       <c r="S112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12427,12 +12432,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12460,10 +12465,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129528987</v>
+        <v>129527352</v>
       </c>
       <c r="B113" t="n">
-        <v>98647</v>
+        <v>91326</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12471,31 +12476,26 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>223597</v>
+        <v>3215</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -12503,10 +12503,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>668525</v>
+        <v>668516</v>
       </c>
       <c r="R113" t="n">
-        <v>6696572</v>
+        <v>6696461</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12566,10 +12566,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129617663</v>
+        <v>129525668</v>
       </c>
       <c r="B114" t="n">
-        <v>91326</v>
+        <v>98705</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12577,26 +12577,31 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3215</v>
+        <v>219798</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -12604,10 +12609,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>668387</v>
+        <v>668562</v>
       </c>
       <c r="R114" t="n">
-        <v>6696641</v>
+        <v>6696327</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12634,12 +12639,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12667,10 +12672,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129609831</v>
+        <v>129617663</v>
       </c>
       <c r="B115" t="n">
-        <v>92508</v>
+        <v>91326</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12678,33 +12683,25 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
@@ -12713,13 +12710,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>668186</v>
+        <v>668387</v>
       </c>
       <c r="R115" t="n">
-        <v>6696475</v>
+        <v>6696641</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12877,10 +12874,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129525668</v>
+        <v>129609831</v>
       </c>
       <c r="B117" t="n">
-        <v>98705</v>
+        <v>92508</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12888,31 +12885,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219798</v>
+        <v>4769</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -12920,13 +12920,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>668562</v>
+        <v>668186</v>
       </c>
       <c r="R117" t="n">
-        <v>6696327</v>
+        <v>6696475</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12950,12 +12950,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12983,10 +12983,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129617669</v>
+        <v>129610357</v>
       </c>
       <c r="B118" t="n">
-        <v>58558</v>
+        <v>92871</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12994,28 +12994,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>208245</v>
+        <v>5964</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
@@ -13023,10 +13029,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>668387</v>
+        <v>668132</v>
       </c>
       <c r="R118" t="n">
-        <v>6696641</v>
+        <v>6696568</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13086,10 +13092,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129610357</v>
+        <v>129610493</v>
       </c>
       <c r="B119" t="n">
-        <v>92871</v>
+        <v>92508</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13097,21 +13103,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -13132,10 +13138,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>668132</v>
+        <v>668244</v>
       </c>
       <c r="R119" t="n">
-        <v>6696568</v>
+        <v>6696585</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13195,10 +13201,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129610493</v>
+        <v>129617669</v>
       </c>
       <c r="B120" t="n">
-        <v>92508</v>
+        <v>58558</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13206,34 +13212,28 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4769</v>
+        <v>208245</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -13241,10 +13241,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>668244</v>
+        <v>668387</v>
       </c>
       <c r="R120" t="n">
-        <v>6696585</v>
+        <v>6696641</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13304,7 +13304,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129528940</v>
+        <v>129610650</v>
       </c>
       <c r="B121" t="n">
         <v>92508</v>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -13350,10 +13350,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>668489</v>
+        <v>668349</v>
       </c>
       <c r="R121" t="n">
-        <v>6696575</v>
+        <v>6696573</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13380,12 +13380,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13413,7 +13413,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129610650</v>
+        <v>129528940</v>
       </c>
       <c r="B122" t="n">
         <v>92508</v>
@@ -13443,7 +13443,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -13459,10 +13459,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>668349</v>
+        <v>668489</v>
       </c>
       <c r="R122" t="n">
-        <v>6696573</v>
+        <v>6696575</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13489,12 +13489,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13522,10 +13522,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129610554</v>
+        <v>129528822</v>
       </c>
       <c r="B123" t="n">
-        <v>92508</v>
+        <v>91326</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13533,33 +13533,25 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
@@ -13568,10 +13560,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>668301</v>
+        <v>668431</v>
       </c>
       <c r="R123" t="n">
-        <v>6696575</v>
+        <v>6696579</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -13598,12 +13590,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13631,10 +13623,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129610501</v>
+        <v>129529116</v>
       </c>
       <c r="B124" t="n">
-        <v>91326</v>
+        <v>92847</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13642,25 +13634,33 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3215</v>
+        <v>4366</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
@@ -13669,10 +13669,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>668257</v>
+        <v>668541</v>
       </c>
       <c r="R124" t="n">
-        <v>6696575</v>
+        <v>6696479</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13699,12 +13699,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13732,7 +13732,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129610447</v>
+        <v>129610501</v>
       </c>
       <c r="B125" t="n">
         <v>91326</v>
@@ -13770,10 +13770,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>668177</v>
+        <v>668257</v>
       </c>
       <c r="R125" t="n">
-        <v>6696570</v>
+        <v>6696575</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13833,10 +13833,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129609949</v>
+        <v>129610447</v>
       </c>
       <c r="B126" t="n">
-        <v>104198</v>
+        <v>91326</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13844,35 +13844,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>222412</v>
+        <v>3215</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -13880,10 +13871,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>668189</v>
+        <v>668177</v>
       </c>
       <c r="R126" t="n">
-        <v>6696541</v>
+        <v>6696570</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13943,10 +13934,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129529116</v>
+        <v>129610554</v>
       </c>
       <c r="B127" t="n">
-        <v>92847</v>
+        <v>92508</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13954,26 +13945,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4366</v>
+        <v>4769</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -13989,10 +13980,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>668541</v>
+        <v>668301</v>
       </c>
       <c r="R127" t="n">
-        <v>6696479</v>
+        <v>6696575</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14019,12 +14010,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14052,10 +14043,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129528822</v>
+        <v>129609949</v>
       </c>
       <c r="B128" t="n">
-        <v>91326</v>
+        <v>104198</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14063,26 +14054,35 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3215</v>
+        <v>222412</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -14090,10 +14090,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>668431</v>
+        <v>668189</v>
       </c>
       <c r="R128" t="n">
-        <v>6696579</v>
+        <v>6696541</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14120,12 +14120,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14153,10 +14153,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129609938</v>
+        <v>129617642</v>
       </c>
       <c r="B129" t="n">
-        <v>91326</v>
+        <v>92871</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14164,25 +14164,33 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3215</v>
+        <v>5964</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
@@ -14191,10 +14199,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>668185</v>
+        <v>668384</v>
       </c>
       <c r="R129" t="n">
-        <v>6696506</v>
+        <v>6696663</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -14254,7 +14262,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129617642</v>
+        <v>129609966</v>
       </c>
       <c r="B130" t="n">
         <v>92871</v>
@@ -14284,7 +14292,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14300,10 +14308,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>668384</v>
+        <v>668187</v>
       </c>
       <c r="R130" t="n">
-        <v>6696663</v>
+        <v>6696536</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -14363,10 +14371,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129609966</v>
+        <v>129617840</v>
       </c>
       <c r="B131" t="n">
-        <v>92871</v>
+        <v>98761</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14374,34 +14382,39 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5964</v>
+        <v>219874</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
@@ -14409,13 +14422,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>668187</v>
+        <v>668276</v>
       </c>
       <c r="R131" t="n">
-        <v>6696536</v>
+        <v>6696503</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14472,10 +14485,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129617840</v>
+        <v>129609938</v>
       </c>
       <c r="B132" t="n">
-        <v>98761</v>
+        <v>91326</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14483,39 +14496,26 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219874</v>
+        <v>3215</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14523,13 +14523,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>668276</v>
+        <v>668185</v>
       </c>
       <c r="R132" t="n">
-        <v>6696503</v>
+        <v>6696506</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14586,10 +14586,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129610655</v>
+        <v>129528897</v>
       </c>
       <c r="B133" t="n">
-        <v>91326</v>
+        <v>101823</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14597,26 +14597,27 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>3215</v>
+        <v>221235</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -14624,10 +14625,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>668355</v>
+        <v>668488</v>
       </c>
       <c r="R133" t="n">
-        <v>6696569</v>
+        <v>6696584</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14654,12 +14655,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14687,10 +14688,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129528897</v>
+        <v>129610655</v>
       </c>
       <c r="B134" t="n">
-        <v>101823</v>
+        <v>91326</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14698,27 +14699,26 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>221235</v>
+        <v>3215</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -14726,10 +14726,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>668488</v>
+        <v>668355</v>
       </c>
       <c r="R134" t="n">
-        <v>6696584</v>
+        <v>6696569</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14756,12 +14756,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14789,37 +14789,37 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129610602</v>
+        <v>129609920</v>
       </c>
       <c r="B135" t="n">
-        <v>91098</v>
+        <v>92508</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6039940</v>
+        <v>4769</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mandarinfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramaria tridentina</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Schild</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -14835,13 +14835,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>668293</v>
+        <v>668179</v>
       </c>
       <c r="R135" t="n">
-        <v>6696561</v>
+        <v>6696523</v>
       </c>
       <c r="S135" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14868,44 +14868,20 @@
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog under gran</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
@@ -14922,10 +14898,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129609920</v>
+        <v>129528947</v>
       </c>
       <c r="B136" t="n">
-        <v>92508</v>
+        <v>91326</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14933,33 +14909,25 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
@@ -14968,13 +14936,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>668179</v>
+        <v>668522</v>
       </c>
       <c r="R136" t="n">
-        <v>6696523</v>
+        <v>6696581</v>
       </c>
       <c r="S136" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14998,12 +14966,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15031,10 +14999,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129610462</v>
+        <v>129528814</v>
       </c>
       <c r="B137" t="n">
-        <v>91326</v>
+        <v>100916</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15042,26 +15010,27 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
@@ -15069,10 +15038,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>668179</v>
+        <v>668434</v>
       </c>
       <c r="R137" t="n">
-        <v>6696587</v>
+        <v>6696572</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -15099,12 +15068,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15132,10 +15101,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129528814</v>
+        <v>129610462</v>
       </c>
       <c r="B138" t="n">
-        <v>100916</v>
+        <v>91326</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15143,27 +15112,26 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
@@ -15171,10 +15139,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>668434</v>
+        <v>668179</v>
       </c>
       <c r="R138" t="n">
-        <v>6696572</v>
+        <v>6696587</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -15201,12 +15169,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15234,36 +15202,44 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129528947</v>
+        <v>129610602</v>
       </c>
       <c r="B139" t="n">
-        <v>91326</v>
+        <v>91098</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>3215</v>
+        <v>6039940</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Mandarinfingersvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Ramaria tridentina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
+          <t>Schild</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
@@ -15272,13 +15248,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>668522</v>
+        <v>668293</v>
       </c>
       <c r="R139" t="n">
-        <v>6696581</v>
+        <v>6696561</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15302,12 +15278,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15316,9 +15302,23 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG139" t="b">
         <v>0</v>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog under gran</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
@@ -15438,7 +15438,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129528723</v>
+        <v>129609795</v>
       </c>
       <c r="B141" t="n">
         <v>91326</v>
@@ -15476,13 +15476,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>668464</v>
+        <v>668206</v>
       </c>
       <c r="R141" t="n">
-        <v>6696569</v>
+        <v>6696477</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15506,12 +15506,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15668,7 +15668,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129609795</v>
+        <v>129528723</v>
       </c>
       <c r="B143" t="n">
         <v>91326</v>
@@ -15706,13 +15706,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>668206</v>
+        <v>668464</v>
       </c>
       <c r="R143" t="n">
-        <v>6696477</v>
+        <v>6696569</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15736,12 +15736,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15971,44 +15971,36 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129610679</v>
+        <v>129528840</v>
       </c>
       <c r="B146" t="n">
-        <v>91088</v>
+        <v>91326</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5747</v>
+        <v>3215</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Christan</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
@@ -16017,7 +16009,7 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>668330</v>
+        <v>668462</v>
       </c>
       <c r="R146" t="n">
         <v>6696584</v>
@@ -16047,22 +16039,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>15:41</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>15:41</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16071,23 +16053,9 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>Gran, men finns tall; kalk</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -16104,36 +16072,44 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129528840</v>
+        <v>129610679</v>
       </c>
       <c r="B147" t="n">
-        <v>91326</v>
+        <v>91088</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3215</v>
+        <v>5747</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
@@ -16142,7 +16118,7 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>668462</v>
+        <v>668330</v>
       </c>
       <c r="R147" t="n">
         <v>6696584</v>
@@ -16172,12 +16148,22 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16186,9 +16172,23 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG147" t="b">
         <v>0</v>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>Gran, men finns tall; kalk</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
@@ -16314,10 +16314,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129610013</v>
+        <v>129609952</v>
       </c>
       <c r="B149" t="n">
-        <v>92847</v>
+        <v>101823</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16325,34 +16325,27 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4366</v>
+        <v>221235</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
@@ -16360,10 +16353,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>668130</v>
+        <v>668194</v>
       </c>
       <c r="R149" t="n">
-        <v>6696576</v>
+        <v>6696543</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -16423,10 +16416,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129609952</v>
+        <v>129528942</v>
       </c>
       <c r="B150" t="n">
-        <v>101823</v>
+        <v>91326</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16434,27 +16427,26 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>221235</v>
+        <v>3215</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -16462,10 +16454,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>668194</v>
+        <v>668496</v>
       </c>
       <c r="R150" t="n">
-        <v>6696543</v>
+        <v>6696582</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -16492,12 +16484,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16525,10 +16517,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129528942</v>
+        <v>129610013</v>
       </c>
       <c r="B151" t="n">
-        <v>91326</v>
+        <v>92847</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16536,25 +16528,33 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3215</v>
+        <v>4366</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
@@ -16563,10 +16563,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>668496</v>
+        <v>668130</v>
       </c>
       <c r="R151" t="n">
-        <v>6696582</v>
+        <v>6696576</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -16593,12 +16593,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16830,10 +16830,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129610394</v>
+        <v>129528072</v>
       </c>
       <c r="B154" t="n">
-        <v>92847</v>
+        <v>91326</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16841,33 +16841,25 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4366</v>
+        <v>3215</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
@@ -16876,13 +16868,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>668132</v>
+        <v>668498</v>
       </c>
       <c r="R154" t="n">
-        <v>6696568</v>
+        <v>6696426</v>
       </c>
       <c r="S154" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16906,12 +16898,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16939,10 +16931,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129528072</v>
+        <v>129610394</v>
       </c>
       <c r="B155" t="n">
-        <v>91326</v>
+        <v>92847</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16950,25 +16942,33 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>3215</v>
+        <v>4366</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
@@ -16977,13 +16977,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>668498</v>
+        <v>668132</v>
       </c>
       <c r="R155" t="n">
-        <v>6696426</v>
+        <v>6696568</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17007,12 +17007,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17040,10 +17040,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129609794</v>
+        <v>129610543</v>
       </c>
       <c r="B156" t="n">
-        <v>92508</v>
+        <v>91326</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17051,33 +17051,25 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
@@ -17086,13 +17078,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>668206</v>
+        <v>668294</v>
       </c>
       <c r="R156" t="n">
-        <v>6696477</v>
+        <v>6696541</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17149,10 +17141,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129610543</v>
+        <v>129609794</v>
       </c>
       <c r="B157" t="n">
-        <v>91326</v>
+        <v>92508</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17160,25 +17152,33 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
@@ -17187,13 +17187,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>668294</v>
+        <v>668206</v>
       </c>
       <c r="R157" t="n">
-        <v>6696541</v>
+        <v>6696477</v>
       </c>
       <c r="S157" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17359,10 +17359,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129610547</v>
+        <v>129610541</v>
       </c>
       <c r="B159" t="n">
-        <v>104198</v>
+        <v>91326</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17370,39 +17370,26 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>222412</v>
+        <v>3215</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -17410,10 +17397,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>668304</v>
+        <v>668266</v>
       </c>
       <c r="R159" t="n">
-        <v>6696565</v>
+        <v>6696524</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -17473,10 +17460,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129610541</v>
+        <v>129610547</v>
       </c>
       <c r="B160" t="n">
-        <v>91326</v>
+        <v>104198</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17484,26 +17471,39 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>3215</v>
+        <v>222412</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
@@ -17511,10 +17511,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>668266</v>
+        <v>668304</v>
       </c>
       <c r="R160" t="n">
-        <v>6696524</v>
+        <v>6696565</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>
@@ -17574,10 +17574,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129610475</v>
+        <v>129528930</v>
       </c>
       <c r="B161" t="n">
-        <v>92508</v>
+        <v>91326</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17585,33 +17585,25 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
@@ -17620,10 +17612,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>668225</v>
+        <v>668489</v>
       </c>
       <c r="R161" t="n">
-        <v>6696609</v>
+        <v>6696575</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -17650,12 +17642,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17683,10 +17675,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129528930</v>
+        <v>129610475</v>
       </c>
       <c r="B162" t="n">
-        <v>91326</v>
+        <v>92508</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17694,25 +17686,33 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
@@ -17721,10 +17721,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>668489</v>
+        <v>668225</v>
       </c>
       <c r="R162" t="n">
-        <v>6696575</v>
+        <v>6696609</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -17751,12 +17751,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17784,7 +17784,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129609969</v>
+        <v>129528721</v>
       </c>
       <c r="B163" t="n">
         <v>91326</v>
@@ -17822,10 +17822,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>668169</v>
+        <v>668471</v>
       </c>
       <c r="R163" t="n">
-        <v>6696511</v>
+        <v>6696556</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -17852,12 +17852,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17885,44 +17885,36 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129610636</v>
+        <v>129526608</v>
       </c>
       <c r="B164" t="n">
-        <v>87005</v>
+        <v>91326</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6003295</v>
+        <v>3215</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
@@ -17931,10 +17923,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>668306</v>
+        <v>668515</v>
       </c>
       <c r="R164" t="n">
-        <v>6696570</v>
+        <v>6696327</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -17961,22 +17953,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17988,11 +17970,6 @@
       <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
@@ -18009,10 +17986,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129528721</v>
+        <v>129529111</v>
       </c>
       <c r="B165" t="n">
-        <v>91326</v>
+        <v>92871</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18020,25 +17997,33 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3215</v>
+        <v>5964</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K165" t="inlineStr"/>
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
@@ -18047,10 +18032,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>668471</v>
+        <v>668539</v>
       </c>
       <c r="R165" t="n">
-        <v>6696556</v>
+        <v>6696478</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -18110,10 +18095,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129529111</v>
+        <v>129609969</v>
       </c>
       <c r="B166" t="n">
-        <v>92871</v>
+        <v>91326</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18121,33 +18106,25 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5964</v>
+        <v>3215</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
@@ -18156,10 +18133,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>668539</v>
+        <v>668169</v>
       </c>
       <c r="R166" t="n">
-        <v>6696478</v>
+        <v>6696511</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -18186,12 +18163,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18219,36 +18196,44 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129526608</v>
+        <v>129610636</v>
       </c>
       <c r="B167" t="n">
-        <v>91326</v>
+        <v>87005</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>3215</v>
+        <v>6003295</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
-      <c r="J167" t="inlineStr"/>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
@@ -18257,10 +18242,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>668515</v>
+        <v>668306</v>
       </c>
       <c r="R167" t="n">
-        <v>6696327</v>
+        <v>6696570</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -18287,12 +18272,22 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18304,6 +18299,11 @@
       <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -11172,10 +11172,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129617873</v>
+        <v>129528815</v>
       </c>
       <c r="B101" t="n">
-        <v>92871</v>
+        <v>101852</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11183,34 +11183,27 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5964</v>
+        <v>221235</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11218,10 +11211,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>668264</v>
+        <v>668434</v>
       </c>
       <c r="R101" t="n">
-        <v>6696500</v>
+        <v>6696572</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11248,12 +11241,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11281,10 +11274,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129528815</v>
+        <v>129617873</v>
       </c>
       <c r="B102" t="n">
-        <v>101823</v>
+        <v>92899</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11292,27 +11285,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221235</v>
+        <v>5964</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -11320,10 +11320,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>668434</v>
+        <v>668264</v>
       </c>
       <c r="R102" t="n">
-        <v>6696572</v>
+        <v>6696500</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11383,44 +11383,36 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129662449</v>
+        <v>129528876</v>
       </c>
       <c r="B103" t="n">
-        <v>91081</v>
+        <v>91354</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>256756</v>
+        <v>3215</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
@@ -11429,13 +11421,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>668437</v>
+        <v>668483</v>
       </c>
       <c r="R103" t="n">
-        <v>6696515</v>
+        <v>6696587</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11462,49 +11454,20 @@
           <t>2025-09-02</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-09-02</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Växer in 2-3 m ø ring runt smultronkantarell</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; gran intill men med tall inom rotavstånd.</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -11524,7 +11487,7 @@
         <v>129527202</v>
       </c>
       <c r="B104" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11622,10 +11585,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129528876</v>
+        <v>129610638</v>
       </c>
       <c r="B105" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11660,10 +11623,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>668483</v>
+        <v>668314</v>
       </c>
       <c r="R105" t="n">
-        <v>6696587</v>
+        <v>6696563</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11690,12 +11653,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11723,38 +11686,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129610538</v>
+        <v>129662449</v>
       </c>
       <c r="B106" t="n">
-        <v>101823</v>
+        <v>91109</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221235</v>
+        <v>256756</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -11762,10 +11732,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>668247</v>
+        <v>668437</v>
       </c>
       <c r="R106" t="n">
-        <v>6696545</v>
+        <v>6696515</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -11792,12 +11762,27 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Växer in 2-3 m ø ring runt smultronkantarell</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11806,9 +11791,23 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; gran intill men med tall inom rotavstånd.</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -11828,7 +11827,7 @@
         <v>129609957</v>
       </c>
       <c r="B107" t="n">
-        <v>88740</v>
+        <v>88768</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11934,10 +11933,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129610638</v>
+        <v>129610538</v>
       </c>
       <c r="B108" t="n">
-        <v>91326</v>
+        <v>101852</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11945,26 +11944,27 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>3215</v>
+        <v>221235</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -11972,13 +11972,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>668314</v>
+        <v>668247</v>
       </c>
       <c r="R108" t="n">
-        <v>6696563</v>
+        <v>6696545</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12038,7 +12038,7 @@
         <v>129528780</v>
       </c>
       <c r="B109" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12136,10 +12136,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129528869</v>
+        <v>129527352</v>
       </c>
       <c r="B110" t="n">
-        <v>98761</v>
+        <v>91354</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12147,39 +12147,26 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219874</v>
+        <v>3215</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -12187,10 +12174,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>668470</v>
+        <v>668516</v>
       </c>
       <c r="R110" t="n">
-        <v>6696562</v>
+        <v>6696461</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12253,7 +12240,7 @@
         <v>129528987</v>
       </c>
       <c r="B111" t="n">
-        <v>98647</v>
+        <v>98676</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12356,10 +12343,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129610545</v>
+        <v>129528869</v>
       </c>
       <c r="B112" t="n">
-        <v>92871</v>
+        <v>98790</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12367,34 +12354,39 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5964</v>
+        <v>219874</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -12402,13 +12394,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>668300</v>
+        <v>668470</v>
       </c>
       <c r="R112" t="n">
-        <v>6696555</v>
+        <v>6696562</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12432,12 +12424,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12465,10 +12457,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129527352</v>
+        <v>129610545</v>
       </c>
       <c r="B113" t="n">
-        <v>91326</v>
+        <v>92899</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12476,25 +12468,33 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3215</v>
+        <v>5964</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
@@ -12503,13 +12503,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>668516</v>
+        <v>668300</v>
       </c>
       <c r="R113" t="n">
-        <v>6696461</v>
+        <v>6696555</v>
       </c>
       <c r="S113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12533,12 +12533,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12566,10 +12566,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129525668</v>
+        <v>129528857</v>
       </c>
       <c r="B114" t="n">
-        <v>98705</v>
+        <v>91354</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12577,31 +12577,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219798</v>
+        <v>3215</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -12609,13 +12604,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>668562</v>
+        <v>668474</v>
       </c>
       <c r="R114" t="n">
-        <v>6696327</v>
+        <v>6696557</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12672,10 +12667,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129617663</v>
+        <v>129525668</v>
       </c>
       <c r="B115" t="n">
-        <v>91326</v>
+        <v>98734</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12683,26 +12678,31 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3215</v>
+        <v>219798</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12710,10 +12710,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>668387</v>
+        <v>668562</v>
       </c>
       <c r="R115" t="n">
-        <v>6696641</v>
+        <v>6696327</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12740,12 +12740,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12773,10 +12773,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129528857</v>
+        <v>129617663</v>
       </c>
       <c r="B116" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12811,13 +12811,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>668474</v>
+        <v>668387</v>
       </c>
       <c r="R116" t="n">
-        <v>6696557</v>
+        <v>6696641</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12841,12 +12841,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12877,7 +12877,7 @@
         <v>129609831</v>
       </c>
       <c r="B117" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>129610357</v>
       </c>
       <c r="B118" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>129610493</v>
       </c>
       <c r="B119" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>129617669</v>
       </c>
       <c r="B120" t="n">
-        <v>58558</v>
+        <v>58561</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>129610650</v>
       </c>
       <c r="B121" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>129528940</v>
       </c>
       <c r="B122" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13522,10 +13522,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129528822</v>
+        <v>129609949</v>
       </c>
       <c r="B123" t="n">
-        <v>91326</v>
+        <v>104227</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13533,26 +13533,35 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3215</v>
+        <v>222412</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13560,10 +13569,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>668431</v>
+        <v>668189</v>
       </c>
       <c r="R123" t="n">
-        <v>6696579</v>
+        <v>6696541</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -13590,12 +13599,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13623,10 +13632,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129529116</v>
+        <v>129610501</v>
       </c>
       <c r="B124" t="n">
-        <v>92847</v>
+        <v>91354</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13634,33 +13643,25 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4366</v>
+        <v>3215</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
@@ -13669,10 +13670,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>668541</v>
+        <v>668257</v>
       </c>
       <c r="R124" t="n">
-        <v>6696479</v>
+        <v>6696575</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -13699,12 +13700,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13732,10 +13733,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129610501</v>
+        <v>129610447</v>
       </c>
       <c r="B125" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13770,10 +13771,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>668257</v>
+        <v>668177</v>
       </c>
       <c r="R125" t="n">
-        <v>6696575</v>
+        <v>6696570</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -13833,10 +13834,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129610447</v>
+        <v>129610554</v>
       </c>
       <c r="B126" t="n">
-        <v>91326</v>
+        <v>92536</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13844,25 +13845,33 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
@@ -13871,10 +13880,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>668177</v>
+        <v>668301</v>
       </c>
       <c r="R126" t="n">
-        <v>6696570</v>
+        <v>6696575</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13934,10 +13943,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129610554</v>
+        <v>129529116</v>
       </c>
       <c r="B127" t="n">
-        <v>92508</v>
+        <v>92875</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13945,26 +13954,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -13980,10 +13989,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>668301</v>
+        <v>668541</v>
       </c>
       <c r="R127" t="n">
-        <v>6696575</v>
+        <v>6696479</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14010,12 +14019,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14043,10 +14052,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129609949</v>
+        <v>129528822</v>
       </c>
       <c r="B128" t="n">
-        <v>104198</v>
+        <v>91354</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14054,35 +14063,26 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>222412</v>
+        <v>3215</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -14090,10 +14090,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>668189</v>
+        <v>668431</v>
       </c>
       <c r="R128" t="n">
-        <v>6696541</v>
+        <v>6696579</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14120,12 +14120,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14153,10 +14153,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129617642</v>
+        <v>129609938</v>
       </c>
       <c r="B129" t="n">
-        <v>92871</v>
+        <v>91354</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14164,33 +14164,25 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5964</v>
+        <v>3215</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
@@ -14199,10 +14191,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>668384</v>
+        <v>668185</v>
       </c>
       <c r="R129" t="n">
-        <v>6696663</v>
+        <v>6696506</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -14262,10 +14254,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129609966</v>
+        <v>129617642</v>
       </c>
       <c r="B130" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14292,7 +14284,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -14308,10 +14300,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>668187</v>
+        <v>668384</v>
       </c>
       <c r="R130" t="n">
-        <v>6696536</v>
+        <v>6696663</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -14371,10 +14363,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129617840</v>
+        <v>129609966</v>
       </c>
       <c r="B131" t="n">
-        <v>98761</v>
+        <v>92899</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14382,39 +14374,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219874</v>
+        <v>5964</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
@@ -14422,13 +14409,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>668276</v>
+        <v>668187</v>
       </c>
       <c r="R131" t="n">
-        <v>6696503</v>
+        <v>6696536</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14485,10 +14472,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129609938</v>
+        <v>129617840</v>
       </c>
       <c r="B132" t="n">
-        <v>91326</v>
+        <v>98790</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14496,26 +14483,39 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3215</v>
+        <v>219874</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14523,13 +14523,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>668185</v>
+        <v>668276</v>
       </c>
       <c r="R132" t="n">
-        <v>6696506</v>
+        <v>6696503</v>
       </c>
       <c r="S132" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14586,10 +14586,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129528897</v>
+        <v>129610655</v>
       </c>
       <c r="B133" t="n">
-        <v>101823</v>
+        <v>91354</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14597,27 +14597,26 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221235</v>
+        <v>3215</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -14625,10 +14624,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>668488</v>
+        <v>668355</v>
       </c>
       <c r="R133" t="n">
-        <v>6696584</v>
+        <v>6696569</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14655,12 +14654,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14688,10 +14687,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129610655</v>
+        <v>129528897</v>
       </c>
       <c r="B134" t="n">
-        <v>91326</v>
+        <v>101852</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14699,26 +14698,27 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3215</v>
+        <v>221235</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -14726,10 +14726,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>668355</v>
+        <v>668488</v>
       </c>
       <c r="R134" t="n">
-        <v>6696569</v>
+        <v>6696584</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14756,12 +14756,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14789,10 +14789,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129609920</v>
+        <v>129528947</v>
       </c>
       <c r="B135" t="n">
-        <v>92508</v>
+        <v>91354</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14800,33 +14800,25 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
@@ -14835,13 +14827,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>668179</v>
+        <v>668522</v>
       </c>
       <c r="R135" t="n">
-        <v>6696523</v>
+        <v>6696581</v>
       </c>
       <c r="S135" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14865,12 +14857,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14898,10 +14890,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129528947</v>
+        <v>129528814</v>
       </c>
       <c r="B136" t="n">
-        <v>91326</v>
+        <v>100945</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14909,26 +14901,27 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -14936,13 +14929,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>668522</v>
+        <v>668434</v>
       </c>
       <c r="R136" t="n">
-        <v>6696581</v>
+        <v>6696572</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14999,10 +14992,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129528814</v>
+        <v>129610462</v>
       </c>
       <c r="B137" t="n">
-        <v>100916</v>
+        <v>91354</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15010,27 +15003,26 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
@@ -15038,10 +15030,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>668434</v>
+        <v>668179</v>
       </c>
       <c r="R137" t="n">
-        <v>6696572</v>
+        <v>6696587</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -15068,12 +15060,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15101,10 +15093,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129610462</v>
+        <v>129609920</v>
       </c>
       <c r="B138" t="n">
-        <v>91326</v>
+        <v>92536</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15112,25 +15104,33 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
@@ -15142,10 +15142,10 @@
         <v>668179</v>
       </c>
       <c r="R138" t="n">
-        <v>6696587</v>
+        <v>6696523</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>129610602</v>
       </c>
       <c r="B139" t="n">
-        <v>91098</v>
+        <v>91126</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>129527256</v>
       </c>
       <c r="B140" t="n">
-        <v>58586</v>
+        <v>58589</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15438,36 +15438,44 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129609795</v>
+        <v>129528546</v>
       </c>
       <c r="B141" t="n">
-        <v>91326</v>
+        <v>88881</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3215</v>
+        <v>816</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Smultronkantarell</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Aphroditeola olida</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
@@ -15476,13 +15484,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>668206</v>
+        <v>668437</v>
       </c>
       <c r="R141" t="n">
-        <v>6696477</v>
+        <v>6696515</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15506,12 +15514,22 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15523,6 +15541,16 @@
       <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>Med gran och tall, omgiven av en Ramaria pallida. Kalk</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
@@ -15539,44 +15567,36 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129528546</v>
+        <v>129528723</v>
       </c>
       <c r="B142" t="n">
-        <v>88853</v>
+        <v>91354</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>816</v>
+        <v>3215</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Smultronkantarell</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Aphroditeola olida</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
@@ -15585,10 +15605,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>668437</v>
+        <v>668464</v>
       </c>
       <c r="R142" t="n">
-        <v>6696515</v>
+        <v>6696569</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15618,19 +15638,9 @@
           <t>2025-09-02</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>14:25</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15642,16 +15652,6 @@
       <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>Med gran och tall, omgiven av en Ramaria pallida. Kalk</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
@@ -15668,10 +15668,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129528723</v>
+        <v>129609795</v>
       </c>
       <c r="B143" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15706,13 +15706,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>668464</v>
+        <v>668206</v>
       </c>
       <c r="R143" t="n">
-        <v>6696569</v>
+        <v>6696477</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15736,12 +15736,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15772,7 +15772,7 @@
         <v>129524780</v>
       </c>
       <c r="B144" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>129528853</v>
       </c>
       <c r="B145" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>129528840</v>
       </c>
       <c r="B146" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>129610679</v>
       </c>
       <c r="B147" t="n">
-        <v>91088</v>
+        <v>91116</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16205,10 +16205,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129610551</v>
+        <v>129529126</v>
       </c>
       <c r="B148" t="n">
-        <v>92871</v>
+        <v>100945</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16216,34 +16216,27 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
@@ -16251,13 +16244,13 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>668301</v>
+        <v>668512</v>
       </c>
       <c r="R148" t="n">
-        <v>6696575</v>
+        <v>6696456</v>
       </c>
       <c r="S148" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16281,12 +16274,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16314,10 +16307,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129609952</v>
+        <v>129526765</v>
       </c>
       <c r="B149" t="n">
-        <v>101823</v>
+        <v>97627</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16325,21 +16318,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>221235</v>
+        <v>221945</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16353,10 +16346,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>668194</v>
+        <v>668522</v>
       </c>
       <c r="R149" t="n">
-        <v>6696543</v>
+        <v>6696350</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -16383,12 +16376,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16419,7 +16412,7 @@
         <v>129528942</v>
       </c>
       <c r="B150" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16517,10 +16510,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129610013</v>
+        <v>129610551</v>
       </c>
       <c r="B151" t="n">
-        <v>92847</v>
+        <v>92899</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16528,26 +16521,26 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -16563,10 +16556,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>668130</v>
+        <v>668301</v>
       </c>
       <c r="R151" t="n">
-        <v>6696576</v>
+        <v>6696575</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -16626,10 +16619,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129529126</v>
+        <v>129610013</v>
       </c>
       <c r="B152" t="n">
-        <v>100916</v>
+        <v>92875</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16637,27 +16630,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>222498</v>
+        <v>4366</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>668512</v>
+        <v>668130</v>
       </c>
       <c r="R152" t="n">
-        <v>6696456</v>
+        <v>6696576</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -16695,12 +16695,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16728,10 +16728,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129526765</v>
+        <v>129609952</v>
       </c>
       <c r="B153" t="n">
-        <v>97598</v>
+        <v>101852</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16739,21 +16739,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221945</v>
+        <v>221235</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16767,10 +16767,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>668522</v>
+        <v>668194</v>
       </c>
       <c r="R153" t="n">
-        <v>6696350</v>
+        <v>6696543</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -16797,12 +16797,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16833,7 +16833,7 @@
         <v>129528072</v>
       </c>
       <c r="B154" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>129610394</v>
       </c>
       <c r="B155" t="n">
-        <v>92847</v>
+        <v>92875</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>129610543</v>
       </c>
       <c r="B156" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>129609794</v>
       </c>
       <c r="B157" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>129609986</v>
       </c>
       <c r="B158" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>129610541</v>
       </c>
       <c r="B159" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>129610547</v>
       </c>
       <c r="B160" t="n">
-        <v>104198</v>
+        <v>104227</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>129528930</v>
       </c>
       <c r="B161" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>129610475</v>
       </c>
       <c r="B162" t="n">
-        <v>92508</v>
+        <v>92536</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17784,10 +17784,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129528721</v>
+        <v>129529111</v>
       </c>
       <c r="B163" t="n">
-        <v>91326</v>
+        <v>92899</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17795,25 +17795,33 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>3215</v>
+        <v>5964</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
@@ -17822,10 +17830,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>668471</v>
+        <v>668539</v>
       </c>
       <c r="R163" t="n">
-        <v>6696556</v>
+        <v>6696478</v>
       </c>
       <c r="S163" t="n">
         <v>5</v>
@@ -17885,10 +17893,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129526608</v>
+        <v>129528721</v>
       </c>
       <c r="B164" t="n">
-        <v>91326</v>
+        <v>91354</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17923,10 +17931,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>668515</v>
+        <v>668471</v>
       </c>
       <c r="R164" t="n">
-        <v>6696327</v>
+        <v>6696556</v>
       </c>
       <c r="S164" t="n">
         <v>5</v>
@@ -17986,10 +17994,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129529111</v>
+        <v>129526608</v>
       </c>
       <c r="B165" t="n">
-        <v>92871</v>
+        <v>91354</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17997,33 +18005,25 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5964</v>
+        <v>3215</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
@@ -18032,10 +18032,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>668539</v>
+        <v>668515</v>
       </c>
       <c r="R165" t="n">
-        <v>6696478</v>
+        <v>6696327</v>
       </c>
       <c r="S165" t="n">
         <v>5</v>
@@ -18095,36 +18095,44 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129609969</v>
+        <v>129610636</v>
       </c>
       <c r="B166" t="n">
-        <v>91326</v>
+        <v>87033</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>3215</v>
+        <v>6003295</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
@@ -18133,10 +18141,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>668169</v>
+        <v>668306</v>
       </c>
       <c r="R166" t="n">
-        <v>6696511</v>
+        <v>6696570</v>
       </c>
       <c r="S166" t="n">
         <v>5</v>
@@ -18166,9 +18174,19 @@
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18180,6 +18198,11 @@
       <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
@@ -18196,44 +18219,36 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129610636</v>
+        <v>129609969</v>
       </c>
       <c r="B167" t="n">
-        <v>87005</v>
+        <v>91354</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6003295</v>
+        <v>3215</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
@@ -18242,10 +18257,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>668306</v>
+        <v>668169</v>
       </c>
       <c r="R167" t="n">
-        <v>6696570</v>
+        <v>6696511</v>
       </c>
       <c r="S167" t="n">
         <v>5</v>
@@ -18275,19 +18290,9 @@
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18299,11 +18304,6 @@
       <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -11585,10 +11585,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129610638</v>
+        <v>129609957</v>
       </c>
       <c r="B105" t="n">
-        <v>91354</v>
+        <v>88768</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11596,25 +11596,33 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3215</v>
+        <v>4379</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
@@ -11623,13 +11631,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>668314</v>
+        <v>668194</v>
       </c>
       <c r="R105" t="n">
-        <v>6696563</v>
+        <v>6696543</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11686,44 +11694,36 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129662449</v>
+        <v>129610638</v>
       </c>
       <c r="B106" t="n">
-        <v>91109</v>
+        <v>91354</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>256756</v>
+        <v>3215</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
@@ -11732,13 +11732,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>668437</v>
+        <v>668314</v>
       </c>
       <c r="R106" t="n">
-        <v>6696515</v>
+        <v>6696563</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11762,27 +11762,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>14:26</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Växer in 2-3 m ø ring runt smultronkantarell</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11791,23 +11776,9 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; gran intill men med tall inom rotavstånd.</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -11824,37 +11795,37 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129609957</v>
+        <v>129662449</v>
       </c>
       <c r="B107" t="n">
-        <v>88768</v>
+        <v>91109</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4379</v>
+        <v>256756</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -11870,10 +11841,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>668194</v>
+        <v>668437</v>
       </c>
       <c r="R107" t="n">
-        <v>6696543</v>
+        <v>6696515</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11900,12 +11871,27 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Växer in 2-3 m ø ring runt smultronkantarell</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11914,9 +11900,23 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; gran intill men med tall inom rotavstånd.</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -12566,10 +12566,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129528857</v>
+        <v>129525668</v>
       </c>
       <c r="B114" t="n">
-        <v>91354</v>
+        <v>98734</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12577,26 +12577,31 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3215</v>
+        <v>219798</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -12604,13 +12609,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>668474</v>
+        <v>668562</v>
       </c>
       <c r="R114" t="n">
-        <v>6696557</v>
+        <v>6696327</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12667,10 +12672,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129525668</v>
+        <v>129617663</v>
       </c>
       <c r="B115" t="n">
-        <v>98734</v>
+        <v>91354</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12678,31 +12683,26 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>219798</v>
+        <v>3215</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12710,10 +12710,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>668562</v>
+        <v>668387</v>
       </c>
       <c r="R115" t="n">
-        <v>6696327</v>
+        <v>6696641</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12740,12 +12740,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12773,10 +12773,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129617663</v>
+        <v>129609831</v>
       </c>
       <c r="B116" t="n">
-        <v>91354</v>
+        <v>92536</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12784,25 +12784,33 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
@@ -12811,13 +12819,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>668387</v>
+        <v>668186</v>
       </c>
       <c r="R116" t="n">
-        <v>6696641</v>
+        <v>6696475</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12874,10 +12882,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129609831</v>
+        <v>129528857</v>
       </c>
       <c r="B117" t="n">
-        <v>92536</v>
+        <v>91354</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12885,33 +12893,25 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
@@ -12920,13 +12920,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>668186</v>
+        <v>668474</v>
       </c>
       <c r="R117" t="n">
-        <v>6696475</v>
+        <v>6696557</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12950,12 +12950,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13304,7 +13304,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129610650</v>
+        <v>129528940</v>
       </c>
       <c r="B121" t="n">
         <v>92536</v>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -13350,10 +13350,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>668349</v>
+        <v>668489</v>
       </c>
       <c r="R121" t="n">
-        <v>6696573</v>
+        <v>6696575</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13380,12 +13380,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13413,7 +13413,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129528940</v>
+        <v>129610650</v>
       </c>
       <c r="B122" t="n">
         <v>92536</v>
@@ -13443,7 +13443,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -13459,10 +13459,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>668489</v>
+        <v>668349</v>
       </c>
       <c r="R122" t="n">
-        <v>6696575</v>
+        <v>6696573</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13489,12 +13489,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14153,10 +14153,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129609938</v>
+        <v>129617840</v>
       </c>
       <c r="B129" t="n">
-        <v>91354</v>
+        <v>98790</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14164,26 +14164,39 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3215</v>
+        <v>219874</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -14191,13 +14204,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>668185</v>
+        <v>668276</v>
       </c>
       <c r="R129" t="n">
-        <v>6696506</v>
+        <v>6696503</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14254,10 +14267,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129617642</v>
+        <v>129609938</v>
       </c>
       <c r="B130" t="n">
-        <v>92899</v>
+        <v>91354</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14265,33 +14278,25 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5964</v>
+        <v>3215</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
@@ -14300,10 +14305,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>668384</v>
+        <v>668185</v>
       </c>
       <c r="R130" t="n">
-        <v>6696663</v>
+        <v>6696506</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -14363,7 +14368,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129609966</v>
+        <v>129617642</v>
       </c>
       <c r="B131" t="n">
         <v>92899</v>
@@ -14393,7 +14398,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -14409,10 +14414,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>668187</v>
+        <v>668384</v>
       </c>
       <c r="R131" t="n">
-        <v>6696536</v>
+        <v>6696663</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -14472,10 +14477,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129617840</v>
+        <v>129609966</v>
       </c>
       <c r="B132" t="n">
-        <v>98790</v>
+        <v>92899</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14483,39 +14488,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219874</v>
+        <v>5964</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14523,13 +14523,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>668276</v>
+        <v>668187</v>
       </c>
       <c r="R132" t="n">
-        <v>6696503</v>
+        <v>6696536</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14890,38 +14890,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129528814</v>
+        <v>129610602</v>
       </c>
       <c r="B136" t="n">
-        <v>100945</v>
+        <v>91126</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>222498</v>
+        <v>6039940</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mandarinfingersvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramaria tridentina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
+          <t>Schild</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
@@ -14929,10 +14936,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>668434</v>
+        <v>668293</v>
       </c>
       <c r="R136" t="n">
-        <v>6696572</v>
+        <v>6696561</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14959,12 +14966,22 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14973,9 +14990,23 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG136" t="b">
         <v>0</v>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog under gran</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
@@ -14992,10 +15023,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129610462</v>
+        <v>129528814</v>
       </c>
       <c r="B137" t="n">
-        <v>91354</v>
+        <v>100945</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15003,26 +15034,27 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
@@ -15030,10 +15062,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>668179</v>
+        <v>668434</v>
       </c>
       <c r="R137" t="n">
-        <v>6696587</v>
+        <v>6696572</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -15060,12 +15092,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15093,10 +15125,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129609920</v>
+        <v>129610462</v>
       </c>
       <c r="B138" t="n">
-        <v>92536</v>
+        <v>91354</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15104,33 +15136,25 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
@@ -15142,10 +15166,10 @@
         <v>668179</v>
       </c>
       <c r="R138" t="n">
-        <v>6696523</v>
+        <v>6696587</v>
       </c>
       <c r="S138" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15202,37 +15226,37 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129610602</v>
+        <v>129609920</v>
       </c>
       <c r="B139" t="n">
-        <v>91126</v>
+        <v>92536</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6039940</v>
+        <v>4769</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mandarinfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ramaria tridentina</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Schild</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15248,13 +15272,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>668293</v>
+        <v>668179</v>
       </c>
       <c r="R139" t="n">
-        <v>6696561</v>
+        <v>6696523</v>
       </c>
       <c r="S139" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15281,44 +15305,20 @@
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog under gran</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
@@ -15335,10 +15335,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129527256</v>
+        <v>129528723</v>
       </c>
       <c r="B140" t="n">
-        <v>58589</v>
+        <v>91354</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15346,28 +15346,26 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>208249</v>
+        <v>3215</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -15375,10 +15373,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>668515</v>
+        <v>668464</v>
       </c>
       <c r="R140" t="n">
-        <v>6696421</v>
+        <v>6696569</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -15567,10 +15565,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129528723</v>
+        <v>129527256</v>
       </c>
       <c r="B142" t="n">
-        <v>91354</v>
+        <v>58589</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15578,26 +15576,28 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3215</v>
+        <v>208249</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -15605,10 +15605,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>668464</v>
+        <v>668515</v>
       </c>
       <c r="R142" t="n">
-        <v>6696569</v>
+        <v>6696421</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -16510,10 +16510,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129610551</v>
+        <v>129610013</v>
       </c>
       <c r="B151" t="n">
-        <v>92899</v>
+        <v>92875</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16521,26 +16521,26 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -16556,10 +16556,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>668301</v>
+        <v>668130</v>
       </c>
       <c r="R151" t="n">
-        <v>6696575</v>
+        <v>6696576</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -16619,10 +16619,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129610013</v>
+        <v>129610551</v>
       </c>
       <c r="B152" t="n">
-        <v>92875</v>
+        <v>92899</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16630,26 +16630,26 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4366</v>
+        <v>5964</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -16665,10 +16665,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>668130</v>
+        <v>668301</v>
       </c>
       <c r="R152" t="n">
-        <v>6696576</v>
+        <v>6696575</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -17040,10 +17040,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129610543</v>
+        <v>129609794</v>
       </c>
       <c r="B156" t="n">
-        <v>91354</v>
+        <v>92536</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17051,25 +17051,33 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
@@ -17078,13 +17086,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>668294</v>
+        <v>668206</v>
       </c>
       <c r="R156" t="n">
-        <v>6696541</v>
+        <v>6696477</v>
       </c>
       <c r="S156" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17141,7 +17149,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129609794</v>
+        <v>129609986</v>
       </c>
       <c r="B157" t="n">
         <v>92536</v>
@@ -17171,7 +17179,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -17187,13 +17195,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>668206</v>
+        <v>668169</v>
       </c>
       <c r="R157" t="n">
-        <v>6696477</v>
+        <v>6696511</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17250,10 +17258,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129609986</v>
+        <v>129610543</v>
       </c>
       <c r="B158" t="n">
-        <v>92536</v>
+        <v>91354</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17261,33 +17269,25 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
@@ -17296,10 +17296,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>668169</v>
+        <v>668294</v>
       </c>
       <c r="R158" t="n">
-        <v>6696511</v>
+        <v>6696541</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -17359,10 +17359,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129610541</v>
+        <v>129610547</v>
       </c>
       <c r="B159" t="n">
-        <v>91354</v>
+        <v>104227</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17370,26 +17370,39 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>3215</v>
+        <v>222412</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -17397,10 +17410,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>668266</v>
+        <v>668304</v>
       </c>
       <c r="R159" t="n">
-        <v>6696524</v>
+        <v>6696565</v>
       </c>
       <c r="S159" t="n">
         <v>5</v>
@@ -17460,10 +17473,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129610547</v>
+        <v>129610541</v>
       </c>
       <c r="B160" t="n">
-        <v>104227</v>
+        <v>91354</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17471,39 +17484,26 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>222412</v>
+        <v>3215</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
@@ -17511,10 +17511,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>668304</v>
+        <v>668266</v>
       </c>
       <c r="R160" t="n">
-        <v>6696565</v>
+        <v>6696524</v>
       </c>
       <c r="S160" t="n">
         <v>5</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -11175,7 +11175,7 @@
         <v>129528815</v>
       </c>
       <c r="B101" t="n">
-        <v>101864</v>
+        <v>101865</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>129617873</v>
       </c>
       <c r="B102" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>129527202</v>
       </c>
       <c r="B103" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>129528876</v>
       </c>
       <c r="B104" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11585,37 +11585,37 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129662449</v>
+        <v>129609957</v>
       </c>
       <c r="B105" t="n">
-        <v>91115</v>
+        <v>88775</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>256756</v>
+        <v>4379</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -11631,10 +11631,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>668437</v>
+        <v>668194</v>
       </c>
       <c r="R105" t="n">
-        <v>6696515</v>
+        <v>6696543</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -11661,27 +11661,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>14:26</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Växer in 2-3 m ø ring runt smultronkantarell</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11690,23 +11675,9 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; gran intill men med tall inom rotavstånd.</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -11726,7 +11697,7 @@
         <v>129610638</v>
       </c>
       <c r="B106" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11824,10 +11795,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129609957</v>
+        <v>129610538</v>
       </c>
       <c r="B107" t="n">
-        <v>88774</v>
+        <v>101865</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11835,34 +11806,27 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4379</v>
+        <v>221235</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -11870,10 +11834,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>668194</v>
+        <v>668247</v>
       </c>
       <c r="R107" t="n">
-        <v>6696543</v>
+        <v>6696545</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11933,38 +11897,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129610538</v>
+        <v>129662449</v>
       </c>
       <c r="B108" t="n">
-        <v>101864</v>
+        <v>91116</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221235</v>
+        <v>256756</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -11972,10 +11943,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>668247</v>
+        <v>668437</v>
       </c>
       <c r="R108" t="n">
-        <v>6696545</v>
+        <v>6696515</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -12002,12 +11973,27 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Växer in 2-3 m ø ring runt smultronkantarell</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12016,9 +12002,23 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; gran intill men med tall inom rotavstånd.</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -12038,7 +12038,7 @@
         <v>129528780</v>
       </c>
       <c r="B109" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12136,10 +12136,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129527352</v>
+        <v>129528987</v>
       </c>
       <c r="B110" t="n">
-        <v>91360</v>
+        <v>98689</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12147,26 +12147,31 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3215</v>
+        <v>223597</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -12174,10 +12179,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>668516</v>
+        <v>668525</v>
       </c>
       <c r="R110" t="n">
-        <v>6696461</v>
+        <v>6696572</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12237,10 +12242,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129528869</v>
+        <v>129527352</v>
       </c>
       <c r="B111" t="n">
-        <v>98802</v>
+        <v>91361</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12248,39 +12253,26 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219874</v>
+        <v>3215</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -12288,10 +12280,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>668470</v>
+        <v>668516</v>
       </c>
       <c r="R111" t="n">
-        <v>6696562</v>
+        <v>6696461</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -12351,10 +12343,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129528987</v>
+        <v>129528869</v>
       </c>
       <c r="B112" t="n">
-        <v>98688</v>
+        <v>98803</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12362,22 +12354,26 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>223597</v>
+        <v>219874</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr"/>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -12385,7 +12381,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
@@ -12394,10 +12394,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>668525</v>
+        <v>668470</v>
       </c>
       <c r="R112" t="n">
-        <v>6696572</v>
+        <v>6696562</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -12460,7 +12460,7 @@
         <v>129680727</v>
       </c>
       <c r="B113" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>129528857</v>
       </c>
       <c r="B114" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>129525668</v>
       </c>
       <c r="B115" t="n">
-        <v>98746</v>
+        <v>98747</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12773,10 +12773,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129609831</v>
+        <v>129617663</v>
       </c>
       <c r="B116" t="n">
-        <v>92542</v>
+        <v>91361</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12784,33 +12784,25 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
@@ -12819,13 +12811,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>668186</v>
+        <v>668387</v>
       </c>
       <c r="R116" t="n">
-        <v>6696475</v>
+        <v>6696641</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12882,10 +12874,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129617663</v>
+        <v>129609831</v>
       </c>
       <c r="B117" t="n">
-        <v>91360</v>
+        <v>92543</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12893,25 +12885,33 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
@@ -12920,13 +12920,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>668387</v>
+        <v>668186</v>
       </c>
       <c r="R117" t="n">
-        <v>6696641</v>
+        <v>6696475</v>
       </c>
       <c r="S117" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12983,10 +12983,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129610493</v>
+        <v>129610357</v>
       </c>
       <c r="B118" t="n">
-        <v>92542</v>
+        <v>92906</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12994,21 +12994,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -13029,10 +13029,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>668244</v>
+        <v>668132</v>
       </c>
       <c r="R118" t="n">
-        <v>6696585</v>
+        <v>6696568</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -13092,10 +13092,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129610357</v>
+        <v>129617669</v>
       </c>
       <c r="B119" t="n">
-        <v>92905</v>
+        <v>58567</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13103,34 +13103,28 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5964</v>
+        <v>208245</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
@@ -13138,10 +13132,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>668132</v>
+        <v>668387</v>
       </c>
       <c r="R119" t="n">
-        <v>6696568</v>
+        <v>6696641</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -13201,10 +13195,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129617669</v>
+        <v>129610493</v>
       </c>
       <c r="B120" t="n">
-        <v>58566</v>
+        <v>92543</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13212,28 +13206,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>208245</v>
+        <v>4769</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
@@ -13241,10 +13241,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>668387</v>
+        <v>668244</v>
       </c>
       <c r="R120" t="n">
-        <v>6696641</v>
+        <v>6696585</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -13304,10 +13304,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129610650</v>
+        <v>129528940</v>
       </c>
       <c r="B121" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -13350,10 +13350,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>668349</v>
+        <v>668489</v>
       </c>
       <c r="R121" t="n">
-        <v>6696573</v>
+        <v>6696575</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13380,12 +13380,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13413,10 +13413,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129528940</v>
+        <v>129610650</v>
       </c>
       <c r="B122" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -13459,10 +13459,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>668489</v>
+        <v>668349</v>
       </c>
       <c r="R122" t="n">
-        <v>6696575</v>
+        <v>6696573</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13489,12 +13489,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13522,10 +13522,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129609949</v>
+        <v>129529116</v>
       </c>
       <c r="B123" t="n">
-        <v>104239</v>
+        <v>92882</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13533,35 +13533,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>222412</v>
+        <v>4366</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -13569,10 +13568,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>668189</v>
+        <v>668541</v>
       </c>
       <c r="R123" t="n">
-        <v>6696541</v>
+        <v>6696479</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -13599,12 +13598,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13635,7 +13634,7 @@
         <v>129528822</v>
       </c>
       <c r="B124" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13736,7 +13735,7 @@
         <v>129610554</v>
       </c>
       <c r="B125" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13842,10 +13841,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129529116</v>
+        <v>129610501</v>
       </c>
       <c r="B126" t="n">
-        <v>92881</v>
+        <v>91361</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13853,33 +13852,25 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4366</v>
+        <v>3215</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
@@ -13888,10 +13879,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>668541</v>
+        <v>668257</v>
       </c>
       <c r="R126" t="n">
-        <v>6696479</v>
+        <v>6696575</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13918,12 +13909,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13951,10 +13942,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129610501</v>
+        <v>129610447</v>
       </c>
       <c r="B127" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13989,10 +13980,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>668257</v>
+        <v>668177</v>
       </c>
       <c r="R127" t="n">
-        <v>6696575</v>
+        <v>6696570</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -14052,10 +14043,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129610447</v>
+        <v>129609949</v>
       </c>
       <c r="B128" t="n">
-        <v>91360</v>
+        <v>104240</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14063,26 +14054,35 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3215</v>
+        <v>222412</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -14090,10 +14090,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>668177</v>
+        <v>668189</v>
       </c>
       <c r="R128" t="n">
-        <v>6696570</v>
+        <v>6696541</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -14153,10 +14153,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129617840</v>
+        <v>129617642</v>
       </c>
       <c r="B129" t="n">
-        <v>98802</v>
+        <v>92906</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14164,21 +14164,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219874</v>
+        <v>5964</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -14188,15 +14188,10 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -14204,13 +14199,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>668276</v>
+        <v>668384</v>
       </c>
       <c r="R129" t="n">
-        <v>6696503</v>
+        <v>6696663</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14267,10 +14262,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129609938</v>
+        <v>129609966</v>
       </c>
       <c r="B130" t="n">
-        <v>91360</v>
+        <v>92906</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14278,25 +14273,33 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>3215</v>
+        <v>5964</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
@@ -14305,10 +14308,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>668185</v>
+        <v>668187</v>
       </c>
       <c r="R130" t="n">
-        <v>6696506</v>
+        <v>6696536</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -14368,10 +14371,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129617642</v>
+        <v>129609938</v>
       </c>
       <c r="B131" t="n">
-        <v>92905</v>
+        <v>91361</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14379,33 +14382,25 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5964</v>
+        <v>3215</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
@@ -14414,10 +14409,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>668384</v>
+        <v>668185</v>
       </c>
       <c r="R131" t="n">
-        <v>6696663</v>
+        <v>6696506</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -14477,10 +14472,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129609966</v>
+        <v>129617840</v>
       </c>
       <c r="B132" t="n">
-        <v>92905</v>
+        <v>98803</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14488,34 +14483,39 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5964</v>
+        <v>219874</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
@@ -14523,13 +14523,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>668187</v>
+        <v>668276</v>
       </c>
       <c r="R132" t="n">
-        <v>6696536</v>
+        <v>6696503</v>
       </c>
       <c r="S132" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14586,10 +14586,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129528897</v>
+        <v>129610655</v>
       </c>
       <c r="B133" t="n">
-        <v>101864</v>
+        <v>91361</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14597,27 +14597,26 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221235</v>
+        <v>3215</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -14625,10 +14624,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>668488</v>
+        <v>668355</v>
       </c>
       <c r="R133" t="n">
-        <v>6696584</v>
+        <v>6696569</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14655,12 +14654,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14688,10 +14687,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129610655</v>
+        <v>129528897</v>
       </c>
       <c r="B134" t="n">
-        <v>91360</v>
+        <v>101865</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14699,26 +14698,27 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3215</v>
+        <v>221235</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -14726,10 +14726,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>668355</v>
+        <v>668488</v>
       </c>
       <c r="R134" t="n">
-        <v>6696569</v>
+        <v>6696584</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14756,12 +14756,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14789,44 +14789,36 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129610602</v>
+        <v>129528947</v>
       </c>
       <c r="B135" t="n">
-        <v>91132</v>
+        <v>91361</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6039940</v>
+        <v>3215</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mandarinfingersvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramaria tridentina</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Schild</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
@@ -14835,13 +14827,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>668293</v>
+        <v>668522</v>
       </c>
       <c r="R135" t="n">
-        <v>6696561</v>
+        <v>6696581</v>
       </c>
       <c r="S135" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14865,22 +14857,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14889,23 +14871,9 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog under gran</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
@@ -14925,7 +14893,7 @@
         <v>129528814</v>
       </c>
       <c r="B136" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15024,10 +14992,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129528947</v>
+        <v>129610462</v>
       </c>
       <c r="B137" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15062,13 +15030,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>668522</v>
+        <v>668179</v>
       </c>
       <c r="R137" t="n">
-        <v>6696581</v>
+        <v>6696587</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15092,12 +15060,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15125,10 +15093,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129610462</v>
+        <v>129609920</v>
       </c>
       <c r="B138" t="n">
-        <v>91360</v>
+        <v>92543</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15136,25 +15104,33 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
@@ -15166,10 +15142,10 @@
         <v>668179</v>
       </c>
       <c r="R138" t="n">
-        <v>6696587</v>
+        <v>6696523</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15226,37 +15202,37 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129609920</v>
+        <v>129610602</v>
       </c>
       <c r="B139" t="n">
-        <v>92542</v>
+        <v>91133</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4769</v>
+        <v>6039940</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mandarinfingersvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria tridentina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Schild</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -15272,13 +15248,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>668179</v>
+        <v>668293</v>
       </c>
       <c r="R139" t="n">
-        <v>6696523</v>
+        <v>6696561</v>
       </c>
       <c r="S139" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15305,20 +15281,44 @@
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-09-06</t>
         </is>
       </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG139" t="b">
         <v>0</v>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog under gran</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
@@ -15335,44 +15335,36 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129528546</v>
+        <v>129528723</v>
       </c>
       <c r="B140" t="n">
-        <v>88887</v>
+        <v>91361</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>816</v>
+        <v>3215</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Smultronkantarell</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Aphroditeola olida</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
@@ -15381,10 +15373,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>668437</v>
+        <v>668464</v>
       </c>
       <c r="R140" t="n">
-        <v>6696515</v>
+        <v>6696569</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -15414,19 +15406,9 @@
           <t>2025-09-02</t>
         </is>
       </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>14:25</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15438,16 +15420,6 @@
       <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>Med gran och tall, omgiven av en Ramaria pallida. Kalk</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
@@ -15464,10 +15436,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129528723</v>
+        <v>129527256</v>
       </c>
       <c r="B141" t="n">
-        <v>91360</v>
+        <v>58595</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15475,26 +15447,28 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3215</v>
+        <v>208249</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -15502,10 +15476,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>668464</v>
+        <v>668515</v>
       </c>
       <c r="R141" t="n">
-        <v>6696569</v>
+        <v>6696421</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -15565,39 +15539,45 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129527256</v>
+        <v>129528546</v>
       </c>
       <c r="B142" t="n">
-        <v>58594</v>
+        <v>88888</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>208249</v>
+        <v>816</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Smultronkantarell</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Aphroditeola olida</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -15605,10 +15585,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>668515</v>
+        <v>668437</v>
       </c>
       <c r="R142" t="n">
-        <v>6696421</v>
+        <v>6696515</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15638,9 +15618,19 @@
           <t>2025-09-02</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15652,6 +15642,16 @@
       <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>Med gran och tall, omgiven av en Ramaria pallida. Kalk</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
@@ -15671,7 +15671,7 @@
         <v>129609795</v>
       </c>
       <c r="B143" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
         <v>129524780</v>
       </c>
       <c r="B144" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>129528853</v>
       </c>
       <c r="B145" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15971,36 +15971,44 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129528840</v>
+        <v>129610679</v>
       </c>
       <c r="B146" t="n">
-        <v>91360</v>
+        <v>91123</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>3215</v>
+        <v>5747</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
@@ -16009,7 +16017,7 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>668462</v>
+        <v>668330</v>
       </c>
       <c r="R146" t="n">
         <v>6696584</v>
@@ -16039,12 +16047,22 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16053,9 +16071,23 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG146" t="b">
         <v>0</v>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>Gran, men finns tall; kalk</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -16072,44 +16104,36 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129610679</v>
+        <v>129528840</v>
       </c>
       <c r="B147" t="n">
-        <v>91122</v>
+        <v>91361</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5747</v>
+        <v>3215</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Christan</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
@@ -16118,7 +16142,7 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>668330</v>
+        <v>668462</v>
       </c>
       <c r="R147" t="n">
         <v>6696584</v>
@@ -16148,22 +16172,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>15:41</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>15:41</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16172,23 +16186,9 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>Gran, men finns tall; kalk</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
@@ -16208,7 +16208,7 @@
         <v>129528942</v>
       </c>
       <c r="B148" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16306,10 +16306,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129529126</v>
+        <v>129526765</v>
       </c>
       <c r="B149" t="n">
-        <v>100957</v>
+        <v>97640</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16317,21 +16317,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16345,13 +16345,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>668512</v>
+        <v>668522</v>
       </c>
       <c r="R149" t="n">
-        <v>6696456</v>
+        <v>6696350</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16408,10 +16408,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129610551</v>
+        <v>129529126</v>
       </c>
       <c r="B150" t="n">
-        <v>92905</v>
+        <v>100958</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16419,34 +16419,27 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
@@ -16454,13 +16447,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>668301</v>
+        <v>668512</v>
       </c>
       <c r="R150" t="n">
-        <v>6696575</v>
+        <v>6696456</v>
       </c>
       <c r="S150" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -16484,12 +16477,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16517,10 +16510,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129609952</v>
+        <v>129610013</v>
       </c>
       <c r="B151" t="n">
-        <v>101864</v>
+        <v>92882</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16528,27 +16521,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>221235</v>
+        <v>4366</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
-      <c r="J151" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
@@ -16556,10 +16556,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>668194</v>
+        <v>668130</v>
       </c>
       <c r="R151" t="n">
-        <v>6696543</v>
+        <v>6696576</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -16619,10 +16619,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129526765</v>
+        <v>129610551</v>
       </c>
       <c r="B152" t="n">
-        <v>97639</v>
+        <v>92906</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16630,27 +16630,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>221945</v>
+        <v>5964</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
@@ -16658,10 +16665,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>668522</v>
+        <v>668301</v>
       </c>
       <c r="R152" t="n">
-        <v>6696350</v>
+        <v>6696575</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -16688,12 +16695,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16721,10 +16728,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129610013</v>
+        <v>129609952</v>
       </c>
       <c r="B153" t="n">
-        <v>92881</v>
+        <v>101865</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16732,34 +16739,27 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4366</v>
+        <v>221235</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
@@ -16767,10 +16767,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>668130</v>
+        <v>668194</v>
       </c>
       <c r="R153" t="n">
-        <v>6696576</v>
+        <v>6696543</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -16830,10 +16830,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129528072</v>
+        <v>129610394</v>
       </c>
       <c r="B154" t="n">
-        <v>91360</v>
+        <v>92882</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16841,25 +16841,33 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>3215</v>
+        <v>4366</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
@@ -16868,13 +16876,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>668498</v>
+        <v>668132</v>
       </c>
       <c r="R154" t="n">
-        <v>6696426</v>
+        <v>6696568</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16898,12 +16906,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16931,10 +16939,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129610394</v>
+        <v>129528072</v>
       </c>
       <c r="B155" t="n">
-        <v>92881</v>
+        <v>91361</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16942,33 +16950,25 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4366</v>
+        <v>3215</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
@@ -16977,13 +16977,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>668132</v>
+        <v>668498</v>
       </c>
       <c r="R155" t="n">
-        <v>6696568</v>
+        <v>6696426</v>
       </c>
       <c r="S155" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17007,12 +17007,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17043,7 +17043,7 @@
         <v>129609794</v>
       </c>
       <c r="B156" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17149,10 +17149,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129609986</v>
+        <v>129610543</v>
       </c>
       <c r="B157" t="n">
-        <v>92542</v>
+        <v>91361</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17160,33 +17160,25 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
@@ -17195,10 +17187,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>668169</v>
+        <v>668294</v>
       </c>
       <c r="R157" t="n">
-        <v>6696511</v>
+        <v>6696541</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -17258,10 +17250,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129610543</v>
+        <v>129609986</v>
       </c>
       <c r="B158" t="n">
-        <v>91360</v>
+        <v>92543</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17269,25 +17261,33 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
@@ -17296,10 +17296,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>668294</v>
+        <v>668169</v>
       </c>
       <c r="R158" t="n">
-        <v>6696541</v>
+        <v>6696511</v>
       </c>
       <c r="S158" t="n">
         <v>5</v>
@@ -17362,7 +17362,7 @@
         <v>129610541</v>
       </c>
       <c r="B159" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>129610547</v>
       </c>
       <c r="B160" t="n">
-        <v>104239</v>
+        <v>104240</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17574,10 +17574,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129610475</v>
+        <v>129528930</v>
       </c>
       <c r="B161" t="n">
-        <v>92542</v>
+        <v>91361</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17585,33 +17585,25 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
@@ -17620,10 +17612,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>668225</v>
+        <v>668489</v>
       </c>
       <c r="R161" t="n">
-        <v>6696609</v>
+        <v>6696575</v>
       </c>
       <c r="S161" t="n">
         <v>5</v>
@@ -17650,12 +17642,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17683,10 +17675,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129528930</v>
+        <v>129610475</v>
       </c>
       <c r="B162" t="n">
-        <v>91360</v>
+        <v>92543</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17694,25 +17686,33 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
@@ -17721,10 +17721,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>668489</v>
+        <v>668225</v>
       </c>
       <c r="R162" t="n">
-        <v>6696575</v>
+        <v>6696609</v>
       </c>
       <c r="S162" t="n">
         <v>5</v>
@@ -17751,12 +17751,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17787,7 +17787,7 @@
         <v>129529111</v>
       </c>
       <c r="B163" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>129528721</v>
       </c>
       <c r="B164" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>129526608</v>
       </c>
       <c r="B165" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>129609969</v>
       </c>
       <c r="B166" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>129610636</v>
       </c>
       <c r="B167" t="n">
-        <v>87039</v>
+        <v>87040</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18320,37 +18320,37 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129679801</v>
+        <v>129680826</v>
       </c>
       <c r="B168" t="n">
-        <v>91122</v>
+        <v>92543</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -18366,10 +18366,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>668448</v>
+        <v>668249</v>
       </c>
       <c r="R168" t="n">
-        <v>6696497</v>
+        <v>6696549</v>
       </c>
       <c r="S168" t="n">
         <v>5</v>
@@ -18399,44 +18399,20 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>Under tall och gran. Kalk.</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
@@ -18453,10 +18429,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129680044</v>
+        <v>129680817</v>
       </c>
       <c r="B169" t="n">
-        <v>91360</v>
+        <v>92543</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18464,25 +18440,33 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
@@ -18491,10 +18475,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>668350</v>
+        <v>668277</v>
       </c>
       <c r="R169" t="n">
-        <v>6696543</v>
+        <v>6696587</v>
       </c>
       <c r="S169" t="n">
         <v>5</v>
@@ -18554,10 +18538,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129679938</v>
+        <v>129680044</v>
       </c>
       <c r="B170" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18592,10 +18576,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>668369</v>
+        <v>668350</v>
       </c>
       <c r="R170" t="n">
-        <v>6696500</v>
+        <v>6696543</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -18655,10 +18639,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129680826</v>
+        <v>129679938</v>
       </c>
       <c r="B171" t="n">
-        <v>92542</v>
+        <v>91361</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18666,33 +18650,25 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
@@ -18701,10 +18677,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>668249</v>
+        <v>668369</v>
       </c>
       <c r="R171" t="n">
-        <v>6696549</v>
+        <v>6696500</v>
       </c>
       <c r="S171" t="n">
         <v>5</v>
@@ -18764,37 +18740,37 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129680817</v>
+        <v>129680819</v>
       </c>
       <c r="B172" t="n">
-        <v>92542</v>
+        <v>87040</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4769</v>
+        <v>6003295</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -18810,10 +18786,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>668277</v>
+        <v>668288</v>
       </c>
       <c r="R172" t="n">
-        <v>6696587</v>
+        <v>6696563</v>
       </c>
       <c r="S172" t="n">
         <v>5</v>
@@ -18843,9 +18819,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18857,6 +18843,11 @@
       <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
@@ -18873,37 +18864,37 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129680819</v>
+        <v>129679801</v>
       </c>
       <c r="B173" t="n">
-        <v>87039</v>
+        <v>91123</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6003295</v>
+        <v>5747</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -18919,10 +18910,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>668288</v>
+        <v>668448</v>
       </c>
       <c r="R173" t="n">
-        <v>6696563</v>
+        <v>6696497</v>
       </c>
       <c r="S173" t="n">
         <v>5</v>
@@ -18954,7 +18945,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -18964,7 +18955,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18973,9 +18964,18 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG173" t="b">
         <v>0</v>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>Under tall och gran. Kalk.</t>
+        </is>
       </c>
       <c r="AR173" t="inlineStr">
         <is>
@@ -18997,10 +18997,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129680779</v>
+        <v>129680827</v>
       </c>
       <c r="B174" t="n">
-        <v>91360</v>
+        <v>86841</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19008,25 +19008,33 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>3215</v>
+        <v>3762</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
@@ -19035,10 +19043,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>668314</v>
+        <v>668238</v>
       </c>
       <c r="R174" t="n">
-        <v>6696534</v>
+        <v>6696548</v>
       </c>
       <c r="S174" t="n">
         <v>5</v>
@@ -19068,9 +19076,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19082,6 +19100,11 @@
       <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
@@ -19098,10 +19121,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129680793</v>
+        <v>129680779</v>
       </c>
       <c r="B175" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19136,13 +19159,13 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>668281</v>
+        <v>668314</v>
       </c>
       <c r="R175" t="n">
-        <v>6696530</v>
+        <v>6696534</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -19199,10 +19222,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129680827</v>
+        <v>129680793</v>
       </c>
       <c r="B176" t="n">
-        <v>86840</v>
+        <v>91361</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19210,33 +19233,25 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>3762</v>
+        <v>3215</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
@@ -19245,13 +19260,13 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>668238</v>
+        <v>668281</v>
       </c>
       <c r="R176" t="n">
-        <v>6696548</v>
+        <v>6696530</v>
       </c>
       <c r="S176" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -19278,19 +19293,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>16:48</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>16:48</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19302,11 +19307,6 @@
       <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
-      </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
@@ -19326,7 +19326,7 @@
         <v>129680822</v>
       </c>
       <c r="B177" t="n">
-        <v>87039</v>
+        <v>87040</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19447,10 +19447,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129680809</v>
+        <v>129680729</v>
       </c>
       <c r="B178" t="n">
-        <v>98746</v>
+        <v>92906</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19458,39 +19458,34 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>219798</v>
+        <v>5964</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L178" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
@@ -19498,10 +19493,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>668275</v>
+        <v>668308</v>
       </c>
       <c r="R178" t="n">
-        <v>6696525</v>
+        <v>6696591</v>
       </c>
       <c r="S178" t="n">
         <v>5</v>
@@ -19534,6 +19529,11 @@
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Ring 3m ø</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19561,10 +19561,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129679811</v>
+        <v>129680931</v>
       </c>
       <c r="B179" t="n">
-        <v>98802</v>
+        <v>87003</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19572,31 +19572,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>219874</v>
+        <v>3674</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L179" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
@@ -19604,10 +19607,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>668458</v>
+        <v>668184</v>
       </c>
       <c r="R179" t="n">
-        <v>6696452</v>
+        <v>6696513</v>
       </c>
       <c r="S179" t="n">
         <v>5</v>
@@ -19637,9 +19640,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19670,7 +19683,7 @@
         <v>129680048</v>
       </c>
       <c r="B180" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -19771,7 +19784,7 @@
         <v>129679777</v>
       </c>
       <c r="B181" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -19869,10 +19882,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129680931</v>
+        <v>129680809</v>
       </c>
       <c r="B182" t="n">
-        <v>87002</v>
+        <v>98747</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19880,34 +19893,39 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>3674</v>
+        <v>219798</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
@@ -19915,10 +19933,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>668184</v>
+        <v>668275</v>
       </c>
       <c r="R182" t="n">
-        <v>6696513</v>
+        <v>6696525</v>
       </c>
       <c r="S182" t="n">
         <v>5</v>
@@ -19948,19 +19966,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>17:22</t>
-        </is>
-      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>17:22</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19988,10 +19996,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129680729</v>
+        <v>129679811</v>
       </c>
       <c r="B183" t="n">
-        <v>92905</v>
+        <v>98803</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19999,34 +20007,31 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5964</v>
+        <v>219874</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
@@ -20034,10 +20039,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>668308</v>
+        <v>668458</v>
       </c>
       <c r="R183" t="n">
-        <v>6696591</v>
+        <v>6696452</v>
       </c>
       <c r="S183" t="n">
         <v>5</v>
@@ -20070,11 +20075,6 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>Ring 3m ø</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20102,10 +20102,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129680717</v>
+        <v>129680810</v>
       </c>
       <c r="B184" t="n">
-        <v>86840</v>
+        <v>92543</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20113,26 +20113,26 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>3762</v>
+        <v>4769</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -20148,10 +20148,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>668318</v>
+        <v>668275</v>
       </c>
       <c r="R184" t="n">
-        <v>6696572</v>
+        <v>6696525</v>
       </c>
       <c r="S184" t="n">
         <v>5</v>
@@ -20181,19 +20181,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>16:20</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20205,11 +20195,6 @@
       <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
@@ -20226,10 +20211,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129680810</v>
+        <v>129680717</v>
       </c>
       <c r="B185" t="n">
-        <v>92542</v>
+        <v>86841</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20237,26 +20222,26 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -20272,10 +20257,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>668275</v>
+        <v>668318</v>
       </c>
       <c r="R185" t="n">
-        <v>6696525</v>
+        <v>6696572</v>
       </c>
       <c r="S185" t="n">
         <v>5</v>
@@ -20305,9 +20290,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20319,6 +20314,11 @@
       <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
@@ -20335,10 +20335,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129680846</v>
+        <v>129679267</v>
       </c>
       <c r="B186" t="n">
-        <v>91360</v>
+        <v>100958</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20346,26 +20346,27 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
@@ -20373,10 +20374,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>668206</v>
+        <v>668560</v>
       </c>
       <c r="R186" t="n">
-        <v>6696543</v>
+        <v>6696830</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20436,10 +20437,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129679267</v>
+        <v>129679273</v>
       </c>
       <c r="B187" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20475,13 +20476,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>668560</v>
+        <v>668566</v>
       </c>
       <c r="R187" t="n">
-        <v>6696830</v>
+        <v>6696824</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -20538,10 +20539,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129679273</v>
+        <v>129680846</v>
       </c>
       <c r="B188" t="n">
-        <v>100957</v>
+        <v>91361</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20549,27 +20550,26 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
@@ -20577,13 +20577,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>668566</v>
+        <v>668206</v>
       </c>
       <c r="R188" t="n">
-        <v>6696824</v>
+        <v>6696543</v>
       </c>
       <c r="S188" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -20640,10 +20640,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129680952</v>
+        <v>129680695</v>
       </c>
       <c r="B189" t="n">
-        <v>91360</v>
+        <v>92543</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20651,25 +20651,33 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
@@ -20678,13 +20686,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>668122</v>
+        <v>668326</v>
       </c>
       <c r="R189" t="n">
-        <v>6696635</v>
+        <v>6696601</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20741,10 +20749,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129679813</v>
+        <v>129679283</v>
       </c>
       <c r="B190" t="n">
-        <v>91360</v>
+        <v>92543</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20752,25 +20760,33 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
@@ -20779,10 +20795,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>668474</v>
+        <v>668566</v>
       </c>
       <c r="R190" t="n">
-        <v>6696455</v>
+        <v>6696824</v>
       </c>
       <c r="S190" t="n">
         <v>5</v>
@@ -20842,36 +20858,44 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129680026</v>
+        <v>129680745</v>
       </c>
       <c r="B191" t="n">
-        <v>91360</v>
+        <v>87040</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>3215</v>
+        <v>6003295</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
@@ -20880,10 +20904,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>668345</v>
+        <v>668309</v>
       </c>
       <c r="R191" t="n">
-        <v>6696510</v>
+        <v>6696573</v>
       </c>
       <c r="S191" t="n">
         <v>5</v>
@@ -20913,9 +20937,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20927,6 +20961,11 @@
       <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
@@ -20943,10 +20982,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129680862</v>
+        <v>129680802</v>
       </c>
       <c r="B192" t="n">
-        <v>87002</v>
+        <v>98747</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -20954,34 +20993,31 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>3674</v>
+        <v>219798</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
@@ -20989,13 +21025,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>668181</v>
+        <v>668284</v>
       </c>
       <c r="R192" t="n">
-        <v>6696507</v>
+        <v>6696528</v>
       </c>
       <c r="S192" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21052,10 +21088,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129680950</v>
+        <v>129679960</v>
       </c>
       <c r="B193" t="n">
-        <v>86840</v>
+        <v>98803</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21063,34 +21099,31 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>3762</v>
+        <v>219874</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr"/>
       <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
@@ -21098,10 +21131,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>668169</v>
+        <v>668350</v>
       </c>
       <c r="R193" t="n">
-        <v>6696546</v>
+        <v>6696502</v>
       </c>
       <c r="S193" t="n">
         <v>5</v>
@@ -21131,19 +21164,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>17:31</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>17:31</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21155,11 +21178,6 @@
       <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
@@ -21176,10 +21194,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129680695</v>
+        <v>129680862</v>
       </c>
       <c r="B194" t="n">
-        <v>92542</v>
+        <v>87003</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21187,26 +21205,26 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4769</v>
+        <v>3674</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -21222,10 +21240,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>668326</v>
+        <v>668181</v>
       </c>
       <c r="R194" t="n">
-        <v>6696601</v>
+        <v>6696507</v>
       </c>
       <c r="S194" t="n">
         <v>5</v>
@@ -21285,10 +21303,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129679283</v>
+        <v>129680950</v>
       </c>
       <c r="B195" t="n">
-        <v>92542</v>
+        <v>86841</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21296,26 +21314,26 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -21331,10 +21349,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>668566</v>
+        <v>668169</v>
       </c>
       <c r="R195" t="n">
-        <v>6696824</v>
+        <v>6696546</v>
       </c>
       <c r="S195" t="n">
         <v>5</v>
@@ -21364,9 +21382,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21378,6 +21406,11 @@
       <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
@@ -21394,10 +21427,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129680802</v>
+        <v>129680952</v>
       </c>
       <c r="B196" t="n">
-        <v>98746</v>
+        <v>91361</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21405,31 +21438,26 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>219798</v>
+        <v>3215</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
@@ -21437,10 +21465,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>668284</v>
+        <v>668122</v>
       </c>
       <c r="R196" t="n">
-        <v>6696528</v>
+        <v>6696635</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21500,10 +21528,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129679960</v>
+        <v>129679813</v>
       </c>
       <c r="B197" t="n">
-        <v>98802</v>
+        <v>91361</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21511,31 +21539,26 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>219874</v>
+        <v>3215</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
       <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
@@ -21543,10 +21566,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>668350</v>
+        <v>668474</v>
       </c>
       <c r="R197" t="n">
-        <v>6696502</v>
+        <v>6696455</v>
       </c>
       <c r="S197" t="n">
         <v>5</v>
@@ -21606,44 +21629,36 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129680745</v>
+        <v>129680026</v>
       </c>
       <c r="B198" t="n">
-        <v>87039</v>
+        <v>91361</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6003295</v>
+        <v>3215</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
       <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
@@ -21652,10 +21667,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>668309</v>
+        <v>668345</v>
       </c>
       <c r="R198" t="n">
-        <v>6696573</v>
+        <v>6696510</v>
       </c>
       <c r="S198" t="n">
         <v>5</v>
@@ -21685,19 +21700,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>16:22</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>16:22</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21709,11 +21714,6 @@
       <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
-      </c>
-      <c r="AR198" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
@@ -21730,10 +21730,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129679656</v>
+        <v>129679863</v>
       </c>
       <c r="B199" t="n">
-        <v>91360</v>
+        <v>92906</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21741,25 +21741,33 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>3215</v>
+        <v>5964</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K199" t="inlineStr"/>
       <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
@@ -21768,10 +21776,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>668567</v>
+        <v>668377</v>
       </c>
       <c r="R199" t="n">
-        <v>6696558</v>
+        <v>6696490</v>
       </c>
       <c r="S199" t="n">
         <v>5</v>
@@ -21831,10 +21839,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129680782</v>
+        <v>129679225</v>
       </c>
       <c r="B200" t="n">
-        <v>91360</v>
+        <v>92543</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21842,25 +21850,33 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K200" t="inlineStr"/>
       <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
@@ -21869,10 +21885,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>668301</v>
+        <v>668575</v>
       </c>
       <c r="R200" t="n">
-        <v>6696546</v>
+        <v>6696825</v>
       </c>
       <c r="S200" t="n">
         <v>5</v>
@@ -21932,10 +21948,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129679318</v>
+        <v>129679656</v>
       </c>
       <c r="B201" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21973,7 +21989,7 @@
         <v>668567</v>
       </c>
       <c r="R201" t="n">
-        <v>6696860</v>
+        <v>6696558</v>
       </c>
       <c r="S201" t="n">
         <v>5</v>
@@ -22033,10 +22049,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129680812</v>
+        <v>129680782</v>
       </c>
       <c r="B202" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22071,10 +22087,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>668266</v>
+        <v>668301</v>
       </c>
       <c r="R202" t="n">
-        <v>6696526</v>
+        <v>6696546</v>
       </c>
       <c r="S202" t="n">
         <v>5</v>
@@ -22134,10 +22150,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129679594</v>
+        <v>129679318</v>
       </c>
       <c r="B203" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22162,16 +22178,8 @@
           <t>(Fr.) Fr.</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
@@ -22180,10 +22188,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>668561</v>
+        <v>668567</v>
       </c>
       <c r="R203" t="n">
-        <v>6696568</v>
+        <v>6696860</v>
       </c>
       <c r="S203" t="n">
         <v>5</v>
@@ -22243,10 +22251,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129679225</v>
+        <v>129680812</v>
       </c>
       <c r="B204" t="n">
-        <v>92542</v>
+        <v>91361</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22254,33 +22262,25 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
@@ -22289,10 +22289,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>668575</v>
+        <v>668266</v>
       </c>
       <c r="R204" t="n">
-        <v>6696825</v>
+        <v>6696526</v>
       </c>
       <c r="S204" t="n">
         <v>5</v>
@@ -22352,10 +22352,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129679863</v>
+        <v>129679594</v>
       </c>
       <c r="B205" t="n">
-        <v>92905</v>
+        <v>91361</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22363,26 +22363,26 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>5964</v>
+        <v>3215</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -22398,10 +22398,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>668377</v>
+        <v>668561</v>
       </c>
       <c r="R205" t="n">
-        <v>6696490</v>
+        <v>6696568</v>
       </c>
       <c r="S205" t="n">
         <v>5</v>
@@ -22461,36 +22461,44 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129680718</v>
+        <v>129679279</v>
       </c>
       <c r="B206" t="n">
-        <v>91360</v>
+        <v>87040</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>3215</v>
+        <v>6003295</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
@@ -22499,13 +22507,13 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>668318</v>
+        <v>668566</v>
       </c>
       <c r="R206" t="n">
-        <v>6696567</v>
+        <v>6696824</v>
       </c>
       <c r="S206" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -22532,9 +22540,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22546,6 +22564,16 @@
       <c r="AF206" t="inlineStr"/>
       <c r="AG206" t="b">
         <v>0</v>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>Kalksvacka; gran</t>
+        </is>
+      </c>
+      <c r="AR206" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
@@ -22565,7 +22593,7 @@
         <v>129679583</v>
       </c>
       <c r="B207" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22663,44 +22691,36 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129679279</v>
+        <v>129680718</v>
       </c>
       <c r="B208" t="n">
-        <v>87039</v>
+        <v>91361</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6003295</v>
+        <v>3215</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
@@ -22709,13 +22729,13 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>668566</v>
+        <v>668318</v>
       </c>
       <c r="R208" t="n">
-        <v>6696824</v>
+        <v>6696567</v>
       </c>
       <c r="S208" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -22742,19 +22762,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>14:17</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22766,16 +22776,6 @@
       <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
-      </c>
-      <c r="AI208" t="inlineStr">
-        <is>
-          <t>Kalksvacka; gran</t>
-        </is>
-      </c>
-      <c r="AR208" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
@@ -22792,10 +22792,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129680786</v>
+        <v>129679943</v>
       </c>
       <c r="B209" t="n">
-        <v>91360</v>
+        <v>92906</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -22803,25 +22803,33 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>3215</v>
+        <v>5964</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K209" t="inlineStr"/>
       <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
@@ -22830,10 +22838,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>668295</v>
+        <v>668365</v>
       </c>
       <c r="R209" t="n">
-        <v>6696542</v>
+        <v>6696502</v>
       </c>
       <c r="S209" t="n">
         <v>5</v>
@@ -22893,10 +22901,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129680657</v>
+        <v>129680786</v>
       </c>
       <c r="B210" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -22931,10 +22939,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>668345</v>
+        <v>668295</v>
       </c>
       <c r="R210" t="n">
-        <v>6696572</v>
+        <v>6696542</v>
       </c>
       <c r="S210" t="n">
         <v>5</v>
@@ -22994,10 +23002,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129679943</v>
+        <v>129680657</v>
       </c>
       <c r="B211" t="n">
-        <v>92905</v>
+        <v>91361</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23005,33 +23013,25 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>5964</v>
+        <v>3215</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr"/>
       <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
@@ -23040,10 +23040,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>668365</v>
+        <v>668345</v>
       </c>
       <c r="R211" t="n">
-        <v>6696502</v>
+        <v>6696572</v>
       </c>
       <c r="S211" t="n">
         <v>5</v>
@@ -23106,7 +23106,7 @@
         <v>129680850</v>
       </c>
       <c r="B212" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23208,7 +23208,7 @@
         <v>129680677</v>
       </c>
       <c r="B213" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>129679204</v>
       </c>
       <c r="B214" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>129680825</v>
       </c>
       <c r="B215" t="n">
-        <v>87039</v>
+        <v>87040</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23542,10 +23542,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129679644</v>
+        <v>129680624</v>
       </c>
       <c r="B216" t="n">
-        <v>91360</v>
+        <v>86841</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23553,25 +23553,33 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>3215</v>
+        <v>3762</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
@@ -23580,10 +23588,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>668576</v>
+        <v>668566</v>
       </c>
       <c r="R216" t="n">
-        <v>6696559</v>
+        <v>6696824</v>
       </c>
       <c r="S216" t="n">
         <v>5</v>
@@ -23613,9 +23621,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z216" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB216" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23627,6 +23645,11 @@
       <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="b">
         <v>0</v>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
@@ -23643,10 +23666,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129679223</v>
+        <v>129679644</v>
       </c>
       <c r="B217" t="n">
-        <v>100957</v>
+        <v>91361</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -23654,27 +23677,26 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
@@ -23682,10 +23704,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>668566</v>
+        <v>668576</v>
       </c>
       <c r="R217" t="n">
-        <v>6696807</v>
+        <v>6696559</v>
       </c>
       <c r="S217" t="n">
         <v>5</v>
@@ -23745,10 +23767,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>129680678</v>
+        <v>129679223</v>
       </c>
       <c r="B218" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23784,10 +23806,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>668362</v>
+        <v>668566</v>
       </c>
       <c r="R218" t="n">
-        <v>6696542</v>
+        <v>6696807</v>
       </c>
       <c r="S218" t="n">
         <v>5</v>
@@ -23847,10 +23869,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129680624</v>
+        <v>129680678</v>
       </c>
       <c r="B219" t="n">
-        <v>86840</v>
+        <v>100958</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23858,34 +23880,27 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>3762</v>
+        <v>222498</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
       <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
@@ -23893,10 +23908,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>668566</v>
+        <v>668362</v>
       </c>
       <c r="R219" t="n">
-        <v>6696824</v>
+        <v>6696542</v>
       </c>
       <c r="S219" t="n">
         <v>5</v>
@@ -23926,19 +23941,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z219" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA219" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB219" t="inlineStr">
-        <is>
-          <t>14:17</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23950,11 +23955,6 @@
       <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
-      </c>
-      <c r="AR219" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
@@ -23974,7 +23974,7 @@
         <v>129680842</v>
       </c>
       <c r="B220" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24085,37 +24085,37 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129679210</v>
+        <v>129679572</v>
       </c>
       <c r="B221" t="n">
-        <v>92905</v>
+        <v>92908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>5964</v>
+        <v>5966</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -24131,10 +24131,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>668585</v>
+        <v>668568</v>
       </c>
       <c r="R221" t="n">
-        <v>6696791</v>
+        <v>6696590</v>
       </c>
       <c r="S221" t="n">
         <v>5</v>
@@ -24178,6 +24178,11 @@
       <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
@@ -24194,37 +24199,37 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129679572</v>
+        <v>129679210</v>
       </c>
       <c r="B222" t="n">
-        <v>92907</v>
+        <v>92906</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -24240,10 +24245,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>668568</v>
+        <v>668585</v>
       </c>
       <c r="R222" t="n">
-        <v>6696590</v>
+        <v>6696791</v>
       </c>
       <c r="S222" t="n">
         <v>5</v>
@@ -24287,11 +24292,6 @@
       <c r="AF222" t="inlineStr"/>
       <c r="AG222" t="b">
         <v>0</v>
-      </c>
-      <c r="AI222" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
@@ -24311,7 +24311,7 @@
         <v>129680047</v>
       </c>
       <c r="B223" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>129680912</v>
       </c>
       <c r="B224" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24526,10 +24526,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129679018</v>
+        <v>129679208</v>
       </c>
       <c r="B225" t="n">
-        <v>97639</v>
+        <v>92882</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24537,27 +24537,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>221945</v>
+        <v>4366</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
@@ -24565,10 +24572,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>668617</v>
+        <v>668589</v>
       </c>
       <c r="R225" t="n">
-        <v>6696806</v>
+        <v>6696799</v>
       </c>
       <c r="S225" t="n">
         <v>5</v>
@@ -24628,10 +24635,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129679208</v>
+        <v>129679866</v>
       </c>
       <c r="B226" t="n">
-        <v>92881</v>
+        <v>92543</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -24639,26 +24646,26 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>4366</v>
+        <v>4769</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -24674,10 +24681,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>668589</v>
+        <v>668368</v>
       </c>
       <c r="R226" t="n">
-        <v>6696799</v>
+        <v>6696491</v>
       </c>
       <c r="S226" t="n">
         <v>5</v>
@@ -24737,10 +24744,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129679866</v>
+        <v>129679917</v>
       </c>
       <c r="B227" t="n">
-        <v>92542</v>
+        <v>92906</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -24748,26 +24755,26 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -24783,10 +24790,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>668368</v>
+        <v>668376</v>
       </c>
       <c r="R227" t="n">
-        <v>6696491</v>
+        <v>6696497</v>
       </c>
       <c r="S227" t="n">
         <v>5</v>
@@ -24846,10 +24853,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129679917</v>
+        <v>129679018</v>
       </c>
       <c r="B228" t="n">
-        <v>92905</v>
+        <v>97640</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -24857,34 +24864,27 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5964</v>
+        <v>221945</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
       <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
@@ -24892,10 +24892,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>668376</v>
+        <v>668617</v>
       </c>
       <c r="R228" t="n">
-        <v>6696497</v>
+        <v>6696806</v>
       </c>
       <c r="S228" t="n">
         <v>5</v>
@@ -24958,7 +24958,7 @@
         <v>129679214</v>
       </c>
       <c r="B229" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>129679263</v>
       </c>
       <c r="B230" t="n">
-        <v>104239</v>
+        <v>104240</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25174,10 +25174,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129679309</v>
+        <v>129679946</v>
       </c>
       <c r="B231" t="n">
-        <v>86840</v>
+        <v>92543</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25185,33 +25185,25 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>3762</v>
+        <v>4769</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr"/>
       <c r="N231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
@@ -25220,10 +25212,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>668559</v>
+        <v>668365</v>
       </c>
       <c r="R231" t="n">
-        <v>6696841</v>
+        <v>6696502</v>
       </c>
       <c r="S231" t="n">
         <v>5</v>
@@ -25253,19 +25245,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z231" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA231" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB231" t="inlineStr">
-        <is>
-          <t>14:20</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -25277,11 +25259,6 @@
       <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="b">
         <v>0</v>
-      </c>
-      <c r="AR231" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
@@ -25298,10 +25275,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129679946</v>
+        <v>129679309</v>
       </c>
       <c r="B232" t="n">
-        <v>92542</v>
+        <v>86841</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -25309,25 +25286,33 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr"/>
-      <c r="J232" t="inlineStr"/>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K232" t="inlineStr"/>
       <c r="N232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
@@ -25336,10 +25321,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>668365</v>
+        <v>668559</v>
       </c>
       <c r="R232" t="n">
-        <v>6696502</v>
+        <v>6696841</v>
       </c>
       <c r="S232" t="n">
         <v>5</v>
@@ -25369,9 +25354,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -25383,6 +25378,11 @@
       <c r="AF232" t="inlineStr"/>
       <c r="AG232" t="b">
         <v>0</v>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
@@ -25402,7 +25402,7 @@
         <v>129680938</v>
       </c>
       <c r="B233" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -25508,37 +25508,37 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129680011</v>
+        <v>129680829</v>
       </c>
       <c r="B234" t="n">
-        <v>87039</v>
+        <v>86841</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6003295</v>
+        <v>3762</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -25554,13 +25554,13 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>668346</v>
+        <v>668239</v>
       </c>
       <c r="R234" t="n">
-        <v>6696508</v>
+        <v>6696546</v>
       </c>
       <c r="S234" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -25599,7 +25599,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -25611,11 +25611,6 @@
       <c r="AF234" t="inlineStr"/>
       <c r="AG234" t="b">
         <v>0</v>
-      </c>
-      <c r="AR234" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
@@ -25635,7 +25630,7 @@
         <v>129680070</v>
       </c>
       <c r="B235" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -25733,37 +25728,37 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>129680829</v>
+        <v>129695129</v>
       </c>
       <c r="B236" t="n">
-        <v>86840</v>
+        <v>91086</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>3762</v>
+        <v>5745</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -25779,10 +25774,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>668239</v>
+        <v>668166</v>
       </c>
       <c r="R236" t="n">
-        <v>6696546</v>
+        <v>6696549</v>
       </c>
       <c r="S236" t="n">
         <v>5</v>
@@ -25814,7 +25809,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -25824,7 +25819,12 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>Fruktkropp i dåligt skick.</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -25833,9 +25833,23 @@
       <c r="AE236" t="b">
         <v>0</v>
       </c>
-      <c r="AF236" t="inlineStr"/>
+      <c r="AF236" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG236" t="b">
         <v>0</v>
+      </c>
+      <c r="AI236" t="inlineStr">
+        <is>
+          <t>Hotspot för svampar; kalkbarrskog; under gran (tall finns ej här)</t>
+        </is>
+      </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
@@ -25852,32 +25866,32 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>129695129</v>
+        <v>129680011</v>
       </c>
       <c r="B237" t="n">
-        <v>91085</v>
+        <v>87040</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5745</v>
+        <v>6003295</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Gyllenfingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Ramaria brunneicontusa</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -25898,13 +25912,13 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>668166</v>
+        <v>668346</v>
       </c>
       <c r="R237" t="n">
-        <v>6696549</v>
+        <v>6696508</v>
       </c>
       <c r="S237" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -25933,7 +25947,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -25943,12 +25957,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>17:29</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>Fruktkropp i dåligt skick.</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25957,18 +25966,9 @@
       <c r="AE237" t="b">
         <v>0</v>
       </c>
-      <c r="AF237" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF237" t="inlineStr"/>
       <c r="AG237" t="b">
         <v>0</v>
-      </c>
-      <c r="AI237" t="inlineStr">
-        <is>
-          <t>Hotspot för svampar; kalkbarrskog; under gran (tall finns ej här)</t>
-        </is>
       </c>
       <c r="AR237" t="inlineStr">
         <is>
@@ -25990,37 +25990,37 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>129679977</v>
+        <v>129679216</v>
       </c>
       <c r="B238" t="n">
-        <v>87039</v>
+        <v>92882</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>6003295</v>
+        <v>4366</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -26036,10 +26036,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>668337</v>
+        <v>668584</v>
       </c>
       <c r="R238" t="n">
-        <v>6696496</v>
+        <v>6696801</v>
       </c>
       <c r="S238" t="n">
         <v>5</v>
@@ -26069,19 +26069,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z238" t="inlineStr">
-        <is>
-          <t>15:53</t>
-        </is>
-      </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t>15:53</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -26093,11 +26083,6 @@
       <c r="AF238" t="inlineStr"/>
       <c r="AG238" t="b">
         <v>0</v>
-      </c>
-      <c r="AR238" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
@@ -26114,37 +26099,37 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>129679216</v>
+        <v>129679977</v>
       </c>
       <c r="B239" t="n">
-        <v>92881</v>
+        <v>87040</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>4366</v>
+        <v>6003295</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -26160,10 +26145,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>668584</v>
+        <v>668337</v>
       </c>
       <c r="R239" t="n">
-        <v>6696801</v>
+        <v>6696496</v>
       </c>
       <c r="S239" t="n">
         <v>5</v>
@@ -26193,9 +26178,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA239" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -26207,6 +26202,11 @@
       <c r="AF239" t="inlineStr"/>
       <c r="AG239" t="b">
         <v>0</v>
+      </c>
+      <c r="AR239" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
@@ -26223,10 +26223,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>129680818</v>
+        <v>129680915</v>
       </c>
       <c r="B240" t="n">
-        <v>91360</v>
+        <v>87003</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -26234,25 +26234,33 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>3215</v>
+        <v>3674</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr"/>
-      <c r="J240" t="inlineStr"/>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K240" t="inlineStr"/>
       <c r="N240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
@@ -26261,13 +26269,13 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>668277</v>
+        <v>668167</v>
       </c>
       <c r="R240" t="n">
-        <v>6696587</v>
+        <v>6696523</v>
       </c>
       <c r="S240" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -26294,9 +26302,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>17:19</t>
+        </is>
+      </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -26324,10 +26342,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>129680915</v>
+        <v>129680806</v>
       </c>
       <c r="B241" t="n">
-        <v>87002</v>
+        <v>91361</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -26335,33 +26353,25 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>3674</v>
+        <v>3215</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J241" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr"/>
       <c r="N241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
@@ -26370,10 +26380,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>668167</v>
+        <v>668277</v>
       </c>
       <c r="R241" t="n">
-        <v>6696523</v>
+        <v>6696516</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -26403,19 +26413,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z241" t="inlineStr">
-        <is>
-          <t>17:19</t>
-        </is>
-      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB241" t="inlineStr">
-        <is>
-          <t>17:19</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -26443,10 +26443,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>129680806</v>
+        <v>129680818</v>
       </c>
       <c r="B242" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -26484,10 +26484,10 @@
         <v>668277</v>
       </c>
       <c r="R242" t="n">
-        <v>6696516</v>
+        <v>6696587</v>
       </c>
       <c r="S242" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -26544,10 +26544,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>129680918</v>
+        <v>129679551</v>
       </c>
       <c r="B243" t="n">
-        <v>86840</v>
+        <v>92543</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -26555,26 +26555,26 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3762</v>
+        <v>4769</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -26590,10 +26590,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>668162</v>
+        <v>668578</v>
       </c>
       <c r="R243" t="n">
-        <v>6696519</v>
+        <v>6696654</v>
       </c>
       <c r="S243" t="n">
         <v>5</v>
@@ -26623,19 +26623,9 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z243" t="inlineStr">
-        <is>
-          <t>17:20</t>
-        </is>
-      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AB243" t="inlineStr">
-        <is>
-          <t>17:20</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -26647,11 +26637,6 @@
       <c r="AF243" t="inlineStr"/>
       <c r="AG243" t="b">
         <v>0</v>
-      </c>
-      <c r="AR243" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT243" t="inlineStr"/>
       <c r="AW243" t="inlineStr">
@@ -26668,10 +26653,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>129679551</v>
+        <v>129680856</v>
       </c>
       <c r="B244" t="n">
-        <v>92542</v>
+        <v>92543</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26698,7 +26683,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -26714,10 +26699,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>668578</v>
+        <v>668185</v>
       </c>
       <c r="R244" t="n">
-        <v>6696654</v>
+        <v>6696534</v>
       </c>
       <c r="S244" t="n">
         <v>5</v>
@@ -26777,10 +26762,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>129680856</v>
+        <v>129680918</v>
       </c>
       <c r="B245" t="n">
-        <v>92542</v>
+        <v>86841</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -26788,21 +26773,21 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>4769</v>
+        <v>3762</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -26823,10 +26808,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>668185</v>
+        <v>668162</v>
       </c>
       <c r="R245" t="n">
-        <v>6696534</v>
+        <v>6696519</v>
       </c>
       <c r="S245" t="n">
         <v>5</v>
@@ -26856,9 +26841,19 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
       <c r="AA245" t="inlineStr">
         <is>
           <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -26870,6 +26865,11 @@
       <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
+      </c>
+      <c r="AR245" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
@@ -26889,7 +26889,7 @@
         <v>129680696</v>
       </c>
       <c r="B246" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>129680814</v>
       </c>
       <c r="B247" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27088,10 +27088,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>129679702</v>
+        <v>129679805</v>
       </c>
       <c r="B248" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27126,10 +27126,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>668472</v>
+        <v>668448</v>
       </c>
       <c r="R248" t="n">
-        <v>6696560</v>
+        <v>6696497</v>
       </c>
       <c r="S248" t="n">
         <v>5</v>
@@ -27189,10 +27189,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>129679672</v>
+        <v>129680040</v>
       </c>
       <c r="B249" t="n">
-        <v>91360</v>
+        <v>101865</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27200,26 +27200,27 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>3215</v>
+        <v>221235</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
       <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
@@ -27227,10 +27228,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>668531</v>
+        <v>668359</v>
       </c>
       <c r="R249" t="n">
-        <v>6696538</v>
+        <v>6696516</v>
       </c>
       <c r="S249" t="n">
         <v>5</v>
@@ -27290,36 +27291,44 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>129679537</v>
+        <v>129707800</v>
       </c>
       <c r="B250" t="n">
-        <v>91360</v>
+        <v>87006</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>3215</v>
+        <v>6037417</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Denisespindling</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Cortinarius olivaceodionysae</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr"/>
-      <c r="J250" t="inlineStr"/>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K250" t="inlineStr"/>
       <c r="N250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
@@ -27328,10 +27337,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>668585</v>
+        <v>668173</v>
       </c>
       <c r="R250" t="n">
-        <v>6696699</v>
+        <v>6696522</v>
       </c>
       <c r="S250" t="n">
         <v>5</v>
@@ -27361,20 +27370,44 @@
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AD250" t="b">
         <v>0</v>
       </c>
       <c r="AE250" t="b">
         <v>0</v>
       </c>
-      <c r="AF250" t="inlineStr"/>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG250" t="b">
         <v>0</v>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>Hotspot; kalkbarrskog; Under gran</t>
+        </is>
+      </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t>Kollekt sparat</t>
+        </is>
       </c>
       <c r="AT250" t="inlineStr"/>
       <c r="AW250" t="inlineStr">
@@ -27391,10 +27424,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>129679805</v>
+        <v>129679702</v>
       </c>
       <c r="B251" t="n">
-        <v>91360</v>
+        <v>91361</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -27429,10 +27462,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>668448</v>
+        <v>668472</v>
       </c>
       <c r="R251" t="n">
-        <v>6696497</v>
+        <v>6696560</v>
       </c>
       <c r="S251" t="n">
         <v>5</v>
@@ -27492,44 +27525,36 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>129707800</v>
+        <v>129679672</v>
       </c>
       <c r="B252" t="n">
-        <v>87005</v>
+        <v>91361</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6037417</v>
+        <v>3215</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
-        </is>
-      </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr"/>
       <c r="N252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
@@ -27538,10 +27563,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>668173</v>
+        <v>668531</v>
       </c>
       <c r="R252" t="n">
-        <v>6696522</v>
+        <v>6696538</v>
       </c>
       <c r="S252" t="n">
         <v>5</v>
@@ -27571,44 +27596,20 @@
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="Z252" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>2025-09-25</t>
         </is>
       </c>
-      <c r="AB252" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AD252" t="b">
         <v>0</v>
       </c>
       <c r="AE252" t="b">
         <v>0</v>
       </c>
-      <c r="AF252" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF252" t="inlineStr"/>
       <c r="AG252" t="b">
         <v>0</v>
-      </c>
-      <c r="AI252" t="inlineStr">
-        <is>
-          <t>Hotspot; kalkbarrskog; Under gran</t>
-        </is>
-      </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>Kollekt sparat</t>
-        </is>
       </c>
       <c r="AT252" t="inlineStr"/>
       <c r="AW252" t="inlineStr">
@@ -27625,10 +27626,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>129680040</v>
+        <v>129679537</v>
       </c>
       <c r="B253" t="n">
-        <v>101864</v>
+        <v>91361</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -27636,27 +27637,26 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>221235</v>
+        <v>3215</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr"/>
-      <c r="L253" t="inlineStr"/>
       <c r="N253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
@@ -27664,10 +27664,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>668359</v>
+        <v>668585</v>
       </c>
       <c r="R253" t="n">
-        <v>6696516</v>
+        <v>6696699</v>
       </c>
       <c r="S253" t="n">
         <v>5</v>

--- a/artfynd/A 29556-2023 artfynd.xlsx
+++ b/artfynd/A 29556-2023 artfynd.xlsx
@@ -11383,10 +11383,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129527202</v>
+        <v>129610538</v>
       </c>
       <c r="B103" t="n">
-        <v>91361</v>
+        <v>101865</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11394,26 +11394,27 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>3215</v>
+        <v>221235</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -11421,13 +11422,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>668552</v>
+        <v>668247</v>
       </c>
       <c r="R103" t="n">
-        <v>6696416</v>
+        <v>6696545</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11451,12 +11452,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11484,10 +11485,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129528876</v>
+        <v>129609957</v>
       </c>
       <c r="B104" t="n">
-        <v>91361</v>
+        <v>88775</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11495,25 +11496,33 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>3215</v>
+        <v>4379</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
@@ -11522,13 +11531,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>668483</v>
+        <v>668194</v>
       </c>
       <c r="R104" t="n">
-        <v>6696587</v>
+        <v>6696543</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11552,12 +11561,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11585,10 +11594,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129609957</v>
+        <v>129610638</v>
       </c>
       <c r="B105" t="n">
-        <v>88775</v>
+        <v>91361</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11596,33 +11605,25 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4379</v>
+        <v>3215</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
@@ -11631,13 +11632,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>668194</v>
+        <v>668314</v>
       </c>
       <c r="R105" t="n">
-        <v>6696543</v>
+        <v>6696563</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11694,7 +11695,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129610638</v>
+        <v>129527202</v>
       </c>
       <c r="B106" t="n">
         <v>91361</v>
@@ -11732,10 +11733,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>668314</v>
+        <v>668552</v>
       </c>
       <c r="R106" t="n">
-        <v>6696563</v>
+        <v>6696416</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11762,12 +11763,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11795,10 +11796,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129610538</v>
+        <v>129528876</v>
       </c>
       <c r="B107" t="n">
-        <v>101865</v>
+        <v>91361</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11806,27 +11807,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221235</v>
+        <v>3215</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -11834,13 +11834,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>668247</v>
+        <v>668483</v>
       </c>
       <c r="R107" t="n">
-        <v>6696545</v>
+        <v>6696587</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11864,12 +11864,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12566,10 +12566,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129528857</v>
+        <v>129525668</v>
       </c>
       <c r="B114" t="n">
-        <v>91361</v>
+        <v>98747</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12577,26 +12577,31 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3215</v>
+        <v>219798</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -12604,13 +12609,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>668474</v>
+        <v>668562</v>
       </c>
       <c r="R114" t="n">
-        <v>6696557</v>
+        <v>6696327</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12667,10 +12672,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129525668</v>
+        <v>129617663</v>
       </c>
       <c r="B115" t="n">
-        <v>98747</v>
+        <v>91361</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12678,31 +12683,26 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>219798</v>
+        <v>3215</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
@@ -12710,10 +12710,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>668562</v>
+        <v>668387</v>
       </c>
       <c r="R115" t="n">
-        <v>6696327</v>
+        <v>6696641</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12740,12 +12740,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12773,10 +12773,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129617663</v>
+        <v>129609831</v>
       </c>
       <c r="B116" t="n">
-        <v>91361</v>
+        <v>92543</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12784,25 +12784,33 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
@@ -12811,13 +12819,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>668387</v>
+        <v>668186</v>
       </c>
       <c r="R116" t="n">
-        <v>6696641</v>
+        <v>6696475</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12874,10 +12882,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129609831</v>
+        <v>129528857</v>
       </c>
       <c r="B117" t="n">
-        <v>92543</v>
+        <v>91361</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12885,33 +12893,25 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
@@ -12920,13 +12920,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>668186</v>
+        <v>668474</v>
       </c>
       <c r="R117" t="n">
-        <v>6696475</v>
+        <v>6696557</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12950,12 +12950,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13304,7 +13304,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129528940</v>
+        <v>129610650</v>
       </c>
       <c r="B121" t="n">
         <v>92543</v>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -13350,10 +13350,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>668489</v>
+        <v>668349</v>
       </c>
       <c r="R121" t="n">
-        <v>6696575</v>
+        <v>6696573</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13380,12 +13380,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13413,7 +13413,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129610650</v>
+        <v>129528940</v>
       </c>
       <c r="B122" t="n">
         <v>92543</v>
@@ -13443,7 +13443,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -13459,10 +13459,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>668349</v>
+        <v>668489</v>
       </c>
       <c r="R122" t="n">
-        <v>6696573</v>
+        <v>6696575</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13489,12 +13489,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14153,10 +14153,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129617642</v>
+        <v>129617840</v>
       </c>
       <c r="B129" t="n">
-        <v>92906</v>
+        <v>98803</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14164,21 +14164,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5964</v>
+        <v>219874</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -14188,10 +14188,15 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -14199,13 +14204,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>668384</v>
+        <v>668276</v>
       </c>
       <c r="R129" t="n">
-        <v>6696663</v>
+        <v>6696503</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14262,10 +14267,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129609966</v>
+        <v>129609938</v>
       </c>
       <c r="B130" t="n">
-        <v>92906</v>
+        <v>91361</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14273,33 +14278,25 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5964</v>
+        <v>3215</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
@@ -14308,10 +14305,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>668187</v>
+        <v>668185</v>
       </c>
       <c r="R130" t="n">
-        <v>6696536</v>
+        <v>6696506</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -14371,10 +14368,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129609938</v>
+        <v>129617642</v>
       </c>
       <c r="B131" t="n">
-        <v>91361</v>
+        <v>92906</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14382,25 +14379,33 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>3215</v>
+        <v>5964</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
@@ -14409,10 +14414,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>668185</v>
+        <v>668384</v>
       </c>
       <c r="R131" t="n">
-        <v>6696506</v>
+        <v>6696663</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -14472,10 +14477,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129617840</v>
+        <v>129609966</v>
       </c>
       <c r="B132" t="n">
-        <v>98803</v>
+        <v>92906</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14483,39 +14488,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219874</v>
+        <v>5964</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c